--- a/data_window.xlsx
+++ b/data_window.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DuAnTrucDH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AFFDAD-30CA-45A0-8E9C-4C1FFD876D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB3A866-43E3-435E-AB99-F8B00C52CBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{15CB32D3-DB1A-4542-B1F9-BD2C57A25BCC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{15CB32D3-DB1A-4542-B1F9-BD2C57A25BCC}"/>
   </bookViews>
   <sheets>
     <sheet name="WindowCL" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="249">
   <si>
     <t>Date</t>
   </si>
@@ -753,52 +753,37 @@
     <t>Dir</t>
   </si>
   <si>
-    <t>Slack Time</t>
-  </si>
-  <si>
     <t>Level</t>
   </si>
   <si>
-    <t>Vung Tau</t>
-  </si>
-  <si>
     <t>Begin UB-Port</t>
   </si>
   <si>
     <t>End UB-Port</t>
   </si>
   <si>
-    <t>Begin UB Port</t>
-  </si>
-  <si>
-    <t>End UB Port</t>
-  </si>
-  <si>
-    <t>Begin UB Starboard</t>
-  </si>
-  <si>
-    <t>End UB Starboard</t>
-  </si>
-  <si>
-    <t>Begin B Port</t>
-  </si>
-  <si>
-    <t>End B Port</t>
-  </si>
-  <si>
-    <t>Begin B Starboard</t>
-  </si>
-  <si>
-    <t>End B Starboard</t>
-  </si>
-  <si>
     <t>Slack</t>
   </si>
   <si>
-    <t>Begin UB-Stb</t>
-  </si>
-  <si>
-    <t>End UB-Stb</t>
+    <t>Begin UB-Starboard</t>
+  </si>
+  <si>
+    <t>End UB-Starboard</t>
+  </si>
+  <si>
+    <t>Begin B-Port</t>
+  </si>
+  <si>
+    <t>End B-Port</t>
+  </si>
+  <si>
+    <t>Begin B-Starboard</t>
+  </si>
+  <si>
+    <t>End B-Starboard</t>
+  </si>
+  <si>
+    <t>VungTau</t>
   </si>
 </sst>
 </file>
@@ -2161,28 +2146,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="204" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C1" s="205" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D1" s="206" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="E1" s="207" t="s">
         <v>237</v>
       </c>
       <c r="F1" s="204" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G1" s="204" t="s">
+        <v>240</v>
+      </c>
+      <c r="H1" s="204" t="s">
         <v>242</v>
       </c>
-      <c r="H1" s="204" t="s">
-        <v>252</v>
-      </c>
       <c r="I1" s="204" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.4">
@@ -5837,40 +5822,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="204" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C1" s="205" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D1" s="206" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E1" s="207" t="s">
         <v>237</v>
       </c>
       <c r="F1" s="204" t="s">
+        <v>239</v>
+      </c>
+      <c r="G1" s="204" t="s">
+        <v>240</v>
+      </c>
+      <c r="H1" s="204" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1" s="204" t="s">
         <v>243</v>
       </c>
-      <c r="G1" s="204" t="s">
+      <c r="J1" s="204" t="s">
         <v>244</v>
       </c>
-      <c r="H1" s="204" t="s">
+      <c r="K1" s="204" t="s">
         <v>245</v>
       </c>
-      <c r="I1" s="204" t="s">
+      <c r="L1" s="204" t="s">
         <v>246</v>
       </c>
-      <c r="J1" s="204" t="s">
+      <c r="M1" s="204" t="s">
         <v>247</v>
-      </c>
-      <c r="K1" s="204" t="s">
-        <v>248</v>
-      </c>
-      <c r="L1" s="204" t="s">
-        <v>249</v>
-      </c>
-      <c r="M1" s="204" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">

--- a/data_window.xlsx
+++ b/data_window.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DuAnTrucDH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB3A866-43E3-435E-AB99-F8B00C52CBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1A6401-EDB8-4FFA-98BA-6CA6F1A6176F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{15CB32D3-DB1A-4542-B1F9-BD2C57A25BCC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{15CB32D3-DB1A-4542-B1F9-BD2C57A25BCC}"/>
   </bookViews>
   <sheets>
     <sheet name="WindowCL" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="249">
   <si>
     <t>Date</t>
   </si>
@@ -5231,8 +5231,8 @@
       <c r="B128" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C128" s="74" t="s">
-        <v>166</v>
+      <c r="C128" s="74">
+        <v>3.3</v>
       </c>
       <c r="D128" s="42" t="s">
         <v>128</v>
@@ -5260,8 +5260,8 @@
       <c r="B129" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="C129" s="74" t="s">
-        <v>168</v>
+      <c r="C129" s="74">
+        <v>2.4</v>
       </c>
       <c r="D129" s="42" t="s">
         <v>160</v>

--- a/data_window.xlsx
+++ b/data_window.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DuAnTrucDH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1A6401-EDB8-4FFA-98BA-6CA6F1A6176F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0F6814-B9CD-441C-B8A5-9C4A2361DF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{15CB32D3-DB1A-4542-B1F9-BD2C57A25BCC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{15CB32D3-DB1A-4542-B1F9-BD2C57A25BCC}"/>
   </bookViews>
   <sheets>
     <sheet name="WindowCL" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2949" uniqueCount="367">
   <si>
     <t>Date</t>
   </si>
@@ -784,6 +784,360 @@
   </si>
   <si>
     <t>VungTau</t>
+  </si>
+  <si>
+    <t>01:46</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>12:57</t>
+  </si>
+  <si>
+    <t>19:48</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>02:29</t>
+  </si>
+  <si>
+    <t>08:03</t>
+  </si>
+  <si>
+    <t>13:17</t>
+  </si>
+  <si>
+    <t>20:18</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>08:36</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>13:37</t>
+  </si>
+  <si>
+    <t>20:48</t>
+  </si>
+  <si>
+    <t>03:50</t>
+  </si>
+  <si>
+    <t>09:08</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>21:53</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>10:13</t>
+  </si>
+  <si>
+    <t>14:43</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>15:08</t>
+  </si>
+  <si>
+    <t>23:11</t>
+  </si>
+  <si>
+    <t>07:26</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>23:56</t>
+  </si>
+  <si>
+    <t>08:32</t>
+  </si>
+  <si>
+    <t>12:39</t>
+  </si>
+  <si>
+    <t>16:07</t>
+  </si>
+  <si>
+    <t>00:49</t>
+  </si>
+  <si>
+    <t>09:23</t>
+  </si>
+  <si>
+    <t>17:07</t>
+  </si>
+  <si>
+    <t>01:51</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>20:11</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>22:03</t>
+  </si>
+  <si>
+    <t>04:09</t>
+  </si>
+  <si>
+    <t>10:56</t>
+  </si>
+  <si>
+    <t>17:28</t>
+  </si>
+  <si>
+    <t>23:19</t>
+  </si>
+  <si>
+    <t>05:12</t>
+  </si>
+  <si>
+    <t>11:21</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>00:23</t>
+  </si>
+  <si>
+    <t>06:07</t>
+  </si>
+  <si>
+    <t>11:49</t>
+  </si>
+  <si>
+    <t>18:43</t>
+  </si>
+  <si>
+    <t>01:22</t>
+  </si>
+  <si>
+    <t>06:58</t>
+  </si>
+  <si>
+    <t>19:23</t>
+  </si>
+  <si>
+    <t>02:19</t>
+  </si>
+  <si>
+    <t>07:46</t>
+  </si>
+  <si>
+    <t>12:48</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>-0.1</t>
+  </si>
+  <si>
+    <t>03:16</t>
+  </si>
+  <si>
+    <t>08:31</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>-0.3</t>
+  </si>
+  <si>
+    <t>09:16</t>
+  </si>
+  <si>
+    <t>13:57</t>
+  </si>
+  <si>
+    <t>21:36</t>
+  </si>
+  <si>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>-0.2</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>10:54</t>
+  </si>
+  <si>
+    <t>15:16</t>
+  </si>
+  <si>
+    <t>23:16</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>11:54</t>
+  </si>
+  <si>
+    <t>16:04</t>
+  </si>
+  <si>
+    <t>00:09</t>
+  </si>
+  <si>
+    <t>08:19</t>
+  </si>
+  <si>
+    <t>13:11</t>
+  </si>
+  <si>
+    <t>17:13</t>
+  </si>
+  <si>
+    <t>01:08</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>19:26</t>
+  </si>
+  <si>
+    <t>09:46</t>
+  </si>
+  <si>
+    <t>21:26</t>
+  </si>
+  <si>
+    <t>03:19</t>
+  </si>
+  <si>
+    <t>10:19</t>
+  </si>
+  <si>
+    <t>17:06</t>
+  </si>
+  <si>
+    <t>04:27</t>
+  </si>
+  <si>
+    <t>00:07</t>
+  </si>
+  <si>
+    <t>05:27</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>18:19</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>11:36</t>
+  </si>
+  <si>
+    <t>18:52</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>01:54</t>
+  </si>
+  <si>
+    <t>07:01</t>
+  </si>
+  <si>
+    <t>12:01</t>
+  </si>
+  <si>
+    <t>19:24</t>
+  </si>
+  <si>
+    <t>02:37</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>12:28</t>
+  </si>
+  <si>
+    <t>19:56</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>Duty pilot</t>
   </si>
 </sst>
 </file>
@@ -848,7 +1202,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -867,8 +1221,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1168,12 +1528,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1772,22 +2169,100 @@
     <xf numFmtId="165" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2125,11 +2600,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9098970E-F68E-4060-9535-B4D7609639E2}">
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:I306"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.5" customWidth="1"/>
-    <col min="4" max="4" width="15.08203125" customWidth="1"/>
+    <col min="2" max="2" width="15.75" customWidth="1"/>
+    <col min="4" max="4" width="11.4140625" customWidth="1"/>
     <col min="6" max="6" width="17.6640625" customWidth="1"/>
     <col min="7" max="7" width="23.08203125" customWidth="1"/>
     <col min="8" max="8" width="27.4140625" customWidth="1"/>
@@ -2142,31 +2617,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="209" t="s">
+      <c r="A1" s="235" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="204" t="s">
+      <c r="B1" s="205" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="205" t="s">
+      <c r="C1" s="206" t="s">
         <v>238</v>
       </c>
-      <c r="D1" s="206" t="s">
+      <c r="D1" s="207" t="s">
         <v>241</v>
       </c>
-      <c r="E1" s="207" t="s">
+      <c r="E1" s="208" t="s">
         <v>237</v>
       </c>
-      <c r="F1" s="204" t="s">
+      <c r="F1" s="205" t="s">
         <v>239</v>
       </c>
-      <c r="G1" s="204" t="s">
+      <c r="G1" s="205" t="s">
         <v>240</v>
       </c>
-      <c r="H1" s="204" t="s">
+      <c r="H1" s="205" t="s">
         <v>242</v>
       </c>
-      <c r="I1" s="204" t="s">
+      <c r="I1" s="205" t="s">
         <v>243</v>
       </c>
     </row>
@@ -5796,6 +6271,3755 @@
       <c r="H151" s="54"/>
       <c r="I151" s="57"/>
     </row>
+    <row r="152" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A152" s="1"/>
+      <c r="B152" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H152" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I152" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A153" s="62">
+        <v>46143</v>
+      </c>
+      <c r="B153" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D153" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E153" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F153" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G153" s="15">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="H153" s="84" t="s">
+        <v>13</v>
+      </c>
+      <c r="I153" s="15">
+        <v>0.53125</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A154" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C154" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D154" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="E154" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F154" s="18">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G154" s="15">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="H154" s="19">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I154" s="15">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A155" s="65"/>
+      <c r="B155" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="C155" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="D155" s="12">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="E155" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F155" s="18">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="G155" s="22">
+        <v>3.125E-2</v>
+      </c>
+      <c r="H155" s="19">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I155" s="22">
+        <v>5.2083333333333336E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A156" s="67"/>
+      <c r="B156" s="24"/>
+      <c r="C156" s="25"/>
+      <c r="D156" s="26"/>
+      <c r="E156" s="27"/>
+      <c r="F156" s="28"/>
+      <c r="G156" s="29"/>
+      <c r="H156" s="30"/>
+      <c r="I156" s="29"/>
+    </row>
+    <row r="157" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A157" s="31"/>
+      <c r="B157" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="C157" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D157" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="E157" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F157" s="36">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G157" s="37">
+        <v>0.3125</v>
+      </c>
+      <c r="H157" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="I157" s="37" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A158" s="73">
+        <v>46144</v>
+      </c>
+      <c r="B158" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="C158" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="D158" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="E158" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="G158" s="45">
+        <v>0.53125</v>
+      </c>
+      <c r="H158" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="I158" s="45">
+        <v>0.55208333333333337</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A159" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B159" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="C159" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D159" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="E159" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F159" s="48">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G159" s="45">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="H159" s="46">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I159" s="45">
+        <v>0.73958333333333337</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A160" s="77"/>
+      <c r="B160" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="C160" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="D160" s="42">
+        <v>0</v>
+      </c>
+      <c r="E160" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F160" s="48">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G160" s="50">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="H160" s="46">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="I160" s="50">
+        <v>7.2916666666666671E-2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A161" s="78"/>
+      <c r="B161" s="52"/>
+      <c r="C161" s="53"/>
+      <c r="D161" s="54"/>
+      <c r="E161" s="55"/>
+      <c r="F161" s="56"/>
+      <c r="G161" s="57"/>
+      <c r="H161" s="54"/>
+      <c r="I161" s="57"/>
+    </row>
+    <row r="162" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A162" s="81"/>
+      <c r="B162" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F162" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="G162" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="H162" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="I162" s="61" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A163" s="82">
+        <v>46145</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C163" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D163" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E163" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F163" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G163" s="63">
+        <v>5.5625</v>
+      </c>
+      <c r="H163" s="16">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="I163" s="15">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A164" s="83" t="s">
+        <v>74</v>
+      </c>
+      <c r="B164" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="C164" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D164" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E164" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F164" s="18">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="G164" s="63">
+        <v>0.78125</v>
+      </c>
+      <c r="H164" s="16">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="I164" s="15">
+        <v>0.76041666666666663</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A165" s="65"/>
+      <c r="B165" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C165" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D165" s="12">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="E165" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F165" s="18">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="G165" s="66">
+        <v>7.2916666666666671E-2</v>
+      </c>
+      <c r="H165" s="16">
+        <v>0.96875</v>
+      </c>
+      <c r="I165" s="22">
+        <v>9.375E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A166" s="67"/>
+      <c r="B166" s="24"/>
+      <c r="C166" s="68"/>
+      <c r="D166" s="26"/>
+      <c r="E166" s="27"/>
+      <c r="F166" s="28"/>
+      <c r="G166" s="30"/>
+      <c r="H166" s="69"/>
+      <c r="I166" s="29"/>
+    </row>
+    <row r="167" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A167" s="31"/>
+      <c r="B167" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="C167" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D167" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F167" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="G167" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="H167" s="72" t="s">
+        <v>164</v>
+      </c>
+      <c r="I167" s="37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A168" s="39">
+        <v>46146</v>
+      </c>
+      <c r="B168" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="C168" s="74" t="s">
+        <v>265</v>
+      </c>
+      <c r="D168" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="E168" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F168" s="48">
+        <v>0.40625</v>
+      </c>
+      <c r="G168" s="45">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H168" s="75">
+        <v>0.4375</v>
+      </c>
+      <c r="I168" s="45">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A169" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="B169" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C169" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="D169" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="E169" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F169" s="48">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G169" s="45">
+        <v>0.78125</v>
+      </c>
+      <c r="H169" s="75">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I169" s="45">
+        <v>0.76041666666666663</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A170" s="49"/>
+      <c r="B170" s="42" t="s">
+        <v>266</v>
+      </c>
+      <c r="C170" s="74" t="s">
+        <v>118</v>
+      </c>
+      <c r="D170" s="42">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E170" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F170" s="48">
+        <v>0.96875</v>
+      </c>
+      <c r="G170" s="50">
+        <v>9.375E-2</v>
+      </c>
+      <c r="H170" s="99">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="I170" s="50">
+        <v>0.11458333333333333</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A171" s="51"/>
+      <c r="B171" s="54"/>
+      <c r="C171" s="79"/>
+      <c r="D171" s="54"/>
+      <c r="E171" s="55"/>
+      <c r="F171" s="56"/>
+      <c r="G171" s="57"/>
+      <c r="H171" s="80"/>
+      <c r="I171" s="57"/>
+    </row>
+    <row r="172" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A172" s="1"/>
+      <c r="B172" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F172" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="G172" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="H172" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="I172" s="61" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A173" s="62">
+        <v>46147</v>
+      </c>
+      <c r="B173" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C173" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D173" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E173" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F173" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G173" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="H173" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I173" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A174" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C174" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E174" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F174" s="18">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G174" s="15">
+        <v>0.8125</v>
+      </c>
+      <c r="H174" s="16">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I174" s="15">
+        <v>0.76041666666666663</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A175" s="65"/>
+      <c r="B175" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C175" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D175" s="12">
+        <v>7.2916666666666671E-2</v>
+      </c>
+      <c r="E175" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F175" s="18">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="G175" s="22">
+        <v>0.125</v>
+      </c>
+      <c r="H175" s="84">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="I175" s="22">
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A176" s="67"/>
+      <c r="B176" s="24"/>
+      <c r="C176" s="68"/>
+      <c r="D176" s="26"/>
+      <c r="E176" s="27"/>
+      <c r="F176" s="85"/>
+      <c r="G176" s="87"/>
+      <c r="H176" s="85"/>
+      <c r="I176" s="87"/>
+    </row>
+    <row r="177" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A177" s="31"/>
+      <c r="B177" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="C177" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="D177" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="E177" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F177" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="G177" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="H177" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="I177" s="37" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A178" s="39">
+        <v>46148</v>
+      </c>
+      <c r="B178" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="C178" s="74" t="s">
+        <v>133</v>
+      </c>
+      <c r="D178" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="E178" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F178" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="G178" s="45">
+        <v>0.625</v>
+      </c>
+      <c r="H178" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="I178" s="45">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A179" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B179" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C179" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="D179" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="E179" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F179" s="48">
+        <v>0.625</v>
+      </c>
+      <c r="G179" s="45">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="H179" s="46">
+        <v>0.625</v>
+      </c>
+      <c r="I179" s="45">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A180" s="49"/>
+      <c r="B180" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C180" s="74" t="s">
+        <v>275</v>
+      </c>
+      <c r="D180" s="42">
+        <v>9.375E-2</v>
+      </c>
+      <c r="E180" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F180" s="44">
+        <v>0</v>
+      </c>
+      <c r="G180" s="50">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="H180" s="88">
+        <v>3.125E-2</v>
+      </c>
+      <c r="I180" s="50">
+        <v>0.17708333333333334</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A181" s="51"/>
+      <c r="B181" s="54"/>
+      <c r="C181" s="79"/>
+      <c r="D181" s="54"/>
+      <c r="E181" s="55"/>
+      <c r="F181" s="56"/>
+      <c r="G181" s="57"/>
+      <c r="H181" s="54"/>
+      <c r="I181" s="57"/>
+    </row>
+    <row r="182" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A182" s="1"/>
+      <c r="B182" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C182" s="90" t="s">
+        <v>97</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F182" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="G182" s="91">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H182" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="I182" s="91">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A183" s="62">
+        <v>46149</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="C183" s="93" t="s">
+        <v>99</v>
+      </c>
+      <c r="D183" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E183" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F183" s="18">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G183" s="15">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H183" s="16">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I183" s="15">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A184" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="B184" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C184" s="93" t="s">
+        <v>191</v>
+      </c>
+      <c r="D184" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E184" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F184" s="18">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="G184" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H184" s="16">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="I184" s="15">
+        <v>0.80208333333333337</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A185" s="65"/>
+      <c r="B185" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C185" s="93" t="s">
+        <v>253</v>
+      </c>
+      <c r="D185" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E185" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F185" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="G185" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="H185" s="84" t="s">
+        <v>22</v>
+      </c>
+      <c r="I185" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A186" s="67"/>
+      <c r="B186" s="26"/>
+      <c r="C186" s="94"/>
+      <c r="D186" s="26"/>
+      <c r="E186" s="27"/>
+      <c r="F186" s="28"/>
+      <c r="G186" s="29"/>
+      <c r="H186" s="69"/>
+      <c r="I186" s="29"/>
+    </row>
+    <row r="187" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A187" s="31"/>
+      <c r="B187" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="C187" s="71" t="s">
+        <v>97</v>
+      </c>
+      <c r="D187" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="E187" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F187" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G187" s="96">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H187" s="72" t="s">
+        <v>69</v>
+      </c>
+      <c r="I187" s="96">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A188" s="39">
+        <v>46150</v>
+      </c>
+      <c r="B188" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="C188" s="74" t="s">
+        <v>137</v>
+      </c>
+      <c r="D188" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="E188" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F188" s="48">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G188" s="45">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H188" s="75">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I188" s="45">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A189" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B189" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="C189" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="D189" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="E189" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F189" s="48">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G189" s="45">
+        <v>0.875</v>
+      </c>
+      <c r="H189" s="75">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I189" s="45">
+        <v>0.84375</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A190" s="49"/>
+      <c r="B190" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="C190" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="D190" s="42" t="s">
+        <v>230</v>
+      </c>
+      <c r="E190" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F190" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G190" s="50" t="s">
+        <v>171</v>
+      </c>
+      <c r="H190" s="99" t="s">
+        <v>54</v>
+      </c>
+      <c r="I190" s="50" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A191" s="51"/>
+      <c r="B191" s="100"/>
+      <c r="C191" s="101"/>
+      <c r="D191" s="100"/>
+      <c r="E191" s="102"/>
+      <c r="F191" s="56"/>
+      <c r="G191" s="57"/>
+      <c r="H191" s="80"/>
+      <c r="I191" s="57"/>
+    </row>
+    <row r="192" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A192" s="1"/>
+      <c r="B192" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C192" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E192" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G192" s="129">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I192" s="129">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A193" s="82">
+        <v>46151</v>
+      </c>
+      <c r="B193" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C193" s="93" t="s">
+        <v>137</v>
+      </c>
+      <c r="D193" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E193" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="F193" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G193" s="104">
+        <v>0.75</v>
+      </c>
+      <c r="H193" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I193" s="104">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A194" s="83" t="s">
+        <v>63</v>
+      </c>
+      <c r="B194" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="C194" s="93" t="s">
+        <v>143</v>
+      </c>
+      <c r="D194" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E194" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F194" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="G194" s="104">
+        <v>0.90625</v>
+      </c>
+      <c r="H194" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="I194" s="104">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A195" s="114"/>
+      <c r="B195" s="12"/>
+      <c r="C195" s="93"/>
+      <c r="D195" s="12"/>
+      <c r="E195" s="13"/>
+      <c r="F195" s="18"/>
+      <c r="G195" s="104"/>
+      <c r="H195" s="18"/>
+      <c r="I195" s="104"/>
+    </row>
+    <row r="196" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A196" s="125"/>
+      <c r="B196" s="26"/>
+      <c r="C196" s="94"/>
+      <c r="D196" s="26"/>
+      <c r="E196" s="27"/>
+      <c r="F196" s="28"/>
+      <c r="G196" s="106"/>
+      <c r="H196" s="28"/>
+      <c r="I196" s="106"/>
+    </row>
+    <row r="197" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A197" s="70"/>
+      <c r="B197" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="C197" s="71" t="s">
+        <v>52</v>
+      </c>
+      <c r="D197" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="E197" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F197" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="G197" s="107">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="H197" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="I197" s="107">
+        <v>0.29166666666666669</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A198" s="73">
+        <v>46152</v>
+      </c>
+      <c r="B198" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="C198" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="D198" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="E198" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F198" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="G198" s="108">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H198" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="I198" s="108">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A199" s="76" t="s">
+        <v>74</v>
+      </c>
+      <c r="B199" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C199" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="D199" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="E199" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="F199" s="48">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G199" s="108">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H199" s="48">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I199" s="108">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A200" s="49"/>
+      <c r="B200" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="C200" s="74" t="s">
+        <v>137</v>
+      </c>
+      <c r="D200" s="42">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E200" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F200" s="48">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G200" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="H200" s="48">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I200" s="108">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A201" s="51"/>
+      <c r="B201" s="54"/>
+      <c r="C201" s="79"/>
+      <c r="D201" s="54"/>
+      <c r="E201" s="55"/>
+      <c r="F201" s="56"/>
+      <c r="G201" s="110"/>
+      <c r="H201" s="56"/>
+      <c r="I201" s="110"/>
+    </row>
+    <row r="202" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A202" s="1"/>
+      <c r="B202" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C202" s="90" t="s">
+        <v>36</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F202" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="G202" s="111">
+        <v>0.3125</v>
+      </c>
+      <c r="H202" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="I202" s="112">
+        <v>0.34375</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A203" s="62">
+        <v>46153</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C203" s="93" t="s">
+        <v>97</v>
+      </c>
+      <c r="D203" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E203" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F203" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="G203" s="113">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H203" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I203" s="104">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A204" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="B204" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C204" s="93" t="s">
+        <v>90</v>
+      </c>
+      <c r="D204" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="E204" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="F204" s="18">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G204" s="113">
+        <v>0.875</v>
+      </c>
+      <c r="H204" s="18">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I204" s="104">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A205" s="65"/>
+      <c r="B205" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="C205" s="93" t="s">
+        <v>99</v>
+      </c>
+      <c r="D205" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E205" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F205" s="18">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="G205" s="115">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="H205" s="18">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="I205" s="105" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A206" s="67"/>
+      <c r="B206" s="26"/>
+      <c r="C206" s="94"/>
+      <c r="D206" s="26"/>
+      <c r="E206" s="27"/>
+      <c r="F206" s="28"/>
+      <c r="G206" s="116"/>
+      <c r="H206" s="28"/>
+      <c r="I206" s="106"/>
+    </row>
+    <row r="207" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A207" s="31"/>
+      <c r="B207" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="C207" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="D207" s="34">
+        <v>0.28125</v>
+      </c>
+      <c r="E207" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F207" s="36">
+        <v>0.15625</v>
+      </c>
+      <c r="G207" s="107">
+        <v>0.34375</v>
+      </c>
+      <c r="H207" s="117">
+        <v>0.1875</v>
+      </c>
+      <c r="I207" s="107">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A208" s="39">
+        <v>46154</v>
+      </c>
+      <c r="B208" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="C208" s="74" t="s">
+        <v>191</v>
+      </c>
+      <c r="D208" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="E208" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F208" s="48">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="G208" s="108">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H208" s="118">
+        <v>0.46875</v>
+      </c>
+      <c r="I208" s="108">
+        <v>0.63541666666666663</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A209" s="183" t="s">
+        <v>92</v>
+      </c>
+      <c r="B209" s="42" t="s">
+        <v>292</v>
+      </c>
+      <c r="C209" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="D209" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="E209" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F209" s="48">
+        <v>0.75</v>
+      </c>
+      <c r="G209" s="108">
+        <v>0.9375</v>
+      </c>
+      <c r="H209" s="118">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="I209" s="108">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A210" s="49"/>
+      <c r="B210" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="C210" s="74" t="s">
+        <v>137</v>
+      </c>
+      <c r="D210" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E210" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F210" s="48">
+        <v>0.9375</v>
+      </c>
+      <c r="G210" s="109" t="s">
+        <v>24</v>
+      </c>
+      <c r="H210" s="118">
+        <v>0.9375</v>
+      </c>
+      <c r="I210" s="109" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A211" s="51"/>
+      <c r="B211" s="54"/>
+      <c r="C211" s="79"/>
+      <c r="D211" s="54"/>
+      <c r="E211" s="55"/>
+      <c r="F211" s="56"/>
+      <c r="G211" s="110"/>
+      <c r="H211" s="120"/>
+      <c r="I211" s="110"/>
+    </row>
+    <row r="212" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A212" s="1"/>
+      <c r="B212" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C212" s="90" t="s">
+        <v>19</v>
+      </c>
+      <c r="D212" s="4">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="E212" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F212" s="58">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="G212" s="112">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="H212" s="58">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="I212" s="121">
+        <v>0.40625</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A213" s="62">
+        <v>46155</v>
+      </c>
+      <c r="B213" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C213" s="93" t="s">
+        <v>191</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E213" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F213" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="G213" s="104">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H213" s="18">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I213" s="104">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A214" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B214" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="C214" s="93" t="s">
+        <v>113</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E214" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F214" s="18">
+        <v>0.78125</v>
+      </c>
+      <c r="G214" s="104">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="H214" s="18">
+        <v>0.8125</v>
+      </c>
+      <c r="I214" s="104">
+        <v>0.96875</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A215" s="65"/>
+      <c r="B215" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C215" s="93" t="s">
+        <v>143</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E215" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F215" s="18">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="G215" s="105" t="s">
+        <v>3</v>
+      </c>
+      <c r="H215" s="18">
+        <v>0.96875</v>
+      </c>
+      <c r="I215" s="105" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A216" s="67"/>
+      <c r="B216" s="26"/>
+      <c r="C216" s="94"/>
+      <c r="D216" s="26"/>
+      <c r="E216" s="27"/>
+      <c r="F216" s="85"/>
+      <c r="G216" s="87"/>
+      <c r="H216" s="85"/>
+      <c r="I216" s="87"/>
+    </row>
+    <row r="217" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A217" s="31"/>
+      <c r="B217" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="C217" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="D217" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E217" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F217" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="G217" s="122">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H217" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="I217" s="122">
+        <v>0.44791666666666669</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A218" s="39">
+        <v>46156</v>
+      </c>
+      <c r="B218" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="C218" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="D218" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="E218" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F218" s="48">
+        <v>0.53125</v>
+      </c>
+      <c r="G218" s="108">
+        <v>0.6875</v>
+      </c>
+      <c r="H218" s="48">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="I218" s="108">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A219" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B219" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="C219" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D219" s="42">
+        <v>0.90625</v>
+      </c>
+      <c r="E219" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F219" s="48">
+        <v>0.8125</v>
+      </c>
+      <c r="G219" s="108">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="H219" s="48">
+        <v>0.84375</v>
+      </c>
+      <c r="I219" s="108">
+        <v>0.97916666666666663</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A220" s="49"/>
+      <c r="B220" s="42"/>
+      <c r="C220" s="74"/>
+      <c r="D220" s="42"/>
+      <c r="E220" s="43"/>
+      <c r="F220" s="48"/>
+      <c r="G220" s="108"/>
+      <c r="H220" s="48"/>
+      <c r="I220" s="108"/>
+    </row>
+    <row r="221" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A221" s="51"/>
+      <c r="B221" s="54"/>
+      <c r="C221" s="79"/>
+      <c r="D221" s="54"/>
+      <c r="E221" s="55"/>
+      <c r="F221" s="56"/>
+      <c r="G221" s="110"/>
+      <c r="H221" s="56"/>
+      <c r="I221" s="110"/>
+    </row>
+    <row r="222" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A222" s="1"/>
+      <c r="B222" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C222" s="90" t="s">
+        <v>97</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E222" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F222" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G222" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="H222" s="58" t="s">
+        <v>22</v>
+      </c>
+      <c r="I222" s="112" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A223" s="62">
+        <v>46157</v>
+      </c>
+      <c r="B223" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="C223" s="93" t="s">
+        <v>250</v>
+      </c>
+      <c r="D223" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E223" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F223" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G223" s="104">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H223" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="I223" s="104">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A224" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B224" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="C224" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D224" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E224" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F224" s="18">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G224" s="104">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="H224" s="18">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I224" s="104">
+        <v>0.67708333333333337</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A225" s="65"/>
+      <c r="B225" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C225" s="93" t="s">
+        <v>275</v>
+      </c>
+      <c r="D225" s="12">
+        <v>0.9375</v>
+      </c>
+      <c r="E225" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F225" s="18">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G225" s="104">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="H225" s="18">
+        <v>0.875</v>
+      </c>
+      <c r="I225" s="105">
+        <v>1.0416666666666666E-2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A226" s="67"/>
+      <c r="B226" s="26"/>
+      <c r="C226" s="94"/>
+      <c r="D226" s="26"/>
+      <c r="E226" s="27"/>
+      <c r="F226" s="28"/>
+      <c r="G226" s="106"/>
+      <c r="H226" s="28"/>
+      <c r="I226" s="106"/>
+    </row>
+    <row r="227" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A227" s="31"/>
+      <c r="B227" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="C227" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D227" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="E227" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F227" s="36">
+        <v>0.11458333333333333</v>
+      </c>
+      <c r="G227" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="H227" s="117" t="s">
+        <v>54</v>
+      </c>
+      <c r="I227" s="107" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A228" s="73">
+        <v>46158</v>
+      </c>
+      <c r="B228" s="42" t="s">
+        <v>306</v>
+      </c>
+      <c r="C228" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="D228" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="E228" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F228" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G228" s="108">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H228" s="119" t="s">
+        <v>70</v>
+      </c>
+      <c r="I228" s="108">
+        <v>0.51041666666666663</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A229" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B229" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="C229" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="D229" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="E229" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F229" s="48">
+        <v>0.5625</v>
+      </c>
+      <c r="G229" s="108">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="H229" s="118">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I229" s="108">
+        <v>0.67708333333333337</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A230" s="77"/>
+      <c r="B230" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="C230" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="D230" s="42">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="E230" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F230" s="133">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="G230" s="134">
+        <v>0</v>
+      </c>
+      <c r="H230" s="133">
+        <v>0.90625</v>
+      </c>
+      <c r="I230" s="134">
+        <v>2.0833333333333332E-2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A231" s="51"/>
+      <c r="B231" s="100"/>
+      <c r="C231" s="101"/>
+      <c r="D231" s="100"/>
+      <c r="E231" s="102"/>
+      <c r="F231" s="56"/>
+      <c r="G231" s="110"/>
+      <c r="H231" s="120"/>
+      <c r="I231" s="110"/>
+    </row>
+    <row r="232" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A232" s="1"/>
+      <c r="B232" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D232" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E232" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F232" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G232" s="103" t="s">
+        <v>69</v>
+      </c>
+      <c r="H232" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I232" s="103" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A233" s="82">
+        <v>46159</v>
+      </c>
+      <c r="B233" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="C233" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D233" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E233" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F233" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G233" s="104">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H233" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I233" s="104">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A234" s="83" t="s">
+        <v>74</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="C234" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D234" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="E234" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F234" s="18">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G234" s="104">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="H234" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I234" s="104">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A235" s="65"/>
+      <c r="B235" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="C235" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="D235" s="12">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="E235" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F235" s="18">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G235" s="105">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="H235" s="18">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="I235" s="105">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A236" s="67"/>
+      <c r="B236" s="24"/>
+      <c r="C236" s="25"/>
+      <c r="D236" s="26"/>
+      <c r="E236" s="27"/>
+      <c r="F236" s="28"/>
+      <c r="G236" s="106"/>
+      <c r="H236" s="28"/>
+      <c r="I236" s="106"/>
+    </row>
+    <row r="237" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A237" s="31"/>
+      <c r="B237" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="C237" s="33">
+        <v>3.6</v>
+      </c>
+      <c r="D237" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E237" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F237" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="G237" s="107" t="s">
+        <v>71</v>
+      </c>
+      <c r="H237" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="I237" s="107" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A238" s="39">
+        <v>46160</v>
+      </c>
+      <c r="B238" s="40" t="s">
+        <v>315</v>
+      </c>
+      <c r="C238" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="D238" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="E238" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F238" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="G238" s="108">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="H238" s="48">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I238" s="108">
+        <v>0.59375</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A239" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="B239" s="40" t="s">
+        <v>316</v>
+      </c>
+      <c r="C239" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D239" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="E239" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F239" s="48">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="G239" s="108">
+        <v>0.75</v>
+      </c>
+      <c r="H239" s="48">
+        <v>0.59375</v>
+      </c>
+      <c r="I239" s="108">
+        <v>0.72916666666666663</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A240" s="49"/>
+      <c r="B240" s="40" t="s">
+        <v>317</v>
+      </c>
+      <c r="C240" s="41" t="s">
+        <v>318</v>
+      </c>
+      <c r="D240" s="42">
+        <v>3.125E-2</v>
+      </c>
+      <c r="E240" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F240" s="48">
+        <v>0.96875</v>
+      </c>
+      <c r="G240" s="109">
+        <v>6.25E-2</v>
+      </c>
+      <c r="H240" s="44">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="I240" s="109">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A241" s="51"/>
+      <c r="B241" s="52"/>
+      <c r="C241" s="53"/>
+      <c r="D241" s="54"/>
+      <c r="E241" s="55"/>
+      <c r="F241" s="56"/>
+      <c r="G241" s="110"/>
+      <c r="H241" s="56"/>
+      <c r="I241" s="110"/>
+    </row>
+    <row r="242" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A242" s="1"/>
+      <c r="B242" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E242" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F242" s="58">
+        <v>0.25</v>
+      </c>
+      <c r="G242" s="111" t="s">
+        <v>13</v>
+      </c>
+      <c r="H242" s="58">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="I242" s="112" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A243" s="62">
+        <v>46161</v>
+      </c>
+      <c r="B243" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="C243" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D243" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E243" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F243" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="G243" s="113">
+        <v>0.59375</v>
+      </c>
+      <c r="H243" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="I243" s="104">
+        <v>0.59375</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A244" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C244" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D244" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E244" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F244" s="18">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="G244" s="113">
+        <v>0.78125</v>
+      </c>
+      <c r="H244" s="18">
+        <v>0.59375</v>
+      </c>
+      <c r="I244" s="104">
+        <v>0.76041666666666663</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A245" s="65"/>
+      <c r="B245" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="C245" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="D245" s="12">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="E245" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F245" s="14">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="G245" s="115">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="H245" s="14">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="I245" s="105">
+        <v>0.10416666666666667</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A246" s="67"/>
+      <c r="B246" s="24"/>
+      <c r="C246" s="68"/>
+      <c r="D246" s="26"/>
+      <c r="E246" s="27"/>
+      <c r="F246" s="28"/>
+      <c r="G246" s="116"/>
+      <c r="H246" s="28"/>
+      <c r="I246" s="106"/>
+    </row>
+    <row r="247" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A247" s="31"/>
+      <c r="B247" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C247" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="D247" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E247" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F247" s="36">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G247" s="122">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H247" s="117">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="I247" s="122">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A248" s="39">
+        <v>46162</v>
+      </c>
+      <c r="B248" s="40" t="s">
+        <v>323</v>
+      </c>
+      <c r="C248" s="74" t="s">
+        <v>137</v>
+      </c>
+      <c r="D248" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="E248" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F248" s="48">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G248" s="108">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="H248" s="118">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I248" s="108">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A249" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B249" s="40" t="s">
+        <v>324</v>
+      </c>
+      <c r="C249" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="D249" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E249" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F249" s="48">
+        <v>0.625</v>
+      </c>
+      <c r="G249" s="108">
+        <v>0.8125</v>
+      </c>
+      <c r="H249" s="118">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I249" s="108">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A250" s="49"/>
+      <c r="B250" s="40" t="s">
+        <v>325</v>
+      </c>
+      <c r="C250" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="D250" s="42">
+        <v>9.375E-2</v>
+      </c>
+      <c r="E250" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F250" s="44">
+        <v>3.125E-2</v>
+      </c>
+      <c r="G250" s="109">
+        <v>0.11458333333333333</v>
+      </c>
+      <c r="H250" s="119">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="I250" s="109">
+        <v>0.13541666666666666</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A251" s="51"/>
+      <c r="B251" s="52"/>
+      <c r="C251" s="79"/>
+      <c r="D251" s="54"/>
+      <c r="E251" s="55"/>
+      <c r="F251" s="56"/>
+      <c r="G251" s="110"/>
+      <c r="H251" s="120"/>
+      <c r="I251" s="110"/>
+    </row>
+    <row r="252" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A252" s="1"/>
+      <c r="B252" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E252" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F252" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="G252" s="121">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H252" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="I252" s="121">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A253" s="62">
+        <v>46163</v>
+      </c>
+      <c r="B253" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C253" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D253" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E253" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F253" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="G253" s="104">
+        <v>0.625</v>
+      </c>
+      <c r="H253" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I253" s="104">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A254" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="B254" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="C254" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D254" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E254" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F254" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="G254" s="104">
+        <v>0.84375</v>
+      </c>
+      <c r="H254" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="I254" s="104">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A255" s="65"/>
+      <c r="B255" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="C255" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D255" s="12">
+        <v>0.125</v>
+      </c>
+      <c r="E255" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F255" s="14">
+        <v>3.125E-2</v>
+      </c>
+      <c r="G255" s="105">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H255" s="14">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="I255" s="105">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A256" s="67"/>
+      <c r="B256" s="24"/>
+      <c r="C256" s="68"/>
+      <c r="D256" s="26"/>
+      <c r="E256" s="27"/>
+      <c r="F256" s="85"/>
+      <c r="G256" s="87"/>
+      <c r="H256" s="85"/>
+      <c r="I256" s="87"/>
+    </row>
+    <row r="257" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A257" s="31"/>
+      <c r="B257" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C257" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D257" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="E257" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F257" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="G257" s="122">
+        <v>0.5</v>
+      </c>
+      <c r="H257" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="I257" s="122">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A258" s="39">
+        <v>46164</v>
+      </c>
+      <c r="B258" s="40" t="s">
+        <v>332</v>
+      </c>
+      <c r="C258" s="74" t="s">
+        <v>137</v>
+      </c>
+      <c r="D258" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="E258" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F258" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="G258" s="108">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H258" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="I258" s="108">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A259" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B259" s="40" t="s">
+        <v>333</v>
+      </c>
+      <c r="C259" s="74" t="s">
+        <v>191</v>
+      </c>
+      <c r="D259" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="E259" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F259" s="48">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G259" s="108">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="H259" s="48">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="I259" s="108">
+        <v>0.86458333333333337</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A260" s="49"/>
+      <c r="B260" s="40"/>
+      <c r="C260" s="74"/>
+      <c r="D260" s="42"/>
+      <c r="E260" s="43"/>
+      <c r="F260" s="48"/>
+      <c r="G260" s="108"/>
+      <c r="H260" s="48"/>
+      <c r="I260" s="108"/>
+    </row>
+    <row r="261" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A261" s="51"/>
+      <c r="B261" s="52"/>
+      <c r="C261" s="79"/>
+      <c r="D261" s="54"/>
+      <c r="E261" s="55"/>
+      <c r="F261" s="56"/>
+      <c r="G261" s="110"/>
+      <c r="H261" s="56"/>
+      <c r="I261" s="110"/>
+    </row>
+    <row r="262" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A262" s="1"/>
+      <c r="B262" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C262" s="90" t="s">
+        <v>118</v>
+      </c>
+      <c r="D262" s="4">
+        <v>0.15625</v>
+      </c>
+      <c r="E262" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F262" s="58">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="G262" s="112">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="H262" s="58">
+        <v>7.2916666666666671E-2</v>
+      </c>
+      <c r="I262" s="112">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A263" s="82">
+        <v>46165</v>
+      </c>
+      <c r="B263" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="C263" s="93" t="s">
+        <v>88</v>
+      </c>
+      <c r="D263" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E263" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F263" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G263" s="104">
+        <v>0.5625</v>
+      </c>
+      <c r="H263" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I263" s="104">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A264" s="83" t="s">
+        <v>63</v>
+      </c>
+      <c r="B264" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="C264" s="93" t="s">
+        <v>99</v>
+      </c>
+      <c r="D264" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E264" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F264" s="18">
+        <v>0.5625</v>
+      </c>
+      <c r="G264" s="104">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H264" s="18">
+        <v>0.5625</v>
+      </c>
+      <c r="I264" s="104">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A265" s="114"/>
+      <c r="B265" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C265" s="93" t="s">
+        <v>143</v>
+      </c>
+      <c r="D265" s="12">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="E265" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F265" s="18">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G265" s="104">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="H265" s="18">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I265" s="104">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A266" s="125"/>
+      <c r="B266" s="24"/>
+      <c r="C266" s="94"/>
+      <c r="D266" s="26"/>
+      <c r="E266" s="27"/>
+      <c r="F266" s="28"/>
+      <c r="G266" s="106"/>
+      <c r="H266" s="28"/>
+      <c r="I266" s="106"/>
+    </row>
+    <row r="267" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A267" s="70"/>
+      <c r="B267" s="32" t="s">
+        <v>338</v>
+      </c>
+      <c r="C267" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="D267" s="34">
+        <v>0.19791666666666666</v>
+      </c>
+      <c r="E267" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F267" s="36">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G267" s="107">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="H267" s="117">
+        <v>0.11458333333333333</v>
+      </c>
+      <c r="I267" s="107">
+        <v>0.29166666666666669</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A268" s="73">
+        <v>46166</v>
+      </c>
+      <c r="B268" s="40" t="s">
+        <v>339</v>
+      </c>
+      <c r="C268" s="74" t="s">
+        <v>191</v>
+      </c>
+      <c r="D268" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="E268" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F268" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="G268" s="108">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H268" s="119" t="s">
+        <v>13</v>
+      </c>
+      <c r="I268" s="108">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A269" s="76" t="s">
+        <v>74</v>
+      </c>
+      <c r="B269" s="40" t="s">
+        <v>340</v>
+      </c>
+      <c r="C269" s="74" t="s">
+        <v>265</v>
+      </c>
+      <c r="D269" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="E269" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="F269" s="48">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G269" s="108">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H269" s="118">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I269" s="108">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A270" s="49"/>
+      <c r="B270" s="40" t="s">
+        <v>341</v>
+      </c>
+      <c r="C270" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="D270" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="E270" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F270" s="48">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G270" s="109" t="s">
+        <v>86</v>
+      </c>
+      <c r="H270" s="118">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I270" s="109" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A271" s="51"/>
+      <c r="B271" s="52"/>
+      <c r="C271" s="101"/>
+      <c r="D271" s="100"/>
+      <c r="E271" s="102"/>
+      <c r="F271" s="56"/>
+      <c r="G271" s="110"/>
+      <c r="H271" s="120"/>
+      <c r="I271" s="110"/>
+    </row>
+    <row r="272" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A272" s="1"/>
+      <c r="B272" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C272" s="90" t="s">
+        <v>10</v>
+      </c>
+      <c r="D272" s="4">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="E272" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F272" s="123">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="G272" s="7">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="H272" s="8">
+        <v>0.15625</v>
+      </c>
+      <c r="I272" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A273" s="62">
+        <v>46167</v>
+      </c>
+      <c r="B273" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="C273" s="93" t="s">
+        <v>191</v>
+      </c>
+      <c r="D273" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E273" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F273" s="124">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="G273" s="15">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="H273" s="16">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="I273" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A274" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="B274" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C274" s="93" t="s">
+        <v>72</v>
+      </c>
+      <c r="D274" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="E274" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F274" s="18">
+        <v>0.71875</v>
+      </c>
+      <c r="G274" s="15">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="H274" s="16">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="I274" s="15">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A275" s="65"/>
+      <c r="B275" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C275" s="93" t="s">
+        <v>99</v>
+      </c>
+      <c r="D275" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E275" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F275" s="18">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G275" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H275" s="16">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I275" s="22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A276" s="67"/>
+      <c r="B276" s="24"/>
+      <c r="C276" s="94"/>
+      <c r="D276" s="26"/>
+      <c r="E276" s="27"/>
+      <c r="F276" s="116"/>
+      <c r="G276" s="29"/>
+      <c r="H276" s="69"/>
+      <c r="I276" s="29"/>
+    </row>
+    <row r="277" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A277" s="31"/>
+      <c r="B277" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="C277" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="D277" s="34">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E277" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F277" s="126">
+        <v>0.17708333333333334</v>
+      </c>
+      <c r="G277" s="127">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="H277" s="128">
+        <v>0.19791666666666666</v>
+      </c>
+      <c r="I277" s="127">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A278" s="39">
+        <v>46168</v>
+      </c>
+      <c r="B278" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="C278" s="74" t="s">
+        <v>191</v>
+      </c>
+      <c r="D278" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="E278" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F278" s="48">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G278" s="45">
+        <v>0.65625</v>
+      </c>
+      <c r="H278" s="46">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="I278" s="45">
+        <v>0.63541666666666663</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A279" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B279" s="40" t="s">
+        <v>346</v>
+      </c>
+      <c r="C279" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="D279" s="42">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="E279" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F279" s="48">
+        <v>0.75</v>
+      </c>
+      <c r="G279" s="45">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="H279" s="46">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I279" s="45">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A280" s="49"/>
+      <c r="B280" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="C280" s="74" t="s">
+        <v>137</v>
+      </c>
+      <c r="D280" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="E280" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F280" s="48">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="G280" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="H280" s="46">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="I280" s="50" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A281" s="51"/>
+      <c r="B281" s="52"/>
+      <c r="C281" s="79"/>
+      <c r="D281" s="54"/>
+      <c r="E281" s="55"/>
+      <c r="F281" s="56"/>
+      <c r="G281" s="57"/>
+      <c r="H281" s="54"/>
+      <c r="I281" s="57"/>
+    </row>
+    <row r="282" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A282" s="1"/>
+      <c r="B282" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C282" s="90" t="s">
+        <v>250</v>
+      </c>
+      <c r="D282" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E282" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F282" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="G282" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="H282" s="60">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="I282" s="91">
+        <v>0.42708333333333331</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A283" s="62">
+        <v>46169</v>
+      </c>
+      <c r="B283" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C283" s="93" t="s">
+        <v>191</v>
+      </c>
+      <c r="D283" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E283" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F283" s="18">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="G283" s="63">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H283" s="16">
+        <v>0.46875</v>
+      </c>
+      <c r="I283" s="15">
+        <v>0.63541666666666663</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A284" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B284" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C284" s="93" t="s">
+        <v>36</v>
+      </c>
+      <c r="D284" s="12">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="E284" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F284" s="18">
+        <v>0.78125</v>
+      </c>
+      <c r="G284" s="63">
+        <v>0.9375</v>
+      </c>
+      <c r="H284" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="I284" s="15">
+        <v>0.96875</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A285" s="65"/>
+      <c r="B285" s="10"/>
+      <c r="C285" s="93"/>
+      <c r="D285" s="12"/>
+      <c r="E285" s="13"/>
+      <c r="F285" s="18"/>
+      <c r="G285" s="63"/>
+      <c r="H285" s="16"/>
+      <c r="I285" s="15"/>
+    </row>
+    <row r="286" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A286" s="67"/>
+      <c r="B286" s="24"/>
+      <c r="C286" s="94"/>
+      <c r="D286" s="26"/>
+      <c r="E286" s="27"/>
+      <c r="F286" s="28"/>
+      <c r="G286" s="30"/>
+      <c r="H286" s="69"/>
+      <c r="I286" s="29"/>
+    </row>
+    <row r="287" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A287" s="31"/>
+      <c r="B287" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="C287" s="71" t="s">
+        <v>159</v>
+      </c>
+      <c r="D287" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E287" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F287" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="G287" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="H287" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="I287" s="37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A288" s="39">
+        <v>46170</v>
+      </c>
+      <c r="B288" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="C288" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="D288" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="E288" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F288" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="G288" s="45">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H288" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="I288" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A289" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B289" s="40" t="s">
+        <v>350</v>
+      </c>
+      <c r="C289" s="74" t="s">
+        <v>191</v>
+      </c>
+      <c r="D289" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="E289" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F289" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="G289" s="45">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H289" s="75">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I289" s="45">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A290" s="49"/>
+      <c r="B290" s="40" t="s">
+        <v>351</v>
+      </c>
+      <c r="C290" s="74" t="s">
+        <v>196</v>
+      </c>
+      <c r="D290" s="42">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E290" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F290" s="48">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="G290" s="45">
+        <v>0.96875</v>
+      </c>
+      <c r="H290" s="75">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="I290" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A291" s="51"/>
+      <c r="B291" s="52"/>
+      <c r="C291" s="79"/>
+      <c r="D291" s="54"/>
+      <c r="E291" s="55"/>
+      <c r="F291" s="56"/>
+      <c r="G291" s="57"/>
+      <c r="H291" s="80"/>
+      <c r="I291" s="57"/>
+    </row>
+    <row r="292" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A292" s="1"/>
+      <c r="B292" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C292" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="D292" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E292" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F292" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="G292" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="H292" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="I292" s="61" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A293" s="62">
+        <v>46171</v>
+      </c>
+      <c r="B293" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C293" s="93" t="s">
+        <v>81</v>
+      </c>
+      <c r="D293" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E293" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F293" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G293" s="15">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H293" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="I293" s="15">
+        <v>0.48958333333333331</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A294" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B294" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="C294" s="93" t="s">
+        <v>191</v>
+      </c>
+      <c r="D294" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="E294" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F294" s="18">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="G294" s="15">
+        <v>0.6875</v>
+      </c>
+      <c r="H294" s="16">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="I294" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A295" s="65"/>
+      <c r="B295" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="C295" s="93" t="s">
+        <v>275</v>
+      </c>
+      <c r="D295" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="E295" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F295" s="18">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="G295" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="H295" s="16">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="I295" s="22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A296" s="67"/>
+      <c r="B296" s="24"/>
+      <c r="C296" s="94"/>
+      <c r="D296" s="26"/>
+      <c r="E296" s="27"/>
+      <c r="F296" s="85"/>
+      <c r="G296" s="87"/>
+      <c r="H296" s="85"/>
+      <c r="I296" s="87"/>
+    </row>
+    <row r="297" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A297" s="31"/>
+      <c r="B297" s="32" t="s">
+        <v>357</v>
+      </c>
+      <c r="C297" s="71" t="s">
+        <v>97</v>
+      </c>
+      <c r="D297" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="E297" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F297" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="G297" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H297" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="I297" s="37" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A298" s="73">
+        <v>46172</v>
+      </c>
+      <c r="B298" s="40" t="s">
+        <v>358</v>
+      </c>
+      <c r="C298" s="74" t="s">
+        <v>265</v>
+      </c>
+      <c r="D298" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="E298" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F298" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="G298" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="H298" s="88" t="s">
+        <v>69</v>
+      </c>
+      <c r="I298" s="45">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A299" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B299" s="40" t="s">
+        <v>359</v>
+      </c>
+      <c r="C299" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="D299" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="E299" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F299" s="48">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G299" s="45">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H299" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="I299" s="45">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A300" s="77"/>
+      <c r="B300" s="40" t="s">
+        <v>360</v>
+      </c>
+      <c r="C300" s="74" t="s">
+        <v>118</v>
+      </c>
+      <c r="D300" s="42">
+        <v>0.96875</v>
+      </c>
+      <c r="E300" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F300" s="48">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="G300" s="50">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="H300" s="46">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I300" s="50">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A301" s="78"/>
+      <c r="B301" s="54"/>
+      <c r="C301" s="79"/>
+      <c r="D301" s="54"/>
+      <c r="E301" s="55"/>
+      <c r="F301" s="56"/>
+      <c r="G301" s="57"/>
+      <c r="H301" s="54"/>
+      <c r="I301" s="57"/>
+    </row>
+    <row r="302" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A302" s="226"/>
+      <c r="B302" s="173" t="s">
+        <v>361</v>
+      </c>
+      <c r="C302" s="185" t="s">
+        <v>191</v>
+      </c>
+      <c r="D302" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E302" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F302" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="G302" s="61" t="s">
+        <v>58</v>
+      </c>
+      <c r="H302" s="227" t="s">
+        <v>24</v>
+      </c>
+      <c r="I302" s="228" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A303" s="194">
+        <v>46173</v>
+      </c>
+      <c r="B303" s="173" t="s">
+        <v>362</v>
+      </c>
+      <c r="C303" s="185" t="s">
+        <v>90</v>
+      </c>
+      <c r="D303" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E303" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F303" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G303" s="15">
+        <v>0.53125</v>
+      </c>
+      <c r="H303" s="84" t="s">
+        <v>58</v>
+      </c>
+      <c r="I303" s="15">
+        <v>0.53125</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A304" s="229" t="s">
+        <v>74</v>
+      </c>
+      <c r="B304" s="173" t="s">
+        <v>363</v>
+      </c>
+      <c r="C304" s="185" t="s">
+        <v>88</v>
+      </c>
+      <c r="D304" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E304" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F304" s="18">
+        <v>0.53125</v>
+      </c>
+      <c r="G304" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H304" s="16">
+        <v>0.53125</v>
+      </c>
+      <c r="I304" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A305" s="230"/>
+      <c r="B305" s="173" t="s">
+        <v>364</v>
+      </c>
+      <c r="C305" s="185" t="s">
+        <v>365</v>
+      </c>
+      <c r="D305" s="12">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="E305" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F305" s="130">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G305" s="231">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="H305" s="218">
+        <v>0.9375</v>
+      </c>
+      <c r="I305" s="231">
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A306" s="232"/>
+      <c r="B306" s="233"/>
+      <c r="C306" s="234"/>
+      <c r="D306" s="67"/>
+      <c r="E306" s="27"/>
+      <c r="F306" s="28"/>
+      <c r="G306" s="29"/>
+      <c r="H306" s="69"/>
+      <c r="I306" s="29"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5803,58 +10027,58 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{928BB44D-9009-4EF5-A7E0-17AFE9C73770}">
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M306"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="17.58203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="21.5" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="18.58203125" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="10" width="16.08203125" customWidth="1"/>
-    <col min="11" max="11" width="15.4140625" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" customWidth="1"/>
-    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="19.08203125" customWidth="1"/>
+    <col min="13" max="13" width="16.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="208" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="204" t="s">
+    <row r="1" spans="1:13" s="204" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="205" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="204" t="s">
+      <c r="B1" s="205" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="205" t="s">
+      <c r="C1" s="206" t="s">
         <v>238</v>
       </c>
-      <c r="D1" s="206" t="s">
+      <c r="D1" s="207" t="s">
         <v>241</v>
       </c>
-      <c r="E1" s="207" t="s">
+      <c r="E1" s="208" t="s">
         <v>237</v>
       </c>
-      <c r="F1" s="204" t="s">
+      <c r="F1" s="205" t="s">
         <v>239</v>
       </c>
-      <c r="G1" s="204" t="s">
+      <c r="G1" s="205" t="s">
         <v>240</v>
       </c>
-      <c r="H1" s="204" t="s">
+      <c r="H1" s="205" t="s">
         <v>242</v>
       </c>
-      <c r="I1" s="204" t="s">
+      <c r="I1" s="205" t="s">
         <v>243</v>
       </c>
-      <c r="J1" s="204" t="s">
+      <c r="J1" s="205" t="s">
         <v>244</v>
       </c>
-      <c r="K1" s="204" t="s">
+      <c r="K1" s="205" t="s">
         <v>245</v>
       </c>
-      <c r="L1" s="204" t="s">
+      <c r="L1" s="205" t="s">
         <v>246</v>
       </c>
-      <c r="M1" s="204" t="s">
+      <c r="M1" s="205" t="s">
         <v>247</v>
       </c>
     </row>
@@ -11012,6 +15236,5335 @@
       <c r="L151" s="54"/>
       <c r="M151" s="57"/>
     </row>
+    <row r="152" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A152" s="1"/>
+      <c r="B152" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C152" s="135" t="s">
+        <v>88</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F152" s="136" t="s">
+        <v>21</v>
+      </c>
+      <c r="G152" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="H152" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="I152" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="J152" s="201">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="K152" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="L152" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="M152" s="61" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A153" s="62">
+        <v>46143</v>
+      </c>
+      <c r="B153" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C153" s="138" t="s">
+        <v>250</v>
+      </c>
+      <c r="D153" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E153" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F153" s="139" t="s">
+        <v>25</v>
+      </c>
+      <c r="G153" s="15">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H153" s="84" t="s">
+        <v>69</v>
+      </c>
+      <c r="I153" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J153" s="139" t="s">
+        <v>69</v>
+      </c>
+      <c r="K153" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="L153" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="M153" s="22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A154" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C154" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="D154" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E154" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F154" s="18">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G154" s="15">
+        <v>0.625</v>
+      </c>
+      <c r="H154" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="I154" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="J154" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K154" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="L154" s="16">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="M154" s="15">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A155" s="65"/>
+      <c r="B155" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="C155" s="140" t="s">
+        <v>253</v>
+      </c>
+      <c r="D155" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E155" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F155" s="18">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="G155" s="15">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="H155" s="16">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I155" s="15">
+        <v>0.90625</v>
+      </c>
+      <c r="J155" s="222">
+        <v>0.8125</v>
+      </c>
+      <c r="K155" s="223">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L155" s="224">
+        <v>0.75</v>
+      </c>
+      <c r="M155" s="223">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A156" s="67"/>
+      <c r="B156" s="24"/>
+      <c r="C156" s="141"/>
+      <c r="D156" s="26"/>
+      <c r="E156" s="27"/>
+      <c r="F156" s="116"/>
+      <c r="G156" s="29"/>
+      <c r="H156" s="69"/>
+      <c r="I156" s="29"/>
+      <c r="J156" s="116"/>
+      <c r="K156" s="29"/>
+      <c r="L156" s="69"/>
+      <c r="M156" s="29"/>
+    </row>
+    <row r="157" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A157" s="31"/>
+      <c r="B157" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="C157" s="142" t="s">
+        <v>2</v>
+      </c>
+      <c r="D157" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="E157" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F157" s="117">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="G157" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="H157" s="38">
+        <v>7.2916666666666671E-2</v>
+      </c>
+      <c r="I157" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="J157" s="117" t="s">
+        <v>37</v>
+      </c>
+      <c r="K157" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="L157" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="M157" s="37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A158" s="73">
+        <v>46144</v>
+      </c>
+      <c r="B158" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="C158" s="144" t="s">
+        <v>72</v>
+      </c>
+      <c r="D158" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="E158" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" s="119" t="s">
+        <v>45</v>
+      </c>
+      <c r="G158" s="45">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H158" s="88">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="I158" s="45">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="J158" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="K158" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="L158" s="88" t="s">
+        <v>6</v>
+      </c>
+      <c r="M158" s="50" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A159" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B159" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="C159" s="144" t="s">
+        <v>2</v>
+      </c>
+      <c r="D159" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="E159" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F159" s="118">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G159" s="45">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="H159" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="I159" s="45">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="J159" s="118">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K159" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="L159" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="M159" s="45">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A160" s="77"/>
+      <c r="B160" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="C160" s="144" t="s">
+        <v>148</v>
+      </c>
+      <c r="D160" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="E160" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F160" s="118">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="G160" s="45">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="H160" s="46">
+        <v>0.84375</v>
+      </c>
+      <c r="I160" s="45">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="J160" s="118">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K160" s="45">
+        <v>0.875</v>
+      </c>
+      <c r="L160" s="46">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M160" s="45">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A161" s="78"/>
+      <c r="B161" s="52"/>
+      <c r="C161" s="145"/>
+      <c r="D161" s="54"/>
+      <c r="E161" s="55"/>
+      <c r="F161" s="120"/>
+      <c r="G161" s="57"/>
+      <c r="H161" s="54"/>
+      <c r="I161" s="57"/>
+      <c r="J161" s="120"/>
+      <c r="K161" s="57"/>
+      <c r="L161" s="54"/>
+      <c r="M161" s="57"/>
+    </row>
+    <row r="162" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A162" s="81"/>
+      <c r="B162" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C162" s="135" t="s">
+        <v>2</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F162" s="136">
+        <v>7.2916666666666671E-2</v>
+      </c>
+      <c r="G162" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="H162" s="60">
+        <v>9.375E-2</v>
+      </c>
+      <c r="I162" s="61">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="J162" s="136" t="s">
+        <v>21</v>
+      </c>
+      <c r="K162" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="L162" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="M162" s="61" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A163" s="82">
+        <v>46145</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C163" s="138" t="s">
+        <v>260</v>
+      </c>
+      <c r="D163" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E163" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F163" s="139" t="s">
+        <v>43</v>
+      </c>
+      <c r="G163" s="63">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H163" s="84" t="s">
+        <v>79</v>
+      </c>
+      <c r="I163" s="15">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="J163" s="139" t="s">
+        <v>58</v>
+      </c>
+      <c r="K163" s="66" t="s">
+        <v>31</v>
+      </c>
+      <c r="L163" s="84" t="s">
+        <v>6</v>
+      </c>
+      <c r="M163" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A164" s="83" t="s">
+        <v>74</v>
+      </c>
+      <c r="B164" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="C164" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="D164" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="E164" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F164" s="124">
+        <v>0.5</v>
+      </c>
+      <c r="G164" s="63">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H164" s="16">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I164" s="15">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="J164" s="124">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K164" s="63">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="L164" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="M164" s="15">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A165" s="65"/>
+      <c r="B165" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C165" s="138" t="s">
+        <v>118</v>
+      </c>
+      <c r="D165" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E165" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F165" s="124">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G165" s="63">
+        <v>0.96875</v>
+      </c>
+      <c r="H165" s="16">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="I165" s="15">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="J165" s="124">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="K165" s="63">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="L165" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="M165" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A166" s="67"/>
+      <c r="B166" s="24"/>
+      <c r="C166" s="146"/>
+      <c r="D166" s="26"/>
+      <c r="E166" s="27"/>
+      <c r="F166" s="116"/>
+      <c r="G166" s="30"/>
+      <c r="H166" s="69"/>
+      <c r="I166" s="29"/>
+      <c r="J166" s="116"/>
+      <c r="K166" s="30"/>
+      <c r="L166" s="69"/>
+      <c r="M166" s="29"/>
+    </row>
+    <row r="167" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A167" s="31"/>
+      <c r="B167" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="C167" s="147" t="s">
+        <v>2</v>
+      </c>
+      <c r="D167" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="E167" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F167" s="117">
+        <v>0.11458333333333333</v>
+      </c>
+      <c r="G167" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="H167" s="72">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="I167" s="37">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="J167" s="117" t="s">
+        <v>39</v>
+      </c>
+      <c r="K167" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="L167" s="72" t="s">
+        <v>149</v>
+      </c>
+      <c r="M167" s="37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A168" s="39">
+        <v>46146</v>
+      </c>
+      <c r="B168" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="C168" s="148" t="s">
+        <v>265</v>
+      </c>
+      <c r="D168" s="149" t="s">
+        <v>199</v>
+      </c>
+      <c r="E168" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F168" s="119" t="s">
+        <v>79</v>
+      </c>
+      <c r="G168" s="45">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="H168" s="99">
+        <v>0.34375</v>
+      </c>
+      <c r="I168" s="45">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="J168" s="119" t="s">
+        <v>46</v>
+      </c>
+      <c r="K168" s="45">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L168" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="M168" s="50" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A169" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="B169" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C169" s="148" t="s">
+        <v>2</v>
+      </c>
+      <c r="D169" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="E169" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F169" s="118">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="G169" s="45">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H169" s="75">
+        <v>0.53125</v>
+      </c>
+      <c r="I169" s="45">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J169" s="118">
+        <v>0.4375</v>
+      </c>
+      <c r="K169" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="L169" s="75">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="M169" s="45">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A170" s="49"/>
+      <c r="B170" s="42" t="s">
+        <v>266</v>
+      </c>
+      <c r="C170" s="148" t="s">
+        <v>118</v>
+      </c>
+      <c r="D170" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="E170" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F170" s="118">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="G170" s="50">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="H170" s="75">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="I170" s="45">
+        <v>0.96875</v>
+      </c>
+      <c r="J170" s="118">
+        <v>0.875</v>
+      </c>
+      <c r="K170" s="45">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="L170" s="75">
+        <v>0.8125</v>
+      </c>
+      <c r="M170" s="45">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A171" s="51"/>
+      <c r="B171" s="54"/>
+      <c r="C171" s="150"/>
+      <c r="D171" s="54"/>
+      <c r="E171" s="55"/>
+      <c r="F171" s="120"/>
+      <c r="G171" s="57"/>
+      <c r="H171" s="80"/>
+      <c r="I171" s="57"/>
+      <c r="J171" s="120"/>
+      <c r="K171" s="57"/>
+      <c r="L171" s="80"/>
+      <c r="M171" s="57"/>
+    </row>
+    <row r="172" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A172" s="1"/>
+      <c r="B172" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C172" s="135" t="s">
+        <v>88</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F172" s="136" t="s">
+        <v>24</v>
+      </c>
+      <c r="G172" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="H172" s="60" t="s">
+        <v>230</v>
+      </c>
+      <c r="I172" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="J172" s="136" t="s">
+        <v>54</v>
+      </c>
+      <c r="K172" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="L172" s="60" t="s">
+        <v>217</v>
+      </c>
+      <c r="M172" s="61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A173" s="62">
+        <v>46147</v>
+      </c>
+      <c r="B173" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C173" s="138" t="s">
+        <v>90</v>
+      </c>
+      <c r="D173" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E173" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F173" s="139" t="s">
+        <v>58</v>
+      </c>
+      <c r="G173" s="15">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="H173" s="84">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="I173" s="15">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="J173" s="139" t="s">
+        <v>60</v>
+      </c>
+      <c r="K173" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="L173" s="84" t="s">
+        <v>25</v>
+      </c>
+      <c r="M173" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A174" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C174" s="138" t="s">
+        <v>88</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E174" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F174" s="124">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="G174" s="15">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H174" s="16">
+        <v>0.53125</v>
+      </c>
+      <c r="I174" s="15">
+        <v>0.65625</v>
+      </c>
+      <c r="J174" s="124">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="K174" s="15">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L174" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="M174" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A175" s="65"/>
+      <c r="B175" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C175" s="138" t="s">
+        <v>148</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E175" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F175" s="124">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="G175" s="22">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="H175" s="16">
+        <v>0.90625</v>
+      </c>
+      <c r="I175" s="22">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="J175" s="124">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="K175" s="15">
+        <v>0.9375</v>
+      </c>
+      <c r="L175" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M175" s="15">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A176" s="67"/>
+      <c r="B176" s="24"/>
+      <c r="C176" s="146"/>
+      <c r="D176" s="26"/>
+      <c r="E176" s="27"/>
+      <c r="F176" s="86"/>
+      <c r="G176" s="87"/>
+      <c r="H176" s="85"/>
+      <c r="I176" s="87"/>
+      <c r="J176" s="86"/>
+      <c r="K176" s="87"/>
+      <c r="L176" s="85"/>
+      <c r="M176" s="87"/>
+    </row>
+    <row r="177" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A177" s="31"/>
+      <c r="B177" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="C177" s="147" t="s">
+        <v>191</v>
+      </c>
+      <c r="D177" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="E177" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F177" s="117" t="s">
+        <v>3</v>
+      </c>
+      <c r="G177" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="H177" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="I177" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="J177" s="117" t="s">
+        <v>217</v>
+      </c>
+      <c r="K177" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="L177" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="M177" s="37" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A178" s="39">
+        <v>46148</v>
+      </c>
+      <c r="B178" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="C178" s="148" t="s">
+        <v>133</v>
+      </c>
+      <c r="D178" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="E178" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F178" s="119" t="s">
+        <v>71</v>
+      </c>
+      <c r="G178" s="45">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H178" s="88">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="I178" s="45">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J178" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="K178" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="L178" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="M178" s="50" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A179" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B179" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C179" s="148" t="s">
+        <v>88</v>
+      </c>
+      <c r="D179" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="E179" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F179" s="118">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G179" s="45">
+        <v>0.6875</v>
+      </c>
+      <c r="H179" s="46">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I179" s="45">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J179" s="118">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="K179" s="45">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L179" s="46">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="M179" s="45">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A180" s="49"/>
+      <c r="B180" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C180" s="148" t="s">
+        <v>275</v>
+      </c>
+      <c r="D180" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E180" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F180" s="118">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="G180" s="50">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="H180" s="46">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="I180" s="50">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="J180" s="118">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K180" s="45">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="L180" s="46">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="M180" s="45">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A181" s="51"/>
+      <c r="B181" s="54"/>
+      <c r="C181" s="150"/>
+      <c r="D181" s="54"/>
+      <c r="E181" s="55"/>
+      <c r="F181" s="120"/>
+      <c r="G181" s="57"/>
+      <c r="H181" s="54"/>
+      <c r="I181" s="57"/>
+      <c r="J181" s="120"/>
+      <c r="K181" s="57"/>
+      <c r="L181" s="54"/>
+      <c r="M181" s="57"/>
+    </row>
+    <row r="182" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A182" s="1"/>
+      <c r="B182" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C182" s="151" t="s">
+        <v>97</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F182" s="136">
+        <v>0.1875</v>
+      </c>
+      <c r="G182" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="H182" s="60">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="I182" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="J182" s="136" t="s">
+        <v>217</v>
+      </c>
+      <c r="K182" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="L182" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="M182" s="61" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A183" s="62">
+        <v>46149</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="C183" s="152" t="s">
+        <v>99</v>
+      </c>
+      <c r="D183" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E183" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F183" s="139" t="s">
+        <v>60</v>
+      </c>
+      <c r="G183" s="15">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H183" s="84" t="s">
+        <v>60</v>
+      </c>
+      <c r="I183" s="15">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J183" s="124">
+        <v>0.4375</v>
+      </c>
+      <c r="K183" s="15">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="L183" s="84" t="s">
+        <v>46</v>
+      </c>
+      <c r="M183" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A184" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="B184" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C184" s="152" t="s">
+        <v>191</v>
+      </c>
+      <c r="D184" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E184" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F184" s="124">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G184" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H184" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I184" s="15">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="J184" s="124">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="K184" s="15">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L184" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="M184" s="15">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A185" s="65"/>
+      <c r="B185" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C185" s="152" t="s">
+        <v>253</v>
+      </c>
+      <c r="D185" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E185" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F185" s="124">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G185" s="22">
+        <v>7.2916666666666671E-2</v>
+      </c>
+      <c r="H185" s="16">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="I185" s="22">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="J185" s="124">
+        <v>0.9375</v>
+      </c>
+      <c r="K185" s="15">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="L185" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="M185" s="15">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A186" s="67"/>
+      <c r="B186" s="26"/>
+      <c r="C186" s="153"/>
+      <c r="D186" s="26"/>
+      <c r="E186" s="27"/>
+      <c r="F186" s="116"/>
+      <c r="G186" s="29"/>
+      <c r="H186" s="69"/>
+      <c r="I186" s="29"/>
+      <c r="J186" s="116"/>
+      <c r="K186" s="29"/>
+      <c r="L186" s="69"/>
+      <c r="M186" s="29"/>
+    </row>
+    <row r="187" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A187" s="31"/>
+      <c r="B187" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="C187" s="147" t="s">
+        <v>97</v>
+      </c>
+      <c r="D187" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E187" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F187" s="154">
+        <v>0.25</v>
+      </c>
+      <c r="G187" s="209">
+        <v>0.4375</v>
+      </c>
+      <c r="H187" s="155">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="I187" s="209">
+        <v>0.4375</v>
+      </c>
+      <c r="J187" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="K187" s="127" t="s">
+        <v>6</v>
+      </c>
+      <c r="L187" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="M187" s="127" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A188" s="39">
+        <v>46150</v>
+      </c>
+      <c r="B188" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="C188" s="148" t="s">
+        <v>137</v>
+      </c>
+      <c r="D188" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="E188" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F188" s="118">
+        <v>0.4375</v>
+      </c>
+      <c r="G188" s="45">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H188" s="75">
+        <v>0.4375</v>
+      </c>
+      <c r="I188" s="45">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J188" s="118" t="s">
+        <v>231</v>
+      </c>
+      <c r="K188" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="L188" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="M188" s="45">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A189" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B189" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="C189" s="148" t="s">
+        <v>97</v>
+      </c>
+      <c r="D189" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="E189" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F189" s="118">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G189" s="45">
+        <v>0.71875</v>
+      </c>
+      <c r="H189" s="75">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I189" s="45">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="J189" s="118" t="s">
+        <v>231</v>
+      </c>
+      <c r="K189" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="L189" s="75">
+        <v>0.5625</v>
+      </c>
+      <c r="M189" s="45">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A190" s="49"/>
+      <c r="B190" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="C190" s="148" t="s">
+        <v>67</v>
+      </c>
+      <c r="D190" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="E190" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F190" s="118">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="G190" s="50">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="H190" s="75">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="I190" s="50">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="J190" s="118">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="K190" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="L190" s="75">
+        <v>0.875</v>
+      </c>
+      <c r="M190" s="45">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A191" s="51"/>
+      <c r="B191" s="100"/>
+      <c r="C191" s="102"/>
+      <c r="D191" s="100"/>
+      <c r="E191" s="102"/>
+      <c r="F191" s="120"/>
+      <c r="G191" s="57"/>
+      <c r="H191" s="80"/>
+      <c r="I191" s="57"/>
+      <c r="J191" s="120"/>
+      <c r="K191" s="57"/>
+      <c r="L191" s="80"/>
+      <c r="M191" s="57"/>
+    </row>
+    <row r="192" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A192" s="1"/>
+      <c r="B192" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C192" s="151" t="s">
+        <v>184</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E192" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F192" s="136">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G192" s="121">
+        <v>0.4375</v>
+      </c>
+      <c r="H192" s="58">
+        <v>0.3125</v>
+      </c>
+      <c r="I192" s="121">
+        <v>0.4375</v>
+      </c>
+      <c r="J192" s="136">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="K192" s="112" t="s">
+        <v>25</v>
+      </c>
+      <c r="L192" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="M192" s="121">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A193" s="82">
+        <v>46151</v>
+      </c>
+      <c r="B193" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C193" s="152" t="s">
+        <v>137</v>
+      </c>
+      <c r="D193" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E193" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F193" s="124">
+        <v>0.4375</v>
+      </c>
+      <c r="G193" s="104">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H193" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="I193" s="104">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J193" s="124" t="s">
+        <v>366</v>
+      </c>
+      <c r="K193" s="104" t="s">
+        <v>231</v>
+      </c>
+      <c r="L193" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="M193" s="104">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A194" s="83" t="s">
+        <v>63</v>
+      </c>
+      <c r="B194" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="C194" s="152" t="s">
+        <v>143</v>
+      </c>
+      <c r="D194" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="E194" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F194" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G194" s="104">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="H194" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I194" s="104">
+        <v>0.71875</v>
+      </c>
+      <c r="J194" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="K194" s="104" t="s">
+        <v>231</v>
+      </c>
+      <c r="L194" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="M194" s="104">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A195" s="114"/>
+      <c r="B195" s="12"/>
+      <c r="C195" s="152"/>
+      <c r="D195" s="12"/>
+      <c r="E195" s="13"/>
+      <c r="F195" s="18"/>
+      <c r="G195" s="104"/>
+      <c r="H195" s="18"/>
+      <c r="I195" s="104"/>
+      <c r="J195" s="18"/>
+      <c r="K195" s="104"/>
+      <c r="L195" s="18"/>
+      <c r="M195" s="104"/>
+    </row>
+    <row r="196" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A196" s="125"/>
+      <c r="B196" s="26"/>
+      <c r="C196" s="153"/>
+      <c r="D196" s="26"/>
+      <c r="E196" s="27"/>
+      <c r="F196" s="116"/>
+      <c r="G196" s="106"/>
+      <c r="H196" s="28"/>
+      <c r="I196" s="106"/>
+      <c r="J196" s="116"/>
+      <c r="K196" s="106"/>
+      <c r="L196" s="28"/>
+      <c r="M196" s="106"/>
+    </row>
+    <row r="197" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A197" s="70"/>
+      <c r="B197" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="C197" s="147" t="s">
+        <v>52</v>
+      </c>
+      <c r="D197" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E197" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F197" s="143">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="G197" s="107">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="H197" s="36">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="I197" s="107">
+        <v>0.11458333333333333</v>
+      </c>
+      <c r="J197" s="117" t="s">
+        <v>21</v>
+      </c>
+      <c r="K197" s="107" t="s">
+        <v>39</v>
+      </c>
+      <c r="L197" s="156">
+        <v>0.9375</v>
+      </c>
+      <c r="M197" s="107" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A198" s="73">
+        <v>46152</v>
+      </c>
+      <c r="B198" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="C198" s="148" t="s">
+        <v>97</v>
+      </c>
+      <c r="D198" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="E198" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F198" s="119">
+        <v>0.3125</v>
+      </c>
+      <c r="G198" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H198" s="44">
+        <v>0.34375</v>
+      </c>
+      <c r="I198" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J198" s="119">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="K198" s="109" t="s">
+        <v>69</v>
+      </c>
+      <c r="L198" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="M198" s="108">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A199" s="76" t="s">
+        <v>74</v>
+      </c>
+      <c r="B199" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C199" s="148" t="s">
+        <v>99</v>
+      </c>
+      <c r="D199" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="E199" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="F199" s="118">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G199" s="108">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H199" s="48">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I199" s="108">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J199" s="118" t="s">
+        <v>231</v>
+      </c>
+      <c r="K199" s="108" t="s">
+        <v>231</v>
+      </c>
+      <c r="L199" s="48">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="M199" s="108">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A200" s="49"/>
+      <c r="B200" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="C200" s="148" t="s">
+        <v>137</v>
+      </c>
+      <c r="D200" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="E200" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F200" s="118">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G200" s="108">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H200" s="48">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I200" s="108">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="J200" s="118" t="s">
+        <v>231</v>
+      </c>
+      <c r="K200" s="108" t="s">
+        <v>231</v>
+      </c>
+      <c r="L200" s="48">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M200" s="108">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A201" s="51"/>
+      <c r="B201" s="54"/>
+      <c r="C201" s="150"/>
+      <c r="D201" s="54"/>
+      <c r="E201" s="55"/>
+      <c r="F201" s="120"/>
+      <c r="G201" s="110"/>
+      <c r="H201" s="56"/>
+      <c r="I201" s="110"/>
+      <c r="J201" s="120"/>
+      <c r="K201" s="110"/>
+      <c r="L201" s="56"/>
+      <c r="M201" s="110"/>
+    </row>
+    <row r="202" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A202" s="1"/>
+      <c r="B202" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C202" s="151" t="s">
+        <v>36</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F202" s="136" t="s">
+        <v>21</v>
+      </c>
+      <c r="G202" s="111">
+        <v>0.1875</v>
+      </c>
+      <c r="H202" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="I202" s="112">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="J202" s="136" t="s">
+        <v>39</v>
+      </c>
+      <c r="K202" s="111" t="s">
+        <v>217</v>
+      </c>
+      <c r="L202" s="132">
+        <v>0.875</v>
+      </c>
+      <c r="M202" s="112" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A203" s="62">
+        <v>46153</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C203" s="152" t="s">
+        <v>97</v>
+      </c>
+      <c r="D203" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E203" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F203" s="139">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G203" s="113">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H203" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="I203" s="104">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J203" s="139">
+        <v>0.25</v>
+      </c>
+      <c r="K203" s="115" t="s">
+        <v>59</v>
+      </c>
+      <c r="L203" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="M203" s="104">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A204" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="B204" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C204" s="152" t="s">
+        <v>90</v>
+      </c>
+      <c r="D204" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E204" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="F204" s="124">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G204" s="113">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H204" s="18">
+        <v>0.5625</v>
+      </c>
+      <c r="I204" s="104">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="J204" s="124" t="s">
+        <v>231</v>
+      </c>
+      <c r="K204" s="113" t="s">
+        <v>231</v>
+      </c>
+      <c r="L204" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="M204" s="104">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A205" s="65"/>
+      <c r="B205" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="C205" s="152" t="s">
+        <v>99</v>
+      </c>
+      <c r="D205" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="E205" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F205" s="124">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="G205" s="113">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="H205" s="18">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="I205" s="104">
+        <v>0.875</v>
+      </c>
+      <c r="J205" s="124" t="s">
+        <v>231</v>
+      </c>
+      <c r="K205" s="113" t="s">
+        <v>231</v>
+      </c>
+      <c r="L205" s="18">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M205" s="104">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A206" s="67"/>
+      <c r="B206" s="26"/>
+      <c r="C206" s="153"/>
+      <c r="D206" s="26"/>
+      <c r="E206" s="27"/>
+      <c r="F206" s="116"/>
+      <c r="G206" s="116"/>
+      <c r="H206" s="28"/>
+      <c r="I206" s="106"/>
+      <c r="J206" s="116"/>
+      <c r="K206" s="116"/>
+      <c r="L206" s="28"/>
+      <c r="M206" s="106"/>
+    </row>
+    <row r="207" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A207" s="31"/>
+      <c r="B207" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="C207" s="147" t="s">
+        <v>29</v>
+      </c>
+      <c r="D207" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E207" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F207" s="117" t="s">
+        <v>7</v>
+      </c>
+      <c r="G207" s="107">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="H207" s="117" t="s">
+        <v>5</v>
+      </c>
+      <c r="I207" s="107" t="s">
+        <v>8</v>
+      </c>
+      <c r="J207" s="117" t="s">
+        <v>149</v>
+      </c>
+      <c r="K207" s="107" t="s">
+        <v>3</v>
+      </c>
+      <c r="L207" s="117" t="s">
+        <v>37</v>
+      </c>
+      <c r="M207" s="107" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A208" s="39">
+        <v>46154</v>
+      </c>
+      <c r="B208" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="C208" s="148" t="s">
+        <v>191</v>
+      </c>
+      <c r="D208" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="E208" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F208" s="119">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="G208" s="108">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H208" s="119">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="I208" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J208" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="K208" s="109" t="s">
+        <v>46</v>
+      </c>
+      <c r="L208" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="M208" s="108">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A209" s="183" t="s">
+        <v>92</v>
+      </c>
+      <c r="B209" s="42" t="s">
+        <v>292</v>
+      </c>
+      <c r="C209" s="148" t="s">
+        <v>72</v>
+      </c>
+      <c r="D209" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E209" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F209" s="118">
+        <v>0.65625</v>
+      </c>
+      <c r="G209" s="108">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H209" s="118">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="I209" s="108">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J209" s="118">
+        <v>0.6875</v>
+      </c>
+      <c r="K209" s="108">
+        <v>0.75</v>
+      </c>
+      <c r="L209" s="118">
+        <v>0.5625</v>
+      </c>
+      <c r="M209" s="108">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A210" s="49"/>
+      <c r="B210" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="C210" s="148" t="s">
+        <v>137</v>
+      </c>
+      <c r="D210" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="E210" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F210" s="118">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G210" s="109" t="s">
+        <v>21</v>
+      </c>
+      <c r="H210" s="118">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I210" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="J210" s="118">
+        <v>0.75</v>
+      </c>
+      <c r="K210" s="108">
+        <v>0.8125</v>
+      </c>
+      <c r="L210" s="118">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M210" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A211" s="51"/>
+      <c r="B211" s="54"/>
+      <c r="C211" s="150"/>
+      <c r="D211" s="54"/>
+      <c r="E211" s="55"/>
+      <c r="F211" s="120"/>
+      <c r="G211" s="110"/>
+      <c r="H211" s="120"/>
+      <c r="I211" s="110"/>
+      <c r="J211" s="120"/>
+      <c r="K211" s="110"/>
+      <c r="L211" s="120"/>
+      <c r="M211" s="110"/>
+    </row>
+    <row r="212" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A212" s="1"/>
+      <c r="B212" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C212" s="151" t="s">
+        <v>19</v>
+      </c>
+      <c r="D212" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E212" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F212" s="136" t="s">
+        <v>24</v>
+      </c>
+      <c r="G212" s="112">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="H212" s="58" t="s">
+        <v>230</v>
+      </c>
+      <c r="I212" s="112" t="s">
+        <v>25</v>
+      </c>
+      <c r="J212" s="136" t="s">
+        <v>44</v>
+      </c>
+      <c r="K212" s="112" t="s">
+        <v>8</v>
+      </c>
+      <c r="L212" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="M212" s="112" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A213" s="62">
+        <v>46155</v>
+      </c>
+      <c r="B213" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C213" s="152" t="s">
+        <v>191</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E213" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F213" s="139" t="s">
+        <v>31</v>
+      </c>
+      <c r="G213" s="104">
+        <v>0.5625</v>
+      </c>
+      <c r="H213" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I213" s="104">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J213" s="139" t="s">
+        <v>58</v>
+      </c>
+      <c r="K213" s="105" t="s">
+        <v>60</v>
+      </c>
+      <c r="L213" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="M213" s="104">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A214" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B214" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="C214" s="152" t="s">
+        <v>113</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E214" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F214" s="124">
+        <v>0.6875</v>
+      </c>
+      <c r="G214" s="104">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="H214" s="18">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="I214" s="104">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="J214" s="124">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="K214" s="104">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="L214" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="M214" s="104">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A215" s="65"/>
+      <c r="B215" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C215" s="152" t="s">
+        <v>143</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E215" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F215" s="124">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="G215" s="105" t="s">
+        <v>7</v>
+      </c>
+      <c r="H215" s="18">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I215" s="105">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="J215" s="124">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K215" s="104">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="L215" s="18">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="M215" s="105" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A216" s="67"/>
+      <c r="B216" s="26"/>
+      <c r="C216" s="153"/>
+      <c r="D216" s="26"/>
+      <c r="E216" s="27"/>
+      <c r="F216" s="86"/>
+      <c r="G216" s="87"/>
+      <c r="H216" s="85"/>
+      <c r="I216" s="87"/>
+      <c r="J216" s="86"/>
+      <c r="K216" s="87"/>
+      <c r="L216" s="85"/>
+      <c r="M216" s="87"/>
+    </row>
+    <row r="217" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A217" s="31"/>
+      <c r="B217" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="C217" s="147" t="s">
+        <v>113</v>
+      </c>
+      <c r="D217" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="E217" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F217" s="117" t="s">
+        <v>3</v>
+      </c>
+      <c r="G217" s="107">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="H217" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="I217" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="J217" s="117" t="s">
+        <v>57</v>
+      </c>
+      <c r="K217" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="L217" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="M217" s="107" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A218" s="39">
+        <v>46156</v>
+      </c>
+      <c r="B218" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="C218" s="148" t="s">
+        <v>88</v>
+      </c>
+      <c r="D218" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="E218" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F218" s="119" t="s">
+        <v>115</v>
+      </c>
+      <c r="G218" s="108">
+        <v>0.5625</v>
+      </c>
+      <c r="H218" s="48">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="I218" s="108">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J218" s="119">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="K218" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="L218" s="48">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M218" s="108">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A219" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B219" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="C219" s="148" t="s">
+        <v>10</v>
+      </c>
+      <c r="D219" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="E219" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F219" s="118">
+        <v>0.71875</v>
+      </c>
+      <c r="G219" s="108">
+        <v>0.84375</v>
+      </c>
+      <c r="H219" s="48">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="I219" s="108">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="J219" s="118">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K219" s="108">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L219" s="48">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M219" s="108">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A220" s="49"/>
+      <c r="B220" s="42"/>
+      <c r="C220" s="148"/>
+      <c r="D220" s="42"/>
+      <c r="E220" s="43"/>
+      <c r="F220" s="118"/>
+      <c r="G220" s="108"/>
+      <c r="H220" s="48"/>
+      <c r="I220" s="108"/>
+      <c r="J220" s="118"/>
+      <c r="K220" s="108"/>
+      <c r="L220" s="48"/>
+      <c r="M220" s="108"/>
+    </row>
+    <row r="221" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A221" s="51"/>
+      <c r="B221" s="54"/>
+      <c r="C221" s="150"/>
+      <c r="D221" s="54"/>
+      <c r="E221" s="55"/>
+      <c r="F221" s="120"/>
+      <c r="G221" s="110"/>
+      <c r="H221" s="56"/>
+      <c r="I221" s="110"/>
+      <c r="J221" s="120"/>
+      <c r="K221" s="110"/>
+      <c r="L221" s="56"/>
+      <c r="M221" s="110"/>
+    </row>
+    <row r="222" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A222" s="1"/>
+      <c r="B222" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C222" s="151" t="s">
+        <v>97</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E222" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F222" s="210">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="G222" s="158" t="s">
+        <v>26</v>
+      </c>
+      <c r="H222" s="211">
+        <v>0.96875</v>
+      </c>
+      <c r="I222" s="158">
+        <v>9.375E-2</v>
+      </c>
+      <c r="J222" s="210">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="K222" s="225">
+        <v>0.9375</v>
+      </c>
+      <c r="L222" s="211">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="M222" s="158" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A223" s="62">
+        <v>46157</v>
+      </c>
+      <c r="B223" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="C223" s="152" t="s">
+        <v>250</v>
+      </c>
+      <c r="D223" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E223" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F223" s="212" t="s">
+        <v>8</v>
+      </c>
+      <c r="G223" s="213" t="s">
+        <v>60</v>
+      </c>
+      <c r="H223" s="214" t="s">
+        <v>6</v>
+      </c>
+      <c r="I223" s="213" t="s">
+        <v>71</v>
+      </c>
+      <c r="J223" s="212" t="s">
+        <v>6</v>
+      </c>
+      <c r="K223" s="213" t="s">
+        <v>69</v>
+      </c>
+      <c r="L223" s="214" t="s">
+        <v>217</v>
+      </c>
+      <c r="M223" s="213" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A224" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B224" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="C224" s="152" t="s">
+        <v>2</v>
+      </c>
+      <c r="D224" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E224" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F224" s="160">
+        <v>0.4375</v>
+      </c>
+      <c r="G224" s="161">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H224" s="162">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I224" s="161">
+        <v>0.5625</v>
+      </c>
+      <c r="J224" s="212" t="s">
+        <v>60</v>
+      </c>
+      <c r="K224" s="161">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L224" s="162">
+        <v>0.4375</v>
+      </c>
+      <c r="M224" s="161">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A225" s="65"/>
+      <c r="B225" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C225" s="152">
+        <v>0.6</v>
+      </c>
+      <c r="D225" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E225" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F225" s="160">
+        <v>0.75</v>
+      </c>
+      <c r="G225" s="161">
+        <v>0.875</v>
+      </c>
+      <c r="H225" s="162">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="I225" s="161">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J225" s="160">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="K225" s="161">
+        <v>0.8125</v>
+      </c>
+      <c r="L225" s="162">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M225" s="161">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A226" s="67"/>
+      <c r="B226" s="26"/>
+      <c r="C226" s="153"/>
+      <c r="D226" s="26"/>
+      <c r="E226" s="27"/>
+      <c r="F226" s="163"/>
+      <c r="G226" s="164"/>
+      <c r="H226" s="165"/>
+      <c r="I226" s="164"/>
+      <c r="J226" s="163"/>
+      <c r="K226" s="164"/>
+      <c r="L226" s="165"/>
+      <c r="M226" s="164"/>
+    </row>
+    <row r="227" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A227" s="31"/>
+      <c r="B227" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="C227" s="147" t="s">
+        <v>2</v>
+      </c>
+      <c r="D227" s="34">
+        <v>9.375E-2</v>
+      </c>
+      <c r="E227" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F227" s="154">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="G227" s="168" t="s">
+        <v>3</v>
+      </c>
+      <c r="H227" s="154">
+        <v>3.125E-2</v>
+      </c>
+      <c r="I227" s="168">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="J227" s="166">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="K227" s="167">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="L227" s="154" t="s">
+        <v>37</v>
+      </c>
+      <c r="M227" s="168" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A228" s="73">
+        <v>46158</v>
+      </c>
+      <c r="B228" s="42" t="s">
+        <v>306</v>
+      </c>
+      <c r="C228" s="148" t="s">
+        <v>72</v>
+      </c>
+      <c r="D228" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="E228" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F228" s="119" t="s">
+        <v>42</v>
+      </c>
+      <c r="G228" s="108">
+        <v>0.40625</v>
+      </c>
+      <c r="H228" s="119">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="I228" s="109" t="s">
+        <v>13</v>
+      </c>
+      <c r="J228" s="119" t="s">
+        <v>25</v>
+      </c>
+      <c r="K228" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="L228" s="119" t="s">
+        <v>57</v>
+      </c>
+      <c r="M228" s="109" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A229" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B229" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="C229" s="148" t="s">
+        <v>16</v>
+      </c>
+      <c r="D229" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="E229" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F229" s="118">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="G229" s="108">
+        <v>0.59375</v>
+      </c>
+      <c r="H229" s="118">
+        <v>0.46875</v>
+      </c>
+      <c r="I229" s="108">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="J229" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="K229" s="108">
+        <v>0.4375</v>
+      </c>
+      <c r="L229" s="118">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="M229" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A230" s="77"/>
+      <c r="B230" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="C230" s="148" t="s">
+        <v>125</v>
+      </c>
+      <c r="D230" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="E230" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F230" s="118">
+        <v>0.78125</v>
+      </c>
+      <c r="G230" s="108">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="H230" s="118">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="I230" s="108">
+        <v>0.875</v>
+      </c>
+      <c r="J230" s="118">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K230" s="108">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L230" s="118">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M230" s="108">
+        <v>0.77083333333333337</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A231" s="78"/>
+      <c r="B231" s="100"/>
+      <c r="C231" s="102"/>
+      <c r="D231" s="100"/>
+      <c r="E231" s="102"/>
+      <c r="F231" s="120"/>
+      <c r="G231" s="110"/>
+      <c r="H231" s="120"/>
+      <c r="I231" s="110"/>
+      <c r="J231" s="120"/>
+      <c r="K231" s="110"/>
+      <c r="L231" s="120"/>
+      <c r="M231" s="110"/>
+    </row>
+    <row r="232" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A232" s="169"/>
+      <c r="B232" s="170" t="s">
+        <v>308</v>
+      </c>
+      <c r="C232" s="171" t="s">
+        <v>41</v>
+      </c>
+      <c r="D232" s="172" t="s">
+        <v>24</v>
+      </c>
+      <c r="E232" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F232" s="58">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G232" s="112" t="s">
+        <v>164</v>
+      </c>
+      <c r="H232" s="58">
+        <v>6.25E-2</v>
+      </c>
+      <c r="I232" s="112">
+        <v>0.17708333333333334</v>
+      </c>
+      <c r="J232" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="K232" s="112" t="s">
+        <v>21</v>
+      </c>
+      <c r="L232" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="M232" s="112" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A233" s="82">
+        <v>46159</v>
+      </c>
+      <c r="B233" s="170" t="s">
+        <v>309</v>
+      </c>
+      <c r="C233" s="171" t="s">
+        <v>81</v>
+      </c>
+      <c r="D233" s="173" t="s">
+        <v>70</v>
+      </c>
+      <c r="E233" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F233" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G233" s="104">
+        <v>0.4375</v>
+      </c>
+      <c r="H233" s="14">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="I233" s="104">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J233" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K233" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="L233" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="M233" s="105" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A234" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="B234" s="170" t="s">
+        <v>310</v>
+      </c>
+      <c r="C234" s="171" t="s">
+        <v>41</v>
+      </c>
+      <c r="D234" s="173" t="s">
+        <v>311</v>
+      </c>
+      <c r="E234" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F234" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="G234" s="104">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H234" s="18">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I234" s="104">
+        <v>0.59375</v>
+      </c>
+      <c r="J234" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="K234" s="104">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="L234" s="18">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="M234" s="104">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A235" s="169"/>
+      <c r="B235" s="170" t="s">
+        <v>312</v>
+      </c>
+      <c r="C235" s="175" t="s">
+        <v>313</v>
+      </c>
+      <c r="D235" s="173" t="s">
+        <v>66</v>
+      </c>
+      <c r="E235" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F235" s="18">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="G235" s="104">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="H235" s="18">
+        <v>0.84375</v>
+      </c>
+      <c r="I235" s="104">
+        <v>0.90625</v>
+      </c>
+      <c r="J235" s="18">
+        <v>0.8125</v>
+      </c>
+      <c r="K235" s="104">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L235" s="18">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M235" s="104">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A236" s="169"/>
+      <c r="B236" s="170"/>
+      <c r="C236" s="175"/>
+      <c r="D236" s="173"/>
+      <c r="E236" s="176"/>
+      <c r="F236" s="28"/>
+      <c r="G236" s="106"/>
+      <c r="H236" s="28"/>
+      <c r="I236" s="106"/>
+      <c r="J236" s="28"/>
+      <c r="K236" s="106"/>
+      <c r="L236" s="28"/>
+      <c r="M236" s="106"/>
+    </row>
+    <row r="237" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A237" s="177"/>
+      <c r="B237" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="C237" s="142">
+        <v>3.6</v>
+      </c>
+      <c r="D237" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="E237" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F237" s="36">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G237" s="107" t="s">
+        <v>42</v>
+      </c>
+      <c r="H237" s="36">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="I237" s="107" t="s">
+        <v>171</v>
+      </c>
+      <c r="J237" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="K237" s="107" t="s">
+        <v>38</v>
+      </c>
+      <c r="L237" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="M237" s="107" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A238" s="39">
+        <v>46160</v>
+      </c>
+      <c r="B238" s="40" t="s">
+        <v>315</v>
+      </c>
+      <c r="C238" s="144" t="s">
+        <v>90</v>
+      </c>
+      <c r="D238" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="E238" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F238" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="G238" s="108">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H238" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="I238" s="108">
+        <v>0.4375</v>
+      </c>
+      <c r="J238" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="K238" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="L238" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="M238" s="109" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A239" s="183" t="s">
+        <v>83</v>
+      </c>
+      <c r="B239" s="40" t="s">
+        <v>316</v>
+      </c>
+      <c r="C239" s="144" t="s">
+        <v>41</v>
+      </c>
+      <c r="D239" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="E239" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F239" s="48">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G239" s="108">
+        <v>0.625</v>
+      </c>
+      <c r="H239" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="I239" s="108">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="J239" s="48">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K239" s="108">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="L239" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="M239" s="108">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A240" s="183"/>
+      <c r="B240" s="40" t="s">
+        <v>317</v>
+      </c>
+      <c r="C240" s="144" t="s">
+        <v>318</v>
+      </c>
+      <c r="D240" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="E240" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F240" s="48">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G240" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="H240" s="48">
+        <v>0.875</v>
+      </c>
+      <c r="I240" s="108">
+        <v>0.9375</v>
+      </c>
+      <c r="J240" s="48">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="K240" s="108">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="L240" s="48">
+        <v>0.8125</v>
+      </c>
+      <c r="M240" s="108">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A241" s="202"/>
+      <c r="B241" s="52"/>
+      <c r="C241" s="145"/>
+      <c r="D241" s="54"/>
+      <c r="E241" s="55"/>
+      <c r="F241" s="56"/>
+      <c r="G241" s="110"/>
+      <c r="H241" s="56"/>
+      <c r="I241" s="110"/>
+      <c r="J241" s="56"/>
+      <c r="K241" s="110"/>
+      <c r="L241" s="56"/>
+      <c r="M241" s="110"/>
+    </row>
+    <row r="242" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A242" s="169"/>
+      <c r="B242" s="170" t="s">
+        <v>177</v>
+      </c>
+      <c r="C242" s="171" t="s">
+        <v>41</v>
+      </c>
+      <c r="D242" s="173" t="s">
+        <v>6</v>
+      </c>
+      <c r="E242" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F242" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="G242" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="H242" s="58">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="I242" s="112">
+        <v>0.28125</v>
+      </c>
+      <c r="J242" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="K242" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="L242" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="M242" s="112" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A243" s="62">
+        <v>46161</v>
+      </c>
+      <c r="B243" s="170" t="s">
+        <v>319</v>
+      </c>
+      <c r="C243" s="171" t="s">
+        <v>133</v>
+      </c>
+      <c r="D243" s="173" t="s">
+        <v>141</v>
+      </c>
+      <c r="E243" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F243" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G243" s="113">
+        <v>0.5</v>
+      </c>
+      <c r="H243" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="I243" s="104">
+        <v>0.5</v>
+      </c>
+      <c r="J243" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="K243" s="113">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L243" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M243" s="105" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A244" s="174" t="s">
+        <v>92</v>
+      </c>
+      <c r="B244" s="170" t="s">
+        <v>320</v>
+      </c>
+      <c r="C244" s="171" t="s">
+        <v>41</v>
+      </c>
+      <c r="D244" s="173" t="s">
+        <v>173</v>
+      </c>
+      <c r="E244" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F244" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="G244" s="113">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H244" s="18">
+        <v>0.53125</v>
+      </c>
+      <c r="I244" s="104">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J244" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="K244" s="113">
+        <v>0.5</v>
+      </c>
+      <c r="L244" s="18">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="M244" s="104">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A245" s="169"/>
+      <c r="B245" s="170" t="s">
+        <v>321</v>
+      </c>
+      <c r="C245" s="171" t="s">
+        <v>318</v>
+      </c>
+      <c r="D245" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="E245" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F245" s="18">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="G245" s="115">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="H245" s="18">
+        <v>0.90625</v>
+      </c>
+      <c r="I245" s="104">
+        <v>0.96875</v>
+      </c>
+      <c r="J245" s="18">
+        <v>0.875</v>
+      </c>
+      <c r="K245" s="113">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="L245" s="18">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M245" s="104">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A246" s="169"/>
+      <c r="B246" s="170"/>
+      <c r="C246" s="171"/>
+      <c r="D246" s="173"/>
+      <c r="E246" s="13"/>
+      <c r="F246" s="28"/>
+      <c r="G246" s="116"/>
+      <c r="H246" s="28"/>
+      <c r="I246" s="106"/>
+      <c r="J246" s="28"/>
+      <c r="K246" s="116"/>
+      <c r="L246" s="28"/>
+      <c r="M246" s="106"/>
+    </row>
+    <row r="247" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A247" s="177"/>
+      <c r="B247" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="C247" s="147" t="s">
+        <v>41</v>
+      </c>
+      <c r="D247" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="E247" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F247" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="G247" s="107">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H247" s="117">
+        <v>0.1875</v>
+      </c>
+      <c r="I247" s="107" t="s">
+        <v>59</v>
+      </c>
+      <c r="J247" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="K247" s="107" t="s">
+        <v>217</v>
+      </c>
+      <c r="L247" s="117" t="s">
+        <v>44</v>
+      </c>
+      <c r="M247" s="107" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A248" s="181">
+        <v>46162</v>
+      </c>
+      <c r="B248" s="42" t="s">
+        <v>323</v>
+      </c>
+      <c r="C248" s="148" t="s">
+        <v>137</v>
+      </c>
+      <c r="D248" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="E248" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F248" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="G248" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H248" s="119">
+        <v>0.34375</v>
+      </c>
+      <c r="I248" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J248" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="K248" s="108">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="L248" s="119" t="s">
+        <v>69</v>
+      </c>
+      <c r="M248" s="109" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A249" s="181" t="s">
+        <v>14</v>
+      </c>
+      <c r="B249" s="42" t="s">
+        <v>324</v>
+      </c>
+      <c r="C249" s="148" t="s">
+        <v>41</v>
+      </c>
+      <c r="D249" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="E249" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F249" s="48">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G249" s="108">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="H249" s="118">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I249" s="108">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J249" s="48">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="K249" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L249" s="118">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="M249" s="108">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A250" s="181"/>
+      <c r="B250" s="42" t="s">
+        <v>325</v>
+      </c>
+      <c r="C250" s="148" t="s">
+        <v>326</v>
+      </c>
+      <c r="D250" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E250" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F250" s="48">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G250" s="109">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="H250" s="118">
+        <v>0.9375</v>
+      </c>
+      <c r="I250" s="109">
+        <v>0</v>
+      </c>
+      <c r="J250" s="48">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K250" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="L250" s="118">
+        <v>0.875</v>
+      </c>
+      <c r="M250" s="108">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A251" s="182"/>
+      <c r="B251" s="54"/>
+      <c r="C251" s="150"/>
+      <c r="D251" s="54"/>
+      <c r="E251" s="55"/>
+      <c r="F251" s="56"/>
+      <c r="G251" s="110"/>
+      <c r="H251" s="120"/>
+      <c r="I251" s="110"/>
+      <c r="J251" s="56"/>
+      <c r="K251" s="110"/>
+      <c r="L251" s="120"/>
+      <c r="M251" s="110"/>
+    </row>
+    <row r="252" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A252" s="169"/>
+      <c r="B252" s="170" t="s">
+        <v>327</v>
+      </c>
+      <c r="C252" s="171" t="s">
+        <v>16</v>
+      </c>
+      <c r="D252" s="173" t="s">
+        <v>43</v>
+      </c>
+      <c r="E252" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F252" s="58" t="s">
+        <v>8</v>
+      </c>
+      <c r="G252" s="112" t="s">
+        <v>13</v>
+      </c>
+      <c r="H252" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="I252" s="112" t="s">
+        <v>70</v>
+      </c>
+      <c r="J252" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="K252" s="112" t="s">
+        <v>57</v>
+      </c>
+      <c r="L252" s="58" t="s">
+        <v>8</v>
+      </c>
+      <c r="M252" s="112" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A253" s="169">
+        <v>46163</v>
+      </c>
+      <c r="B253" s="170" t="s">
+        <v>328</v>
+      </c>
+      <c r="C253" s="171" t="s">
+        <v>137</v>
+      </c>
+      <c r="D253" s="173" t="s">
+        <v>151</v>
+      </c>
+      <c r="E253" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F253" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G253" s="104">
+        <v>0.5625</v>
+      </c>
+      <c r="H253" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I253" s="104">
+        <v>0.5625</v>
+      </c>
+      <c r="J253" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="K253" s="104">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="L253" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="M253" s="104">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A254" s="169" t="s">
+        <v>32</v>
+      </c>
+      <c r="B254" s="170" t="s">
+        <v>329</v>
+      </c>
+      <c r="C254" s="171" t="s">
+        <v>2</v>
+      </c>
+      <c r="D254" s="173" t="s">
+        <v>226</v>
+      </c>
+      <c r="E254" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F254" s="18">
+        <v>0.5625</v>
+      </c>
+      <c r="G254" s="104">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H254" s="18">
+        <v>0.5625</v>
+      </c>
+      <c r="I254" s="104">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="J254" s="18">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="K254" s="104">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="L254" s="18">
+        <v>0.5625</v>
+      </c>
+      <c r="M254" s="104">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A255" s="169"/>
+      <c r="B255" s="170" t="s">
+        <v>330</v>
+      </c>
+      <c r="C255" s="171" t="s">
+        <v>331</v>
+      </c>
+      <c r="D255" s="173" t="s">
+        <v>21</v>
+      </c>
+      <c r="E255" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F255" s="18">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="G255" s="105">
+        <v>6.25E-2</v>
+      </c>
+      <c r="H255" s="18">
+        <v>0.96875</v>
+      </c>
+      <c r="I255" s="105">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="J255" s="18">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="K255" s="105" t="s">
+        <v>37</v>
+      </c>
+      <c r="L255" s="18">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="M255" s="104">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A256" s="169"/>
+      <c r="B256" s="170"/>
+      <c r="C256" s="171"/>
+      <c r="D256" s="173"/>
+      <c r="E256" s="13"/>
+      <c r="F256" s="85"/>
+      <c r="G256" s="87"/>
+      <c r="H256" s="85"/>
+      <c r="I256" s="87"/>
+      <c r="J256" s="85"/>
+      <c r="K256" s="87"/>
+      <c r="L256" s="85"/>
+      <c r="M256" s="87"/>
+    </row>
+    <row r="257" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A257" s="177"/>
+      <c r="B257" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C257" s="147" t="s">
+        <v>2</v>
+      </c>
+      <c r="D257" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="E257" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F257" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="G257" s="107" t="s">
+        <v>115</v>
+      </c>
+      <c r="H257" s="36">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="I257" s="107" t="s">
+        <v>115</v>
+      </c>
+      <c r="J257" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="K257" s="107" t="s">
+        <v>6</v>
+      </c>
+      <c r="L257" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="M257" s="107" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A258" s="183">
+        <v>46164</v>
+      </c>
+      <c r="B258" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="C258" s="148" t="s">
+        <v>137</v>
+      </c>
+      <c r="D258" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="E258" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F258" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="G258" s="108">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H258" s="44">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="I258" s="108">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J258" s="48">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="K258" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L258" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="M258" s="108">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A259" s="183" t="s">
+        <v>48</v>
+      </c>
+      <c r="B259" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="C259" s="148" t="s">
+        <v>191</v>
+      </c>
+      <c r="D259" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="E259" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F259" s="48">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G259" s="108">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="H259" s="48">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I259" s="108">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="J259" s="48">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="K259" s="108">
+        <v>0.5625</v>
+      </c>
+      <c r="L259" s="48">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="M259" s="108">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A260" s="183"/>
+      <c r="B260" s="42"/>
+      <c r="C260" s="148"/>
+      <c r="D260" s="42"/>
+      <c r="E260" s="43"/>
+      <c r="F260" s="48"/>
+      <c r="G260" s="108"/>
+      <c r="H260" s="48"/>
+      <c r="I260" s="108"/>
+      <c r="J260" s="48"/>
+      <c r="K260" s="108"/>
+      <c r="L260" s="48"/>
+      <c r="M260" s="108"/>
+    </row>
+    <row r="261" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A261" s="202"/>
+      <c r="B261" s="54"/>
+      <c r="C261" s="150"/>
+      <c r="D261" s="54"/>
+      <c r="E261" s="55"/>
+      <c r="F261" s="56"/>
+      <c r="G261" s="110"/>
+      <c r="H261" s="56"/>
+      <c r="I261" s="110"/>
+      <c r="J261" s="56"/>
+      <c r="K261" s="110"/>
+      <c r="L261" s="56"/>
+      <c r="M261" s="110"/>
+    </row>
+    <row r="262" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A262" s="169"/>
+      <c r="B262" s="173" t="s">
+        <v>334</v>
+      </c>
+      <c r="C262" s="185" t="s">
+        <v>118</v>
+      </c>
+      <c r="D262" s="173" t="s">
+        <v>38</v>
+      </c>
+      <c r="E262" s="184" t="s">
+        <v>12</v>
+      </c>
+      <c r="F262" s="132">
+        <v>0.96875</v>
+      </c>
+      <c r="G262" s="112">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="H262" s="132">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="I262" s="112">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="J262" s="132">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="K262" s="112" t="s">
+        <v>21</v>
+      </c>
+      <c r="L262" s="132">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="M262" s="121">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A263" s="179">
+        <v>46165</v>
+      </c>
+      <c r="B263" s="173" t="s">
+        <v>335</v>
+      </c>
+      <c r="C263" s="185" t="s">
+        <v>88</v>
+      </c>
+      <c r="D263" s="173" t="s">
+        <v>13</v>
+      </c>
+      <c r="E263" s="184" t="s">
+        <v>4</v>
+      </c>
+      <c r="F263" s="14">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G263" s="104">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="H263" s="14">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="I263" s="104">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="J263" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="K263" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="L263" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M263" s="104">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A264" s="179" t="s">
+        <v>63</v>
+      </c>
+      <c r="B264" s="173" t="s">
+        <v>336</v>
+      </c>
+      <c r="C264" s="185" t="s">
+        <v>99</v>
+      </c>
+      <c r="D264" s="173" t="s">
+        <v>49</v>
+      </c>
+      <c r="E264" s="184" t="s">
+        <v>12</v>
+      </c>
+      <c r="F264" s="18">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="G264" s="104">
+        <v>0.625</v>
+      </c>
+      <c r="H264" s="18">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="I264" s="104">
+        <v>0.625</v>
+      </c>
+      <c r="J264" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="K264" s="104" t="s">
+        <v>231</v>
+      </c>
+      <c r="L264" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="M264" s="104">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A265" s="179"/>
+      <c r="B265" s="173" t="s">
+        <v>337</v>
+      </c>
+      <c r="C265" s="185" t="s">
+        <v>143</v>
+      </c>
+      <c r="D265" s="173" t="s">
+        <v>123</v>
+      </c>
+      <c r="E265" s="92" t="s">
+        <v>4</v>
+      </c>
+      <c r="F265" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="G265" s="104">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H265" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="I265" s="104">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="J265" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="K265" s="104" t="s">
+        <v>231</v>
+      </c>
+      <c r="L265" s="18">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="M265" s="104">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A266" s="179"/>
+      <c r="B266" s="173"/>
+      <c r="C266" s="185"/>
+      <c r="D266" s="173"/>
+      <c r="E266" s="13"/>
+      <c r="F266" s="28"/>
+      <c r="G266" s="106"/>
+      <c r="H266" s="28"/>
+      <c r="I266" s="106"/>
+      <c r="J266" s="28"/>
+      <c r="K266" s="106"/>
+      <c r="L266" s="28"/>
+      <c r="M266" s="106"/>
+    </row>
+    <row r="267" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A267" s="195"/>
+      <c r="B267" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="C267" s="147" t="s">
+        <v>67</v>
+      </c>
+      <c r="D267" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="E267" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F267" s="126" t="s">
+        <v>78</v>
+      </c>
+      <c r="G267" s="168">
+        <v>0.15625</v>
+      </c>
+      <c r="H267" s="154" t="s">
+        <v>86</v>
+      </c>
+      <c r="I267" s="168">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="J267" s="126" t="s">
+        <v>21</v>
+      </c>
+      <c r="K267" s="168" t="s">
+        <v>39</v>
+      </c>
+      <c r="L267" s="166">
+        <v>0.9375</v>
+      </c>
+      <c r="M267" s="168" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A268" s="196">
+        <v>46166</v>
+      </c>
+      <c r="B268" s="42" t="s">
+        <v>339</v>
+      </c>
+      <c r="C268" s="148" t="s">
+        <v>191</v>
+      </c>
+      <c r="D268" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="E268" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F268" s="44">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="G268" s="108">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H268" s="119">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="I268" s="108">
+        <v>0.46875</v>
+      </c>
+      <c r="J268" s="44">
+        <v>0.25</v>
+      </c>
+      <c r="K268" s="109" t="s">
+        <v>69</v>
+      </c>
+      <c r="L268" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="M268" s="108">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A269" s="196" t="s">
+        <v>74</v>
+      </c>
+      <c r="B269" s="42" t="s">
+        <v>340</v>
+      </c>
+      <c r="C269" s="148" t="s">
+        <v>265</v>
+      </c>
+      <c r="D269" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="E269" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F269" s="48">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="G269" s="108">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H269" s="118">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I269" s="108">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="J269" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="K269" s="108" t="s">
+        <v>231</v>
+      </c>
+      <c r="L269" s="118">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="M269" s="108">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A270" s="196"/>
+      <c r="B270" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="C270" s="148">
+        <v>2.6</v>
+      </c>
+      <c r="D270" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="E270" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F270" s="48">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="G270" s="108">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="H270" s="118">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="I270" s="108">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="J270" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="K270" s="108" t="s">
+        <v>231</v>
+      </c>
+      <c r="L270" s="118">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M270" s="108">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A271" s="188"/>
+      <c r="B271" s="189"/>
+      <c r="C271" s="190"/>
+      <c r="D271" s="100"/>
+      <c r="E271" s="102"/>
+      <c r="F271" s="56"/>
+      <c r="G271" s="110"/>
+      <c r="H271" s="120"/>
+      <c r="I271" s="110"/>
+      <c r="J271" s="56"/>
+      <c r="K271" s="110"/>
+      <c r="L271" s="120"/>
+      <c r="M271" s="110"/>
+    </row>
+    <row r="272" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A272" s="191"/>
+      <c r="B272" s="172" t="s">
+        <v>110</v>
+      </c>
+      <c r="C272" s="192" t="s">
+        <v>10</v>
+      </c>
+      <c r="D272" s="172" t="s">
+        <v>44</v>
+      </c>
+      <c r="E272" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F272" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="G272" s="61">
+        <v>0.19791666666666666</v>
+      </c>
+      <c r="H272" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="I272" s="61">
+        <v>0.17708333333333334</v>
+      </c>
+      <c r="J272" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="K272" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="L272" s="137">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="M272" s="61" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A273" s="199">
+        <v>46167</v>
+      </c>
+      <c r="B273" s="173" t="s">
+        <v>342</v>
+      </c>
+      <c r="C273" s="185" t="s">
+        <v>191</v>
+      </c>
+      <c r="D273" s="173" t="s">
+        <v>269</v>
+      </c>
+      <c r="E273" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F273" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="G273" s="15">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="H273" s="84">
+        <v>0.375</v>
+      </c>
+      <c r="I273" s="15">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="J273" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K273" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="L273" s="84" t="s">
+        <v>46</v>
+      </c>
+      <c r="M273" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A274" s="199" t="s">
+        <v>83</v>
+      </c>
+      <c r="B274" s="173" t="s">
+        <v>204</v>
+      </c>
+      <c r="C274" s="185" t="s">
+        <v>72</v>
+      </c>
+      <c r="D274" s="173" t="s">
+        <v>34</v>
+      </c>
+      <c r="E274" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F274" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="G274" s="15">
+        <v>0.8125</v>
+      </c>
+      <c r="H274" s="16">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="I274" s="15">
+        <v>0.8125</v>
+      </c>
+      <c r="J274" s="18">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="K274" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="L274" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="M274" s="15">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A275" s="198"/>
+      <c r="B275" s="173" t="s">
+        <v>343</v>
+      </c>
+      <c r="C275" s="185" t="s">
+        <v>99</v>
+      </c>
+      <c r="D275" s="173" t="s">
+        <v>222</v>
+      </c>
+      <c r="E275" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F275" s="18">
+        <v>0.8125</v>
+      </c>
+      <c r="G275" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H275" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="I275" s="15">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="J275" s="18">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K275" s="15">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L275" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="M275" s="15">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A276" s="198"/>
+      <c r="B276" s="173"/>
+      <c r="C276" s="185"/>
+      <c r="D276" s="173"/>
+      <c r="E276" s="176"/>
+      <c r="F276" s="28"/>
+      <c r="G276" s="29"/>
+      <c r="H276" s="69"/>
+      <c r="I276" s="29"/>
+      <c r="J276" s="28"/>
+      <c r="K276" s="29"/>
+      <c r="L276" s="69"/>
+      <c r="M276" s="29"/>
+    </row>
+    <row r="277" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A277" s="186"/>
+      <c r="B277" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="C277" s="147" t="s">
+        <v>19</v>
+      </c>
+      <c r="D277" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="E277" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F277" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="G277" s="37">
+        <v>0.25</v>
+      </c>
+      <c r="H277" s="38">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="I277" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="J277" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="K277" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="L277" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="M277" s="37" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A278" s="187">
+        <v>46168</v>
+      </c>
+      <c r="B278" s="42" t="s">
+        <v>345</v>
+      </c>
+      <c r="C278" s="148" t="s">
+        <v>191</v>
+      </c>
+      <c r="D278" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E278" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F278" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="G278" s="45">
+        <v>0.53125</v>
+      </c>
+      <c r="H278" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="I278" s="45">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="J278" s="44">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="K278" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="L278" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="M278" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A279" s="187" t="s">
+        <v>92</v>
+      </c>
+      <c r="B279" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="C279" s="148" t="s">
+        <v>113</v>
+      </c>
+      <c r="D279" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E279" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F279" s="48">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G279" s="45">
+        <v>0.84375</v>
+      </c>
+      <c r="H279" s="46">
+        <v>0.6875</v>
+      </c>
+      <c r="I279" s="45">
+        <v>0.8125</v>
+      </c>
+      <c r="J279" s="48">
+        <v>0.6875</v>
+      </c>
+      <c r="K279" s="45">
+        <v>0.75</v>
+      </c>
+      <c r="L279" s="46">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="M279" s="45">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A280" s="187"/>
+      <c r="B280" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="C280" s="148" t="s">
+        <v>137</v>
+      </c>
+      <c r="D280" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="E280" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F280" s="48">
+        <v>0.875</v>
+      </c>
+      <c r="G280" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="H280" s="46">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="I280" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="J280" s="48">
+        <v>0.8125</v>
+      </c>
+      <c r="K280" s="45">
+        <v>0.875</v>
+      </c>
+      <c r="L280" s="46">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="M280" s="50" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A281" s="197"/>
+      <c r="B281" s="54"/>
+      <c r="C281" s="150"/>
+      <c r="D281" s="54"/>
+      <c r="E281" s="55"/>
+      <c r="F281" s="56"/>
+      <c r="G281" s="57"/>
+      <c r="H281" s="54"/>
+      <c r="I281" s="57"/>
+      <c r="J281" s="56"/>
+      <c r="K281" s="57"/>
+      <c r="L281" s="54"/>
+      <c r="M281" s="57"/>
+    </row>
+    <row r="282" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A282" s="198"/>
+      <c r="B282" s="173" t="s">
+        <v>347</v>
+      </c>
+      <c r="C282" s="185" t="s">
+        <v>250</v>
+      </c>
+      <c r="D282" s="173" t="s">
+        <v>6</v>
+      </c>
+      <c r="E282" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F282" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="G282" s="59" t="s">
+        <v>59</v>
+      </c>
+      <c r="H282" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="I282" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="J282" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="K282" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="L282" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="M282" s="61" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A283" s="199">
+        <v>46169</v>
+      </c>
+      <c r="B283" s="173" t="s">
+        <v>206</v>
+      </c>
+      <c r="C283" s="185" t="s">
+        <v>191</v>
+      </c>
+      <c r="D283" s="173" t="s">
+        <v>114</v>
+      </c>
+      <c r="E283" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F283" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G283" s="63">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H283" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="I283" s="15">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J283" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="K283" s="66" t="s">
+        <v>60</v>
+      </c>
+      <c r="L283" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="M283" s="15">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A284" s="199" t="s">
+        <v>14</v>
+      </c>
+      <c r="B284" s="173" t="s">
+        <v>50</v>
+      </c>
+      <c r="C284" s="185" t="s">
+        <v>36</v>
+      </c>
+      <c r="D284" s="173" t="s">
+        <v>102</v>
+      </c>
+      <c r="E284" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F284" s="18">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="G284" s="63">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="H284" s="16">
+        <v>0.71875</v>
+      </c>
+      <c r="I284" s="15">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="J284" s="18">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K284" s="63">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="L284" s="16">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="M284" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A285" s="198"/>
+      <c r="B285" s="173"/>
+      <c r="C285" s="185"/>
+      <c r="D285" s="173"/>
+      <c r="E285" s="13"/>
+      <c r="F285" s="18"/>
+      <c r="G285" s="63"/>
+      <c r="H285" s="16"/>
+      <c r="I285" s="15"/>
+      <c r="J285" s="18"/>
+      <c r="K285" s="63"/>
+      <c r="L285" s="16"/>
+      <c r="M285" s="15"/>
+    </row>
+    <row r="286" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A286" s="198"/>
+      <c r="B286" s="173"/>
+      <c r="C286" s="185"/>
+      <c r="D286" s="173"/>
+      <c r="E286" s="176"/>
+      <c r="F286" s="28"/>
+      <c r="G286" s="30"/>
+      <c r="H286" s="69"/>
+      <c r="I286" s="29"/>
+      <c r="J286" s="28"/>
+      <c r="K286" s="30"/>
+      <c r="L286" s="69"/>
+      <c r="M286" s="29"/>
+    </row>
+    <row r="287" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A287" s="186"/>
+      <c r="B287" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="C287" s="147" t="s">
+        <v>159</v>
+      </c>
+      <c r="D287" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="E287" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F287" s="156">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G287" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="H287" s="215">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="I287" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="J287" s="156">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="K287" s="96">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="L287" s="215">
+        <v>0.9375</v>
+      </c>
+      <c r="M287" s="37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A288" s="187">
+        <v>46170</v>
+      </c>
+      <c r="B288" s="42" t="s">
+        <v>349</v>
+      </c>
+      <c r="C288" s="148" t="s">
+        <v>72</v>
+      </c>
+      <c r="D288" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E288" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F288" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="G288" s="50">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="H288" s="99">
+        <v>0.125</v>
+      </c>
+      <c r="I288" s="50">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="J288" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="K288" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="L288" s="99" t="s">
+        <v>54</v>
+      </c>
+      <c r="M288" s="50" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A289" s="187" t="s">
+        <v>32</v>
+      </c>
+      <c r="B289" s="42" t="s">
+        <v>350</v>
+      </c>
+      <c r="C289" s="148" t="s">
+        <v>191</v>
+      </c>
+      <c r="D289" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="E289" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F289" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="G289" s="45">
+        <v>0.5625</v>
+      </c>
+      <c r="H289" s="75">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I289" s="45">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J289" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="K289" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="L289" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="M289" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A290" s="187"/>
+      <c r="B290" s="42" t="s">
+        <v>351</v>
+      </c>
+      <c r="C290" s="148" t="s">
+        <v>196</v>
+      </c>
+      <c r="D290" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="E290" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F290" s="48">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="G290" s="45">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="H290" s="75">
+        <v>0.75</v>
+      </c>
+      <c r="I290" s="45">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J290" s="48">
+        <v>0.75</v>
+      </c>
+      <c r="K290" s="45">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L290" s="75">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M290" s="45">
+        <v>0.72916666666666663</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A291" s="197"/>
+      <c r="B291" s="54"/>
+      <c r="C291" s="150"/>
+      <c r="D291" s="54"/>
+      <c r="E291" s="55"/>
+      <c r="F291" s="56"/>
+      <c r="G291" s="57"/>
+      <c r="H291" s="80"/>
+      <c r="I291" s="57"/>
+      <c r="J291" s="56"/>
+      <c r="K291" s="57"/>
+      <c r="L291" s="80"/>
+      <c r="M291" s="57"/>
+    </row>
+    <row r="292" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A292" s="198"/>
+      <c r="B292" s="173" t="s">
+        <v>352</v>
+      </c>
+      <c r="C292" s="185" t="s">
+        <v>184</v>
+      </c>
+      <c r="D292" s="173" t="s">
+        <v>54</v>
+      </c>
+      <c r="E292" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F292" s="132">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="G292" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="H292" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="I292" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="J292" s="132">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K292" s="91">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="L292" s="137">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="M292" s="61" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A293" s="198">
+        <v>46171</v>
+      </c>
+      <c r="B293" s="173" t="s">
+        <v>353</v>
+      </c>
+      <c r="C293" s="185" t="s">
+        <v>81</v>
+      </c>
+      <c r="D293" s="173" t="s">
+        <v>59</v>
+      </c>
+      <c r="E293" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F293" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G293" s="22">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="H293" s="84">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="I293" s="22">
+        <v>0.375</v>
+      </c>
+      <c r="J293" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K293" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="L293" s="84" t="s">
+        <v>217</v>
+      </c>
+      <c r="M293" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A294" s="198" t="s">
+        <v>48</v>
+      </c>
+      <c r="B294" s="173" t="s">
+        <v>354</v>
+      </c>
+      <c r="C294" s="185" t="s">
+        <v>191</v>
+      </c>
+      <c r="D294" s="173" t="s">
+        <v>62</v>
+      </c>
+      <c r="E294" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F294" s="14">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="G294" s="15">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="H294" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I294" s="15">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J294" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="K294" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="L294" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M294" s="15">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A295" s="198"/>
+      <c r="B295" s="173" t="s">
+        <v>355</v>
+      </c>
+      <c r="C295" s="185" t="s">
+        <v>275</v>
+      </c>
+      <c r="D295" s="173" t="s">
+        <v>356</v>
+      </c>
+      <c r="E295" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F295" s="18">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="G295" s="15">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="H295" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I295" s="15">
+        <v>0.875</v>
+      </c>
+      <c r="J295" s="18">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="K295" s="15">
+        <v>0.8125</v>
+      </c>
+      <c r="L295" s="16">
+        <v>0.6875</v>
+      </c>
+      <c r="M295" s="15">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A296" s="198"/>
+      <c r="B296" s="173"/>
+      <c r="C296" s="185"/>
+      <c r="D296" s="173"/>
+      <c r="E296" s="176"/>
+      <c r="F296" s="85"/>
+      <c r="G296" s="87"/>
+      <c r="H296" s="85"/>
+      <c r="I296" s="87"/>
+      <c r="J296" s="85"/>
+      <c r="K296" s="87"/>
+      <c r="L296" s="85"/>
+      <c r="M296" s="87"/>
+    </row>
+    <row r="297" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A297" s="186"/>
+      <c r="B297" s="34" t="s">
+        <v>357</v>
+      </c>
+      <c r="C297" s="147" t="s">
+        <v>97</v>
+      </c>
+      <c r="D297" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="E297" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F297" s="36">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="G297" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="H297" s="38">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="I297" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="J297" s="156">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="K297" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="L297" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="M297" s="37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A298" s="196">
+        <v>46172</v>
+      </c>
+      <c r="B298" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="C298" s="148" t="s">
+        <v>265</v>
+      </c>
+      <c r="D298" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="E298" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F298" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="G298" s="45">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H298" s="88">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="I298" s="45">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="J298" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="K298" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="L298" s="88" t="s">
+        <v>3</v>
+      </c>
+      <c r="M298" s="50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A299" s="196" t="s">
+        <v>63</v>
+      </c>
+      <c r="B299" s="42" t="s">
+        <v>359</v>
+      </c>
+      <c r="C299" s="148" t="s">
+        <v>88</v>
+      </c>
+      <c r="D299" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="E299" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F299" s="48">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G299" s="45">
+        <v>0.59375</v>
+      </c>
+      <c r="H299" s="46">
+        <v>0.4375</v>
+      </c>
+      <c r="I299" s="45">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J299" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="K299" s="45">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L299" s="46">
+        <v>0.4375</v>
+      </c>
+      <c r="M299" s="45">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A300" s="196"/>
+      <c r="B300" s="42" t="s">
+        <v>360</v>
+      </c>
+      <c r="C300" s="148" t="s">
+        <v>118</v>
+      </c>
+      <c r="D300" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="E300" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F300" s="48">
+        <v>0.78125</v>
+      </c>
+      <c r="G300" s="45">
+        <v>0.90625</v>
+      </c>
+      <c r="H300" s="46">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="I300" s="45">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="J300" s="48">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K300" s="45">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L300" s="46">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M300" s="45">
+        <v>0.77083333333333337</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A301" s="216"/>
+      <c r="B301" s="54"/>
+      <c r="C301" s="150"/>
+      <c r="D301" s="54"/>
+      <c r="E301" s="55"/>
+      <c r="F301" s="56"/>
+      <c r="G301" s="57"/>
+      <c r="H301" s="54"/>
+      <c r="I301" s="57"/>
+      <c r="J301" s="56"/>
+      <c r="K301" s="57"/>
+      <c r="L301" s="54"/>
+      <c r="M301" s="57"/>
+    </row>
+    <row r="302" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A302" s="194"/>
+      <c r="B302" s="173" t="s">
+        <v>361</v>
+      </c>
+      <c r="C302" s="185" t="s">
+        <v>191</v>
+      </c>
+      <c r="D302" s="173" t="s">
+        <v>44</v>
+      </c>
+      <c r="E302" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F302" s="58">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G302" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="H302" s="60">
+        <v>6.25E-2</v>
+      </c>
+      <c r="I302" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="J302" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="K302" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="L302" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="M302" s="61" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A303" s="194">
+        <v>46173</v>
+      </c>
+      <c r="B303" s="173" t="s">
+        <v>362</v>
+      </c>
+      <c r="C303" s="185" t="s">
+        <v>90</v>
+      </c>
+      <c r="D303" s="173" t="s">
+        <v>70</v>
+      </c>
+      <c r="E303" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F303" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G303" s="15">
+        <v>0.4375</v>
+      </c>
+      <c r="H303" s="84">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="I303" s="15">
+        <v>0.4375</v>
+      </c>
+      <c r="J303" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="K303" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="L303" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="M303" s="22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A304" s="194" t="s">
+        <v>74</v>
+      </c>
+      <c r="B304" s="173" t="s">
+        <v>363</v>
+      </c>
+      <c r="C304" s="185" t="s">
+        <v>88</v>
+      </c>
+      <c r="D304" s="173" t="s">
+        <v>91</v>
+      </c>
+      <c r="E304" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F304" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="G304" s="15">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H304" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I304" s="15">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J304" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="K304" s="15">
+        <v>0.4375</v>
+      </c>
+      <c r="L304" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="M304" s="15">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A305" s="198"/>
+      <c r="B305" s="173" t="s">
+        <v>364</v>
+      </c>
+      <c r="C305" s="185" t="s">
+        <v>365</v>
+      </c>
+      <c r="D305" s="173" t="s">
+        <v>66</v>
+      </c>
+      <c r="E305" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F305" s="130">
+        <v>0.8125</v>
+      </c>
+      <c r="G305" s="217">
+        <v>13.4375</v>
+      </c>
+      <c r="H305" s="218">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I305" s="217">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="J305" s="130">
+        <v>0.8125</v>
+      </c>
+      <c r="K305" s="217">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L305" s="218">
+        <v>0.75</v>
+      </c>
+      <c r="M305" s="217">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A306" s="198"/>
+      <c r="B306" s="219"/>
+      <c r="C306" s="176"/>
+      <c r="D306" s="219"/>
+      <c r="E306" s="176"/>
+      <c r="F306" s="220"/>
+      <c r="G306" s="221"/>
+      <c r="H306" s="173"/>
+      <c r="I306" s="221"/>
+      <c r="J306" s="220"/>
+      <c r="K306" s="221"/>
+      <c r="L306" s="173"/>
+      <c r="M306" s="221"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_window.xlsx
+++ b/data_window.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DuAnTrucDH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0F6814-B9CD-441C-B8A5-9C4A2361DF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75522A25-378C-4E28-8EF2-1801C508DE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{15CB32D3-DB1A-4542-B1F9-BD2C57A25BCC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{15CB32D3-DB1A-4542-B1F9-BD2C57A25BCC}"/>
   </bookViews>
   <sheets>
     <sheet name="WindowCL" sheetId="2" r:id="rId1"/>
@@ -20529,7 +20529,7 @@
         <v>0.8125</v>
       </c>
       <c r="G305" s="217">
-        <v>13.4375</v>
+        <v>0.9375</v>
       </c>
       <c r="H305" s="218">
         <v>0.83333333333333337</v>

--- a/data_window.xlsx
+++ b/data_window.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DuAnTrucDH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEDD062-9A12-4B56-956E-052978A50FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A864A61-A9A9-4712-94EB-125F65BBA78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{15CB32D3-DB1A-4542-B1F9-BD2C57A25BCC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{15CB32D3-DB1A-4542-B1F9-BD2C57A25BCC}"/>
   </bookViews>
   <sheets>
     <sheet name="WindowCL" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2948" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4395" uniqueCount="460">
   <si>
     <t>Date</t>
   </si>
@@ -1135,6 +1135,288 @@
   </si>
   <si>
     <t>Duty pilot</t>
+  </si>
+  <si>
+    <t>03:17</t>
+  </si>
+  <si>
+    <t>08:17</t>
+  </si>
+  <si>
+    <t>12:56</t>
+  </si>
+  <si>
+    <t>20:29</t>
+  </si>
+  <si>
+    <t>03:56</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>21:04</t>
+  </si>
+  <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>13:54</t>
+  </si>
+  <si>
+    <t>21:39</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>22:53</t>
+  </si>
+  <si>
+    <t>23:32</t>
+  </si>
+  <si>
+    <t>07:28</t>
+  </si>
+  <si>
+    <t>12:27</t>
+  </si>
+  <si>
+    <t>16:24</t>
+  </si>
+  <si>
+    <t>00:14</t>
+  </si>
+  <si>
+    <t>08:04</t>
+  </si>
+  <si>
+    <t>13:32</t>
+  </si>
+  <si>
+    <t>17:43</t>
+  </si>
+  <si>
+    <t>01:02</t>
+  </si>
+  <si>
+    <t>08:37</t>
+  </si>
+  <si>
+    <t>14:41</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>01:56</t>
+  </si>
+  <si>
+    <t>16:39</t>
+  </si>
+  <si>
+    <t>04:14</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>17:29</t>
+  </si>
+  <si>
+    <t>00:28</t>
+  </si>
+  <si>
+    <t>05:28</t>
+  </si>
+  <si>
+    <t>18:17</t>
+  </si>
+  <si>
+    <t>01:33</t>
+  </si>
+  <si>
+    <t>06:34</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>02:32</t>
+  </si>
+  <si>
+    <t>12:13</t>
+  </si>
+  <si>
+    <t>19:53</t>
+  </si>
+  <si>
+    <t>-0.4</t>
+  </si>
+  <si>
+    <t>03:27</t>
+  </si>
+  <si>
+    <t>08:21</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>-0.5</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>09:09</t>
+  </si>
+  <si>
+    <t>13:43</t>
+  </si>
+  <si>
+    <t>21:28</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>09:57</t>
+  </si>
+  <si>
+    <t>14:31</t>
+  </si>
+  <si>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>10:47</t>
+  </si>
+  <si>
+    <t>15:23</t>
+  </si>
+  <si>
+    <t>23:01</t>
+  </si>
+  <si>
+    <t>06:41</t>
+  </si>
+  <si>
+    <t>11:42</t>
+  </si>
+  <si>
+    <t>16:23</t>
+  </si>
+  <si>
+    <t>23:46</t>
+  </si>
+  <si>
+    <t>07:22</t>
+  </si>
+  <si>
+    <t>12:44</t>
+  </si>
+  <si>
+    <t>17:41</t>
+  </si>
+  <si>
+    <t>00:31</t>
+  </si>
+  <si>
+    <t>13:53</t>
+  </si>
+  <si>
+    <t>01:17</t>
+  </si>
+  <si>
+    <t>15:06</t>
+  </si>
+  <si>
+    <t>21:14</t>
+  </si>
+  <si>
+    <t>02:08</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>16:12</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>17:04</t>
+  </si>
+  <si>
+    <t>00:11</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>17:48</t>
+  </si>
+  <si>
+    <t>01:16</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>10:42</t>
+  </si>
+  <si>
+    <t>18:27</t>
+  </si>
+  <si>
+    <t>02:03</t>
+  </si>
+  <si>
+    <t>06:43</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>02:43</t>
+  </si>
+  <si>
+    <t>11:56</t>
+  </si>
+  <si>
+    <t>19:41</t>
+  </si>
+  <si>
+    <t>03:18</t>
+  </si>
+  <si>
+    <t>12:33</t>
+  </si>
+  <si>
+    <t>20:17</t>
+  </si>
+  <si>
+    <t>17;45</t>
+  </si>
+  <si>
+    <t>04;30</t>
   </si>
 </sst>
 </file>
@@ -1225,7 +1507,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1562,12 +1844,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2262,6 +2557,33 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2597,7 +2919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9098970E-F68E-4060-9535-B4D7609639E2}">
-  <dimension ref="A1:I306"/>
+  <dimension ref="A1:I456"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.75" customWidth="1"/>
@@ -10017,6 +10339,3632 @@
       <c r="H306" s="69"/>
       <c r="I306" s="29"/>
     </row>
+    <row r="307" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A307" s="1"/>
+      <c r="B307" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C307" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E307" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F307" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G307" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H307" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I307" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A308" s="62">
+        <v>46174</v>
+      </c>
+      <c r="B308" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C308" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D308" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E308" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F308" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G308" s="15">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H308" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="I308" s="15">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A309" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="B309" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="C309" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D309" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E309" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F309" s="18">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G309" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H309" s="19">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I309" s="15">
+        <v>0.69791666666666663</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A310" s="65"/>
+      <c r="B310" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C310" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D310" s="12">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="E310" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F310" s="236">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G310" s="237" t="s">
+        <v>22</v>
+      </c>
+      <c r="H310" s="238">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="I310" s="237" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A311" s="67"/>
+      <c r="B311" s="24"/>
+      <c r="C311" s="25"/>
+      <c r="D311" s="26"/>
+      <c r="E311" s="27"/>
+      <c r="F311" s="28"/>
+      <c r="G311" s="29"/>
+      <c r="H311" s="30"/>
+      <c r="I311" s="29"/>
+    </row>
+    <row r="312" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A312" s="31"/>
+      <c r="B312" s="32" t="s">
+        <v>370</v>
+      </c>
+      <c r="C312" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D312" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="E312" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F312" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="G312" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H312" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="I312" s="37" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A313" s="39">
+        <v>46175</v>
+      </c>
+      <c r="B313" s="40" t="s">
+        <v>371</v>
+      </c>
+      <c r="C313" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="D313" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="E313" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F313" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="G313" s="45">
+        <v>0.5625</v>
+      </c>
+      <c r="H313" s="88" t="s">
+        <v>69</v>
+      </c>
+      <c r="I313" s="45">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A314" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B314" s="40" t="s">
+        <v>372</v>
+      </c>
+      <c r="C314" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D314" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="E314" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F314" s="48">
+        <v>0.5625</v>
+      </c>
+      <c r="G314" s="45">
+        <v>0.75</v>
+      </c>
+      <c r="H314" s="46">
+        <v>0.5625</v>
+      </c>
+      <c r="I314" s="45">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A315" s="49"/>
+      <c r="B315" s="40" t="s">
+        <v>373</v>
+      </c>
+      <c r="C315" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D315" s="42">
+        <v>3.125E-2</v>
+      </c>
+      <c r="E315" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F315" s="48">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="G315" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="H315" s="46">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="I315" s="50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A316" s="51"/>
+      <c r="B316" s="52"/>
+      <c r="C316" s="53"/>
+      <c r="D316" s="54"/>
+      <c r="E316" s="55"/>
+      <c r="F316" s="56"/>
+      <c r="G316" s="57"/>
+      <c r="H316" s="54"/>
+      <c r="I316" s="57"/>
+    </row>
+    <row r="317" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A317" s="1"/>
+      <c r="B317" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E317" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F317" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="G317" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="H317" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="I317" s="61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A318" s="62">
+        <v>46176</v>
+      </c>
+      <c r="B318" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C318" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D318" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E318" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F318" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G318" s="63">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H318" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="I318" s="15">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A319" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B319" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="C319" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D319" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E319" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F319" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G319" s="63">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H319" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I319" s="15">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A320" s="65"/>
+      <c r="B320" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="C320" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="D320" s="12">
+        <v>6.25E-2</v>
+      </c>
+      <c r="E320" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F320" s="18">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="G320" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="H320" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="I320" s="22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A321" s="67"/>
+      <c r="B321" s="24"/>
+      <c r="C321" s="68"/>
+      <c r="D321" s="26"/>
+      <c r="E321" s="27"/>
+      <c r="F321" s="28"/>
+      <c r="G321" s="30"/>
+      <c r="H321" s="69"/>
+      <c r="I321" s="29"/>
+    </row>
+    <row r="322" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A322" s="31"/>
+      <c r="B322" s="34" t="s">
+        <v>377</v>
+      </c>
+      <c r="C322" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="D322" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E322" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F322" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G322" s="96">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H322" s="72" t="s">
+        <v>42</v>
+      </c>
+      <c r="I322" s="96">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A323" s="39">
+        <v>46177</v>
+      </c>
+      <c r="B323" s="42" t="s">
+        <v>378</v>
+      </c>
+      <c r="C323" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D323" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="E323" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F323" s="48">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G323" s="45">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="H323" s="75">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I323" s="45">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A324" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B324" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="C324" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="D324" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="E324" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F324" s="48">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G324" s="45">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H324" s="75">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I324" s="45">
+        <v>0.77083333333333337</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A325" s="49"/>
+      <c r="B325" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="C325" s="74" t="s">
+        <v>364</v>
+      </c>
+      <c r="D325" s="42">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="E325" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F325" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="G325" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="H325" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="I325" s="50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A326" s="51"/>
+      <c r="B326" s="54"/>
+      <c r="C326" s="79"/>
+      <c r="D326" s="54"/>
+      <c r="E326" s="55"/>
+      <c r="F326" s="56"/>
+      <c r="G326" s="57"/>
+      <c r="H326" s="80"/>
+      <c r="I326" s="57"/>
+    </row>
+    <row r="327" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A327" s="1"/>
+      <c r="B327" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C327" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D327" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E327" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F327" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="G327" s="91">
+        <v>0.4375</v>
+      </c>
+      <c r="H327" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="I327" s="91">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A328" s="62">
+        <v>46178</v>
+      </c>
+      <c r="B328" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C328" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="D328" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E328" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F328" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="G328" s="15">
+        <v>0.625</v>
+      </c>
+      <c r="H328" s="16">
+        <v>0.4375</v>
+      </c>
+      <c r="I328" s="15">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A329" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B329" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C329" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D329" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E329" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F329" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="G329" s="15">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="H329" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="I329" s="15">
+        <v>0.80208333333333337</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A330" s="65"/>
+      <c r="B330" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="C330" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D330" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E330" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F330" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G330" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H330" s="84" t="s">
+        <v>38</v>
+      </c>
+      <c r="I330" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A331" s="67"/>
+      <c r="B331" s="24"/>
+      <c r="C331" s="68"/>
+      <c r="D331" s="26"/>
+      <c r="E331" s="27"/>
+      <c r="F331" s="85"/>
+      <c r="G331" s="87"/>
+      <c r="H331" s="85"/>
+      <c r="I331" s="87"/>
+    </row>
+    <row r="332" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A332" s="31"/>
+      <c r="B332" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="C332" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="D332" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E332" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F332" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="G332" s="96">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H332" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="I332" s="96">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A333" s="73">
+        <v>46179</v>
+      </c>
+      <c r="B333" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="C333" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D333" s="42">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="E333" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F333" s="48">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="G333" s="45">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H333" s="46">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I333" s="45">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A334" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B334" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="C334" s="74" t="s">
+        <v>183</v>
+      </c>
+      <c r="D334" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="E334" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F334" s="48">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="G334" s="45">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="H334" s="46">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="I334" s="45">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A335" s="77"/>
+      <c r="B335" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="C335" s="74" t="s">
+        <v>274</v>
+      </c>
+      <c r="D335" s="42">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="E335" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F335" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="G335" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="H335" s="88" t="s">
+        <v>22</v>
+      </c>
+      <c r="I335" s="50" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A336" s="78"/>
+      <c r="B336" s="54"/>
+      <c r="C336" s="79"/>
+      <c r="D336" s="54"/>
+      <c r="E336" s="55"/>
+      <c r="F336" s="56"/>
+      <c r="G336" s="57"/>
+      <c r="H336" s="54"/>
+      <c r="I336" s="57"/>
+    </row>
+    <row r="337" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A337" s="81"/>
+      <c r="B337" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C337" s="90" t="s">
+        <v>96</v>
+      </c>
+      <c r="D337" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E337" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F337" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="G337" s="91">
+        <v>0.5</v>
+      </c>
+      <c r="H337" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="I337" s="91">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A338" s="82">
+        <v>46180</v>
+      </c>
+      <c r="B338" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="C338" s="93" t="s">
+        <v>89</v>
+      </c>
+      <c r="D338" s="12">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E338" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F338" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="G338" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H338" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="I338" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A339" s="83" t="s">
+        <v>73</v>
+      </c>
+      <c r="B339" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="C339" s="93" t="s">
+        <v>158</v>
+      </c>
+      <c r="D339" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E339" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F339" s="18">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G339" s="15">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="H339" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I339" s="15">
+        <v>0.86458333333333337</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A340" s="65"/>
+      <c r="B340" s="12"/>
+      <c r="C340" s="93"/>
+      <c r="D340" s="12"/>
+      <c r="E340" s="13"/>
+      <c r="F340" s="18"/>
+      <c r="G340" s="15"/>
+      <c r="H340" s="16"/>
+      <c r="I340" s="15"/>
+    </row>
+    <row r="341" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A341" s="67"/>
+      <c r="B341" s="26"/>
+      <c r="C341" s="94"/>
+      <c r="D341" s="26"/>
+      <c r="E341" s="27"/>
+      <c r="F341" s="28"/>
+      <c r="G341" s="29"/>
+      <c r="H341" s="69"/>
+      <c r="I341" s="29"/>
+    </row>
+    <row r="342" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A342" s="31"/>
+      <c r="B342" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="C342" s="71" t="s">
+        <v>66</v>
+      </c>
+      <c r="D342" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E342" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F342" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="G342" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="H342" s="72" t="s">
+        <v>7</v>
+      </c>
+      <c r="I342" s="37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A343" s="39">
+        <v>46181</v>
+      </c>
+      <c r="B343" s="42" t="s">
+        <v>387</v>
+      </c>
+      <c r="C343" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="D343" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E343" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F343" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="G343" s="45">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H343" s="99" t="s">
+        <v>70</v>
+      </c>
+      <c r="I343" s="45">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A344" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B344" s="42" t="s">
+        <v>388</v>
+      </c>
+      <c r="C344" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="D344" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E344" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F344" s="48">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G344" s="45">
+        <v>0.75</v>
+      </c>
+      <c r="H344" s="75">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I344" s="45">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A345" s="49"/>
+      <c r="B345" s="42" t="s">
+        <v>389</v>
+      </c>
+      <c r="C345" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="D345" s="42">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="E345" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F345" s="48">
+        <v>0.75</v>
+      </c>
+      <c r="G345" s="45">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="H345" s="75">
+        <v>0.75</v>
+      </c>
+      <c r="I345" s="45">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A346" s="51"/>
+      <c r="B346" s="100"/>
+      <c r="C346" s="101"/>
+      <c r="D346" s="100"/>
+      <c r="E346" s="102"/>
+      <c r="F346" s="56"/>
+      <c r="G346" s="57"/>
+      <c r="H346" s="80"/>
+      <c r="I346" s="57"/>
+    </row>
+    <row r="347" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A347" s="1"/>
+      <c r="B347" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C347" s="90" t="s">
+        <v>10</v>
+      </c>
+      <c r="D347" s="239" t="s">
+        <v>56</v>
+      </c>
+      <c r="E347" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F347" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G347" s="103" t="s">
+        <v>42</v>
+      </c>
+      <c r="H347" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I347" s="103" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A348" s="62">
+        <v>46182</v>
+      </c>
+      <c r="B348" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="C348" s="93" t="s">
+        <v>96</v>
+      </c>
+      <c r="D348" s="12">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="E348" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F348" s="14">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="G348" s="104">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="H348" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="I348" s="104">
+        <v>0.55208333333333337</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A349" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B349" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="C349" s="93" t="s">
+        <v>71</v>
+      </c>
+      <c r="D349" s="12">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="E349" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F349" s="18">
+        <v>0.65625</v>
+      </c>
+      <c r="G349" s="104">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H349" s="18">
+        <v>0.6875</v>
+      </c>
+      <c r="I349" s="104">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A350" s="65"/>
+      <c r="B350" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="C350" s="93" t="s">
+        <v>132</v>
+      </c>
+      <c r="D350" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="E350" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F350" s="18">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G350" s="105" t="s">
+        <v>38</v>
+      </c>
+      <c r="H350" s="18">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I350" s="105" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A351" s="67"/>
+      <c r="B351" s="26"/>
+      <c r="C351" s="94"/>
+      <c r="D351" s="26"/>
+      <c r="E351" s="27"/>
+      <c r="F351" s="28"/>
+      <c r="G351" s="106"/>
+      <c r="H351" s="28"/>
+      <c r="I351" s="106"/>
+    </row>
+    <row r="352" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A352" s="31"/>
+      <c r="B352" s="34" t="s">
+        <v>394</v>
+      </c>
+      <c r="C352" s="71" t="s">
+        <v>105</v>
+      </c>
+      <c r="D352" s="34">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="E352" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F352" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="G352" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="H352" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="I352" s="107" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A353" s="39">
+        <v>46183</v>
+      </c>
+      <c r="B353" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="C353" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="D353" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E353" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F353" s="48">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="G353" s="108">
+        <v>0.59375</v>
+      </c>
+      <c r="H353" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="I353" s="108">
+        <v>0.57291666666666663</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A354" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B354" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="C354" s="74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D354" s="42">
+        <v>0.8125</v>
+      </c>
+      <c r="E354" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F354" s="48">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G354" s="108">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="H354" s="48">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="I354" s="108">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A355" s="49"/>
+      <c r="B355" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="C355" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D355" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="E355" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F355" s="48">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G355" s="109" t="s">
+        <v>39</v>
+      </c>
+      <c r="H355" s="48">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I355" s="109" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A356" s="51"/>
+      <c r="B356" s="54"/>
+      <c r="C356" s="79"/>
+      <c r="D356" s="54"/>
+      <c r="E356" s="55"/>
+      <c r="F356" s="56"/>
+      <c r="G356" s="110"/>
+      <c r="H356" s="56"/>
+      <c r="I356" s="110"/>
+    </row>
+    <row r="357" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A357" s="1"/>
+      <c r="B357" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C357" s="90" t="s">
+        <v>60</v>
+      </c>
+      <c r="D357" s="4">
+        <v>0.28125</v>
+      </c>
+      <c r="E357" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F357" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="G357" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="H357" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="I357" s="112" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A358" s="62">
+        <v>46184</v>
+      </c>
+      <c r="B358" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C358" s="93" t="s">
+        <v>190</v>
+      </c>
+      <c r="D358" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E358" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F358" s="18">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="G358" s="113">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H358" s="18">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="I358" s="104">
+        <v>0.59375</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A359" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="B359" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="C359" s="93" t="s">
+        <v>10</v>
+      </c>
+      <c r="D359" s="12">
+        <v>0.84375</v>
+      </c>
+      <c r="E359" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F359" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="G359" s="113">
+        <v>0.90625</v>
+      </c>
+      <c r="H359" s="18">
+        <v>0.78125</v>
+      </c>
+      <c r="I359" s="104">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A360" s="65"/>
+      <c r="B360" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C360" s="93" t="s">
+        <v>158</v>
+      </c>
+      <c r="D360" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E360" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F360" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G360" s="115" t="s">
+        <v>44</v>
+      </c>
+      <c r="H360" s="18">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="I360" s="105" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A361" s="67"/>
+      <c r="B361" s="26"/>
+      <c r="C361" s="94"/>
+      <c r="D361" s="26"/>
+      <c r="E361" s="27"/>
+      <c r="F361" s="28"/>
+      <c r="G361" s="116"/>
+      <c r="H361" s="28"/>
+      <c r="I361" s="106"/>
+    </row>
+    <row r="362" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A362" s="31"/>
+      <c r="B362" s="34" t="s">
+        <v>396</v>
+      </c>
+      <c r="C362" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="D362" s="34">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="E362" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F362" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G362" s="107" t="s">
+        <v>114</v>
+      </c>
+      <c r="H362" s="117" t="s">
+        <v>44</v>
+      </c>
+      <c r="I362" s="122">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A363" s="39">
+        <v>46185</v>
+      </c>
+      <c r="B363" s="42" t="s">
+        <v>397</v>
+      </c>
+      <c r="C363" s="74" t="s">
+        <v>87</v>
+      </c>
+      <c r="D363" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="E363" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F363" s="48">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="G363" s="108">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="H363" s="118">
+        <v>0.4375</v>
+      </c>
+      <c r="I363" s="108">
+        <v>0.61458333333333337</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A364" s="183" t="s">
+        <v>48</v>
+      </c>
+      <c r="B364" s="42" t="s">
+        <v>398</v>
+      </c>
+      <c r="C364" s="74" t="s">
+        <v>147</v>
+      </c>
+      <c r="D364" s="42">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="E364" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F364" s="48">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="G364" s="108">
+        <v>0.9375</v>
+      </c>
+      <c r="H364" s="118">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I364" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A365" s="49"/>
+      <c r="B365" s="42"/>
+      <c r="C365" s="74"/>
+      <c r="D365" s="42"/>
+      <c r="E365" s="43"/>
+      <c r="F365" s="48"/>
+      <c r="G365" s="108"/>
+      <c r="H365" s="118"/>
+      <c r="I365" s="108"/>
+    </row>
+    <row r="366" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A366" s="51"/>
+      <c r="B366" s="54"/>
+      <c r="C366" s="79"/>
+      <c r="D366" s="54"/>
+      <c r="E366" s="55"/>
+      <c r="F366" s="56"/>
+      <c r="G366" s="110"/>
+      <c r="H366" s="120"/>
+      <c r="I366" s="110"/>
+    </row>
+    <row r="367" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A367" s="1"/>
+      <c r="B367" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C367" s="90" t="s">
+        <v>183</v>
+      </c>
+      <c r="D367" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E367" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F367" s="58" t="s">
+        <v>22</v>
+      </c>
+      <c r="G367" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="H367" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="I367" s="112" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A368" s="82">
+        <v>46186</v>
+      </c>
+      <c r="B368" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="C368" s="93" t="s">
+        <v>264</v>
+      </c>
+      <c r="D368" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E368" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F368" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G368" s="104">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H368" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="I368" s="104">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A369" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B369" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C369" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D369" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E369" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F369" s="18">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G369" s="104">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H369" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I369" s="104">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A370" s="114"/>
+      <c r="B370" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="C370" s="93" t="s">
+        <v>124</v>
+      </c>
+      <c r="D370" s="12">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E370" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F370" s="18">
+        <v>0.84375</v>
+      </c>
+      <c r="G370" s="104">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="H370" s="18">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="I370" s="104">
+        <v>0.97916666666666663</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A371" s="125"/>
+      <c r="B371" s="26"/>
+      <c r="C371" s="94"/>
+      <c r="D371" s="26"/>
+      <c r="E371" s="27"/>
+      <c r="F371" s="85"/>
+      <c r="G371" s="87"/>
+      <c r="H371" s="85"/>
+      <c r="I371" s="87"/>
+    </row>
+    <row r="372" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A372" s="70"/>
+      <c r="B372" s="34" t="s">
+        <v>402</v>
+      </c>
+      <c r="C372" s="71" t="s">
+        <v>87</v>
+      </c>
+      <c r="D372" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="E372" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F372" s="36">
+        <v>0.11458333333333333</v>
+      </c>
+      <c r="G372" s="107">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="H372" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="I372" s="107">
+        <v>0.27083333333333331</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A373" s="73">
+        <v>46187</v>
+      </c>
+      <c r="B373" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="C373" s="74" t="s">
+        <v>89</v>
+      </c>
+      <c r="D373" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="E373" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F373" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="G373" s="108">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H373" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="I373" s="108">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A374" s="76" t="s">
+        <v>73</v>
+      </c>
+      <c r="B374" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="C374" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="D374" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="E374" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F374" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="G374" s="108">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H374" s="48">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I374" s="108">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A375" s="49"/>
+      <c r="B375" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="C375" s="74" t="s">
+        <v>325</v>
+      </c>
+      <c r="D375" s="42">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="E375" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F375" s="48">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="G375" s="108">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="H375" s="48">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I375" s="109" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A376" s="51"/>
+      <c r="B376" s="54"/>
+      <c r="C376" s="79"/>
+      <c r="D376" s="54"/>
+      <c r="E376" s="55"/>
+      <c r="F376" s="56"/>
+      <c r="G376" s="110"/>
+      <c r="H376" s="56"/>
+      <c r="I376" s="110"/>
+    </row>
+    <row r="377" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A377" s="1"/>
+      <c r="B377" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C377" s="90" t="s">
+        <v>16</v>
+      </c>
+      <c r="D377" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E377" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F377" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="G377" s="112" t="s">
+        <v>78</v>
+      </c>
+      <c r="H377" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="I377" s="112" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A378" s="62">
+        <v>46188</v>
+      </c>
+      <c r="B378" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C378" s="93" t="s">
+        <v>98</v>
+      </c>
+      <c r="D378" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E378" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F378" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="G378" s="104">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H378" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="I378" s="104">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A379" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="B379" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="C379" s="93" t="s">
+        <v>41</v>
+      </c>
+      <c r="D379" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E379" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F379" s="18">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G379" s="104">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H379" s="18">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I379" s="104">
+        <v>0.67708333333333337</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A380" s="65"/>
+      <c r="B380" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="C380" s="93" t="s">
+        <v>408</v>
+      </c>
+      <c r="D380" s="12">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="E380" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F380" s="18">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G380" s="105">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="H380" s="18">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="I380" s="105" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A381" s="67"/>
+      <c r="B381" s="26"/>
+      <c r="C381" s="94"/>
+      <c r="D381" s="26"/>
+      <c r="E381" s="27"/>
+      <c r="F381" s="28"/>
+      <c r="G381" s="106"/>
+      <c r="H381" s="28"/>
+      <c r="I381" s="106"/>
+    </row>
+    <row r="382" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A382" s="31"/>
+      <c r="B382" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="C382" s="71">
+        <v>3.6</v>
+      </c>
+      <c r="D382" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="E382" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F382" s="36">
+        <v>0.21875</v>
+      </c>
+      <c r="G382" s="107" t="s">
+        <v>69</v>
+      </c>
+      <c r="H382" s="117">
+        <v>0.19791666666666666</v>
+      </c>
+      <c r="I382" s="107" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A383" s="39">
+        <v>46189</v>
+      </c>
+      <c r="B383" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="C383" s="74">
+        <v>2.6</v>
+      </c>
+      <c r="D383" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="E383" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F383" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G383" s="108">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H383" s="119" t="s">
+        <v>114</v>
+      </c>
+      <c r="I383" s="108">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A384" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B384" s="42" t="s">
+        <v>250</v>
+      </c>
+      <c r="C384" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="D384" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="E384" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F384" s="48">
+        <v>0.5625</v>
+      </c>
+      <c r="G384" s="108">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="H384" s="118">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I384" s="108">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A385" s="49"/>
+      <c r="B385" s="42" t="s">
+        <v>411</v>
+      </c>
+      <c r="C385" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="D385" s="42">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="E385" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F385" s="133">
+        <v>0.96875</v>
+      </c>
+      <c r="G385" s="134" t="s">
+        <v>22</v>
+      </c>
+      <c r="H385" s="133">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="I385" s="134" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A386" s="51"/>
+      <c r="B386" s="100"/>
+      <c r="C386" s="101"/>
+      <c r="D386" s="100"/>
+      <c r="E386" s="102"/>
+      <c r="F386" s="56"/>
+      <c r="G386" s="110"/>
+      <c r="H386" s="120"/>
+      <c r="I386" s="110"/>
+    </row>
+    <row r="387" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A387" s="1"/>
+      <c r="B387" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D387" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E387" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F387" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="G387" s="103">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="H387" s="6">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="I387" s="103" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A388" s="62">
+        <v>46190</v>
+      </c>
+      <c r="B388" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C388" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="D388" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E388" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F388" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G388" s="104">
+        <v>0.5625</v>
+      </c>
+      <c r="H388" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="I388" s="104">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A389" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B389" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="C389" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D389" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E389" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F389" s="18">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G389" s="104">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H389" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I389" s="104">
+        <v>0.73958333333333337</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A390" s="65"/>
+      <c r="B390" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C390" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="D390" s="12">
+        <v>6.25E-2</v>
+      </c>
+      <c r="E390" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F390" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G390" s="105" t="s">
+        <v>5</v>
+      </c>
+      <c r="H390" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I390" s="105" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A391" s="67"/>
+      <c r="B391" s="24"/>
+      <c r="C391" s="25"/>
+      <c r="D391" s="26"/>
+      <c r="E391" s="27"/>
+      <c r="F391" s="28"/>
+      <c r="G391" s="106"/>
+      <c r="H391" s="28"/>
+      <c r="I391" s="106"/>
+    </row>
+    <row r="392" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A392" s="31"/>
+      <c r="B392" s="32" t="s">
+        <v>417</v>
+      </c>
+      <c r="C392" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D392" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E392" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F392" s="36">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G392" s="122">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H392" s="36">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="I392" s="122">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A393" s="73">
+        <v>46191</v>
+      </c>
+      <c r="B393" s="40" t="s">
+        <v>418</v>
+      </c>
+      <c r="C393" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="D393" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="E393" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F393" s="48">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G393" s="108">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="H393" s="48">
+        <v>0.4375</v>
+      </c>
+      <c r="I393" s="108">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A394" s="76" t="s">
+        <v>32</v>
+      </c>
+      <c r="B394" s="40" t="s">
+        <v>419</v>
+      </c>
+      <c r="C394" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D394" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="E394" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F394" s="48">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G394" s="108">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H394" s="48">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I394" s="108">
+        <v>0.77083333333333337</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A395" s="77"/>
+      <c r="B395" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="C395" s="41" t="s">
+        <v>317</v>
+      </c>
+      <c r="D395" s="42">
+        <v>9.375E-2</v>
+      </c>
+      <c r="E395" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F395" s="44">
+        <v>3.125E-2</v>
+      </c>
+      <c r="G395" s="109" t="s">
+        <v>216</v>
+      </c>
+      <c r="H395" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="I395" s="109" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A396" s="78"/>
+      <c r="B396" s="52"/>
+      <c r="C396" s="53"/>
+      <c r="D396" s="54"/>
+      <c r="E396" s="55"/>
+      <c r="F396" s="56"/>
+      <c r="G396" s="110"/>
+      <c r="H396" s="56"/>
+      <c r="I396" s="110"/>
+    </row>
+    <row r="397" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A397" s="81"/>
+      <c r="B397" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C397" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D397" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E397" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F397" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="G397" s="240">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H397" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="I397" s="121">
+        <v>0.44791666666666669</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A398" s="82">
+        <v>46192</v>
+      </c>
+      <c r="B398" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="C398" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D398" s="12">
+        <v>0.59375</v>
+      </c>
+      <c r="E398" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F398" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="G398" s="113">
+        <v>0.625</v>
+      </c>
+      <c r="H398" s="18">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I398" s="104">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A399" s="83" t="s">
+        <v>48</v>
+      </c>
+      <c r="B399" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="C399" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D399" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E399" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F399" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="G399" s="113">
+        <v>0.84375</v>
+      </c>
+      <c r="H399" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="I399" s="104">
+        <v>0.82291666666666663</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A400" s="114"/>
+      <c r="B400" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="C400" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D400" s="12">
+        <v>0.11458333333333333</v>
+      </c>
+      <c r="E400" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F400" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G400" s="115" t="s">
+        <v>44</v>
+      </c>
+      <c r="H400" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I400" s="105" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A401" s="67"/>
+      <c r="B401" s="24"/>
+      <c r="C401" s="68"/>
+      <c r="D401" s="26"/>
+      <c r="E401" s="27"/>
+      <c r="F401" s="28"/>
+      <c r="G401" s="116"/>
+      <c r="H401" s="28"/>
+      <c r="I401" s="106"/>
+    </row>
+    <row r="402" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A402" s="31"/>
+      <c r="B402" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="C402" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D402" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="E402" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F402" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="G402" s="122">
+        <v>0.5</v>
+      </c>
+      <c r="H402" s="117" t="s">
+        <v>78</v>
+      </c>
+      <c r="I402" s="122">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A403" s="39">
+        <v>46193</v>
+      </c>
+      <c r="B403" s="40" t="s">
+        <v>425</v>
+      </c>
+      <c r="C403" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="D403" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="E403" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F403" s="48">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G403" s="108">
+        <v>0.6875</v>
+      </c>
+      <c r="H403" s="118">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="I403" s="108">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A404" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="B404" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="C404" s="74" t="s">
+        <v>183</v>
+      </c>
+      <c r="D404" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="E404" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F404" s="48">
+        <v>0.6875</v>
+      </c>
+      <c r="G404" s="108">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="H404" s="118">
+        <v>0.6875</v>
+      </c>
+      <c r="I404" s="108">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A405" s="49"/>
+      <c r="B405" s="40" t="s">
+        <v>427</v>
+      </c>
+      <c r="C405" s="74" t="s">
+        <v>147</v>
+      </c>
+      <c r="D405" s="42">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="E405" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F405" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G405" s="109" t="s">
+        <v>163</v>
+      </c>
+      <c r="H405" s="119" t="s">
+        <v>53</v>
+      </c>
+      <c r="I405" s="109" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A406" s="51"/>
+      <c r="B406" s="52"/>
+      <c r="C406" s="79"/>
+      <c r="D406" s="54"/>
+      <c r="E406" s="55"/>
+      <c r="F406" s="56"/>
+      <c r="G406" s="110"/>
+      <c r="H406" s="120"/>
+      <c r="I406" s="110"/>
+    </row>
+    <row r="407" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A407" s="1"/>
+      <c r="B407" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C407" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D407" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E407" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F407" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="G407" s="121">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="H407" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="I407" s="121">
+        <v>0.48958333333333331</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A408" s="62">
+        <v>46194</v>
+      </c>
+      <c r="B408" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="C408" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D408" s="12">
+        <v>0.6875</v>
+      </c>
+      <c r="E408" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F408" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G408" s="104">
+        <v>0.75</v>
+      </c>
+      <c r="H408" s="18">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="I408" s="104">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A409" s="64" t="s">
+        <v>73</v>
+      </c>
+      <c r="B409" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="C409" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D409" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E409" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F409" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="G409" s="104">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="H409" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="I409" s="104">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A410" s="65"/>
+      <c r="B410" s="10"/>
+      <c r="C410" s="11"/>
+      <c r="D410" s="12"/>
+      <c r="E410" s="13"/>
+      <c r="F410" s="18"/>
+      <c r="G410" s="104"/>
+      <c r="H410" s="18"/>
+      <c r="I410" s="104"/>
+    </row>
+    <row r="411" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A411" s="67"/>
+      <c r="B411" s="24"/>
+      <c r="C411" s="68"/>
+      <c r="D411" s="26"/>
+      <c r="E411" s="27"/>
+      <c r="F411" s="85"/>
+      <c r="G411" s="87"/>
+      <c r="H411" s="85"/>
+      <c r="I411" s="87"/>
+    </row>
+    <row r="412" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A412" s="31"/>
+      <c r="B412" s="32" t="s">
+        <v>431</v>
+      </c>
+      <c r="C412" s="71" t="s">
+        <v>195</v>
+      </c>
+      <c r="D412" s="34">
+        <v>0.17708333333333334</v>
+      </c>
+      <c r="E412" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F412" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="G412" s="107" t="s">
+        <v>6</v>
+      </c>
+      <c r="H412" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="I412" s="107" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A413" s="39">
+        <v>46195</v>
+      </c>
+      <c r="B413" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C413" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="D413" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E413" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F413" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="G413" s="108">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H413" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="I413" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A414" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B414" s="40" t="s">
+        <v>432</v>
+      </c>
+      <c r="C414" s="74" t="s">
+        <v>120</v>
+      </c>
+      <c r="D414" s="42">
+        <v>0.75</v>
+      </c>
+      <c r="E414" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F414" s="48">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="G414" s="108">
+        <v>0.8125</v>
+      </c>
+      <c r="H414" s="48">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="I414" s="108">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A415" s="49"/>
+      <c r="B415" s="40" t="s">
+        <v>340</v>
+      </c>
+      <c r="C415" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D415" s="42" t="s">
+        <v>221</v>
+      </c>
+      <c r="E415" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F415" s="48">
+        <v>0.8125</v>
+      </c>
+      <c r="G415" s="109" t="s">
+        <v>21</v>
+      </c>
+      <c r="H415" s="48">
+        <v>0.8125</v>
+      </c>
+      <c r="I415" s="109" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A416" s="51"/>
+      <c r="B416" s="52"/>
+      <c r="C416" s="79"/>
+      <c r="D416" s="54"/>
+      <c r="E416" s="55"/>
+      <c r="F416" s="56"/>
+      <c r="G416" s="110"/>
+      <c r="H416" s="56"/>
+      <c r="I416" s="110"/>
+    </row>
+    <row r="417" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A417" s="1"/>
+      <c r="B417" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C417" s="90" t="s">
+        <v>105</v>
+      </c>
+      <c r="D417" s="4">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="E417" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F417" s="58">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G417" s="112" t="s">
+        <v>45</v>
+      </c>
+      <c r="H417" s="58">
+        <v>0.11458333333333333</v>
+      </c>
+      <c r="I417" s="112" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A418" s="62">
+        <v>46196</v>
+      </c>
+      <c r="B418" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C418" s="93" t="s">
+        <v>96</v>
+      </c>
+      <c r="D418" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E418" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F418" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G418" s="104">
+        <v>0.5625</v>
+      </c>
+      <c r="H418" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="I418" s="104">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A419" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B419" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="C419" s="93" t="s">
+        <v>112</v>
+      </c>
+      <c r="D419" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E419" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F419" s="18">
+        <v>0.6875</v>
+      </c>
+      <c r="G419" s="104">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="H419" s="18">
+        <v>0.71875</v>
+      </c>
+      <c r="I419" s="104">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A420" s="65"/>
+      <c r="B420" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="C420" s="93" t="s">
+        <v>89</v>
+      </c>
+      <c r="D420" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E420" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F420" s="18">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="G420" s="105" t="s">
+        <v>26</v>
+      </c>
+      <c r="H420" s="18">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="I420" s="105" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A421" s="67"/>
+      <c r="B421" s="24"/>
+      <c r="C421" s="94"/>
+      <c r="D421" s="26"/>
+      <c r="E421" s="27"/>
+      <c r="F421" s="28"/>
+      <c r="G421" s="106"/>
+      <c r="H421" s="28"/>
+      <c r="I421" s="106"/>
+    </row>
+    <row r="422" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A422" s="31"/>
+      <c r="B422" s="32" t="s">
+        <v>436</v>
+      </c>
+      <c r="C422" s="71" t="s">
+        <v>249</v>
+      </c>
+      <c r="D422" s="34">
+        <v>0.25</v>
+      </c>
+      <c r="E422" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F422" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="G422" s="107" t="s">
+        <v>57</v>
+      </c>
+      <c r="H422" s="117" t="s">
+        <v>26</v>
+      </c>
+      <c r="I422" s="107" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A423" s="39">
+        <v>46197</v>
+      </c>
+      <c r="B423" s="40" t="s">
+        <v>437</v>
+      </c>
+      <c r="C423" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="D423" s="42">
+        <v>0.5</v>
+      </c>
+      <c r="E423" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F423" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="G423" s="108">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H423" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="I423" s="108">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A424" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B424" s="40" t="s">
+        <v>438</v>
+      </c>
+      <c r="C424" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="D424" s="42">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E424" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F424" s="48">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="G424" s="108">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="H424" s="118">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="I424" s="108">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A425" s="49"/>
+      <c r="B425" s="40" t="s">
+        <v>439</v>
+      </c>
+      <c r="C425" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D425" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="E425" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F425" s="48">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="G425" s="109" t="s">
+        <v>56</v>
+      </c>
+      <c r="H425" s="118">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="I425" s="109" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A426" s="51"/>
+      <c r="B426" s="52"/>
+      <c r="C426" s="101"/>
+      <c r="D426" s="100"/>
+      <c r="E426" s="102"/>
+      <c r="F426" s="56"/>
+      <c r="G426" s="110"/>
+      <c r="H426" s="120"/>
+      <c r="I426" s="110"/>
+    </row>
+    <row r="427" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A427" s="1"/>
+      <c r="B427" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C427" s="90" t="s">
+        <v>259</v>
+      </c>
+      <c r="D427" s="4">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="E427" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F427" s="123" t="s">
+        <v>56</v>
+      </c>
+      <c r="G427" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H427" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I427" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A428" s="62">
+        <v>46198</v>
+      </c>
+      <c r="B428" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="C428" s="93" t="s">
+        <v>96</v>
+      </c>
+      <c r="D428" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E428" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F428" s="124">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="G428" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="H428" s="84" t="s">
+        <v>114</v>
+      </c>
+      <c r="I428" s="15">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A429" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="B429" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="C429" s="93" t="s">
+        <v>52</v>
+      </c>
+      <c r="D429" s="12">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="E429" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F429" s="18">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="G429" s="15">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="H429" s="16">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="I429" s="15">
+        <v>0.94791666666666663</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A430" s="65"/>
+      <c r="B430" s="10"/>
+      <c r="C430" s="93"/>
+      <c r="D430" s="12"/>
+      <c r="E430" s="13"/>
+      <c r="F430" s="18"/>
+      <c r="G430" s="15"/>
+      <c r="H430" s="16"/>
+      <c r="I430" s="15"/>
+    </row>
+    <row r="431" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A431" s="67"/>
+      <c r="B431" s="24"/>
+      <c r="C431" s="94"/>
+      <c r="D431" s="26"/>
+      <c r="E431" s="27"/>
+      <c r="F431" s="116"/>
+      <c r="G431" s="29"/>
+      <c r="H431" s="69"/>
+      <c r="I431" s="29"/>
+    </row>
+    <row r="432" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A432" s="31"/>
+      <c r="B432" s="32" t="s">
+        <v>442</v>
+      </c>
+      <c r="C432" s="71" t="s">
+        <v>136</v>
+      </c>
+      <c r="D432" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E432" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F432" s="126" t="s">
+        <v>38</v>
+      </c>
+      <c r="G432" s="127" t="s">
+        <v>6</v>
+      </c>
+      <c r="H432" s="128" t="s">
+        <v>77</v>
+      </c>
+      <c r="I432" s="127" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A433" s="39">
+        <v>46199</v>
+      </c>
+      <c r="B433" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C433" s="74">
+        <v>2.4</v>
+      </c>
+      <c r="D433" s="42">
+        <v>0.34375</v>
+      </c>
+      <c r="E433" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F433" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="G433" s="45">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H433" s="88" t="s">
+        <v>6</v>
+      </c>
+      <c r="I433" s="45">
+        <v>0.42708333333333331</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A434" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B434" s="40" t="s">
+        <v>443</v>
+      </c>
+      <c r="C434" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="D434" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="E434" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F434" s="48">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="G434" s="45">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="H434" s="46">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="I434" s="45">
+        <v>0.61458333333333337</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A435" s="49"/>
+      <c r="B435" s="40" t="s">
+        <v>444</v>
+      </c>
+      <c r="C435" s="74" t="s">
+        <v>252</v>
+      </c>
+      <c r="D435" s="42">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="E435" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F435" s="48">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="G435" s="45">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="H435" s="46">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I435" s="45">
+        <v>0.96875</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A436" s="51"/>
+      <c r="B436" s="52"/>
+      <c r="C436" s="79"/>
+      <c r="D436" s="54"/>
+      <c r="E436" s="55"/>
+      <c r="F436" s="56"/>
+      <c r="G436" s="57"/>
+      <c r="H436" s="54"/>
+      <c r="I436" s="57"/>
+    </row>
+    <row r="437" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A437" s="1"/>
+      <c r="B437" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C437" s="90" t="s">
+        <v>142</v>
+      </c>
+      <c r="D437" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E437" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F437" s="58" t="s">
+        <v>53</v>
+      </c>
+      <c r="G437" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="H437" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="I437" s="61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A438" s="82">
+        <v>46200</v>
+      </c>
+      <c r="B438" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="C438" s="93" t="s">
+        <v>132</v>
+      </c>
+      <c r="D438" s="12">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="E438" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F438" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G438" s="63">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H438" s="84" t="s">
+        <v>25</v>
+      </c>
+      <c r="I438" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A439" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B439" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="C439" s="93" t="s">
+        <v>96</v>
+      </c>
+      <c r="D439" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E439" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F439" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="G439" s="63">
+        <v>0.65625</v>
+      </c>
+      <c r="H439" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I439" s="15">
+        <v>0.63541666666666663</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A440" s="114"/>
+      <c r="B440" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="C440" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="D440" s="12">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="E440" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F440" s="18">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G440" s="63">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="H440" s="16">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="I440" s="22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A441" s="125"/>
+      <c r="B441" s="24"/>
+      <c r="C441" s="94"/>
+      <c r="D441" s="26"/>
+      <c r="E441" s="27"/>
+      <c r="F441" s="28"/>
+      <c r="G441" s="30"/>
+      <c r="H441" s="69"/>
+      <c r="I441" s="29"/>
+    </row>
+    <row r="442" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A442" s="70"/>
+      <c r="B442" s="32" t="s">
+        <v>449</v>
+      </c>
+      <c r="C442" s="71" t="s">
+        <v>183</v>
+      </c>
+      <c r="D442" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="E442" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F442" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="G442" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="H442" s="72" t="s">
+        <v>148</v>
+      </c>
+      <c r="I442" s="37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A443" s="73">
+        <v>46201</v>
+      </c>
+      <c r="B443" s="40" t="s">
+        <v>450</v>
+      </c>
+      <c r="C443" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D443" s="42">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E443" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F443" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G443" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H443" s="99" t="s">
+        <v>58</v>
+      </c>
+      <c r="I443" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A444" s="76" t="s">
+        <v>73</v>
+      </c>
+      <c r="B444" s="40" t="s">
+        <v>451</v>
+      </c>
+      <c r="C444" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="D444" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="E444" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F444" s="48">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G444" s="45">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H444" s="75">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I444" s="45">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A445" s="77"/>
+      <c r="B445" s="40" t="s">
+        <v>404</v>
+      </c>
+      <c r="C445" s="74" t="s">
+        <v>117</v>
+      </c>
+      <c r="D445" s="42">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="E445" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F445" s="48">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G445" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="H445" s="75">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="I445" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A446" s="51"/>
+      <c r="B446" s="52"/>
+      <c r="C446" s="79"/>
+      <c r="D446" s="54"/>
+      <c r="E446" s="55"/>
+      <c r="F446" s="56"/>
+      <c r="G446" s="57"/>
+      <c r="H446" s="80"/>
+      <c r="I446" s="57"/>
+    </row>
+    <row r="447" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A447" s="1"/>
+      <c r="B447" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C447" s="90" t="s">
+        <v>96</v>
+      </c>
+      <c r="D447" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E447" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F447" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="G447" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="H447" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="I447" s="61" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A448" s="62">
+        <v>46202</v>
+      </c>
+      <c r="B448" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C448" s="93" t="s">
+        <v>132</v>
+      </c>
+      <c r="D448" s="12">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="E448" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F448" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G448" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="H448" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I448" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A449" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="B449" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="C449" s="93" t="s">
+        <v>190</v>
+      </c>
+      <c r="D449" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E449" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F449" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="G449" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H449" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="I449" s="15">
+        <v>0.67708333333333337</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A450" s="65"/>
+      <c r="B450" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="C450" s="93" t="s">
+        <v>364</v>
+      </c>
+      <c r="D450" s="12">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="E450" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F450" s="18">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="G450" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H450" s="16">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="I450" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A451" s="67"/>
+      <c r="B451" s="24"/>
+      <c r="C451" s="94"/>
+      <c r="D451" s="26"/>
+      <c r="E451" s="27"/>
+      <c r="F451" s="85"/>
+      <c r="G451" s="87"/>
+      <c r="H451" s="85"/>
+      <c r="I451" s="87"/>
+    </row>
+    <row r="452" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A452" s="31"/>
+      <c r="B452" s="32" t="s">
+        <v>455</v>
+      </c>
+      <c r="C452" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="D452" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E452" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F452" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="G452" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="H452" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="I452" s="37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A453" s="39">
+        <v>46203</v>
+      </c>
+      <c r="B453" s="40" t="s">
+        <v>387</v>
+      </c>
+      <c r="C453" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D453" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="E453" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F453" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="G453" s="45">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H453" s="88" t="s">
+        <v>46</v>
+      </c>
+      <c r="I453" s="45">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A454" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B454" s="40" t="s">
+        <v>456</v>
+      </c>
+      <c r="C454" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="D454" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="E454" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F454" s="48">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G454" s="45">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H454" s="46">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I454" s="45">
+        <v>0.69791666666666663</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A455" s="49"/>
+      <c r="B455" s="40" t="s">
+        <v>457</v>
+      </c>
+      <c r="C455" s="74" t="s">
+        <v>124</v>
+      </c>
+      <c r="D455" s="42">
+        <v>0</v>
+      </c>
+      <c r="E455" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F455" s="48">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G455" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="H455" s="46">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="I455" s="50" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A456" s="51"/>
+      <c r="B456" s="54"/>
+      <c r="C456" s="79"/>
+      <c r="D456" s="54"/>
+      <c r="E456" s="55"/>
+      <c r="F456" s="56"/>
+      <c r="G456" s="57"/>
+      <c r="H456" s="54"/>
+      <c r="I456" s="57"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10024,7 +13972,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{928BB44D-9009-4EF5-A7E0-17AFE9C73770}">
-  <dimension ref="A1:M306"/>
+  <dimension ref="A1:M456"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
@@ -20562,6 +24510,5160 @@
       <c r="L306" s="173"/>
       <c r="M306" s="221"/>
     </row>
+    <row r="307" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A307" s="1"/>
+      <c r="B307" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C307" s="135" t="s">
+        <v>87</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E307" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F307" s="136" t="s">
+        <v>53</v>
+      </c>
+      <c r="G307" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="H307" s="60" t="s">
+        <v>148</v>
+      </c>
+      <c r="I307" s="61" t="s">
+        <v>6</v>
+      </c>
+      <c r="J307" s="136">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K307" s="61">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="L307" s="60">
+        <v>6.25E-2</v>
+      </c>
+      <c r="M307" s="61" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A308" s="62">
+        <v>46174</v>
+      </c>
+      <c r="B308" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C308" s="138" t="s">
+        <v>89</v>
+      </c>
+      <c r="D308" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E308" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F308" s="139" t="s">
+        <v>25</v>
+      </c>
+      <c r="G308" s="15">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="H308" s="84">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="I308" s="15">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="J308" s="139" t="s">
+        <v>57</v>
+      </c>
+      <c r="K308" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="L308" s="84" t="s">
+        <v>6</v>
+      </c>
+      <c r="M308" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A309" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="B309" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="C309" s="138" t="s">
+        <v>87</v>
+      </c>
+      <c r="D309" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E309" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F309" s="18">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="G309" s="15">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H309" s="16">
+        <v>0.46875</v>
+      </c>
+      <c r="I309" s="15">
+        <v>0.59375</v>
+      </c>
+      <c r="J309" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K309" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="L309" s="16">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="M309" s="15">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="310" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A310" s="65"/>
+      <c r="B310" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C310" s="140" t="s">
+        <v>124</v>
+      </c>
+      <c r="D310" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E310" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F310" s="222">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="G310" s="223">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="H310" s="224">
+        <v>0.84375</v>
+      </c>
+      <c r="I310" s="223">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="J310" s="222">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K310" s="223">
+        <v>0.875</v>
+      </c>
+      <c r="L310" s="224">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M310" s="223">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="311" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A311" s="67"/>
+      <c r="B311" s="24"/>
+      <c r="C311" s="141"/>
+      <c r="D311" s="26"/>
+      <c r="E311" s="27"/>
+      <c r="F311" s="116"/>
+      <c r="G311" s="29"/>
+      <c r="H311" s="69"/>
+      <c r="I311" s="29"/>
+      <c r="J311" s="116"/>
+      <c r="K311" s="29"/>
+      <c r="L311" s="69"/>
+      <c r="M311" s="29"/>
+    </row>
+    <row r="312" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A312" s="31"/>
+      <c r="B312" s="32" t="s">
+        <v>370</v>
+      </c>
+      <c r="C312" s="142" t="s">
+        <v>87</v>
+      </c>
+      <c r="D312" s="34">
+        <v>0.19791666666666666</v>
+      </c>
+      <c r="E312" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F312" s="117">
+        <v>9.375E-2</v>
+      </c>
+      <c r="G312" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="H312" s="38">
+        <v>0.125</v>
+      </c>
+      <c r="I312" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="J312" s="117" t="s">
+        <v>39</v>
+      </c>
+      <c r="K312" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="L312" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="M312" s="37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="313" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A313" s="39">
+        <v>46175</v>
+      </c>
+      <c r="B313" s="40" t="s">
+        <v>371</v>
+      </c>
+      <c r="C313" s="144" t="s">
+        <v>132</v>
+      </c>
+      <c r="D313" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="E313" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F313" s="119" t="s">
+        <v>25</v>
+      </c>
+      <c r="G313" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H313" s="88" t="s">
+        <v>68</v>
+      </c>
+      <c r="I313" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="J313" s="119" t="s">
+        <v>46</v>
+      </c>
+      <c r="K313" s="45">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L313" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="M313" s="50" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="314" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A314" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B314" s="40" t="s">
+        <v>372</v>
+      </c>
+      <c r="C314" s="144" t="s">
+        <v>87</v>
+      </c>
+      <c r="D314" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="E314" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F314" s="118">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G314" s="45">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="H314" s="46">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I314" s="45">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="J314" s="118">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K314" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="L314" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="M314" s="45">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="315" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A315" s="49"/>
+      <c r="B315" s="40" t="s">
+        <v>373</v>
+      </c>
+      <c r="C315" s="144" t="s">
+        <v>124</v>
+      </c>
+      <c r="D315" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="E315" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F315" s="118">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G315" s="45">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="H315" s="46">
+        <v>0.875</v>
+      </c>
+      <c r="I315" s="45">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="J315" s="118">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="K315" s="45">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="L315" s="46">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="M315" s="45">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="316" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A316" s="51"/>
+      <c r="B316" s="52"/>
+      <c r="C316" s="145"/>
+      <c r="D316" s="54"/>
+      <c r="E316" s="55"/>
+      <c r="F316" s="120"/>
+      <c r="G316" s="57"/>
+      <c r="H316" s="54"/>
+      <c r="I316" s="57"/>
+      <c r="J316" s="120"/>
+      <c r="K316" s="57"/>
+      <c r="L316" s="54"/>
+      <c r="M316" s="57"/>
+    </row>
+    <row r="317" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A317" s="1"/>
+      <c r="B317" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C317" s="135" t="s">
+        <v>87</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E317" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F317" s="136" t="s">
+        <v>44</v>
+      </c>
+      <c r="G317" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="H317" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="I317" s="61" t="s">
+        <v>78</v>
+      </c>
+      <c r="J317" s="136" t="s">
+        <v>53</v>
+      </c>
+      <c r="K317" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="L317" s="60" t="s">
+        <v>216</v>
+      </c>
+      <c r="M317" s="61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A318" s="62">
+        <v>46176</v>
+      </c>
+      <c r="B318" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C318" s="138" t="s">
+        <v>132</v>
+      </c>
+      <c r="D318" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E318" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F318" s="139" t="s">
+        <v>78</v>
+      </c>
+      <c r="G318" s="63">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H318" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="I318" s="15">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="J318" s="139" t="s">
+        <v>59</v>
+      </c>
+      <c r="K318" s="63">
+        <v>0.4375</v>
+      </c>
+      <c r="L318" s="84" t="s">
+        <v>25</v>
+      </c>
+      <c r="M318" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="319" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A319" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B319" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="C319" s="138" t="s">
+        <v>87</v>
+      </c>
+      <c r="D319" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E319" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F319" s="124">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="G319" s="63">
+        <v>0.65625</v>
+      </c>
+      <c r="H319" s="16">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="I319" s="15">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="J319" s="124">
+        <v>0.4375</v>
+      </c>
+      <c r="K319" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="L319" s="16">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="M319" s="15">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A320" s="65"/>
+      <c r="B320" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="C320" s="138" t="s">
+        <v>364</v>
+      </c>
+      <c r="D320" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E320" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F320" s="124">
+        <v>0.875</v>
+      </c>
+      <c r="G320" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="H320" s="16">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="I320" s="15">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="J320" s="124">
+        <v>0.875</v>
+      </c>
+      <c r="K320" s="63">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="L320" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="M320" s="15">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="321" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A321" s="67"/>
+      <c r="B321" s="24"/>
+      <c r="C321" s="146"/>
+      <c r="D321" s="26"/>
+      <c r="E321" s="27"/>
+      <c r="F321" s="116"/>
+      <c r="G321" s="30"/>
+      <c r="H321" s="69"/>
+      <c r="I321" s="29"/>
+      <c r="J321" s="116"/>
+      <c r="K321" s="30"/>
+      <c r="L321" s="69"/>
+      <c r="M321" s="29"/>
+    </row>
+    <row r="322" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A322" s="31"/>
+      <c r="B322" s="34" t="s">
+        <v>377</v>
+      </c>
+      <c r="C322" s="147" t="s">
+        <v>190</v>
+      </c>
+      <c r="D322" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="E322" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F322" s="117" t="s">
+        <v>3</v>
+      </c>
+      <c r="G322" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="H322" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="I322" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="J322" s="117" t="s">
+        <v>148</v>
+      </c>
+      <c r="K322" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="L322" s="72" t="s">
+        <v>44</v>
+      </c>
+      <c r="M322" s="37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A323" s="39">
+        <v>46177</v>
+      </c>
+      <c r="B323" s="42" t="s">
+        <v>378</v>
+      </c>
+      <c r="C323" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="D323" s="149">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E323" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F323" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="G323" s="45">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="H323" s="99" t="s">
+        <v>70</v>
+      </c>
+      <c r="I323" s="45">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="J323" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="K323" s="45">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="L323" s="99" t="s">
+        <v>58</v>
+      </c>
+      <c r="M323" s="50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A324" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B324" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="C324" s="148" t="s">
+        <v>190</v>
+      </c>
+      <c r="D324" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="E324" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F324" s="118">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="G324" s="45">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H324" s="75">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="I324" s="45">
+        <v>0.65625</v>
+      </c>
+      <c r="J324" s="118">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="K324" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="L324" s="75">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="M324" s="45">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="325" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A325" s="49"/>
+      <c r="B325" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="C325" s="148" t="s">
+        <v>364</v>
+      </c>
+      <c r="D325" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E325" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F325" s="118">
+        <v>0.90625</v>
+      </c>
+      <c r="G325" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="H325" s="75">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="I325" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="J325" s="118">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K325" s="45">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="L325" s="75">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="M325" s="45">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A326" s="51"/>
+      <c r="B326" s="54"/>
+      <c r="C326" s="150"/>
+      <c r="D326" s="54"/>
+      <c r="E326" s="55"/>
+      <c r="F326" s="120"/>
+      <c r="G326" s="57"/>
+      <c r="H326" s="80"/>
+      <c r="I326" s="57"/>
+      <c r="J326" s="120"/>
+      <c r="K326" s="57"/>
+      <c r="L326" s="80"/>
+      <c r="M326" s="57"/>
+    </row>
+    <row r="327" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A327" s="1"/>
+      <c r="B327" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C327" s="135" t="s">
+        <v>190</v>
+      </c>
+      <c r="D327" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E327" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F327" s="136">
+        <v>0.1875</v>
+      </c>
+      <c r="G327" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="H327" s="60">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="I327" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="J327" s="136">
+        <v>0.125</v>
+      </c>
+      <c r="K327" s="61">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="L327" s="60">
+        <v>0.1875</v>
+      </c>
+      <c r="M327" s="61" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A328" s="62">
+        <v>46178</v>
+      </c>
+      <c r="B328" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C328" s="138">
+        <v>2.6</v>
+      </c>
+      <c r="D328" s="12">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E328" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F328" s="139" t="s">
+        <v>59</v>
+      </c>
+      <c r="G328" s="15">
+        <v>0.53125</v>
+      </c>
+      <c r="H328" s="84" t="s">
+        <v>59</v>
+      </c>
+      <c r="I328" s="15">
+        <v>0.53125</v>
+      </c>
+      <c r="J328" s="124">
+        <v>0.4375</v>
+      </c>
+      <c r="K328" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="L328" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="M328" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="329" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A329" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B329" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C329" s="138" t="s">
+        <v>96</v>
+      </c>
+      <c r="D329" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E329" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F329" s="124">
+        <v>0.53125</v>
+      </c>
+      <c r="G329" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H329" s="16">
+        <v>0.53125</v>
+      </c>
+      <c r="I329" s="15">
+        <v>0.6875</v>
+      </c>
+      <c r="J329" s="124">
+        <v>0.5</v>
+      </c>
+      <c r="K329" s="15">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L329" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="M329" s="15">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A330" s="65"/>
+      <c r="B330" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="C330" s="138" t="s">
+        <v>147</v>
+      </c>
+      <c r="D330" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E330" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F330" s="124">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G330" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H330" s="16">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="I330" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="J330" s="124">
+        <v>0.9375</v>
+      </c>
+      <c r="K330" s="15">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="L330" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="M330" s="15">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A331" s="67"/>
+      <c r="B331" s="24"/>
+      <c r="C331" s="146"/>
+      <c r="D331" s="26"/>
+      <c r="E331" s="27"/>
+      <c r="F331" s="86"/>
+      <c r="G331" s="87"/>
+      <c r="H331" s="85"/>
+      <c r="I331" s="87"/>
+      <c r="J331" s="86"/>
+      <c r="K331" s="87"/>
+      <c r="L331" s="85"/>
+      <c r="M331" s="87"/>
+    </row>
+    <row r="332" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A332" s="31"/>
+      <c r="B332" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="C332" s="147" t="s">
+        <v>96</v>
+      </c>
+      <c r="D332" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E332" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F332" s="117" t="s">
+        <v>6</v>
+      </c>
+      <c r="G332" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="H332" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="I332" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J332" s="117" t="s">
+        <v>216</v>
+      </c>
+      <c r="K332" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="L332" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="M332" s="37" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A333" s="73">
+        <v>46179</v>
+      </c>
+      <c r="B333" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="C333" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="D333" s="42">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="E333" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F333" s="119" t="s">
+        <v>114</v>
+      </c>
+      <c r="G333" s="45">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H333" s="88" t="s">
+        <v>114</v>
+      </c>
+      <c r="I333" s="45">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="J333" s="118">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="K333" s="45">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L333" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="M333" s="45">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A334" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B334" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="C334" s="148" t="s">
+        <v>183</v>
+      </c>
+      <c r="D334" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="E334" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F334" s="118">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="G334" s="45">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H334" s="46">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="I334" s="45">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="J334" s="118">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="K334" s="45">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="L334" s="46">
+        <v>0.5625</v>
+      </c>
+      <c r="M334" s="45">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A335" s="77"/>
+      <c r="B335" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="C335" s="148" t="s">
+        <v>274</v>
+      </c>
+      <c r="D335" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E335" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F335" s="118">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="G335" s="50">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="H335" s="46">
+        <v>0.96875</v>
+      </c>
+      <c r="I335" s="50">
+        <v>6.25E-2</v>
+      </c>
+      <c r="J335" s="118">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="K335" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="L335" s="46">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="M335" s="45">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A336" s="78"/>
+      <c r="B336" s="54"/>
+      <c r="C336" s="150"/>
+      <c r="D336" s="54"/>
+      <c r="E336" s="55"/>
+      <c r="F336" s="120"/>
+      <c r="G336" s="57"/>
+      <c r="H336" s="54"/>
+      <c r="I336" s="57"/>
+      <c r="J336" s="120"/>
+      <c r="K336" s="57"/>
+      <c r="L336" s="54"/>
+      <c r="M336" s="57"/>
+    </row>
+    <row r="337" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A337" s="81"/>
+      <c r="B337" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C337" s="151" t="s">
+        <v>96</v>
+      </c>
+      <c r="D337" s="4">
+        <v>0.34375</v>
+      </c>
+      <c r="E337" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F337" s="136">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="G337" s="91">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H337" s="60">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="I337" s="91">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J337" s="136" t="s">
+        <v>3</v>
+      </c>
+      <c r="K337" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="L337" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="M337" s="61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A338" s="82">
+        <v>46180</v>
+      </c>
+      <c r="B338" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="C338" s="152" t="s">
+        <v>89</v>
+      </c>
+      <c r="D338" s="12">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="E338" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F338" s="124">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G338" s="15">
+        <v>0.59375</v>
+      </c>
+      <c r="H338" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I338" s="15">
+        <v>0.59375</v>
+      </c>
+      <c r="J338" s="124" t="s">
+        <v>230</v>
+      </c>
+      <c r="K338" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="L338" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="M338" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A339" s="83" t="s">
+        <v>73</v>
+      </c>
+      <c r="B339" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="C339" s="152" t="s">
+        <v>158</v>
+      </c>
+      <c r="D339" s="12">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E339" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F339" s="124">
+        <v>0.59375</v>
+      </c>
+      <c r="G339" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H339" s="16">
+        <v>0.59375</v>
+      </c>
+      <c r="I339" s="15">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="J339" s="124" t="s">
+        <v>230</v>
+      </c>
+      <c r="K339" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="L339" s="16">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="M339" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A340" s="114"/>
+      <c r="B340" s="12"/>
+      <c r="C340" s="152"/>
+      <c r="D340" s="12"/>
+      <c r="E340" s="13"/>
+      <c r="F340" s="124"/>
+      <c r="G340" s="15"/>
+      <c r="H340" s="16"/>
+      <c r="I340" s="15"/>
+      <c r="J340" s="124"/>
+      <c r="K340" s="15"/>
+      <c r="L340" s="16"/>
+      <c r="M340" s="15"/>
+    </row>
+    <row r="341" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A341" s="67"/>
+      <c r="B341" s="26"/>
+      <c r="C341" s="153"/>
+      <c r="D341" s="26"/>
+      <c r="E341" s="27"/>
+      <c r="F341" s="116"/>
+      <c r="G341" s="29"/>
+      <c r="H341" s="69"/>
+      <c r="I341" s="29"/>
+      <c r="J341" s="116"/>
+      <c r="K341" s="29"/>
+      <c r="L341" s="69"/>
+      <c r="M341" s="29"/>
+    </row>
+    <row r="342" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A342" s="31"/>
+      <c r="B342" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="C342" s="147" t="s">
+        <v>66</v>
+      </c>
+      <c r="D342" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="E342" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F342" s="166">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="G342" s="127">
+        <v>0.125</v>
+      </c>
+      <c r="H342" s="155" t="s">
+        <v>37</v>
+      </c>
+      <c r="I342" s="127">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="J342" s="154" t="s">
+        <v>37</v>
+      </c>
+      <c r="K342" s="127" t="s">
+        <v>38</v>
+      </c>
+      <c r="L342" s="243">
+        <v>0.875</v>
+      </c>
+      <c r="M342" s="209">
+        <v>0.97916666666666663</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A343" s="39">
+        <v>46181</v>
+      </c>
+      <c r="B343" s="42" t="s">
+        <v>387</v>
+      </c>
+      <c r="C343" s="148" t="s">
+        <v>96</v>
+      </c>
+      <c r="D343" s="42">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="E343" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F343" s="119">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="G343" s="45">
+        <v>0.4375</v>
+      </c>
+      <c r="H343" s="99">
+        <v>0.28125</v>
+      </c>
+      <c r="I343" s="45">
+        <v>0.4375</v>
+      </c>
+      <c r="J343" s="119">
+        <v>0.1875</v>
+      </c>
+      <c r="K343" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="L343" s="99" t="s">
+        <v>25</v>
+      </c>
+      <c r="M343" s="45">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="344" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A344" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B344" s="42" t="s">
+        <v>388</v>
+      </c>
+      <c r="C344" s="148" t="s">
+        <v>264</v>
+      </c>
+      <c r="D344" s="42">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E344" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F344" s="118">
+        <v>0.4375</v>
+      </c>
+      <c r="G344" s="45">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H344" s="75">
+        <v>0.46875</v>
+      </c>
+      <c r="I344" s="45">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J344" s="118" t="s">
+        <v>230</v>
+      </c>
+      <c r="K344" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="L344" s="75">
+        <v>0.4375</v>
+      </c>
+      <c r="M344" s="45">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="345" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A345" s="49"/>
+      <c r="B345" s="42" t="s">
+        <v>389</v>
+      </c>
+      <c r="C345" s="148" t="s">
+        <v>98</v>
+      </c>
+      <c r="D345" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E345" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F345" s="118">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G345" s="45">
+        <v>0.8125</v>
+      </c>
+      <c r="H345" s="75">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I345" s="45">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J345" s="118" t="s">
+        <v>230</v>
+      </c>
+      <c r="K345" s="45" t="s">
+        <v>365</v>
+      </c>
+      <c r="L345" s="75">
+        <v>0.625</v>
+      </c>
+      <c r="M345" s="45">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="346" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A346" s="51"/>
+      <c r="B346" s="100"/>
+      <c r="C346" s="102"/>
+      <c r="D346" s="100"/>
+      <c r="E346" s="102"/>
+      <c r="F346" s="120"/>
+      <c r="G346" s="57"/>
+      <c r="H346" s="80"/>
+      <c r="I346" s="57"/>
+      <c r="J346" s="120"/>
+      <c r="K346" s="57"/>
+      <c r="L346" s="80"/>
+      <c r="M346" s="57"/>
+    </row>
+    <row r="347" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A347" s="1"/>
+      <c r="B347" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C347" s="151" t="s">
+        <v>10</v>
+      </c>
+      <c r="D347" s="4">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="E347" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F347" s="136" t="s">
+        <v>77</v>
+      </c>
+      <c r="G347" s="112" t="s">
+        <v>44</v>
+      </c>
+      <c r="H347" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="I347" s="112" t="s">
+        <v>216</v>
+      </c>
+      <c r="J347" s="136" t="s">
+        <v>21</v>
+      </c>
+      <c r="K347" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="L347" s="132">
+        <v>0.9375</v>
+      </c>
+      <c r="M347" s="112" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="348" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A348" s="62">
+        <v>46182</v>
+      </c>
+      <c r="B348" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="C348" s="152" t="s">
+        <v>96</v>
+      </c>
+      <c r="D348" s="12">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="E348" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F348" s="139">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G348" s="104">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H348" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="I348" s="104">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="J348" s="139">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="K348" s="105" t="s">
+        <v>25</v>
+      </c>
+      <c r="L348" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="M348" s="104">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="349" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A349" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B349" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="C349" s="152" t="s">
+        <v>71</v>
+      </c>
+      <c r="D349" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E349" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F349" s="18">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="G349" s="104">
+        <v>0.75</v>
+      </c>
+      <c r="H349" s="18">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="I349" s="104">
+        <v>0.75</v>
+      </c>
+      <c r="J349" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="K349" s="104">
+        <v>0.6875</v>
+      </c>
+      <c r="L349" s="18">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="M349" s="104">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="350" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A350" s="65"/>
+      <c r="B350" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="C350" s="152" t="s">
+        <v>132</v>
+      </c>
+      <c r="D350" s="12">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="E350" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F350" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="G350" s="104">
+        <v>0.9375</v>
+      </c>
+      <c r="H350" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="I350" s="104">
+        <v>0.90625</v>
+      </c>
+      <c r="J350" s="18">
+        <v>0.6875</v>
+      </c>
+      <c r="K350" s="104">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="L350" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="M350" s="104">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="351" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A351" s="67"/>
+      <c r="B351" s="26"/>
+      <c r="C351" s="153"/>
+      <c r="D351" s="26"/>
+      <c r="E351" s="27"/>
+      <c r="F351" s="116"/>
+      <c r="G351" s="106"/>
+      <c r="H351" s="28"/>
+      <c r="I351" s="106"/>
+      <c r="J351" s="116"/>
+      <c r="K351" s="106"/>
+      <c r="L351" s="28"/>
+      <c r="M351" s="106"/>
+    </row>
+    <row r="352" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A352" s="31"/>
+      <c r="B352" s="34" t="s">
+        <v>394</v>
+      </c>
+      <c r="C352" s="147" t="s">
+        <v>105</v>
+      </c>
+      <c r="D352" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="E352" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F352" s="117" t="s">
+        <v>21</v>
+      </c>
+      <c r="G352" s="107" t="s">
+        <v>56</v>
+      </c>
+      <c r="H352" s="36">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="I352" s="107" t="s">
+        <v>3</v>
+      </c>
+      <c r="J352" s="117" t="s">
+        <v>39</v>
+      </c>
+      <c r="K352" s="107" t="s">
+        <v>216</v>
+      </c>
+      <c r="L352" s="156">
+        <v>0.9375</v>
+      </c>
+      <c r="M352" s="107" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="353" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A353" s="39">
+        <v>46183</v>
+      </c>
+      <c r="B353" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="C353" s="148" t="s">
+        <v>190</v>
+      </c>
+      <c r="D353" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="E353" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F353" s="119" t="s">
+        <v>58</v>
+      </c>
+      <c r="G353" s="108">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H353" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="I353" s="108">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="J353" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="K353" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="L353" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="M353" s="108">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="354" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A354" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B354" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="C354" s="148" t="s">
+        <v>112</v>
+      </c>
+      <c r="D354" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="E354" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F354" s="118">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="G354" s="108">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H354" s="48">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="I354" s="108">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="J354" s="118">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="K354" s="108">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="L354" s="48">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="M354" s="108">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="355" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A355" s="49"/>
+      <c r="B355" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="C355" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="D355" s="42">
+        <v>0.9375</v>
+      </c>
+      <c r="E355" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F355" s="118">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="G355" s="109" t="s">
+        <v>77</v>
+      </c>
+      <c r="H355" s="48">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="I355" s="109" t="s">
+        <v>77</v>
+      </c>
+      <c r="J355" s="118">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="K355" s="108">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L355" s="48">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="M355" s="109" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="356" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A356" s="51"/>
+      <c r="B356" s="54"/>
+      <c r="C356" s="150"/>
+      <c r="D356" s="54"/>
+      <c r="E356" s="55"/>
+      <c r="F356" s="120"/>
+      <c r="G356" s="110"/>
+      <c r="H356" s="56"/>
+      <c r="I356" s="110"/>
+      <c r="J356" s="120"/>
+      <c r="K356" s="110"/>
+      <c r="L356" s="56"/>
+      <c r="M356" s="110"/>
+    </row>
+    <row r="357" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A357" s="1"/>
+      <c r="B357" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C357" s="151" t="s">
+        <v>60</v>
+      </c>
+      <c r="D357" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E357" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F357" s="136" t="s">
+        <v>77</v>
+      </c>
+      <c r="G357" s="111" t="s">
+        <v>42</v>
+      </c>
+      <c r="H357" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="I357" s="112" t="s">
+        <v>170</v>
+      </c>
+      <c r="J357" s="136" t="s">
+        <v>148</v>
+      </c>
+      <c r="K357" s="111" t="s">
+        <v>3</v>
+      </c>
+      <c r="L357" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="M357" s="112" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="358" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A358" s="62">
+        <v>46184</v>
+      </c>
+      <c r="B358" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C358" s="152" t="s">
+        <v>190</v>
+      </c>
+      <c r="D358" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E358" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F358" s="139" t="s">
+        <v>70</v>
+      </c>
+      <c r="G358" s="113">
+        <v>0.5</v>
+      </c>
+      <c r="H358" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="I358" s="104">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="J358" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="K358" s="115">
+        <v>0.3125</v>
+      </c>
+      <c r="L358" s="14">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M358" s="104">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="359" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A359" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="B359" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="C359" s="152" t="s">
+        <v>10</v>
+      </c>
+      <c r="D359" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E359" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F359" s="124">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G359" s="113">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="H359" s="18">
+        <v>0.6875</v>
+      </c>
+      <c r="I359" s="104">
+        <v>0.78125</v>
+      </c>
+      <c r="J359" s="124">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="K359" s="113">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="L359" s="18">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="M359" s="104">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="360" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A360" s="65"/>
+      <c r="B360" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C360" s="152" t="s">
+        <v>158</v>
+      </c>
+      <c r="D360" s="12">
+        <v>0</v>
+      </c>
+      <c r="E360" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F360" s="124">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="G360" s="115">
+        <v>6.25E-2</v>
+      </c>
+      <c r="H360" s="18">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I360" s="105">
+        <v>6.25E-2</v>
+      </c>
+      <c r="J360" s="124">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K360" s="113">
+        <v>0.875</v>
+      </c>
+      <c r="L360" s="18">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="M360" s="105" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="361" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A361" s="67"/>
+      <c r="B361" s="26"/>
+      <c r="C361" s="153"/>
+      <c r="D361" s="26"/>
+      <c r="E361" s="27"/>
+      <c r="F361" s="116"/>
+      <c r="G361" s="116"/>
+      <c r="H361" s="28"/>
+      <c r="I361" s="106"/>
+      <c r="J361" s="116"/>
+      <c r="K361" s="116"/>
+      <c r="L361" s="28"/>
+      <c r="M361" s="106"/>
+    </row>
+    <row r="362" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A362" s="31"/>
+      <c r="B362" s="34" t="s">
+        <v>396</v>
+      </c>
+      <c r="C362" s="147" t="s">
+        <v>71</v>
+      </c>
+      <c r="D362" s="34">
+        <v>0.21875</v>
+      </c>
+      <c r="E362" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F362" s="117">
+        <v>6.25E-2</v>
+      </c>
+      <c r="G362" s="107" t="s">
+        <v>58</v>
+      </c>
+      <c r="H362" s="117" t="s">
+        <v>5</v>
+      </c>
+      <c r="I362" s="107" t="s">
+        <v>45</v>
+      </c>
+      <c r="J362" s="117" t="s">
+        <v>3</v>
+      </c>
+      <c r="K362" s="107" t="s">
+        <v>6</v>
+      </c>
+      <c r="L362" s="117" t="s">
+        <v>38</v>
+      </c>
+      <c r="M362" s="107" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="363" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A363" s="39">
+        <v>46185</v>
+      </c>
+      <c r="B363" s="42" t="s">
+        <v>397</v>
+      </c>
+      <c r="C363" s="148" t="s">
+        <v>87</v>
+      </c>
+      <c r="D363" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="E363" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F363" s="119" t="s">
+        <v>70</v>
+      </c>
+      <c r="G363" s="108">
+        <v>0.5</v>
+      </c>
+      <c r="H363" s="119" t="s">
+        <v>69</v>
+      </c>
+      <c r="I363" s="108">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="J363" s="119" t="s">
+        <v>25</v>
+      </c>
+      <c r="K363" s="109" t="s">
+        <v>57</v>
+      </c>
+      <c r="L363" s="119" t="s">
+        <v>46</v>
+      </c>
+      <c r="M363" s="108">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="364" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A364" s="183" t="s">
+        <v>48</v>
+      </c>
+      <c r="B364" s="42" t="s">
+        <v>398</v>
+      </c>
+      <c r="C364" s="148" t="s">
+        <v>147</v>
+      </c>
+      <c r="D364" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="E364" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F364" s="118">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="G364" s="108">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="H364" s="118">
+        <v>0.71875</v>
+      </c>
+      <c r="I364" s="108">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="J364" s="118">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="K364" s="108">
+        <v>0.75</v>
+      </c>
+      <c r="L364" s="118">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="M364" s="108">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="365" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A365" s="49"/>
+      <c r="B365" s="42"/>
+      <c r="C365" s="148"/>
+      <c r="D365" s="42"/>
+      <c r="E365" s="43"/>
+      <c r="F365" s="118"/>
+      <c r="G365" s="108"/>
+      <c r="H365" s="118"/>
+      <c r="I365" s="108"/>
+      <c r="J365" s="118"/>
+      <c r="K365" s="108"/>
+      <c r="L365" s="118"/>
+      <c r="M365" s="108"/>
+    </row>
+    <row r="366" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A366" s="51"/>
+      <c r="B366" s="54"/>
+      <c r="C366" s="150"/>
+      <c r="D366" s="54"/>
+      <c r="E366" s="55"/>
+      <c r="F366" s="120"/>
+      <c r="G366" s="110"/>
+      <c r="H366" s="120"/>
+      <c r="I366" s="110"/>
+      <c r="J366" s="120"/>
+      <c r="K366" s="110"/>
+      <c r="L366" s="120"/>
+      <c r="M366" s="110"/>
+    </row>
+    <row r="367" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A367" s="1"/>
+      <c r="B367" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C367" s="151" t="s">
+        <v>183</v>
+      </c>
+      <c r="D367" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E367" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F367" s="201">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="G367" s="112" t="s">
+        <v>26</v>
+      </c>
+      <c r="H367" s="132">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="I367" s="112" t="s">
+        <v>26</v>
+      </c>
+      <c r="J367" s="201">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K367" s="121">
+        <v>0.9375</v>
+      </c>
+      <c r="L367" s="132">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="M367" s="112" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="368" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A368" s="82">
+        <v>46186</v>
+      </c>
+      <c r="B368" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="C368" s="152" t="s">
+        <v>264</v>
+      </c>
+      <c r="D368" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E368" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F368" s="139" t="s">
+        <v>26</v>
+      </c>
+      <c r="G368" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="H368" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I368" s="105" t="s">
+        <v>57</v>
+      </c>
+      <c r="J368" s="139" t="s">
+        <v>8</v>
+      </c>
+      <c r="K368" s="105" t="s">
+        <v>25</v>
+      </c>
+      <c r="L368" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="M368" s="105" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="369" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A369" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B369" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C369" s="152" t="s">
+        <v>2</v>
+      </c>
+      <c r="D369" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E369" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F369" s="139" t="s">
+        <v>59</v>
+      </c>
+      <c r="G369" s="104">
+        <v>0.53125</v>
+      </c>
+      <c r="H369" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I369" s="104">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="J369" s="139" t="s">
+        <v>58</v>
+      </c>
+      <c r="K369" s="105" t="s">
+        <v>59</v>
+      </c>
+      <c r="L369" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="M369" s="104">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="370" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A370" s="114"/>
+      <c r="B370" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="C370" s="152" t="s">
+        <v>124</v>
+      </c>
+      <c r="D370" s="12">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="E370" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F370" s="124">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="G370" s="104">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="H370" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="I370" s="104">
+        <v>0.84375</v>
+      </c>
+      <c r="J370" s="124">
+        <v>0.75</v>
+      </c>
+      <c r="K370" s="104">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L370" s="18">
+        <v>0.6875</v>
+      </c>
+      <c r="M370" s="104">
+        <v>0.72916666666666663</v>
+      </c>
+    </row>
+    <row r="371" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A371" s="125"/>
+      <c r="B371" s="26"/>
+      <c r="C371" s="153"/>
+      <c r="D371" s="26"/>
+      <c r="E371" s="27"/>
+      <c r="F371" s="86"/>
+      <c r="G371" s="87"/>
+      <c r="H371" s="85"/>
+      <c r="I371" s="87"/>
+      <c r="J371" s="86"/>
+      <c r="K371" s="87"/>
+      <c r="L371" s="85"/>
+      <c r="M371" s="87"/>
+    </row>
+    <row r="372" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A372" s="70"/>
+      <c r="B372" s="34" t="s">
+        <v>402</v>
+      </c>
+      <c r="C372" s="147" t="s">
+        <v>87</v>
+      </c>
+      <c r="D372" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="E372" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F372" s="117" t="s">
+        <v>21</v>
+      </c>
+      <c r="G372" s="107" t="s">
+        <v>176</v>
+      </c>
+      <c r="H372" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="I372" s="107" t="s">
+        <v>229</v>
+      </c>
+      <c r="J372" s="143">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="K372" s="122">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="L372" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M372" s="107" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="373" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A373" s="73">
+        <v>46187</v>
+      </c>
+      <c r="B373" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="C373" s="148" t="s">
+        <v>89</v>
+      </c>
+      <c r="D373" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="E373" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F373" s="119" t="s">
+        <v>163</v>
+      </c>
+      <c r="G373" s="109" t="s">
+        <v>59</v>
+      </c>
+      <c r="H373" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="I373" s="109" t="s">
+        <v>59</v>
+      </c>
+      <c r="J373" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="K373" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="L373" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="M373" s="109" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="374" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A374" s="76" t="s">
+        <v>73</v>
+      </c>
+      <c r="B374" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="C374" s="148" t="s">
+        <v>16</v>
+      </c>
+      <c r="D374" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E374" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F374" s="119" t="s">
+        <v>114</v>
+      </c>
+      <c r="G374" s="108">
+        <v>0.5625</v>
+      </c>
+      <c r="H374" s="48">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="I374" s="108">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J374" s="119" t="s">
+        <v>57</v>
+      </c>
+      <c r="K374" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="L374" s="48">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M374" s="108">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="375" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A375" s="49"/>
+      <c r="B375" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="C375" s="148" t="s">
+        <v>325</v>
+      </c>
+      <c r="D375" s="42" t="s">
+        <v>355</v>
+      </c>
+      <c r="E375" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F375" s="118">
+        <v>0.78125</v>
+      </c>
+      <c r="G375" s="108">
+        <v>0.84375</v>
+      </c>
+      <c r="H375" s="48">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="I375" s="108">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="J375" s="118">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="K375" s="108">
+        <v>0.8125</v>
+      </c>
+      <c r="L375" s="48">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M375" s="108">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="376" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A376" s="51"/>
+      <c r="B376" s="54"/>
+      <c r="C376" s="150"/>
+      <c r="D376" s="54"/>
+      <c r="E376" s="55"/>
+      <c r="F376" s="120"/>
+      <c r="G376" s="110"/>
+      <c r="H376" s="56"/>
+      <c r="I376" s="110"/>
+      <c r="J376" s="120"/>
+      <c r="K376" s="110"/>
+      <c r="L376" s="56"/>
+      <c r="M376" s="110"/>
+    </row>
+    <row r="377" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A377" s="1"/>
+      <c r="B377" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C377" s="151" t="s">
+        <v>16</v>
+      </c>
+      <c r="D377" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E377" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F377" s="157" t="s">
+        <v>39</v>
+      </c>
+      <c r="G377" s="158">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="H377" s="159" t="s">
+        <v>53</v>
+      </c>
+      <c r="I377" s="158" t="s">
+        <v>163</v>
+      </c>
+      <c r="J377" s="157" t="s">
+        <v>37</v>
+      </c>
+      <c r="K377" s="158" t="s">
+        <v>21</v>
+      </c>
+      <c r="L377" s="159" t="s">
+        <v>38</v>
+      </c>
+      <c r="M377" s="158" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="378" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A378" s="62">
+        <v>46188</v>
+      </c>
+      <c r="B378" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C378" s="152" t="s">
+        <v>98</v>
+      </c>
+      <c r="D378" s="12">
+        <v>0.34375</v>
+      </c>
+      <c r="E378" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F378" s="212">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="G378" s="161">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H378" s="214">
+        <v>0.25</v>
+      </c>
+      <c r="I378" s="161">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J378" s="212" t="s">
+        <v>68</v>
+      </c>
+      <c r="K378" s="213" t="s">
+        <v>46</v>
+      </c>
+      <c r="L378" s="214" t="s">
+        <v>56</v>
+      </c>
+      <c r="M378" s="213" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="379" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A379" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="B379" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="C379" s="152" t="s">
+        <v>41</v>
+      </c>
+      <c r="D379" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E379" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F379" s="160">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G379" s="161">
+        <v>0.59375</v>
+      </c>
+      <c r="H379" s="162">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="I379" s="161">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="J379" s="212" t="s">
+        <v>46</v>
+      </c>
+      <c r="K379" s="161">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L379" s="162">
+        <v>0.4375</v>
+      </c>
+      <c r="M379" s="161">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="380" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A380" s="65"/>
+      <c r="B380" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="C380" s="152" t="s">
+        <v>408</v>
+      </c>
+      <c r="D380" s="12">
+        <v>0.875</v>
+      </c>
+      <c r="E380" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F380" s="160">
+        <v>0.8125</v>
+      </c>
+      <c r="G380" s="161">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="H380" s="162">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I380" s="161">
+        <v>0.90625</v>
+      </c>
+      <c r="J380" s="160">
+        <v>0.8125</v>
+      </c>
+      <c r="K380" s="161">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L380" s="162">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M380" s="161">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="381" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A381" s="67"/>
+      <c r="B381" s="26"/>
+      <c r="C381" s="153"/>
+      <c r="D381" s="26"/>
+      <c r="E381" s="27"/>
+      <c r="F381" s="163"/>
+      <c r="G381" s="164"/>
+      <c r="H381" s="165"/>
+      <c r="I381" s="164"/>
+      <c r="J381" s="163"/>
+      <c r="K381" s="164"/>
+      <c r="L381" s="165"/>
+      <c r="M381" s="164"/>
+    </row>
+    <row r="382" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A382" s="31"/>
+      <c r="B382" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="C382" s="147">
+        <v>3.6</v>
+      </c>
+      <c r="D382" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="E382" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F382" s="154" t="s">
+        <v>148</v>
+      </c>
+      <c r="G382" s="168" t="s">
+        <v>55</v>
+      </c>
+      <c r="H382" s="154" t="s">
+        <v>216</v>
+      </c>
+      <c r="I382" s="168" t="s">
+        <v>42</v>
+      </c>
+      <c r="J382" s="154" t="s">
+        <v>38</v>
+      </c>
+      <c r="K382" s="168" t="s">
+        <v>39</v>
+      </c>
+      <c r="L382" s="154" t="s">
+        <v>53</v>
+      </c>
+      <c r="M382" s="168" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="383" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A383" s="39">
+        <v>46189</v>
+      </c>
+      <c r="B383" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="C383" s="148">
+        <v>2.6</v>
+      </c>
+      <c r="D383" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E383" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F383" s="119" t="s">
+        <v>45</v>
+      </c>
+      <c r="G383" s="108">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="H383" s="119" t="s">
+        <v>43</v>
+      </c>
+      <c r="I383" s="108">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="J383" s="119" t="s">
+        <v>57</v>
+      </c>
+      <c r="K383" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="L383" s="119" t="s">
+        <v>8</v>
+      </c>
+      <c r="M383" s="109" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="384" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A384" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B384" s="42" t="s">
+        <v>250</v>
+      </c>
+      <c r="C384" s="148" t="s">
+        <v>41</v>
+      </c>
+      <c r="D384" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="E384" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F384" s="118">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="G384" s="108">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H384" s="118">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I384" s="108">
+        <v>0.59375</v>
+      </c>
+      <c r="J384" s="119">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K384" s="108">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="L384" s="118">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="M384" s="108">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="385" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A385" s="49"/>
+      <c r="B385" s="42" t="s">
+        <v>411</v>
+      </c>
+      <c r="C385" s="148" t="s">
+        <v>412</v>
+      </c>
+      <c r="D385" s="42">
+        <v>0.90625</v>
+      </c>
+      <c r="E385" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F385" s="118">
+        <v>0.84375</v>
+      </c>
+      <c r="G385" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="H385" s="118">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="I385" s="108">
+        <v>0.9375</v>
+      </c>
+      <c r="J385" s="118">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K385" s="108">
+        <v>0.875</v>
+      </c>
+      <c r="L385" s="118">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="M385" s="108">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="386" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A386" s="51"/>
+      <c r="B386" s="100"/>
+      <c r="C386" s="102"/>
+      <c r="D386" s="100"/>
+      <c r="E386" s="102"/>
+      <c r="F386" s="120"/>
+      <c r="G386" s="110"/>
+      <c r="H386" s="120"/>
+      <c r="I386" s="110"/>
+      <c r="J386" s="120"/>
+      <c r="K386" s="110"/>
+      <c r="L386" s="120"/>
+      <c r="M386" s="110"/>
+    </row>
+    <row r="387" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A387" s="169"/>
+      <c r="B387" s="170" t="s">
+        <v>413</v>
+      </c>
+      <c r="C387" s="171" t="s">
+        <v>41</v>
+      </c>
+      <c r="D387" s="172" t="s">
+        <v>170</v>
+      </c>
+      <c r="E387" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F387" s="58">
+        <v>0.125</v>
+      </c>
+      <c r="G387" s="112" t="s">
+        <v>68</v>
+      </c>
+      <c r="H387" s="58">
+        <v>0.125</v>
+      </c>
+      <c r="I387" s="112" t="s">
+        <v>25</v>
+      </c>
+      <c r="J387" s="58" t="s">
+        <v>53</v>
+      </c>
+      <c r="K387" s="112" t="s">
+        <v>148</v>
+      </c>
+      <c r="L387" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="M387" s="112" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="388" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A388" s="62">
+        <v>46190</v>
+      </c>
+      <c r="B388" s="170" t="s">
+        <v>414</v>
+      </c>
+      <c r="C388" s="171">
+        <v>2.6</v>
+      </c>
+      <c r="D388" s="173">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E388" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F388" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="G388" s="104">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H388" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="I388" s="105">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="J388" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="K388" s="104">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L388" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M388" s="105" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="389" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A389" s="174" t="s">
+        <v>14</v>
+      </c>
+      <c r="B389" s="170" t="s">
+        <v>415</v>
+      </c>
+      <c r="C389" s="171" t="s">
+        <v>41</v>
+      </c>
+      <c r="D389" s="173" t="s">
+        <v>228</v>
+      </c>
+      <c r="E389" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F389" s="18">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="G389" s="104">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H389" s="18">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="I389" s="104">
+        <v>0.625</v>
+      </c>
+      <c r="J389" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="K389" s="104">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="L389" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="M389" s="104">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="390" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A390" s="169"/>
+      <c r="B390" s="170" t="s">
+        <v>416</v>
+      </c>
+      <c r="C390" s="175" t="s">
+        <v>412</v>
+      </c>
+      <c r="D390" s="173">
+        <v>0.9375</v>
+      </c>
+      <c r="E390" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F390" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="G390" s="105">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="H390" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="I390" s="105">
+        <v>0.96875</v>
+      </c>
+      <c r="J390" s="18">
+        <v>0.875</v>
+      </c>
+      <c r="K390" s="104">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="L390" s="18">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M390" s="104">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="391" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A391" s="169"/>
+      <c r="B391" s="170"/>
+      <c r="C391" s="175"/>
+      <c r="D391" s="173"/>
+      <c r="E391" s="176"/>
+      <c r="F391" s="28"/>
+      <c r="G391" s="106"/>
+      <c r="H391" s="28"/>
+      <c r="I391" s="106"/>
+      <c r="J391" s="28"/>
+      <c r="K391" s="106"/>
+      <c r="L391" s="28"/>
+      <c r="M391" s="106"/>
+    </row>
+    <row r="392" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A392" s="177"/>
+      <c r="B392" s="32" t="s">
+        <v>417</v>
+      </c>
+      <c r="C392" s="142" t="s">
+        <v>16</v>
+      </c>
+      <c r="D392" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E392" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F392" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="G392" s="107" t="s">
+        <v>78</v>
+      </c>
+      <c r="H392" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="I392" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="J392" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="K392" s="107" t="s">
+        <v>216</v>
+      </c>
+      <c r="L392" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="M392" s="107" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="393" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A393" s="39">
+        <v>46191</v>
+      </c>
+      <c r="B393" s="40" t="s">
+        <v>418</v>
+      </c>
+      <c r="C393" s="144" t="s">
+        <v>98</v>
+      </c>
+      <c r="D393" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="E393" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F393" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="G393" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H393" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="I393" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J393" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="K393" s="108">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="L393" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="M393" s="109" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="394" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A394" s="183" t="s">
+        <v>32</v>
+      </c>
+      <c r="B394" s="40" t="s">
+        <v>419</v>
+      </c>
+      <c r="C394" s="144" t="s">
+        <v>16</v>
+      </c>
+      <c r="D394" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="E394" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F394" s="48">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G394" s="108">
+        <v>0.6875</v>
+      </c>
+      <c r="H394" s="48">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I394" s="108">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J394" s="48">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="K394" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L394" s="48">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="M394" s="108">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="395" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A395" s="183"/>
+      <c r="B395" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="C395" s="144" t="s">
+        <v>317</v>
+      </c>
+      <c r="D395" s="42">
+        <v>0.96875</v>
+      </c>
+      <c r="E395" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F395" s="48">
+        <v>0.90625</v>
+      </c>
+      <c r="G395" s="109" t="s">
+        <v>21</v>
+      </c>
+      <c r="H395" s="48">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="I395" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="J395" s="48">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K395" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="L395" s="48">
+        <v>0.875</v>
+      </c>
+      <c r="M395" s="108">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="396" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A396" s="202"/>
+      <c r="B396" s="52"/>
+      <c r="C396" s="145"/>
+      <c r="D396" s="54"/>
+      <c r="E396" s="55"/>
+      <c r="F396" s="56"/>
+      <c r="G396" s="110"/>
+      <c r="H396" s="56"/>
+      <c r="I396" s="110"/>
+      <c r="J396" s="56"/>
+      <c r="K396" s="110"/>
+      <c r="L396" s="56"/>
+      <c r="M396" s="110"/>
+    </row>
+    <row r="397" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A397" s="169"/>
+      <c r="B397" s="170" t="s">
+        <v>420</v>
+      </c>
+      <c r="C397" s="171" t="s">
+        <v>16</v>
+      </c>
+      <c r="D397" s="173" t="s">
+        <v>68</v>
+      </c>
+      <c r="E397" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F397" s="58" t="s">
+        <v>8</v>
+      </c>
+      <c r="G397" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="H397" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="I397" s="112" t="s">
+        <v>70</v>
+      </c>
+      <c r="J397" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="K397" s="111" t="s">
+        <v>3</v>
+      </c>
+      <c r="L397" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="M397" s="112" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="398" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A398" s="62">
+        <v>46192</v>
+      </c>
+      <c r="B398" s="170" t="s">
+        <v>421</v>
+      </c>
+      <c r="C398" s="171" t="s">
+        <v>132</v>
+      </c>
+      <c r="D398" s="173">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="E398" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F398" s="14">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="G398" s="113">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H398" s="18">
+        <v>0.40625</v>
+      </c>
+      <c r="I398" s="104">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J398" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="K398" s="113">
+        <v>0.5</v>
+      </c>
+      <c r="L398" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M398" s="104">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="399" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A399" s="174" t="s">
+        <v>48</v>
+      </c>
+      <c r="B399" s="170" t="s">
+        <v>422</v>
+      </c>
+      <c r="C399" s="171" t="s">
+        <v>87</v>
+      </c>
+      <c r="D399" s="173" t="s">
+        <v>225</v>
+      </c>
+      <c r="E399" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F399" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G399" s="113">
+        <v>0.71875</v>
+      </c>
+      <c r="H399" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I399" s="104">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="J399" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="K399" s="113">
+        <v>0.5625</v>
+      </c>
+      <c r="L399" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="M399" s="104">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="400" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A400" s="169"/>
+      <c r="B400" s="170" t="s">
+        <v>423</v>
+      </c>
+      <c r="C400" s="171" t="s">
+        <v>129</v>
+      </c>
+      <c r="D400" s="173">
+        <v>0</v>
+      </c>
+      <c r="E400" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F400" s="18">
+        <v>0.9375</v>
+      </c>
+      <c r="G400" s="115" t="s">
+        <v>22</v>
+      </c>
+      <c r="H400" s="18">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="I400" s="105" t="s">
+        <v>85</v>
+      </c>
+      <c r="J400" s="18">
+        <v>0.9375</v>
+      </c>
+      <c r="K400" s="113">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="L400" s="18">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="M400" s="104">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="401" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A401" s="169"/>
+      <c r="B401" s="170"/>
+      <c r="C401" s="171"/>
+      <c r="D401" s="173"/>
+      <c r="E401" s="13"/>
+      <c r="F401" s="28"/>
+      <c r="G401" s="116"/>
+      <c r="H401" s="28"/>
+      <c r="I401" s="106"/>
+      <c r="J401" s="28"/>
+      <c r="K401" s="116"/>
+      <c r="L401" s="28"/>
+      <c r="M401" s="106"/>
+    </row>
+    <row r="402" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A402" s="177"/>
+      <c r="B402" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="C402" s="147" t="s">
+        <v>2</v>
+      </c>
+      <c r="D402" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E402" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F402" s="36">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="G402" s="107" t="s">
+        <v>31</v>
+      </c>
+      <c r="H402" s="117">
+        <v>0.25</v>
+      </c>
+      <c r="I402" s="107" t="s">
+        <v>59</v>
+      </c>
+      <c r="J402" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="K402" s="107" t="s">
+        <v>56</v>
+      </c>
+      <c r="L402" s="117" t="s">
+        <v>8</v>
+      </c>
+      <c r="M402" s="107" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="403" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A403" s="241">
+        <v>46193</v>
+      </c>
+      <c r="B403" s="42" t="s">
+        <v>425</v>
+      </c>
+      <c r="C403" s="148" t="s">
+        <v>264</v>
+      </c>
+      <c r="D403" s="42">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E403" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F403" s="48">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="G403" s="108">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="H403" s="118">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="I403" s="108">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="J403" s="48">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="K403" s="108">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L403" s="119" t="s">
+        <v>46</v>
+      </c>
+      <c r="M403" s="108">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="404" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A404" s="241" t="s">
+        <v>62</v>
+      </c>
+      <c r="B404" s="42" t="s">
+        <v>426</v>
+      </c>
+      <c r="C404" s="148" t="s">
+        <v>183</v>
+      </c>
+      <c r="D404" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="E404" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F404" s="48">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G404" s="108">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H404" s="118">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I404" s="108">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="J404" s="48">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="K404" s="108">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L404" s="118">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="M404" s="108">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="405" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A405" s="241"/>
+      <c r="B405" s="42" t="s">
+        <v>427</v>
+      </c>
+      <c r="C405" s="148" t="s">
+        <v>147</v>
+      </c>
+      <c r="D405" s="42">
+        <v>3.125E-2</v>
+      </c>
+      <c r="E405" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F405" s="48">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="G405" s="109" t="s">
+        <v>5</v>
+      </c>
+      <c r="H405" s="118">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="I405" s="109" t="s">
+        <v>7</v>
+      </c>
+      <c r="J405" s="48">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="K405" s="109" t="s">
+        <v>21</v>
+      </c>
+      <c r="L405" s="118">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="M405" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="406" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A406" s="242"/>
+      <c r="B406" s="54"/>
+      <c r="C406" s="150"/>
+      <c r="D406" s="54"/>
+      <c r="E406" s="55"/>
+      <c r="F406" s="56"/>
+      <c r="G406" s="110"/>
+      <c r="H406" s="120"/>
+      <c r="I406" s="110"/>
+      <c r="J406" s="56"/>
+      <c r="K406" s="110"/>
+      <c r="L406" s="120"/>
+      <c r="M406" s="110"/>
+    </row>
+    <row r="407" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A407" s="179"/>
+      <c r="B407" s="170" t="s">
+        <v>428</v>
+      </c>
+      <c r="C407" s="171" t="s">
+        <v>87</v>
+      </c>
+      <c r="D407" s="173" t="s">
+        <v>70</v>
+      </c>
+      <c r="E407" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F407" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="G407" s="112" t="s">
+        <v>114</v>
+      </c>
+      <c r="H407" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="I407" s="112" t="s">
+        <v>13</v>
+      </c>
+      <c r="J407" s="58" t="s">
+        <v>8</v>
+      </c>
+      <c r="K407" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="L407" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="M407" s="112" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="408" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A408" s="179">
+        <v>46194</v>
+      </c>
+      <c r="B408" s="170" t="s">
+        <v>429</v>
+      </c>
+      <c r="C408" s="171" t="s">
+        <v>259</v>
+      </c>
+      <c r="D408" s="173">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="E408" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F408" s="18">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="G408" s="104">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H408" s="18">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="I408" s="104">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J408" s="14">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="K408" s="105">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L408" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M408" s="105">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="409" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A409" s="179" t="s">
+        <v>73</v>
+      </c>
+      <c r="B409" s="170" t="s">
+        <v>430</v>
+      </c>
+      <c r="C409" s="171" t="s">
+        <v>136</v>
+      </c>
+      <c r="D409" s="173" t="s">
+        <v>93</v>
+      </c>
+      <c r="E409" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F409" s="18">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="G409" s="104">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="H409" s="18">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="I409" s="104">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="J409" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="K409" s="104">
+        <v>0.625</v>
+      </c>
+      <c r="L409" s="18">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="M409" s="104">
+        <v>0.77083333333333337</v>
+      </c>
+    </row>
+    <row r="410" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A410" s="179"/>
+      <c r="B410" s="170"/>
+      <c r="C410" s="171"/>
+      <c r="D410" s="173"/>
+      <c r="E410" s="176"/>
+      <c r="F410" s="18"/>
+      <c r="G410" s="104"/>
+      <c r="H410" s="18"/>
+      <c r="I410" s="104"/>
+      <c r="J410" s="18"/>
+      <c r="K410" s="104"/>
+      <c r="L410" s="18"/>
+      <c r="M410" s="104"/>
+    </row>
+    <row r="411" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A411" s="169"/>
+      <c r="B411" s="170"/>
+      <c r="C411" s="171"/>
+      <c r="D411" s="173"/>
+      <c r="E411" s="13"/>
+      <c r="F411" s="85"/>
+      <c r="G411" s="87"/>
+      <c r="H411" s="85"/>
+      <c r="I411" s="87"/>
+      <c r="J411" s="85"/>
+      <c r="K411" s="87"/>
+      <c r="L411" s="85"/>
+      <c r="M411" s="87"/>
+    </row>
+    <row r="412" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A412" s="177"/>
+      <c r="B412" s="34" t="s">
+        <v>431</v>
+      </c>
+      <c r="C412" s="147" t="s">
+        <v>195</v>
+      </c>
+      <c r="D412" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E412" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F412" s="156">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="G412" s="107" t="s">
+        <v>44</v>
+      </c>
+      <c r="H412" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="I412" s="107" t="s">
+        <v>148</v>
+      </c>
+      <c r="J412" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="K412" s="107" t="s">
+        <v>38</v>
+      </c>
+      <c r="L412" s="156">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="M412" s="122">
+        <v>0.97916666666666663</v>
+      </c>
+    </row>
+    <row r="413" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A413" s="183">
+        <v>46195</v>
+      </c>
+      <c r="B413" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C413" s="148" t="s">
+        <v>190</v>
+      </c>
+      <c r="D413" s="42">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="E413" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F413" s="44">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G413" s="108">
+        <v>0.4375</v>
+      </c>
+      <c r="H413" s="44">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="I413" s="108">
+        <v>0.40625</v>
+      </c>
+      <c r="J413" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="K413" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="L413" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="M413" s="109" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="414" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A414" s="183" t="s">
+        <v>82</v>
+      </c>
+      <c r="B414" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="C414" s="148" t="s">
+        <v>120</v>
+      </c>
+      <c r="D414" s="42">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="E414" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F414" s="48">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G414" s="108">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H414" s="48">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I414" s="108">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="J414" s="48">
+        <v>0.5625</v>
+      </c>
+      <c r="K414" s="108">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L414" s="48">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="M414" s="108">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="415" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A415" s="183"/>
+      <c r="B415" s="42" t="s">
+        <v>340</v>
+      </c>
+      <c r="C415" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="D415" s="42">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E415" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F415" s="48">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G415" s="108">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="H415" s="48">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="I415" s="108">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="J415" s="48">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="K415" s="108">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="L415" s="48">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M415" s="108">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="416" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A416" s="202"/>
+      <c r="B416" s="54"/>
+      <c r="C416" s="150"/>
+      <c r="D416" s="54"/>
+      <c r="E416" s="55"/>
+      <c r="F416" s="56"/>
+      <c r="G416" s="110"/>
+      <c r="H416" s="56"/>
+      <c r="I416" s="110"/>
+      <c r="J416" s="56"/>
+      <c r="K416" s="110"/>
+      <c r="L416" s="56"/>
+      <c r="M416" s="110"/>
+    </row>
+    <row r="417" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A417" s="169"/>
+      <c r="B417" s="173" t="s">
+        <v>433</v>
+      </c>
+      <c r="C417" s="185" t="s">
+        <v>105</v>
+      </c>
+      <c r="D417" s="173" t="s">
+        <v>5</v>
+      </c>
+      <c r="E417" s="184" t="s">
+        <v>12</v>
+      </c>
+      <c r="F417" s="132">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="G417" s="112" t="s">
+        <v>229</v>
+      </c>
+      <c r="H417" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="I417" s="112" t="s">
+        <v>24</v>
+      </c>
+      <c r="J417" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="K417" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="L417" s="132">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="M417" s="112" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="418" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A418" s="169">
+        <v>46196</v>
+      </c>
+      <c r="B418" s="173" t="s">
+        <v>314</v>
+      </c>
+      <c r="C418" s="185" t="s">
+        <v>96</v>
+      </c>
+      <c r="D418" s="173">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="E418" s="184" t="s">
+        <v>4</v>
+      </c>
+      <c r="F418" s="14">
+        <v>0.28125</v>
+      </c>
+      <c r="G418" s="104">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H418" s="14">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="I418" s="104">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="J418" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="K418" s="105" t="s">
+        <v>25</v>
+      </c>
+      <c r="L418" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="M418" s="105" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="419" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A419" s="169" t="s">
+        <v>91</v>
+      </c>
+      <c r="B419" s="173" t="s">
+        <v>434</v>
+      </c>
+      <c r="C419" s="185" t="s">
+        <v>112</v>
+      </c>
+      <c r="D419" s="173" t="s">
+        <v>193</v>
+      </c>
+      <c r="E419" s="184" t="s">
+        <v>12</v>
+      </c>
+      <c r="F419" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G419" s="104">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H419" s="18">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I419" s="104">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J419" s="18">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="K419" s="104">
+        <v>0.75</v>
+      </c>
+      <c r="L419" s="18">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="M419" s="104">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="420" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A420" s="169"/>
+      <c r="B420" s="173" t="s">
+        <v>435</v>
+      </c>
+      <c r="C420" s="185" t="s">
+        <v>89</v>
+      </c>
+      <c r="D420" s="173">
+        <v>0.90625</v>
+      </c>
+      <c r="E420" s="92" t="s">
+        <v>4</v>
+      </c>
+      <c r="F420" s="18">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G420" s="105" t="s">
+        <v>37</v>
+      </c>
+      <c r="H420" s="18">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I420" s="105" t="s">
+        <v>37</v>
+      </c>
+      <c r="J420" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="K420" s="104">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L420" s="18">
+        <v>0.8125</v>
+      </c>
+      <c r="M420" s="104">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="421" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A421" s="169"/>
+      <c r="B421" s="173"/>
+      <c r="C421" s="185"/>
+      <c r="D421" s="173"/>
+      <c r="E421" s="13"/>
+      <c r="F421" s="28"/>
+      <c r="G421" s="106"/>
+      <c r="H421" s="28"/>
+      <c r="I421" s="106"/>
+      <c r="J421" s="28"/>
+      <c r="K421" s="106"/>
+      <c r="L421" s="28"/>
+      <c r="M421" s="106"/>
+    </row>
+    <row r="422" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A422" s="186"/>
+      <c r="B422" s="34" t="s">
+        <v>436</v>
+      </c>
+      <c r="C422" s="147" t="s">
+        <v>249</v>
+      </c>
+      <c r="D422" s="34">
+        <v>0.125</v>
+      </c>
+      <c r="E422" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F422" s="126" t="s">
+        <v>37</v>
+      </c>
+      <c r="G422" s="168" t="s">
+        <v>170</v>
+      </c>
+      <c r="H422" s="154" t="s">
+        <v>37</v>
+      </c>
+      <c r="I422" s="168" t="s">
+        <v>56</v>
+      </c>
+      <c r="J422" s="126" t="s">
+        <v>39</v>
+      </c>
+      <c r="K422" s="168" t="s">
+        <v>216</v>
+      </c>
+      <c r="L422" s="166">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="M422" s="168" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="423" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A423" s="187">
+        <v>46197</v>
+      </c>
+      <c r="B423" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="C423" s="148" t="s">
+        <v>96</v>
+      </c>
+      <c r="D423" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="E423" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F423" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="G423" s="108">
+        <v>0.46875</v>
+      </c>
+      <c r="H423" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="I423" s="108">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="J423" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="K423" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="L423" s="119" t="s">
+        <v>58</v>
+      </c>
+      <c r="M423" s="108">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="424" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A424" s="187" t="s">
+        <v>14</v>
+      </c>
+      <c r="B424" s="42" t="s">
+        <v>438</v>
+      </c>
+      <c r="C424" s="148" t="s">
+        <v>29</v>
+      </c>
+      <c r="D424" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="E424" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F424" s="48">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="G424" s="108">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="H424" s="118">
+        <v>0.65625</v>
+      </c>
+      <c r="I424" s="108">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="J424" s="48">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="K424" s="108">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="L424" s="118">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="M424" s="108">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="425" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A425" s="187"/>
+      <c r="B425" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="C425" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="D425" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E425" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F425" s="48">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="G425" s="109" t="s">
+        <v>38</v>
+      </c>
+      <c r="H425" s="118">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="I425" s="109" t="s">
+        <v>38</v>
+      </c>
+      <c r="J425" s="48">
+        <v>0.8125</v>
+      </c>
+      <c r="K425" s="108">
+        <v>0.875</v>
+      </c>
+      <c r="L425" s="118">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="M425" s="109" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="426" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A426" s="188"/>
+      <c r="B426" s="189"/>
+      <c r="C426" s="190"/>
+      <c r="D426" s="100"/>
+      <c r="E426" s="102"/>
+      <c r="F426" s="56"/>
+      <c r="G426" s="110"/>
+      <c r="H426" s="120"/>
+      <c r="I426" s="110"/>
+      <c r="J426" s="56"/>
+      <c r="K426" s="110"/>
+      <c r="L426" s="120"/>
+      <c r="M426" s="110"/>
+    </row>
+    <row r="427" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A427" s="191"/>
+      <c r="B427" s="172" t="s">
+        <v>257</v>
+      </c>
+      <c r="C427" s="192" t="s">
+        <v>259</v>
+      </c>
+      <c r="D427" s="172">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E427" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F427" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="G427" s="61" t="s">
+        <v>25</v>
+      </c>
+      <c r="H427" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="I427" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="J427" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="K427" s="61" t="s">
+        <v>56</v>
+      </c>
+      <c r="L427" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="M427" s="61" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="428" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A428" s="199">
+        <v>46198</v>
+      </c>
+      <c r="B428" s="173" t="s">
+        <v>440</v>
+      </c>
+      <c r="C428" s="185" t="s">
+        <v>96</v>
+      </c>
+      <c r="D428" s="173" t="s">
+        <v>140</v>
+      </c>
+      <c r="E428" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F428" s="14">
+        <v>0.3125</v>
+      </c>
+      <c r="G428" s="15">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H428" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I428" s="15">
+        <v>0.46875</v>
+      </c>
+      <c r="J428" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K428" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="L428" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="M428" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="429" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A429" s="199" t="s">
+        <v>32</v>
+      </c>
+      <c r="B429" s="173" t="s">
+        <v>441</v>
+      </c>
+      <c r="C429" s="185" t="s">
+        <v>52</v>
+      </c>
+      <c r="D429" s="173">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="E429" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F429" s="18">
+        <v>0.6875</v>
+      </c>
+      <c r="G429" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H429" s="16">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="I429" s="15">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="J429" s="18">
+        <v>0.6875</v>
+      </c>
+      <c r="K429" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="L429" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="M429" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="430" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A430" s="198"/>
+      <c r="B430" s="173"/>
+      <c r="C430" s="185"/>
+      <c r="D430" s="173"/>
+      <c r="E430" s="176"/>
+      <c r="F430" s="18"/>
+      <c r="G430" s="15"/>
+      <c r="H430" s="16"/>
+      <c r="I430" s="15"/>
+      <c r="J430" s="18"/>
+      <c r="K430" s="15"/>
+      <c r="L430" s="16"/>
+      <c r="M430" s="15"/>
+    </row>
+    <row r="431" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A431" s="198"/>
+      <c r="B431" s="173"/>
+      <c r="C431" s="185"/>
+      <c r="D431" s="173"/>
+      <c r="E431" s="176"/>
+      <c r="F431" s="28"/>
+      <c r="G431" s="29"/>
+      <c r="H431" s="69"/>
+      <c r="I431" s="29"/>
+      <c r="J431" s="28"/>
+      <c r="K431" s="29"/>
+      <c r="L431" s="69"/>
+      <c r="M431" s="29"/>
+    </row>
+    <row r="432" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A432" s="186"/>
+      <c r="B432" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="C432" s="147" t="s">
+        <v>136</v>
+      </c>
+      <c r="D432" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E432" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F432" s="156">
+        <v>0.9375</v>
+      </c>
+      <c r="G432" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="H432" s="200">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="I432" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="J432" s="156">
+        <v>0.875</v>
+      </c>
+      <c r="K432" s="96">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="L432" s="200">
+        <v>0.9375</v>
+      </c>
+      <c r="M432" s="37" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="433" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A433" s="187">
+        <v>46199</v>
+      </c>
+      <c r="B433" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C433" s="148">
+        <v>2.4</v>
+      </c>
+      <c r="D433" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E433" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F433" s="44" t="s">
+        <v>216</v>
+      </c>
+      <c r="G433" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="H433" s="88" t="s">
+        <v>216</v>
+      </c>
+      <c r="I433" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="J433" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="K433" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="L433" s="88" t="s">
+        <v>53</v>
+      </c>
+      <c r="M433" s="50" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="434" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A434" s="187" t="s">
+        <v>48</v>
+      </c>
+      <c r="B434" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="C434" s="148" t="s">
+        <v>96</v>
+      </c>
+      <c r="D434" s="42">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="E434" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F434" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="G434" s="45">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="H434" s="88" t="s">
+        <v>46</v>
+      </c>
+      <c r="I434" s="45">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="J434" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="K434" s="50">
+        <v>0.3125</v>
+      </c>
+      <c r="L434" s="88">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M434" s="45">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="435" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A435" s="187"/>
+      <c r="B435" s="42" t="s">
+        <v>444</v>
+      </c>
+      <c r="C435" s="148" t="s">
+        <v>252</v>
+      </c>
+      <c r="D435" s="42">
+        <v>0.78125</v>
+      </c>
+      <c r="E435" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F435" s="48">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G435" s="45">
+        <v>0.84375</v>
+      </c>
+      <c r="H435" s="46">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="I435" s="45">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="J435" s="48">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K435" s="45">
+        <v>0.75</v>
+      </c>
+      <c r="L435" s="46">
+        <v>0.625</v>
+      </c>
+      <c r="M435" s="45">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="436" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A436" s="197"/>
+      <c r="B436" s="54"/>
+      <c r="C436" s="150"/>
+      <c r="D436" s="54"/>
+      <c r="E436" s="55"/>
+      <c r="F436" s="56"/>
+      <c r="G436" s="57"/>
+      <c r="H436" s="54"/>
+      <c r="I436" s="57"/>
+      <c r="J436" s="56"/>
+      <c r="K436" s="57"/>
+      <c r="L436" s="54"/>
+      <c r="M436" s="57"/>
+    </row>
+    <row r="437" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A437" s="198"/>
+      <c r="B437" s="173" t="s">
+        <v>445</v>
+      </c>
+      <c r="C437" s="185" t="s">
+        <v>142</v>
+      </c>
+      <c r="D437" s="173" t="s">
+        <v>53</v>
+      </c>
+      <c r="E437" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F437" s="132">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="G437" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="H437" s="60">
+        <v>0</v>
+      </c>
+      <c r="I437" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="J437" s="132">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K437" s="244">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="L437" s="137">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="M437" s="61" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="438" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A438" s="193">
+        <v>46200</v>
+      </c>
+      <c r="B438" s="173" t="s">
+        <v>446</v>
+      </c>
+      <c r="C438" s="185" t="s">
+        <v>132</v>
+      </c>
+      <c r="D438" s="173">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E438" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F438" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G438" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="H438" s="84" t="s">
+        <v>44</v>
+      </c>
+      <c r="I438" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="J438" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="K438" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="L438" s="84" t="s">
+        <v>216</v>
+      </c>
+      <c r="M438" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="439" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A439" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="B439" s="173" t="s">
+        <v>447</v>
+      </c>
+      <c r="C439" s="185" t="s">
+        <v>96</v>
+      </c>
+      <c r="D439" s="173" t="s">
+        <v>30</v>
+      </c>
+      <c r="E439" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F439" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G439" s="63">
+        <v>0.53125</v>
+      </c>
+      <c r="H439" s="84" t="s">
+        <v>59</v>
+      </c>
+      <c r="I439" s="15">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="J439" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="K439" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="L439" s="84" t="s">
+        <v>59</v>
+      </c>
+      <c r="M439" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="440" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A440" s="194"/>
+      <c r="B440" s="173" t="s">
+        <v>448</v>
+      </c>
+      <c r="C440" s="185" t="s">
+        <v>147</v>
+      </c>
+      <c r="D440" s="173">
+        <v>0.8125</v>
+      </c>
+      <c r="E440" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F440" s="18" t="s">
+        <v>458</v>
+      </c>
+      <c r="G440" s="63">
+        <v>0.875</v>
+      </c>
+      <c r="H440" s="16">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="I440" s="15">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J440" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="K440" s="63">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L440" s="16">
+        <v>0.6875</v>
+      </c>
+      <c r="M440" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+    </row>
+    <row r="441" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A441" s="194"/>
+      <c r="B441" s="173"/>
+      <c r="C441" s="185"/>
+      <c r="D441" s="173"/>
+      <c r="E441" s="176"/>
+      <c r="F441" s="28"/>
+      <c r="G441" s="30"/>
+      <c r="H441" s="69"/>
+      <c r="I441" s="29"/>
+      <c r="J441" s="28"/>
+      <c r="K441" s="30"/>
+      <c r="L441" s="69"/>
+      <c r="M441" s="29"/>
+    </row>
+    <row r="442" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A442" s="195"/>
+      <c r="B442" s="34" t="s">
+        <v>449</v>
+      </c>
+      <c r="C442" s="147" t="s">
+        <v>183</v>
+      </c>
+      <c r="D442" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="E442" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F442" s="36">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="G442" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="H442" s="72">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="I442" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="J442" s="156">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="K442" s="96">
+        <v>0</v>
+      </c>
+      <c r="L442" s="72">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="M442" s="37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="443" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A443" s="196">
+        <v>46201</v>
+      </c>
+      <c r="B443" s="42" t="s">
+        <v>450</v>
+      </c>
+      <c r="C443" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="D443" s="42">
+        <v>0.3125</v>
+      </c>
+      <c r="E443" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F443" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="G443" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="H443" s="99" t="s">
+        <v>3</v>
+      </c>
+      <c r="I443" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J443" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="K443" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="L443" s="99" t="s">
+        <v>3</v>
+      </c>
+      <c r="M443" s="50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="444" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A444" s="196" t="s">
+        <v>73</v>
+      </c>
+      <c r="B444" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="C444" s="148" t="s">
+        <v>96</v>
+      </c>
+      <c r="D444" s="42">
+        <v>0.5</v>
+      </c>
+      <c r="E444" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F444" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="G444" s="45">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H444" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="I444" s="45">
+        <v>0.53125</v>
+      </c>
+      <c r="J444" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="K444" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="L444" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="M444" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="445" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A445" s="187"/>
+      <c r="B445" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="C445" s="148" t="s">
+        <v>117</v>
+      </c>
+      <c r="D445" s="42">
+        <v>0.84375</v>
+      </c>
+      <c r="E445" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F445" s="48">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="G445" s="45">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="H445" s="75">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I445" s="45">
+        <v>0.875</v>
+      </c>
+      <c r="J445" s="48">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="K445" s="45">
+        <v>0.8125</v>
+      </c>
+      <c r="L445" s="75">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M445" s="45">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="446" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A446" s="197"/>
+      <c r="B446" s="54"/>
+      <c r="C446" s="150"/>
+      <c r="D446" s="54"/>
+      <c r="E446" s="55"/>
+      <c r="F446" s="56"/>
+      <c r="G446" s="57"/>
+      <c r="H446" s="80"/>
+      <c r="I446" s="57"/>
+      <c r="J446" s="56"/>
+      <c r="K446" s="57"/>
+      <c r="L446" s="80"/>
+      <c r="M446" s="57"/>
+    </row>
+    <row r="447" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A447" s="198"/>
+      <c r="B447" s="173" t="s">
+        <v>452</v>
+      </c>
+      <c r="C447" s="185" t="s">
+        <v>96</v>
+      </c>
+      <c r="D447" s="173" t="s">
+        <v>229</v>
+      </c>
+      <c r="E447" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F447" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="G447" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="H447" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="I447" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="J447" s="132">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="K447" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="L447" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="M447" s="61" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="448" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A448" s="198">
+        <v>46202</v>
+      </c>
+      <c r="B448" s="173" t="s">
+        <v>278</v>
+      </c>
+      <c r="C448" s="185" t="s">
+        <v>132</v>
+      </c>
+      <c r="D448" s="173">
+        <v>0.34375</v>
+      </c>
+      <c r="E448" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F448" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G448" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H448" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="I448" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J448" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="K448" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="L448" s="84" t="s">
+        <v>459</v>
+      </c>
+      <c r="M448" s="22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="449" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A449" s="198" t="s">
+        <v>82</v>
+      </c>
+      <c r="B449" s="173" t="s">
+        <v>453</v>
+      </c>
+      <c r="C449" s="185" t="s">
+        <v>190</v>
+      </c>
+      <c r="D449" s="173" t="s">
+        <v>72</v>
+      </c>
+      <c r="E449" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F449" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G449" s="15">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H449" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I449" s="15">
+        <v>0.5625</v>
+      </c>
+      <c r="J449" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="K449" s="15">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="L449" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M449" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="450" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A450" s="198"/>
+      <c r="B450" s="173" t="s">
+        <v>454</v>
+      </c>
+      <c r="C450" s="185" t="s">
+        <v>364</v>
+      </c>
+      <c r="D450" s="173" t="s">
+        <v>51</v>
+      </c>
+      <c r="E450" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F450" s="18">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G450" s="15">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="H450" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="I450" s="15">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="J450" s="18">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K450" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L450" s="16">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M450" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+    </row>
+    <row r="451" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A451" s="198"/>
+      <c r="B451" s="173"/>
+      <c r="C451" s="185"/>
+      <c r="D451" s="173"/>
+      <c r="E451" s="176"/>
+      <c r="F451" s="85"/>
+      <c r="G451" s="87"/>
+      <c r="H451" s="85"/>
+      <c r="I451" s="87"/>
+      <c r="J451" s="85"/>
+      <c r="K451" s="87"/>
+      <c r="L451" s="85"/>
+      <c r="M451" s="87"/>
+    </row>
+    <row r="452" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A452" s="186"/>
+      <c r="B452" s="34" t="s">
+        <v>455</v>
+      </c>
+      <c r="C452" s="147" t="s">
+        <v>190</v>
+      </c>
+      <c r="D452" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E452" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F452" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="G452" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="H452" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="I452" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="J452" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="K452" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="L452" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="M452" s="37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="453" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A453" s="187">
+        <v>46203</v>
+      </c>
+      <c r="B453" s="42" t="s">
+        <v>387</v>
+      </c>
+      <c r="C453" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="D453" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="E453" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F453" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="G453" s="45">
+        <v>0.4375</v>
+      </c>
+      <c r="H453" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="I453" s="45">
+        <v>0.4375</v>
+      </c>
+      <c r="J453" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="K453" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="L453" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="M453" s="50" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="454" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A454" s="187" t="s">
+        <v>91</v>
+      </c>
+      <c r="B454" s="42" t="s">
+        <v>456</v>
+      </c>
+      <c r="C454" s="148" t="s">
+        <v>190</v>
+      </c>
+      <c r="D454" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="E454" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F454" s="48">
+        <v>0.4375</v>
+      </c>
+      <c r="G454" s="45">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H454" s="46">
+        <v>0.4375</v>
+      </c>
+      <c r="I454" s="45">
+        <v>0.5625</v>
+      </c>
+      <c r="J454" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="K454" s="45">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L454" s="46">
+        <v>0.4375</v>
+      </c>
+      <c r="M454" s="45">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="455" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A455" s="187"/>
+      <c r="B455" s="42" t="s">
+        <v>457</v>
+      </c>
+      <c r="C455" s="148" t="s">
+        <v>124</v>
+      </c>
+      <c r="D455" s="42">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="E455" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F455" s="48">
+        <v>0.8125</v>
+      </c>
+      <c r="G455" s="45">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="H455" s="46">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I455" s="45">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="J455" s="48">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K455" s="45">
+        <v>0.875</v>
+      </c>
+      <c r="L455" s="46">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M455" s="45">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="456" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A456" s="197"/>
+      <c r="B456" s="54"/>
+      <c r="C456" s="150"/>
+      <c r="D456" s="54"/>
+      <c r="E456" s="55"/>
+      <c r="F456" s="56"/>
+      <c r="G456" s="57"/>
+      <c r="H456" s="54"/>
+      <c r="I456" s="57"/>
+      <c r="J456" s="56"/>
+      <c r="K456" s="57"/>
+      <c r="L456" s="54"/>
+      <c r="M456" s="57"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_window.xlsx
+++ b/data_window.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DuAnTrucDH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A864A61-A9A9-4712-94EB-125F65BBA78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F41A762-9B26-4F41-A17E-9BAC8AFB60AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{15CB32D3-DB1A-4542-B1F9-BD2C57A25BCC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{15CB32D3-DB1A-4542-B1F9-BD2C57A25BCC}"/>
   </bookViews>
   <sheets>
     <sheet name="WindowCL" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4395" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6010" uniqueCount="547">
   <si>
     <t>Date</t>
   </si>
@@ -1417,6 +1417,267 @@
   </si>
   <si>
     <t>04;30</t>
+  </si>
+  <si>
+    <t>03:51</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>20:52</t>
+  </si>
+  <si>
+    <t>04:24</t>
+  </si>
+  <si>
+    <t>13:47</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>09:51</t>
+  </si>
+  <si>
+    <t>14:24</t>
+  </si>
+  <si>
+    <t>21:59</t>
+  </si>
+  <si>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>10:29</t>
+  </si>
+  <si>
+    <t>15:03</t>
+  </si>
+  <si>
+    <t>22:32</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>15:47</t>
+  </si>
+  <si>
+    <t>23:06</t>
+  </si>
+  <si>
+    <t>16:42</t>
+  </si>
+  <si>
+    <t>23:42</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>17:58</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>07:13</t>
+  </si>
+  <si>
+    <t>13:44</t>
+  </si>
+  <si>
+    <t>01:06</t>
+  </si>
+  <si>
+    <t>14:49</t>
+  </si>
+  <si>
+    <t>02:02</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>15:56</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>03:22</t>
+  </si>
+  <si>
+    <t>09:12</t>
+  </si>
+  <si>
+    <t>17:02</t>
+  </si>
+  <si>
+    <t>05:04</t>
+  </si>
+  <si>
+    <t>10:06</t>
+  </si>
+  <si>
+    <t>01:47</t>
+  </si>
+  <si>
+    <t>06:26</t>
+  </si>
+  <si>
+    <t>11:02</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>02:38</t>
+  </si>
+  <si>
+    <t>07:24</t>
+  </si>
+  <si>
+    <t>11:58</t>
+  </si>
+  <si>
+    <t>08:13</t>
+  </si>
+  <si>
+    <t>20:32</t>
+  </si>
+  <si>
+    <t>04:01</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>21:17</t>
+  </si>
+  <si>
+    <t>04:38</t>
+  </si>
+  <si>
+    <t>09:42</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>10:27</t>
+  </si>
+  <si>
+    <t>22:38</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>11:13</t>
+  </si>
+  <si>
+    <t>16:33</t>
+  </si>
+  <si>
+    <t>12:02</t>
+  </si>
+  <si>
+    <t>23:51</t>
+  </si>
+  <si>
+    <t>06:38</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>19:09</t>
+  </si>
+  <si>
+    <t>07:04</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>20:53</t>
+  </si>
+  <si>
+    <t>01:01</t>
+  </si>
+  <si>
+    <t>07:33</t>
+  </si>
+  <si>
+    <t>22:42</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>01:26</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>18:06</t>
+  </si>
+  <si>
+    <t>18:49</t>
+  </si>
+  <si>
+    <t>02:31</t>
+  </si>
+  <si>
+    <t>07:17</t>
+  </si>
+  <si>
+    <t>19:27</t>
+  </si>
+  <si>
+    <t>02:57</t>
+  </si>
+  <si>
+    <t>07:51</t>
+  </si>
+  <si>
+    <t>20:02</t>
+  </si>
+  <si>
+    <t>08:23</t>
+  </si>
+  <si>
+    <t>13:09</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>13:49</t>
+  </si>
+  <si>
+    <t>21:06</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -1429,7 +1690,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="dd/mm"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1480,6 +1741,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1507,7 +1783,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -1857,12 +2133,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="329">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2584,6 +2950,258 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2919,7 +3537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9098970E-F68E-4060-9535-B4D7609639E2}">
-  <dimension ref="A1:I456"/>
+  <dimension ref="A1:I611"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.75" customWidth="1"/>
@@ -13965,6 +14583,3755 @@
       <c r="H456" s="54"/>
       <c r="I456" s="57"/>
     </row>
+    <row r="457" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A457" s="1"/>
+      <c r="B457" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C457" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D457" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E457" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F457" s="245" t="s">
+        <v>8</v>
+      </c>
+      <c r="G457" s="246" t="s">
+        <v>59</v>
+      </c>
+      <c r="H457" s="247" t="s">
+        <v>56</v>
+      </c>
+      <c r="I457" s="246" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A458" s="62">
+        <v>46204</v>
+      </c>
+      <c r="B458" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="C458" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D458" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E458" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F458" s="248" t="s">
+        <v>59</v>
+      </c>
+      <c r="G458" s="249">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H458" s="250" t="s">
+        <v>59</v>
+      </c>
+      <c r="I458" s="249">
+        <v>0.55208333333333337</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A459" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B459" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="C459" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D459" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E459" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F459" s="251">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="G459" s="249">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="H459" s="252">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="I459" s="249">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="460" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A460" s="65"/>
+      <c r="B460" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="C460" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D460" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E460" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F460" s="251">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="G460" s="253" t="s">
+        <v>53</v>
+      </c>
+      <c r="H460" s="252">
+        <v>0.96875</v>
+      </c>
+      <c r="I460" s="253" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A461" s="67"/>
+      <c r="B461" s="24"/>
+      <c r="C461" s="25"/>
+      <c r="D461" s="26"/>
+      <c r="E461" s="27"/>
+      <c r="F461" s="254"/>
+      <c r="G461" s="255"/>
+      <c r="H461" s="256"/>
+      <c r="I461" s="255"/>
+    </row>
+    <row r="462" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A462" s="31"/>
+      <c r="B462" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="C462" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="D462" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="E462" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F462" s="257" t="s">
+        <v>42</v>
+      </c>
+      <c r="G462" s="258" t="s">
+        <v>13</v>
+      </c>
+      <c r="H462" s="259" t="s">
+        <v>8</v>
+      </c>
+      <c r="I462" s="258" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A463" s="39">
+        <v>46205</v>
+      </c>
+      <c r="B463" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C463" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="D463" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E463" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F463" s="260" t="s">
+        <v>13</v>
+      </c>
+      <c r="G463" s="261">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H463" s="262" t="s">
+        <v>13</v>
+      </c>
+      <c r="I463" s="261">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A464" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B464" s="40" t="s">
+        <v>465</v>
+      </c>
+      <c r="C464" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="D464" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="E464" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F464" s="263">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G464" s="261">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H464" s="264">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I464" s="261">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="465" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A465" s="49"/>
+      <c r="B465" s="40" t="s">
+        <v>342</v>
+      </c>
+      <c r="C465" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D465" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E465" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F465" s="263">
+        <v>0.96875</v>
+      </c>
+      <c r="G465" s="265" t="s">
+        <v>148</v>
+      </c>
+      <c r="H465" s="264">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="I465" s="265" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A466" s="51"/>
+      <c r="B466" s="52"/>
+      <c r="C466" s="53"/>
+      <c r="D466" s="54"/>
+      <c r="E466" s="55"/>
+      <c r="F466" s="266"/>
+      <c r="G466" s="267"/>
+      <c r="H466" s="268"/>
+      <c r="I466" s="267"/>
+    </row>
+    <row r="467" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A467" s="1"/>
+      <c r="B467" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C467" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D467" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E467" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F467" s="269">
+        <v>0.26041666666666669</v>
+      </c>
+      <c r="G467" s="270" t="s">
+        <v>13</v>
+      </c>
+      <c r="H467" s="271" t="s">
+        <v>6</v>
+      </c>
+      <c r="I467" s="272">
+        <v>0.38541666666666669</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A468" s="62">
+        <v>46206</v>
+      </c>
+      <c r="B468" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="C468" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D468" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E468" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F468" s="248" t="s">
+        <v>13</v>
+      </c>
+      <c r="G468" s="273">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="H468" s="250" t="s">
+        <v>13</v>
+      </c>
+      <c r="I468" s="249">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="469" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A469" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B469" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="C469" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D469" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E469" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F469" s="251">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="G469" s="273">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="H469" s="274">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I469" s="249">
+        <v>0.78125</v>
+      </c>
+    </row>
+    <row r="470" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A470" s="65"/>
+      <c r="B470" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="C470" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="D470" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E470" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F470" s="251">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="G470" s="275" t="s">
+        <v>24</v>
+      </c>
+      <c r="H470" s="250" t="s">
+        <v>21</v>
+      </c>
+      <c r="I470" s="253" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="471" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A471" s="67"/>
+      <c r="B471" s="24"/>
+      <c r="C471" s="68"/>
+      <c r="D471" s="26"/>
+      <c r="E471" s="27"/>
+      <c r="F471" s="254"/>
+      <c r="G471" s="256"/>
+      <c r="H471" s="276"/>
+      <c r="I471" s="255"/>
+    </row>
+    <row r="472" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A472" s="31"/>
+      <c r="B472" s="34" t="s">
+        <v>470</v>
+      </c>
+      <c r="C472" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="D472" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E472" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F472" s="257" t="s">
+        <v>45</v>
+      </c>
+      <c r="G472" s="277">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="H472" s="278" t="s">
+        <v>55</v>
+      </c>
+      <c r="I472" s="277">
+        <v>0.44791666666666669</v>
+      </c>
+    </row>
+    <row r="473" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A473" s="73">
+        <v>46207</v>
+      </c>
+      <c r="B473" s="42" t="s">
+        <v>471</v>
+      </c>
+      <c r="C473" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="D473" s="42" t="s">
+        <v>310</v>
+      </c>
+      <c r="E473" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F473" s="263">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="G473" s="261">
+        <v>0.625</v>
+      </c>
+      <c r="H473" s="279">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="I473" s="261">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="474" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A474" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B474" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="C474" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="D474" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E474" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F474" s="263">
+        <v>0.625</v>
+      </c>
+      <c r="G474" s="261">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="H474" s="279">
+        <v>0.625</v>
+      </c>
+      <c r="I474" s="261">
+        <v>0.80208333333333337</v>
+      </c>
+    </row>
+    <row r="475" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A475" s="77"/>
+      <c r="B475" s="42" t="s">
+        <v>473</v>
+      </c>
+      <c r="C475" s="74" t="s">
+        <v>117</v>
+      </c>
+      <c r="D475" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="E475" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F475" s="260" t="s">
+        <v>21</v>
+      </c>
+      <c r="G475" s="265" t="s">
+        <v>229</v>
+      </c>
+      <c r="H475" s="280" t="s">
+        <v>38</v>
+      </c>
+      <c r="I475" s="265" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="476" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A476" s="78"/>
+      <c r="B476" s="54"/>
+      <c r="C476" s="79"/>
+      <c r="D476" s="54"/>
+      <c r="E476" s="55"/>
+      <c r="F476" s="266"/>
+      <c r="G476" s="267"/>
+      <c r="H476" s="281"/>
+      <c r="I476" s="267"/>
+    </row>
+    <row r="477" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A477" s="81"/>
+      <c r="B477" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C477" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D477" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E477" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F477" s="269" t="s">
+        <v>43</v>
+      </c>
+      <c r="G477" s="282">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H477" s="271" t="s">
+        <v>45</v>
+      </c>
+      <c r="I477" s="282">
+        <v>0.44791666666666669</v>
+      </c>
+    </row>
+    <row r="478" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A478" s="82">
+        <v>46208</v>
+      </c>
+      <c r="B478" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="C478" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D478" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E478" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F478" s="251">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G478" s="249">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H478" s="274">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I478" s="249">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="479" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A479" s="83" t="s">
+        <v>73</v>
+      </c>
+      <c r="B479" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="C479" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D479" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E479" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F479" s="251">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="G479" s="249">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="H479" s="274">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="I479" s="249">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="480" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A480" s="65"/>
+      <c r="B480" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="C480" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D480" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="E480" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F480" s="248" t="s">
+        <v>85</v>
+      </c>
+      <c r="G480" s="253" t="s">
+        <v>176</v>
+      </c>
+      <c r="H480" s="250" t="s">
+        <v>39</v>
+      </c>
+      <c r="I480" s="253" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="481" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A481" s="67"/>
+      <c r="B481" s="24"/>
+      <c r="C481" s="68"/>
+      <c r="D481" s="26"/>
+      <c r="E481" s="27"/>
+      <c r="F481" s="283"/>
+      <c r="G481" s="284"/>
+      <c r="H481" s="283"/>
+      <c r="I481" s="284"/>
+    </row>
+    <row r="482" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A482" s="31"/>
+      <c r="B482" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C482" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="D482" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E482" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F482" s="257">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="G482" s="277">
+        <v>0.46875</v>
+      </c>
+      <c r="H482" s="259" t="s">
+        <v>68</v>
+      </c>
+      <c r="I482" s="277">
+        <v>0.44791666666666669</v>
+      </c>
+    </row>
+    <row r="483" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A483" s="39">
+        <v>46209</v>
+      </c>
+      <c r="B483" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="C483" s="74" t="s">
+        <v>71</v>
+      </c>
+      <c r="D483" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="E483" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F483" s="263">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G483" s="261">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H483" s="264">
+        <v>0.5625</v>
+      </c>
+      <c r="I483" s="261">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="484" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A484" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B484" s="42" t="s">
+        <v>478</v>
+      </c>
+      <c r="C484" s="74" t="s">
+        <v>158</v>
+      </c>
+      <c r="D484" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="E484" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F484" s="263">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G484" s="261">
+        <v>0.90625</v>
+      </c>
+      <c r="H484" s="264">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I484" s="261">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="485" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A485" s="49"/>
+      <c r="B485" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="C485" s="74" t="s">
+        <v>195</v>
+      </c>
+      <c r="D485" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="E485" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F485" s="260" t="s">
+        <v>38</v>
+      </c>
+      <c r="G485" s="265" t="s">
+        <v>163</v>
+      </c>
+      <c r="H485" s="262" t="s">
+        <v>7</v>
+      </c>
+      <c r="I485" s="265" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="486" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A486" s="51"/>
+      <c r="B486" s="54"/>
+      <c r="C486" s="79"/>
+      <c r="D486" s="54"/>
+      <c r="E486" s="55"/>
+      <c r="F486" s="266"/>
+      <c r="G486" s="267"/>
+      <c r="H486" s="268"/>
+      <c r="I486" s="267"/>
+    </row>
+    <row r="487" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A487" s="1"/>
+      <c r="B487" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C487" s="90" t="s">
+        <v>190</v>
+      </c>
+      <c r="D487" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E487" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F487" s="269" t="s">
+        <v>57</v>
+      </c>
+      <c r="G487" s="282">
+        <v>0.5</v>
+      </c>
+      <c r="H487" s="271" t="s">
+        <v>58</v>
+      </c>
+      <c r="I487" s="282">
+        <v>0.46875</v>
+      </c>
+    </row>
+    <row r="488" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A488" s="62">
+        <v>46210</v>
+      </c>
+      <c r="B488" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="C488" s="93" t="s">
+        <v>249</v>
+      </c>
+      <c r="D488" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E488" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F488" s="251">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="G488" s="249">
+        <v>0.75</v>
+      </c>
+      <c r="H488" s="274">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I488" s="249">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="489" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A489" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B489" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="C489" s="93" t="s">
+        <v>98</v>
+      </c>
+      <c r="D489" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E489" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F489" s="251">
+        <v>0.75</v>
+      </c>
+      <c r="G489" s="249">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="H489" s="274">
+        <v>0.75</v>
+      </c>
+      <c r="I489" s="249">
+        <v>0.92708333333333337</v>
+      </c>
+    </row>
+    <row r="490" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A490" s="65"/>
+      <c r="B490" s="12"/>
+      <c r="C490" s="93"/>
+      <c r="D490" s="12"/>
+      <c r="E490" s="13"/>
+      <c r="F490" s="251"/>
+      <c r="G490" s="249"/>
+      <c r="H490" s="274"/>
+      <c r="I490" s="249"/>
+    </row>
+    <row r="491" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A491" s="67"/>
+      <c r="B491" s="26"/>
+      <c r="C491" s="94"/>
+      <c r="D491" s="26"/>
+      <c r="E491" s="27"/>
+      <c r="F491" s="254"/>
+      <c r="G491" s="255"/>
+      <c r="H491" s="276"/>
+      <c r="I491" s="255"/>
+    </row>
+    <row r="492" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A492" s="31"/>
+      <c r="B492" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="C492" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="D492" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E492" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F492" s="257" t="s">
+        <v>22</v>
+      </c>
+      <c r="G492" s="258" t="s">
+        <v>170</v>
+      </c>
+      <c r="H492" s="278" t="s">
+        <v>53</v>
+      </c>
+      <c r="I492" s="258" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="493" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A493" s="39">
+        <v>46211</v>
+      </c>
+      <c r="B493" s="42" t="s">
+        <v>483</v>
+      </c>
+      <c r="C493" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="D493" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E493" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F493" s="260" t="s">
+        <v>46</v>
+      </c>
+      <c r="G493" s="261">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="H493" s="280" t="s">
+        <v>57</v>
+      </c>
+      <c r="I493" s="261">
+        <v>0.48958333333333331</v>
+      </c>
+    </row>
+    <row r="494" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A494" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B494" s="42" t="s">
+        <v>484</v>
+      </c>
+      <c r="C494" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="D494" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E494" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F494" s="263">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="G494" s="261">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H494" s="279">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="I494" s="265" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="495" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A495" s="49"/>
+      <c r="B495" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="C495" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D495" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="E495" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F495" s="263">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G495" s="265" t="s">
+        <v>21</v>
+      </c>
+      <c r="H495" s="279">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I495" s="265" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="496" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A496" s="51"/>
+      <c r="B496" s="100"/>
+      <c r="C496" s="101"/>
+      <c r="D496" s="100"/>
+      <c r="E496" s="102"/>
+      <c r="F496" s="266"/>
+      <c r="G496" s="267"/>
+      <c r="H496" s="281"/>
+      <c r="I496" s="267"/>
+    </row>
+    <row r="497" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A497" s="1"/>
+      <c r="B497" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C497" s="90" t="s">
+        <v>60</v>
+      </c>
+      <c r="D497" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E497" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F497" s="245" t="s">
+        <v>21</v>
+      </c>
+      <c r="G497" s="285" t="s">
+        <v>55</v>
+      </c>
+      <c r="H497" s="245" t="s">
+        <v>21</v>
+      </c>
+      <c r="I497" s="285" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="498" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A498" s="62">
+        <v>46212</v>
+      </c>
+      <c r="B498" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C498" s="93" t="s">
+        <v>190</v>
+      </c>
+      <c r="D498" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E498" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F498" s="248" t="s">
+        <v>69</v>
+      </c>
+      <c r="G498" s="286">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H498" s="248" t="s">
+        <v>70</v>
+      </c>
+      <c r="I498" s="286">
+        <v>0.51041666666666663</v>
+      </c>
+    </row>
+    <row r="499" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A499" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="B499" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="C499" s="93" t="s">
+        <v>36</v>
+      </c>
+      <c r="D499" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E499" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F499" s="251">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="G499" s="286">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="H499" s="251">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="I499" s="286">
+        <v>0.88541666666666663</v>
+      </c>
+    </row>
+    <row r="500" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A500" s="65"/>
+      <c r="B500" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C500" s="93" t="s">
+        <v>132</v>
+      </c>
+      <c r="D500" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E500" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F500" s="251">
+        <v>0.90625</v>
+      </c>
+      <c r="G500" s="287" t="s">
+        <v>216</v>
+      </c>
+      <c r="H500" s="251">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="I500" s="287" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="501" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A501" s="67"/>
+      <c r="B501" s="26"/>
+      <c r="C501" s="94"/>
+      <c r="D501" s="26"/>
+      <c r="E501" s="27"/>
+      <c r="F501" s="254"/>
+      <c r="G501" s="288"/>
+      <c r="H501" s="254"/>
+      <c r="I501" s="288"/>
+    </row>
+    <row r="502" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A502" s="31"/>
+      <c r="B502" s="34" t="s">
+        <v>487</v>
+      </c>
+      <c r="C502" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="D502" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E502" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F502" s="257" t="s">
+        <v>216</v>
+      </c>
+      <c r="G502" s="289" t="s">
+        <v>46</v>
+      </c>
+      <c r="H502" s="257" t="s">
+        <v>216</v>
+      </c>
+      <c r="I502" s="289" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="503" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A503" s="39">
+        <v>46213</v>
+      </c>
+      <c r="B503" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="C503" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="D503" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="E503" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F503" s="260" t="s">
+        <v>59</v>
+      </c>
+      <c r="G503" s="290">
+        <v>0.5625</v>
+      </c>
+      <c r="H503" s="260" t="s">
+        <v>46</v>
+      </c>
+      <c r="I503" s="290">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="504" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A504" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B504" s="42" t="s">
+        <v>489</v>
+      </c>
+      <c r="C504" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="D504" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="E504" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F504" s="263">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="G504" s="290">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="H504" s="263">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="I504" s="290">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="505" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A505" s="49"/>
+      <c r="B505" s="42" t="s">
+        <v>490</v>
+      </c>
+      <c r="C505" s="74">
+        <v>2.8</v>
+      </c>
+      <c r="D505" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="E505" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F505" s="260" t="s">
+        <v>37</v>
+      </c>
+      <c r="G505" s="291" t="s">
+        <v>3</v>
+      </c>
+      <c r="H505" s="263">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="I505" s="291" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="506" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A506" s="51"/>
+      <c r="B506" s="54"/>
+      <c r="C506" s="79"/>
+      <c r="D506" s="54"/>
+      <c r="E506" s="55"/>
+      <c r="F506" s="266"/>
+      <c r="G506" s="292"/>
+      <c r="H506" s="266"/>
+      <c r="I506" s="292"/>
+    </row>
+    <row r="507" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A507" s="1"/>
+      <c r="B507" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C507" s="90" t="s">
+        <v>89</v>
+      </c>
+      <c r="D507" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E507" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F507" s="269" t="s">
+        <v>3</v>
+      </c>
+      <c r="G507" s="293" t="s">
+        <v>59</v>
+      </c>
+      <c r="H507" s="269" t="s">
+        <v>3</v>
+      </c>
+      <c r="I507" s="294" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="508" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A508" s="82">
+        <v>46214</v>
+      </c>
+      <c r="B508" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="C508" s="93" t="s">
+        <v>190</v>
+      </c>
+      <c r="D508" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E508" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F508" s="248" t="s">
+        <v>59</v>
+      </c>
+      <c r="G508" s="295">
+        <v>0.59375</v>
+      </c>
+      <c r="H508" s="248" t="s">
+        <v>59</v>
+      </c>
+      <c r="I508" s="286">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="509" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A509" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B509" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="C509" s="93">
+        <v>0.4</v>
+      </c>
+      <c r="D509" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E509" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F509" s="251">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="G509" s="295">
+        <v>0.96875</v>
+      </c>
+      <c r="H509" s="251">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I509" s="286">
+        <v>0.98958333333333337</v>
+      </c>
+    </row>
+    <row r="510" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A510" s="114"/>
+      <c r="B510" s="12"/>
+      <c r="C510" s="93"/>
+      <c r="D510" s="12"/>
+      <c r="E510" s="13"/>
+      <c r="F510" s="251"/>
+      <c r="G510" s="295"/>
+      <c r="H510" s="251"/>
+      <c r="I510" s="286"/>
+    </row>
+    <row r="511" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A511" s="125"/>
+      <c r="B511" s="26"/>
+      <c r="C511" s="94"/>
+      <c r="D511" s="26"/>
+      <c r="E511" s="27"/>
+      <c r="F511" s="254"/>
+      <c r="G511" s="296"/>
+      <c r="H511" s="254"/>
+      <c r="I511" s="288"/>
+    </row>
+    <row r="512" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A512" s="70"/>
+      <c r="B512" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C512" s="71" t="s">
+        <v>183</v>
+      </c>
+      <c r="D512" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="E512" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F512" s="257" t="s">
+        <v>39</v>
+      </c>
+      <c r="G512" s="289" t="s">
+        <v>8</v>
+      </c>
+      <c r="H512" s="297" t="s">
+        <v>38</v>
+      </c>
+      <c r="I512" s="289" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="513" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A513" s="73">
+        <v>46215</v>
+      </c>
+      <c r="B513" s="42" t="s">
+        <v>494</v>
+      </c>
+      <c r="C513" s="74" t="s">
+        <v>136</v>
+      </c>
+      <c r="D513" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E513" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F513" s="260" t="s">
+        <v>8</v>
+      </c>
+      <c r="G513" s="290">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H513" s="298" t="s">
+        <v>8</v>
+      </c>
+      <c r="I513" s="290">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="514" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A514" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="B514" s="42" t="s">
+        <v>495</v>
+      </c>
+      <c r="C514" s="74" t="s">
+        <v>87</v>
+      </c>
+      <c r="D514" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="E514" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F514" s="263">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G514" s="290">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H514" s="299">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I514" s="290">
+        <v>0.59375</v>
+      </c>
+    </row>
+    <row r="515" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A515" s="49"/>
+      <c r="B515" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C515" s="74" t="s">
+        <v>129</v>
+      </c>
+      <c r="D515" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="E515" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F515" s="263">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="G515" s="290">
+        <v>0.96875</v>
+      </c>
+      <c r="H515" s="299">
+        <v>0.84375</v>
+      </c>
+      <c r="I515" s="291" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="516" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A516" s="51"/>
+      <c r="B516" s="54"/>
+      <c r="C516" s="79"/>
+      <c r="D516" s="54"/>
+      <c r="E516" s="55"/>
+      <c r="F516" s="266"/>
+      <c r="G516" s="292"/>
+      <c r="H516" s="300"/>
+      <c r="I516" s="292"/>
+    </row>
+    <row r="517" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A517" s="1"/>
+      <c r="B517" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C517" s="90" t="s">
+        <v>87</v>
+      </c>
+      <c r="D517" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E517" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F517" s="269" t="s">
+        <v>26</v>
+      </c>
+      <c r="G517" s="294" t="s">
+        <v>25</v>
+      </c>
+      <c r="H517" s="269" t="s">
+        <v>5</v>
+      </c>
+      <c r="I517" s="294" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="518" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A518" s="62">
+        <v>46216</v>
+      </c>
+      <c r="B518" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="C518" s="93" t="s">
+        <v>136</v>
+      </c>
+      <c r="D518" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E518" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F518" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="G518" s="286">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H518" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="I518" s="286">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="519" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A519" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="B519" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="C519" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D519" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E519" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F519" s="251">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G519" s="286">
+        <v>0.65625</v>
+      </c>
+      <c r="H519" s="251">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I519" s="286">
+        <v>0.63541666666666663</v>
+      </c>
+    </row>
+    <row r="520" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A520" s="65"/>
+      <c r="B520" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="C520" s="93" t="s">
+        <v>325</v>
+      </c>
+      <c r="D520" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="E520" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F520" s="251">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="G520" s="286">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="H520" s="251">
+        <v>0.90625</v>
+      </c>
+      <c r="I520" s="287" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="521" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A521" s="67"/>
+      <c r="B521" s="26"/>
+      <c r="C521" s="94"/>
+      <c r="D521" s="26"/>
+      <c r="E521" s="27"/>
+      <c r="F521" s="283"/>
+      <c r="G521" s="284"/>
+      <c r="H521" s="283"/>
+      <c r="I521" s="284"/>
+    </row>
+    <row r="522" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A522" s="31"/>
+      <c r="B522" s="34" t="s">
+        <v>500</v>
+      </c>
+      <c r="C522" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D522" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="E522" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F522" s="257" t="s">
+        <v>176</v>
+      </c>
+      <c r="G522" s="289" t="s">
+        <v>43</v>
+      </c>
+      <c r="H522" s="257" t="s">
+        <v>44</v>
+      </c>
+      <c r="I522" s="289" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="523" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A523" s="39">
+        <v>46217</v>
+      </c>
+      <c r="B523" s="42" t="s">
+        <v>501</v>
+      </c>
+      <c r="C523" s="74" t="s">
+        <v>136</v>
+      </c>
+      <c r="D523" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="E523" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F523" s="260" t="s">
+        <v>43</v>
+      </c>
+      <c r="G523" s="290">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H523" s="260" t="s">
+        <v>43</v>
+      </c>
+      <c r="I523" s="290">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="524" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A524" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B524" s="42" t="s">
+        <v>502</v>
+      </c>
+      <c r="C524" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="D524" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="E524" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F524" s="263">
+        <v>0.53125</v>
+      </c>
+      <c r="G524" s="290">
+        <v>0.6875</v>
+      </c>
+      <c r="H524" s="263">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I524" s="290">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="525" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A525" s="49"/>
+      <c r="B525" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="C525" s="74" t="s">
+        <v>408</v>
+      </c>
+      <c r="D525" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="E525" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F525" s="263">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G525" s="291" t="s">
+        <v>85</v>
+      </c>
+      <c r="H525" s="263">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="I525" s="291" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="526" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A526" s="51"/>
+      <c r="B526" s="54"/>
+      <c r="C526" s="79"/>
+      <c r="D526" s="54"/>
+      <c r="E526" s="55"/>
+      <c r="F526" s="266"/>
+      <c r="G526" s="292"/>
+      <c r="H526" s="266"/>
+      <c r="I526" s="292"/>
+    </row>
+    <row r="527" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A527" s="1"/>
+      <c r="B527" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C527" s="90" t="s">
+        <v>16</v>
+      </c>
+      <c r="D527" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E527" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F527" s="269" t="s">
+        <v>6</v>
+      </c>
+      <c r="G527" s="294" t="s">
+        <v>57</v>
+      </c>
+      <c r="H527" s="269" t="s">
+        <v>8</v>
+      </c>
+      <c r="I527" s="294" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="528" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A528" s="62">
+        <v>46218</v>
+      </c>
+      <c r="B528" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="C528" s="93" t="s">
+        <v>98</v>
+      </c>
+      <c r="D528" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E528" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F528" s="248" t="s">
+        <v>57</v>
+      </c>
+      <c r="G528" s="286">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H528" s="248" t="s">
+        <v>46</v>
+      </c>
+      <c r="I528" s="286">
+        <v>0.55208333333333337</v>
+      </c>
+    </row>
+    <row r="529" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A529" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B529" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C529" s="93" t="s">
+        <v>41</v>
+      </c>
+      <c r="D529" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E529" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F529" s="251">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G529" s="286">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H529" s="251">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="I529" s="286">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="530" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A530" s="65"/>
+      <c r="B530" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="C530" s="93" t="s">
+        <v>408</v>
+      </c>
+      <c r="D530" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E530" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F530" s="251">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="G530" s="287" t="s">
+        <v>22</v>
+      </c>
+      <c r="H530" s="251">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="I530" s="287" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="531" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A531" s="67"/>
+      <c r="B531" s="26"/>
+      <c r="C531" s="94"/>
+      <c r="D531" s="26"/>
+      <c r="E531" s="27"/>
+      <c r="F531" s="254"/>
+      <c r="G531" s="288"/>
+      <c r="H531" s="254"/>
+      <c r="I531" s="288"/>
+    </row>
+    <row r="532" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A532" s="31"/>
+      <c r="B532" s="34" t="s">
+        <v>505</v>
+      </c>
+      <c r="C532" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="D532" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="E532" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F532" s="257">
+        <v>0.25</v>
+      </c>
+      <c r="G532" s="289" t="s">
+        <v>59</v>
+      </c>
+      <c r="H532" s="297">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="I532" s="289" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="533" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A533" s="39">
+        <v>46219</v>
+      </c>
+      <c r="B533" s="42" t="s">
+        <v>506</v>
+      </c>
+      <c r="C533" s="74">
+        <v>2.4</v>
+      </c>
+      <c r="D533" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E533" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F533" s="260" t="s">
+        <v>31</v>
+      </c>
+      <c r="G533" s="290">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H533" s="299">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I533" s="290">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="534" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A534" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B534" s="42" t="s">
+        <v>465</v>
+      </c>
+      <c r="C534" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="D534" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="E534" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F534" s="263">
+        <v>0.625</v>
+      </c>
+      <c r="G534" s="290">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="H534" s="299">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I534" s="290">
+        <v>0.73958333333333337</v>
+      </c>
+    </row>
+    <row r="535" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A535" s="49"/>
+      <c r="B535" s="42" t="s">
+        <v>507</v>
+      </c>
+      <c r="C535" s="74" t="s">
+        <v>317</v>
+      </c>
+      <c r="D535" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E535" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F535" s="301">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="G535" s="302" t="s">
+        <v>53</v>
+      </c>
+      <c r="H535" s="301" t="s">
+        <v>21</v>
+      </c>
+      <c r="I535" s="302" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="536" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A536" s="51"/>
+      <c r="B536" s="100"/>
+      <c r="C536" s="101"/>
+      <c r="D536" s="100"/>
+      <c r="E536" s="102"/>
+      <c r="F536" s="266"/>
+      <c r="G536" s="292"/>
+      <c r="H536" s="300"/>
+      <c r="I536" s="292"/>
+    </row>
+    <row r="537" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A537" s="1"/>
+      <c r="B537" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C537" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D537" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E537" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F537" s="245" t="s">
+        <v>55</v>
+      </c>
+      <c r="G537" s="285" t="s">
+        <v>13</v>
+      </c>
+      <c r="H537" s="245" t="s">
+        <v>42</v>
+      </c>
+      <c r="I537" s="285" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="538" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A538" s="62">
+        <v>46220</v>
+      </c>
+      <c r="B538" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="C538" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D538" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E538" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F538" s="251">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="G538" s="286">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H538" s="251">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I538" s="286">
+        <v>0.63541666666666663</v>
+      </c>
+    </row>
+    <row r="539" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A539" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B539" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C539" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D539" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E539" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F539" s="251">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="G539" s="286">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="H539" s="251">
+        <v>0.65625</v>
+      </c>
+      <c r="I539" s="286">
+        <v>0.78125</v>
+      </c>
+    </row>
+    <row r="540" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A540" s="65"/>
+      <c r="B540" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="C540" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="D540" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E540" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F540" s="248" t="s">
+        <v>77</v>
+      </c>
+      <c r="G540" s="287" t="s">
+        <v>26</v>
+      </c>
+      <c r="H540" s="248" t="s">
+        <v>85</v>
+      </c>
+      <c r="I540" s="287" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="541" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A541" s="67"/>
+      <c r="B541" s="24"/>
+      <c r="C541" s="25"/>
+      <c r="D541" s="26"/>
+      <c r="E541" s="27"/>
+      <c r="F541" s="254"/>
+      <c r="G541" s="288"/>
+      <c r="H541" s="254"/>
+      <c r="I541" s="288"/>
+    </row>
+    <row r="542" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A542" s="31"/>
+      <c r="B542" s="32" t="s">
+        <v>511</v>
+      </c>
+      <c r="C542" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D542" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E542" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F542" s="257">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G542" s="303">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H542" s="257" t="s">
+        <v>25</v>
+      </c>
+      <c r="I542" s="289" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="543" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A543" s="73">
+        <v>46221</v>
+      </c>
+      <c r="B543" s="40" t="s">
+        <v>512</v>
+      </c>
+      <c r="C543" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="D543" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="E543" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F543" s="263">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G543" s="290">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H543" s="263">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="I543" s="290">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="544" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A544" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B544" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="C544" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D544" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="E544" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F544" s="263">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G544" s="290">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="H544" s="263">
+        <v>0.6875</v>
+      </c>
+      <c r="I544" s="290">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="545" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A545" s="77"/>
+      <c r="B545" s="40" t="s">
+        <v>513</v>
+      </c>
+      <c r="C545" s="41" t="s">
+        <v>364</v>
+      </c>
+      <c r="D545" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="E545" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F545" s="260" t="s">
+        <v>85</v>
+      </c>
+      <c r="G545" s="291" t="s">
+        <v>229</v>
+      </c>
+      <c r="H545" s="260" t="s">
+        <v>22</v>
+      </c>
+      <c r="I545" s="291" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="546" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A546" s="78"/>
+      <c r="B546" s="52"/>
+      <c r="C546" s="53"/>
+      <c r="D546" s="54"/>
+      <c r="E546" s="55"/>
+      <c r="F546" s="266"/>
+      <c r="G546" s="292"/>
+      <c r="H546" s="266"/>
+      <c r="I546" s="292"/>
+    </row>
+    <row r="547" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A547" s="81"/>
+      <c r="B547" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C547" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D547" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E547" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F547" s="269" t="s">
+        <v>43</v>
+      </c>
+      <c r="G547" s="304">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="H547" s="269" t="s">
+        <v>45</v>
+      </c>
+      <c r="I547" s="305">
+        <v>0.42708333333333331</v>
+      </c>
+    </row>
+    <row r="548" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A548" s="82">
+        <v>46222</v>
+      </c>
+      <c r="B548" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="C548" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D548" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E548" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F548" s="251">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G548" s="295">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H548" s="251">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="I548" s="286">
+        <v>0.69791666666666663</v>
+      </c>
+    </row>
+    <row r="549" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A549" s="83" t="s">
+        <v>73</v>
+      </c>
+      <c r="B549" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="C549" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D549" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E549" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F549" s="251">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="G549" s="295">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="H549" s="251">
+        <v>0.71875</v>
+      </c>
+      <c r="I549" s="286">
+        <v>0.86458333333333337</v>
+      </c>
+    </row>
+    <row r="550" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A550" s="65"/>
+      <c r="B550" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="C550" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D550" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="E550" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F550" s="248" t="s">
+        <v>38</v>
+      </c>
+      <c r="G550" s="306" t="s">
+        <v>176</v>
+      </c>
+      <c r="H550" s="248" t="s">
+        <v>7</v>
+      </c>
+      <c r="I550" s="287" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="551" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A551" s="67"/>
+      <c r="B551" s="24"/>
+      <c r="C551" s="68"/>
+      <c r="D551" s="26"/>
+      <c r="E551" s="27"/>
+      <c r="F551" s="254"/>
+      <c r="G551" s="296"/>
+      <c r="H551" s="254"/>
+      <c r="I551" s="288"/>
+    </row>
+    <row r="552" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A552" s="31"/>
+      <c r="B552" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="C552" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="D552" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E552" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F552" s="257" t="s">
+        <v>58</v>
+      </c>
+      <c r="G552" s="303">
+        <v>0.46875</v>
+      </c>
+      <c r="H552" s="297" t="s">
+        <v>68</v>
+      </c>
+      <c r="I552" s="303">
+        <v>0.44791666666666669</v>
+      </c>
+    </row>
+    <row r="553" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A553" s="39">
+        <v>46223</v>
+      </c>
+      <c r="B553" s="40" t="s">
+        <v>517</v>
+      </c>
+      <c r="C553" s="74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D553" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="E553" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F553" s="263">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="G553" s="290">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H553" s="299">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I553" s="290">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="554" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A554" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B554" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="C554" s="74" t="s">
+        <v>158</v>
+      </c>
+      <c r="D554" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="E554" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F554" s="263">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="G554" s="290">
+        <v>0.9375</v>
+      </c>
+      <c r="H554" s="299">
+        <v>0.75</v>
+      </c>
+      <c r="I554" s="290">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="555" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A555" s="49"/>
+      <c r="B555" s="40" t="s">
+        <v>518</v>
+      </c>
+      <c r="C555" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="D555" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="E555" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F555" s="260" t="s">
+        <v>38</v>
+      </c>
+      <c r="G555" s="291" t="s">
+        <v>163</v>
+      </c>
+      <c r="H555" s="298" t="s">
+        <v>7</v>
+      </c>
+      <c r="I555" s="291" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="556" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A556" s="51"/>
+      <c r="B556" s="52"/>
+      <c r="C556" s="79"/>
+      <c r="D556" s="54"/>
+      <c r="E556" s="55"/>
+      <c r="F556" s="266"/>
+      <c r="G556" s="292"/>
+      <c r="H556" s="300"/>
+      <c r="I556" s="292"/>
+    </row>
+    <row r="557" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A557" s="1"/>
+      <c r="B557" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C557" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D557" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E557" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F557" s="269" t="s">
+        <v>78</v>
+      </c>
+      <c r="G557" s="305">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H557" s="269" t="s">
+        <v>43</v>
+      </c>
+      <c r="I557" s="305">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="558" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A558" s="62">
+        <v>46224</v>
+      </c>
+      <c r="B558" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="C558" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D558" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E558" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F558" s="251">
+        <v>0.59375</v>
+      </c>
+      <c r="G558" s="286">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H558" s="251">
+        <v>0.625</v>
+      </c>
+      <c r="I558" s="286">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="559" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A559" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B559" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="C559" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D559" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E559" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F559" s="251">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G559" s="286">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="H559" s="251">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I559" s="286">
+        <v>0.97916666666666663</v>
+      </c>
+    </row>
+    <row r="560" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A560" s="65"/>
+      <c r="B560" s="10"/>
+      <c r="C560" s="11"/>
+      <c r="D560" s="12"/>
+      <c r="E560" s="13"/>
+      <c r="F560" s="251"/>
+      <c r="G560" s="286"/>
+      <c r="H560" s="251"/>
+      <c r="I560" s="286"/>
+    </row>
+    <row r="561" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A561" s="67"/>
+      <c r="B561" s="24"/>
+      <c r="C561" s="68"/>
+      <c r="D561" s="26"/>
+      <c r="E561" s="27"/>
+      <c r="F561" s="283"/>
+      <c r="G561" s="284"/>
+      <c r="H561" s="283"/>
+      <c r="I561" s="284"/>
+    </row>
+    <row r="562" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A562" s="31"/>
+      <c r="B562" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="C562" s="71" t="s">
+        <v>60</v>
+      </c>
+      <c r="D562" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E562" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F562" s="307">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="G562" s="289" t="s">
+        <v>27</v>
+      </c>
+      <c r="H562" s="307">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="I562" s="289" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="563" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A563" s="39">
+        <v>46225</v>
+      </c>
+      <c r="B563" s="40" t="s">
+        <v>522</v>
+      </c>
+      <c r="C563" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="D563" s="42">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E563" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F563" s="260" t="s">
+        <v>58</v>
+      </c>
+      <c r="G563" s="290">
+        <v>0.5</v>
+      </c>
+      <c r="H563" s="260" t="s">
+        <v>68</v>
+      </c>
+      <c r="I563" s="290">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="564" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A564" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B564" s="40" t="s">
+        <v>523</v>
+      </c>
+      <c r="C564" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="D564" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E564" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F564" s="263">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="G564" s="290">
+        <v>0.84375</v>
+      </c>
+      <c r="H564" s="263">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I564" s="290">
+        <v>0.84375</v>
+      </c>
+    </row>
+    <row r="565" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A565" s="49"/>
+      <c r="B565" s="40" t="s">
+        <v>524</v>
+      </c>
+      <c r="C565" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D565" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="E565" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F565" s="263">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="G565" s="291" t="s">
+        <v>39</v>
+      </c>
+      <c r="H565" s="263">
+        <v>0.84375</v>
+      </c>
+      <c r="I565" s="291" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="566" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A566" s="51"/>
+      <c r="B566" s="52"/>
+      <c r="C566" s="79"/>
+      <c r="D566" s="54"/>
+      <c r="E566" s="55"/>
+      <c r="F566" s="266"/>
+      <c r="G566" s="292"/>
+      <c r="H566" s="266"/>
+      <c r="I566" s="292"/>
+    </row>
+    <row r="567" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A567" s="1"/>
+      <c r="B567" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C567" s="90" t="s">
+        <v>259</v>
+      </c>
+      <c r="D567" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E567" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F567" s="269" t="s">
+        <v>39</v>
+      </c>
+      <c r="G567" s="294" t="s">
+        <v>58</v>
+      </c>
+      <c r="H567" s="269" t="s">
+        <v>39</v>
+      </c>
+      <c r="I567" s="294" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="568" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A568" s="62">
+        <v>46226</v>
+      </c>
+      <c r="B568" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="C568" s="93" t="s">
+        <v>183</v>
+      </c>
+      <c r="D568" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E568" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F568" s="248" t="s">
+        <v>58</v>
+      </c>
+      <c r="G568" s="286">
+        <v>0.53125</v>
+      </c>
+      <c r="H568" s="248" t="s">
+        <v>58</v>
+      </c>
+      <c r="I568" s="286">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="569" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A569" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="B569" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="C569" s="93" t="s">
+        <v>36</v>
+      </c>
+      <c r="D569" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E569" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F569" s="251">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="G569" s="286">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="H569" s="251">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="I569" s="286">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="570" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A570" s="65"/>
+      <c r="B570" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="C570" s="93" t="s">
+        <v>132</v>
+      </c>
+      <c r="D570" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E570" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F570" s="251">
+        <v>0.9375</v>
+      </c>
+      <c r="G570" s="287" t="s">
+        <v>216</v>
+      </c>
+      <c r="H570" s="251">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I570" s="287" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="571" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A571" s="67"/>
+      <c r="B571" s="24"/>
+      <c r="C571" s="94"/>
+      <c r="D571" s="26"/>
+      <c r="E571" s="27"/>
+      <c r="F571" s="254"/>
+      <c r="G571" s="288"/>
+      <c r="H571" s="254"/>
+      <c r="I571" s="288"/>
+    </row>
+    <row r="572" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A572" s="31"/>
+      <c r="B572" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C572" s="71" t="s">
+        <v>89</v>
+      </c>
+      <c r="D572" s="308" t="s">
+        <v>27</v>
+      </c>
+      <c r="E572" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F572" s="257" t="s">
+        <v>216</v>
+      </c>
+      <c r="G572" s="289" t="s">
+        <v>57</v>
+      </c>
+      <c r="H572" s="297" t="s">
+        <v>216</v>
+      </c>
+      <c r="I572" s="289" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="573" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A573" s="39">
+        <v>46227</v>
+      </c>
+      <c r="B573" s="40" t="s">
+        <v>528</v>
+      </c>
+      <c r="C573" s="74" t="s">
+        <v>183</v>
+      </c>
+      <c r="D573" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E573" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F573" s="260" t="s">
+        <v>57</v>
+      </c>
+      <c r="G573" s="290">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="H573" s="298" t="s">
+        <v>57</v>
+      </c>
+      <c r="I573" s="290">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="574" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A574" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B574" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="C574" s="74" t="s">
+        <v>52</v>
+      </c>
+      <c r="D574" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="E574" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F574" s="263">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G574" s="290">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="H574" s="299">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="I574" s="290">
+        <v>0.94791666666666663</v>
+      </c>
+    </row>
+    <row r="575" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A575" s="49"/>
+      <c r="B575" s="40"/>
+      <c r="C575" s="74"/>
+      <c r="D575" s="42"/>
+      <c r="E575" s="43"/>
+      <c r="F575" s="263"/>
+      <c r="G575" s="290"/>
+      <c r="H575" s="299"/>
+      <c r="I575" s="290"/>
+    </row>
+    <row r="576" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A576" s="51"/>
+      <c r="B576" s="52"/>
+      <c r="C576" s="101"/>
+      <c r="D576" s="100"/>
+      <c r="E576" s="102"/>
+      <c r="F576" s="266"/>
+      <c r="G576" s="292"/>
+      <c r="H576" s="300"/>
+      <c r="I576" s="292"/>
+    </row>
+    <row r="577" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A577" s="1"/>
+      <c r="B577" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C577" s="90" t="s">
+        <v>136</v>
+      </c>
+      <c r="D577" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E577" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F577" s="309" t="s">
+        <v>77</v>
+      </c>
+      <c r="G577" s="246" t="s">
+        <v>6</v>
+      </c>
+      <c r="H577" s="310">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="I577" s="246" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="578" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A578" s="82">
+        <v>46228</v>
+      </c>
+      <c r="B578" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="C578" s="93" t="s">
+        <v>98</v>
+      </c>
+      <c r="D578" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E578" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F578" s="311" t="s">
+        <v>6</v>
+      </c>
+      <c r="G578" s="253" t="s">
+        <v>31</v>
+      </c>
+      <c r="H578" s="250" t="s">
+        <v>6</v>
+      </c>
+      <c r="I578" s="253" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="579" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A579" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B579" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="C579" s="93" t="s">
+        <v>183</v>
+      </c>
+      <c r="D579" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E579" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F579" s="248" t="s">
+        <v>31</v>
+      </c>
+      <c r="G579" s="249">
+        <v>0.59375</v>
+      </c>
+      <c r="H579" s="250" t="s">
+        <v>31</v>
+      </c>
+      <c r="I579" s="249">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="580" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A580" s="114"/>
+      <c r="B580" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C580" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="D580" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E580" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F580" s="251">
+        <v>0.75</v>
+      </c>
+      <c r="G580" s="249">
+        <v>0.9375</v>
+      </c>
+      <c r="H580" s="274">
+        <v>0.78125</v>
+      </c>
+      <c r="I580" s="249">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="581" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A581" s="125"/>
+      <c r="B581" s="24"/>
+      <c r="C581" s="94"/>
+      <c r="D581" s="26"/>
+      <c r="E581" s="27"/>
+      <c r="F581" s="296"/>
+      <c r="G581" s="255"/>
+      <c r="H581" s="276"/>
+      <c r="I581" s="255"/>
+    </row>
+    <row r="582" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A582" s="70"/>
+      <c r="B582" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="C582" s="71" t="s">
+        <v>142</v>
+      </c>
+      <c r="D582" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="E582" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F582" s="312" t="s">
+        <v>53</v>
+      </c>
+      <c r="G582" s="313" t="s">
+        <v>68</v>
+      </c>
+      <c r="H582" s="314" t="s">
+        <v>22</v>
+      </c>
+      <c r="I582" s="313" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="583" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A583" s="73">
+        <v>46229</v>
+      </c>
+      <c r="B583" s="40" t="s">
+        <v>531</v>
+      </c>
+      <c r="C583" s="74" t="s">
+        <v>136</v>
+      </c>
+      <c r="D583" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="E583" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F583" s="260" t="s">
+        <v>68</v>
+      </c>
+      <c r="G583" s="261">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H583" s="262" t="s">
+        <v>68</v>
+      </c>
+      <c r="I583" s="261">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="584" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A584" s="76" t="s">
+        <v>73</v>
+      </c>
+      <c r="B584" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C584" s="74" t="s">
+        <v>183</v>
+      </c>
+      <c r="D584" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="E584" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F584" s="263">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G584" s="261">
+        <v>0.625</v>
+      </c>
+      <c r="H584" s="264">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I584" s="261">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="585" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A585" s="49"/>
+      <c r="B585" s="40" t="s">
+        <v>532</v>
+      </c>
+      <c r="C585" s="74" t="s">
+        <v>274</v>
+      </c>
+      <c r="D585" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="E585" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F585" s="263">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G585" s="261">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="H585" s="264">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I585" s="265" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="586" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A586" s="51"/>
+      <c r="B586" s="52"/>
+      <c r="C586" s="79"/>
+      <c r="D586" s="54"/>
+      <c r="E586" s="55"/>
+      <c r="F586" s="266"/>
+      <c r="G586" s="267"/>
+      <c r="H586" s="268"/>
+      <c r="I586" s="267"/>
+    </row>
+    <row r="587" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A587" s="1"/>
+      <c r="B587" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C587" s="90" t="s">
+        <v>183</v>
+      </c>
+      <c r="D587" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E587" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F587" s="269" t="s">
+        <v>148</v>
+      </c>
+      <c r="G587" s="270" t="s">
+        <v>58</v>
+      </c>
+      <c r="H587" s="271" t="s">
+        <v>53</v>
+      </c>
+      <c r="I587" s="272" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="588" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A588" s="62">
+        <v>46230</v>
+      </c>
+      <c r="B588" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="C588" s="93" t="s">
+        <v>98</v>
+      </c>
+      <c r="D588" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E588" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F588" s="248" t="s">
+        <v>58</v>
+      </c>
+      <c r="G588" s="273">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H588" s="250" t="s">
+        <v>58</v>
+      </c>
+      <c r="I588" s="249">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="589" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A589" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="B589" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C589" s="93" t="s">
+        <v>96</v>
+      </c>
+      <c r="D589" s="12">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="E589" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F589" s="251">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="G589" s="273">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H589" s="274">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I589" s="249">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="590" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A590" s="65"/>
+      <c r="B590" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="C590" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="D590" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="E590" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F590" s="251">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="G590" s="275" t="s">
+        <v>37</v>
+      </c>
+      <c r="H590" s="274">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="I590" s="253" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="591" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A591" s="67"/>
+      <c r="B591" s="24"/>
+      <c r="C591" s="94"/>
+      <c r="D591" s="26"/>
+      <c r="E591" s="27"/>
+      <c r="F591" s="254"/>
+      <c r="G591" s="256"/>
+      <c r="H591" s="276"/>
+      <c r="I591" s="255"/>
+    </row>
+    <row r="592" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A592" s="31"/>
+      <c r="B592" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="C592" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="D592" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="E592" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F592" s="257" t="s">
+        <v>229</v>
+      </c>
+      <c r="G592" s="258" t="s">
+        <v>57</v>
+      </c>
+      <c r="H592" s="278" t="s">
+        <v>24</v>
+      </c>
+      <c r="I592" s="258" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="593" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A593" s="39">
+        <v>46231</v>
+      </c>
+      <c r="B593" s="40" t="s">
+        <v>535</v>
+      </c>
+      <c r="C593" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D593" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="E593" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F593" s="260" t="s">
+        <v>57</v>
+      </c>
+      <c r="G593" s="261">
+        <v>0.5</v>
+      </c>
+      <c r="H593" s="280" t="s">
+        <v>57</v>
+      </c>
+      <c r="I593" s="265" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="594" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A594" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B594" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="C594" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="D594" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="E594" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F594" s="263">
+        <v>0.5</v>
+      </c>
+      <c r="G594" s="261">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="H594" s="279">
+        <v>0.5</v>
+      </c>
+      <c r="I594" s="261">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="595" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A595" s="49"/>
+      <c r="B595" s="40" t="s">
+        <v>536</v>
+      </c>
+      <c r="C595" s="74" t="s">
+        <v>117</v>
+      </c>
+      <c r="D595" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="E595" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F595" s="263">
+        <v>0.875</v>
+      </c>
+      <c r="G595" s="265" t="s">
+        <v>21</v>
+      </c>
+      <c r="H595" s="279">
+        <v>0.90625</v>
+      </c>
+      <c r="I595" s="265" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="596" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A596" s="51"/>
+      <c r="B596" s="52"/>
+      <c r="C596" s="79"/>
+      <c r="D596" s="54"/>
+      <c r="E596" s="55"/>
+      <c r="F596" s="266"/>
+      <c r="G596" s="267"/>
+      <c r="H596" s="281"/>
+      <c r="I596" s="267"/>
+    </row>
+    <row r="597" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A597" s="1"/>
+      <c r="B597" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C597" s="90" t="s">
+        <v>190</v>
+      </c>
+      <c r="D597" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E597" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F597" s="269" t="s">
+        <v>176</v>
+      </c>
+      <c r="G597" s="272" t="s">
+        <v>46</v>
+      </c>
+      <c r="H597" s="271" t="s">
+        <v>229</v>
+      </c>
+      <c r="I597" s="272" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="598" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A598" s="62">
+        <v>46232</v>
+      </c>
+      <c r="B598" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="C598" s="93" t="s">
+        <v>89</v>
+      </c>
+      <c r="D598" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E598" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F598" s="248" t="s">
+        <v>46</v>
+      </c>
+      <c r="G598" s="249">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H598" s="250" t="s">
+        <v>46</v>
+      </c>
+      <c r="I598" s="249">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="599" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A599" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B599" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C599" s="93" t="s">
+        <v>190</v>
+      </c>
+      <c r="D599" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E599" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F599" s="251">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G599" s="249">
+        <v>0.71875</v>
+      </c>
+      <c r="H599" s="274">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I599" s="249">
+        <v>0.69791666666666663</v>
+      </c>
+    </row>
+    <row r="600" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A600" s="65"/>
+      <c r="B600" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="C600" s="93" t="s">
+        <v>364</v>
+      </c>
+      <c r="D600" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E600" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F600" s="251">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G600" s="253" t="s">
+        <v>38</v>
+      </c>
+      <c r="H600" s="250">
+        <v>0.9375</v>
+      </c>
+      <c r="I600" s="253" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="601" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A601" s="67"/>
+      <c r="B601" s="24"/>
+      <c r="C601" s="94"/>
+      <c r="D601" s="26"/>
+      <c r="E601" s="27"/>
+      <c r="F601" s="283"/>
+      <c r="G601" s="284"/>
+      <c r="H601" s="283"/>
+      <c r="I601" s="284"/>
+    </row>
+    <row r="602" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A602" s="31"/>
+      <c r="B602" s="32" t="s">
+        <v>491</v>
+      </c>
+      <c r="C602" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="D602" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E602" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F602" s="257" t="s">
+        <v>56</v>
+      </c>
+      <c r="G602" s="258" t="s">
+        <v>59</v>
+      </c>
+      <c r="H602" s="259" t="s">
+        <v>3</v>
+      </c>
+      <c r="I602" s="258" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="603" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A603" s="39">
+        <v>46233</v>
+      </c>
+      <c r="B603" s="40" t="s">
+        <v>540</v>
+      </c>
+      <c r="C603" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="D603" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="E603" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F603" s="260" t="s">
+        <v>59</v>
+      </c>
+      <c r="G603" s="261">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H603" s="262" t="s">
+        <v>31</v>
+      </c>
+      <c r="I603" s="261">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="604" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A604" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B604" s="40" t="s">
+        <v>541</v>
+      </c>
+      <c r="C604" s="74" t="s">
+        <v>87</v>
+      </c>
+      <c r="D604" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="E604" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F604" s="263">
+        <v>0.5625</v>
+      </c>
+      <c r="G604" s="261">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="H604" s="264">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I604" s="261">
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="605" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A605" s="49"/>
+      <c r="B605" s="40" t="s">
+        <v>542</v>
+      </c>
+      <c r="C605" s="74" t="s">
+        <v>124</v>
+      </c>
+      <c r="D605" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E605" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F605" s="263">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="G605" s="265" t="s">
+        <v>39</v>
+      </c>
+      <c r="H605" s="264">
+        <v>0.96875</v>
+      </c>
+      <c r="I605" s="265" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="606" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A606" s="51"/>
+      <c r="B606" s="54"/>
+      <c r="C606" s="79"/>
+      <c r="D606" s="54"/>
+      <c r="E606" s="55"/>
+      <c r="F606" s="266"/>
+      <c r="G606" s="267"/>
+      <c r="H606" s="268"/>
+      <c r="I606" s="267"/>
+    </row>
+    <row r="607" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A607" s="315"/>
+      <c r="B607" s="173" t="s">
+        <v>229</v>
+      </c>
+      <c r="C607" s="185" t="s">
+        <v>87</v>
+      </c>
+      <c r="D607" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E607" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F607" s="269" t="s">
+        <v>170</v>
+      </c>
+      <c r="G607" s="272">
+        <v>0.375</v>
+      </c>
+      <c r="H607" s="316" t="s">
+        <v>56</v>
+      </c>
+      <c r="I607" s="317">
+        <v>0.35416666666666669</v>
+      </c>
+    </row>
+    <row r="608" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A608" s="198">
+        <v>46234</v>
+      </c>
+      <c r="B608" s="173" t="s">
+        <v>543</v>
+      </c>
+      <c r="C608" s="185" t="s">
+        <v>80</v>
+      </c>
+      <c r="D608" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E608" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F608" s="248" t="s">
+        <v>31</v>
+      </c>
+      <c r="G608" s="249">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H608" s="274">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="I608" s="249">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="609" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A609" s="230" t="s">
+        <v>48</v>
+      </c>
+      <c r="B609" s="173" t="s">
+        <v>544</v>
+      </c>
+      <c r="C609" s="185" t="s">
+        <v>87</v>
+      </c>
+      <c r="D609" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E609" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F609" s="251">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="G609" s="249">
+        <v>0.78125</v>
+      </c>
+      <c r="H609" s="274">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I609" s="249">
+        <v>0.76041666666666663</v>
+      </c>
+    </row>
+    <row r="610" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A610" s="230"/>
+      <c r="B610" s="173" t="s">
+        <v>545</v>
+      </c>
+      <c r="C610" s="185" t="s">
+        <v>364</v>
+      </c>
+      <c r="D610" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E610" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F610" s="318">
+        <v>0.96875</v>
+      </c>
+      <c r="G610" s="319" t="s">
+        <v>5</v>
+      </c>
+      <c r="H610" s="320">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="I610" s="319" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="611" spans="1:9" ht="16" x14ac:dyDescent="0.4">
+      <c r="A611" s="232"/>
+      <c r="B611" s="233"/>
+      <c r="C611" s="234"/>
+      <c r="D611" s="67"/>
+      <c r="E611" s="27"/>
+      <c r="F611" s="254"/>
+      <c r="G611" s="255"/>
+      <c r="H611" s="276"/>
+      <c r="I611" s="255"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13972,7 +18339,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{928BB44D-9009-4EF5-A7E0-17AFE9C73770}">
-  <dimension ref="A1:M456"/>
+  <dimension ref="A1:M611"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
@@ -29664,6 +34031,5337 @@
       <c r="L456" s="54"/>
       <c r="M456" s="57"/>
     </row>
+    <row r="457" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A457" s="1"/>
+      <c r="B457" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C457" s="135" t="s">
+        <v>190</v>
+      </c>
+      <c r="D457" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E457" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F457" s="136" t="s">
+        <v>148</v>
+      </c>
+      <c r="G457" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="H457" s="60" t="s">
+        <v>216</v>
+      </c>
+      <c r="I457" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="J457" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="K457" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="L457" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="M457" s="61" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="458" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A458" s="62">
+        <v>46204</v>
+      </c>
+      <c r="B458" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="C458" s="138" t="s">
+        <v>132</v>
+      </c>
+      <c r="D458" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E458" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F458" s="139" t="s">
+        <v>55</v>
+      </c>
+      <c r="G458" s="15">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H458" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="I458" s="15">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="J458" s="139" t="s">
+        <v>57</v>
+      </c>
+      <c r="K458" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L458" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="M458" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="459" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A459" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B459" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="C459" s="138" t="s">
+        <v>87</v>
+      </c>
+      <c r="D459" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E459" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F459" s="18">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G459" s="15">
+        <v>0.625</v>
+      </c>
+      <c r="H459" s="16">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I459" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="J459" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K459" s="15">
+        <v>0.4375</v>
+      </c>
+      <c r="L459" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="M459" s="15">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="460" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A460" s="65"/>
+      <c r="B460" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="C460" s="140" t="s">
+        <v>124</v>
+      </c>
+      <c r="D460" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E460" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F460" s="18">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="G460" s="15">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="H460" s="16">
+        <v>0.84375</v>
+      </c>
+      <c r="I460" s="15">
+        <v>0.9375</v>
+      </c>
+      <c r="J460" s="18">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="K460" s="15">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="L460" s="16">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="M460" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="461" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A461" s="67"/>
+      <c r="B461" s="24"/>
+      <c r="C461" s="141"/>
+      <c r="D461" s="26"/>
+      <c r="E461" s="27"/>
+      <c r="F461" s="116"/>
+      <c r="G461" s="29"/>
+      <c r="H461" s="69"/>
+      <c r="I461" s="29"/>
+      <c r="J461" s="116"/>
+      <c r="K461" s="29"/>
+      <c r="L461" s="69"/>
+      <c r="M461" s="29"/>
+    </row>
+    <row r="462" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A462" s="31"/>
+      <c r="B462" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="C462" s="142" t="s">
+        <v>190</v>
+      </c>
+      <c r="D462" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="E462" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F462" s="117" t="s">
+        <v>216</v>
+      </c>
+      <c r="G462" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H462" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="I462" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="J462" s="117" t="s">
+        <v>53</v>
+      </c>
+      <c r="K462" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="L462" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="M462" s="37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="463" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A463" s="39">
+        <v>46205</v>
+      </c>
+      <c r="B463" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C463" s="144" t="s">
+        <v>89</v>
+      </c>
+      <c r="D463" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="E463" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F463" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="G463" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="H463" s="88" t="s">
+        <v>58</v>
+      </c>
+      <c r="I463" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="J463" s="119" t="s">
+        <v>59</v>
+      </c>
+      <c r="K463" s="45">
+        <v>0.4375</v>
+      </c>
+      <c r="L463" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="M463" s="50" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="464" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A464" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B464" s="40" t="s">
+        <v>465</v>
+      </c>
+      <c r="C464" s="144" t="s">
+        <v>190</v>
+      </c>
+      <c r="D464" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="E464" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F464" s="118">
+        <v>0.5</v>
+      </c>
+      <c r="G464" s="45">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H464" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="I464" s="45">
+        <v>0.625</v>
+      </c>
+      <c r="J464" s="118">
+        <v>0.4375</v>
+      </c>
+      <c r="K464" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="L464" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="M464" s="45">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="465" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A465" s="49"/>
+      <c r="B465" s="40" t="s">
+        <v>342</v>
+      </c>
+      <c r="C465" s="144" t="s">
+        <v>124</v>
+      </c>
+      <c r="D465" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="E465" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F465" s="118">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G465" s="45">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="H465" s="88" t="s">
+        <v>159</v>
+      </c>
+      <c r="I465" s="45">
+        <v>0.96875</v>
+      </c>
+      <c r="J465" s="118">
+        <v>0.875</v>
+      </c>
+      <c r="K465" s="45">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="L465" s="46">
+        <v>0.8125</v>
+      </c>
+      <c r="M465" s="45">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="466" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A466" s="51"/>
+      <c r="B466" s="52"/>
+      <c r="C466" s="145"/>
+      <c r="D466" s="54"/>
+      <c r="E466" s="55"/>
+      <c r="F466" s="120"/>
+      <c r="G466" s="57"/>
+      <c r="H466" s="54"/>
+      <c r="I466" s="57"/>
+      <c r="J466" s="120"/>
+      <c r="K466" s="57"/>
+      <c r="L466" s="54"/>
+      <c r="M466" s="57"/>
+    </row>
+    <row r="467" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A467" s="1"/>
+      <c r="B467" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C467" s="135" t="s">
+        <v>190</v>
+      </c>
+      <c r="D467" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E467" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F467" s="136" t="s">
+        <v>44</v>
+      </c>
+      <c r="G467" s="59">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="H467" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="I467" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="J467" s="136" t="s">
+        <v>148</v>
+      </c>
+      <c r="K467" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="L467" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="M467" s="61" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="468" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A468" s="62">
+        <v>46206</v>
+      </c>
+      <c r="B468" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="C468" s="138" t="s">
+        <v>89</v>
+      </c>
+      <c r="D468" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E468" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F468" s="139">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="G468" s="63">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H468" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="I468" s="15">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J468" s="139" t="s">
+        <v>31</v>
+      </c>
+      <c r="K468" s="63">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="L468" s="84" t="s">
+        <v>68</v>
+      </c>
+      <c r="M468" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="469" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A469" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B469" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="C469" s="138" t="s">
+        <v>190</v>
+      </c>
+      <c r="D469" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E469" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F469" s="124">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G469" s="63">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H469" s="16">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I469" s="15">
+        <v>0.65625</v>
+      </c>
+      <c r="J469" s="124">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="K469" s="63">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L469" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="M469" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="470" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A470" s="65"/>
+      <c r="B470" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="C470" s="138" t="s">
+        <v>364</v>
+      </c>
+      <c r="D470" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E470" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F470" s="124">
+        <v>0.875</v>
+      </c>
+      <c r="G470" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="H470" s="16">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="I470" s="15">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="J470" s="124">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="K470" s="63">
+        <v>0.9375</v>
+      </c>
+      <c r="L470" s="16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M470" s="15">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="471" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A471" s="67"/>
+      <c r="B471" s="24"/>
+      <c r="C471" s="146"/>
+      <c r="D471" s="26"/>
+      <c r="E471" s="27"/>
+      <c r="F471" s="116"/>
+      <c r="G471" s="30"/>
+      <c r="H471" s="69"/>
+      <c r="I471" s="29"/>
+      <c r="J471" s="116"/>
+      <c r="K471" s="30"/>
+      <c r="L471" s="69"/>
+      <c r="M471" s="29"/>
+    </row>
+    <row r="472" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A472" s="31"/>
+      <c r="B472" s="34" t="s">
+        <v>470</v>
+      </c>
+      <c r="C472" s="147" t="s">
+        <v>190</v>
+      </c>
+      <c r="D472" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="E472" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F472" s="117" t="s">
+        <v>3</v>
+      </c>
+      <c r="G472" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="H472" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="I472" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="J472" s="117" t="s">
+        <v>216</v>
+      </c>
+      <c r="K472" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="L472" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="M472" s="37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="473" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A473" s="73">
+        <v>46207</v>
+      </c>
+      <c r="B473" s="42" t="s">
+        <v>471</v>
+      </c>
+      <c r="C473" s="148" t="s">
+        <v>264</v>
+      </c>
+      <c r="D473" s="149" t="s">
+        <v>11</v>
+      </c>
+      <c r="E473" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F473" s="119" t="s">
+        <v>57</v>
+      </c>
+      <c r="G473" s="45">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H473" s="99" t="s">
+        <v>46</v>
+      </c>
+      <c r="I473" s="45">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J473" s="118">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K473" s="45">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="L473" s="99" t="s">
+        <v>58</v>
+      </c>
+      <c r="M473" s="50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="474" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A474" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B474" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="C474" s="148" t="s">
+        <v>96</v>
+      </c>
+      <c r="D474" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="E474" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F474" s="118">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G474" s="45">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="H474" s="75">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I474" s="45">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="J474" s="118">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="K474" s="45">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="L474" s="75">
+        <v>0.5625</v>
+      </c>
+      <c r="M474" s="45">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="475" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A475" s="77"/>
+      <c r="B475" s="42" t="s">
+        <v>473</v>
+      </c>
+      <c r="C475" s="148" t="s">
+        <v>117</v>
+      </c>
+      <c r="D475" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="E475" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F475" s="118">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="G475" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="H475" s="75">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I475" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="J475" s="118">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K475" s="45">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="L475" s="75">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="M475" s="45">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="476" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A476" s="78"/>
+      <c r="B476" s="54"/>
+      <c r="C476" s="150"/>
+      <c r="D476" s="54"/>
+      <c r="E476" s="55"/>
+      <c r="F476" s="120"/>
+      <c r="G476" s="57"/>
+      <c r="H476" s="80"/>
+      <c r="I476" s="57"/>
+      <c r="J476" s="120"/>
+      <c r="K476" s="57"/>
+      <c r="L476" s="80"/>
+      <c r="M476" s="57"/>
+    </row>
+    <row r="477" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A477" s="81"/>
+      <c r="B477" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C477" s="135" t="s">
+        <v>190</v>
+      </c>
+      <c r="D477" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E477" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F477" s="136" t="s">
+        <v>56</v>
+      </c>
+      <c r="G477" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="H477" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="I477" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="J477" s="136" t="s">
+        <v>44</v>
+      </c>
+      <c r="K477" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="L477" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="M477" s="61" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="478" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A478" s="82">
+        <v>46208</v>
+      </c>
+      <c r="B478" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="C478" s="138" t="s">
+        <v>80</v>
+      </c>
+      <c r="D478" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E478" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F478" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="G478" s="15">
+        <v>0.5625</v>
+      </c>
+      <c r="H478" s="16">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="I478" s="15">
+        <v>0.5625</v>
+      </c>
+      <c r="J478" s="124">
+        <v>0.4375</v>
+      </c>
+      <c r="K478" s="15">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L478" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="M478" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="479" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A479" s="83" t="s">
+        <v>73</v>
+      </c>
+      <c r="B479" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="C479" s="138" t="s">
+        <v>183</v>
+      </c>
+      <c r="D479" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E479" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F479" s="124">
+        <v>0.5625</v>
+      </c>
+      <c r="G479" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H479" s="16">
+        <v>0.5625</v>
+      </c>
+      <c r="I479" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="J479" s="124">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="K479" s="15">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L479" s="16">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="M479" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="480" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A480" s="114"/>
+      <c r="B480" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="C480" s="138" t="s">
+        <v>274</v>
+      </c>
+      <c r="D480" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E480" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F480" s="124">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G480" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H480" s="16">
+        <v>0.9375</v>
+      </c>
+      <c r="I480" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J480" s="124">
+        <v>0.9375</v>
+      </c>
+      <c r="K480" s="15">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="L480" s="16">
+        <v>0.875</v>
+      </c>
+      <c r="M480" s="15">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="481" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A481" s="67"/>
+      <c r="B481" s="24"/>
+      <c r="C481" s="146"/>
+      <c r="D481" s="26"/>
+      <c r="E481" s="27"/>
+      <c r="F481" s="86"/>
+      <c r="G481" s="87"/>
+      <c r="H481" s="85"/>
+      <c r="I481" s="87"/>
+      <c r="J481" s="86"/>
+      <c r="K481" s="87"/>
+      <c r="L481" s="85"/>
+      <c r="M481" s="87"/>
+    </row>
+    <row r="482" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A482" s="31"/>
+      <c r="B482" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C482" s="147" t="s">
+        <v>190</v>
+      </c>
+      <c r="D482" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="E482" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F482" s="117" t="s">
+        <v>8</v>
+      </c>
+      <c r="G482" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H482" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="I482" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="J482" s="117" t="s">
+        <v>3</v>
+      </c>
+      <c r="K482" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="L482" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="M482" s="37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="483" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A483" s="39">
+        <v>46209</v>
+      </c>
+      <c r="B483" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="C483" s="148" t="s">
+        <v>71</v>
+      </c>
+      <c r="D483" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="E483" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F483" s="118">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="G483" s="45">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H483" s="46">
+        <v>0.46875</v>
+      </c>
+      <c r="I483" s="45">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J483" s="118">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="K483" s="45">
+        <v>0.5625</v>
+      </c>
+      <c r="L483" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="M483" s="45">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="484" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A484" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B484" s="42" t="s">
+        <v>478</v>
+      </c>
+      <c r="C484" s="148" t="s">
+        <v>158</v>
+      </c>
+      <c r="D484" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="E484" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F484" s="118">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G484" s="45">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H484" s="46">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I484" s="45">
+        <v>0.75</v>
+      </c>
+      <c r="J484" s="118">
+        <v>0.5625</v>
+      </c>
+      <c r="K484" s="45">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="L484" s="46">
+        <v>0.625</v>
+      </c>
+      <c r="M484" s="45">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="485" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A485" s="49"/>
+      <c r="B485" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="C485" s="148" t="s">
+        <v>195</v>
+      </c>
+      <c r="D485" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="E485" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F485" s="118">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G485" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="H485" s="46">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="I485" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="J485" s="118">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="K485" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="L485" s="46">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="M485" s="45">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="486" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A486" s="51"/>
+      <c r="B486" s="54"/>
+      <c r="C486" s="150"/>
+      <c r="D486" s="54"/>
+      <c r="E486" s="55"/>
+      <c r="F486" s="120"/>
+      <c r="G486" s="57"/>
+      <c r="H486" s="54"/>
+      <c r="I486" s="57"/>
+      <c r="J486" s="120"/>
+      <c r="K486" s="57"/>
+      <c r="L486" s="54"/>
+      <c r="M486" s="57"/>
+    </row>
+    <row r="487" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A487" s="1"/>
+      <c r="B487" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C487" s="151" t="s">
+        <v>190</v>
+      </c>
+      <c r="D487" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E487" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F487" s="136" t="s">
+        <v>6</v>
+      </c>
+      <c r="G487" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="H487" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="I487" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="J487" s="136" t="s">
+        <v>3</v>
+      </c>
+      <c r="K487" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="L487" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="M487" s="61" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="488" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A488" s="62">
+        <v>46210</v>
+      </c>
+      <c r="B488" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="C488" s="152" t="s">
+        <v>249</v>
+      </c>
+      <c r="D488" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E488" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F488" s="124">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="G488" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H488" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="I488" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J488" s="124">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="K488" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="L488" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M488" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="489" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A489" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B489" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="C489" s="152" t="s">
+        <v>98</v>
+      </c>
+      <c r="D489" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E489" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F489" s="124">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G489" s="15">
+        <v>0.84375</v>
+      </c>
+      <c r="H489" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I489" s="15">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="J489" s="124">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="K489" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L489" s="84">
+        <v>0.6875</v>
+      </c>
+      <c r="M489" s="15">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="490" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A490" s="65"/>
+      <c r="B490" s="12"/>
+      <c r="C490" s="152"/>
+      <c r="D490" s="12"/>
+      <c r="E490" s="13"/>
+      <c r="F490" s="124"/>
+      <c r="G490" s="15"/>
+      <c r="H490" s="16"/>
+      <c r="I490" s="15"/>
+      <c r="J490" s="124"/>
+      <c r="K490" s="15"/>
+      <c r="L490" s="16"/>
+      <c r="M490" s="15"/>
+    </row>
+    <row r="491" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A491" s="67"/>
+      <c r="B491" s="26"/>
+      <c r="C491" s="153"/>
+      <c r="D491" s="26"/>
+      <c r="E491" s="27"/>
+      <c r="F491" s="116"/>
+      <c r="G491" s="29"/>
+      <c r="H491" s="69"/>
+      <c r="I491" s="29"/>
+      <c r="J491" s="116"/>
+      <c r="K491" s="29"/>
+      <c r="L491" s="69"/>
+      <c r="M491" s="29"/>
+    </row>
+    <row r="492" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A492" s="31"/>
+      <c r="B492" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="C492" s="147" t="s">
+        <v>29</v>
+      </c>
+      <c r="D492" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E492" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F492" s="166">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="G492" s="127" t="s">
+        <v>148</v>
+      </c>
+      <c r="H492" s="243">
+        <v>0.96875</v>
+      </c>
+      <c r="I492" s="127" t="s">
+        <v>53</v>
+      </c>
+      <c r="J492" s="154" t="s">
+        <v>37</v>
+      </c>
+      <c r="K492" s="127" t="s">
+        <v>38</v>
+      </c>
+      <c r="L492" s="243">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="M492" s="209">
+        <v>0.97916666666666663</v>
+      </c>
+    </row>
+    <row r="493" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A493" s="39">
+        <v>46211</v>
+      </c>
+      <c r="B493" s="42" t="s">
+        <v>483</v>
+      </c>
+      <c r="C493" s="148" t="s">
+        <v>190</v>
+      </c>
+      <c r="D493" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="E493" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F493" s="119">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="G493" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="H493" s="99">
+        <v>0.25</v>
+      </c>
+      <c r="I493" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="J493" s="119" t="s">
+        <v>3</v>
+      </c>
+      <c r="K493" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="L493" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="M493" s="50" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="494" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A494" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B494" s="42" t="s">
+        <v>484</v>
+      </c>
+      <c r="C494" s="148" t="s">
+        <v>19</v>
+      </c>
+      <c r="D494" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="E494" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F494" s="118">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G494" s="45">
+        <v>0.6875</v>
+      </c>
+      <c r="H494" s="75">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="I494" s="45">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J494" s="118">
+        <v>0.5625</v>
+      </c>
+      <c r="K494" s="45">
+        <v>0.625</v>
+      </c>
+      <c r="L494" s="75">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="M494" s="45">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="495" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A495" s="49"/>
+      <c r="B495" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="C495" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="D495" s="42">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="E495" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F495" s="118">
+        <v>0.71875</v>
+      </c>
+      <c r="G495" s="45">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="H495" s="75">
+        <v>0.75</v>
+      </c>
+      <c r="I495" s="45">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="J495" s="118">
+        <v>0.6875</v>
+      </c>
+      <c r="K495" s="45">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="L495" s="75">
+        <v>0.75</v>
+      </c>
+      <c r="M495" s="45">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="496" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A496" s="51"/>
+      <c r="B496" s="100"/>
+      <c r="C496" s="102"/>
+      <c r="D496" s="100"/>
+      <c r="E496" s="102"/>
+      <c r="F496" s="120"/>
+      <c r="G496" s="57"/>
+      <c r="H496" s="80"/>
+      <c r="I496" s="57"/>
+      <c r="J496" s="120"/>
+      <c r="K496" s="57"/>
+      <c r="L496" s="80"/>
+      <c r="M496" s="57"/>
+    </row>
+    <row r="497" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A497" s="1"/>
+      <c r="B497" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C497" s="151" t="s">
+        <v>60</v>
+      </c>
+      <c r="D497" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E497" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F497" s="201">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="G497" s="112" t="s">
+        <v>229</v>
+      </c>
+      <c r="H497" s="132">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="I497" s="112" t="s">
+        <v>24</v>
+      </c>
+      <c r="J497" s="136" t="s">
+        <v>21</v>
+      </c>
+      <c r="K497" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="L497" s="132">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="M497" s="112" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="498" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A498" s="62">
+        <v>46212</v>
+      </c>
+      <c r="B498" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C498" s="152" t="s">
+        <v>190</v>
+      </c>
+      <c r="D498" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E498" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F498" s="139">
+        <v>0.25</v>
+      </c>
+      <c r="G498" s="104">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H498" s="14">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="I498" s="105" t="s">
+        <v>31</v>
+      </c>
+      <c r="J498" s="139" t="s">
+        <v>3</v>
+      </c>
+      <c r="K498" s="105">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="L498" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="M498" s="105" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="499" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A499" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="B499" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="C499" s="152" t="s">
+        <v>36</v>
+      </c>
+      <c r="D499" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E499" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F499" s="18">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="G499" s="104">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="H499" s="18">
+        <v>0.59375</v>
+      </c>
+      <c r="I499" s="104">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="J499" s="18">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="K499" s="104">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L499" s="18">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="M499" s="104">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="500" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A500" s="65"/>
+      <c r="B500" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C500" s="152" t="s">
+        <v>132</v>
+      </c>
+      <c r="D500" s="12">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="E500" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F500" s="18">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="G500" s="105" t="s">
+        <v>37</v>
+      </c>
+      <c r="H500" s="18">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="I500" s="105" t="s">
+        <v>37</v>
+      </c>
+      <c r="J500" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="K500" s="104">
+        <v>0.8125</v>
+      </c>
+      <c r="L500" s="18">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M500" s="104">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="501" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A501" s="67"/>
+      <c r="B501" s="26"/>
+      <c r="C501" s="153"/>
+      <c r="D501" s="26"/>
+      <c r="E501" s="27"/>
+      <c r="F501" s="116"/>
+      <c r="G501" s="106"/>
+      <c r="H501" s="28"/>
+      <c r="I501" s="106"/>
+      <c r="J501" s="116"/>
+      <c r="K501" s="106"/>
+      <c r="L501" s="28"/>
+      <c r="M501" s="106"/>
+    </row>
+    <row r="502" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A502" s="31"/>
+      <c r="B502" s="34" t="s">
+        <v>487</v>
+      </c>
+      <c r="C502" s="147" t="s">
+        <v>259</v>
+      </c>
+      <c r="D502" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="E502" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F502" s="117" t="s">
+        <v>37</v>
+      </c>
+      <c r="G502" s="107" t="s">
+        <v>170</v>
+      </c>
+      <c r="H502" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I502" s="107" t="s">
+        <v>56</v>
+      </c>
+      <c r="J502" s="117" t="s">
+        <v>39</v>
+      </c>
+      <c r="K502" s="107" t="s">
+        <v>216</v>
+      </c>
+      <c r="L502" s="156">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="M502" s="107" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="503" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A503" s="39">
+        <v>46213</v>
+      </c>
+      <c r="B503" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="C503" s="148" t="s">
+        <v>190</v>
+      </c>
+      <c r="D503" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E503" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F503" s="119" t="s">
+        <v>25</v>
+      </c>
+      <c r="G503" s="108">
+        <v>0.4375</v>
+      </c>
+      <c r="H503" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="I503" s="108">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J503" s="119" t="s">
+        <v>8</v>
+      </c>
+      <c r="K503" s="109" t="s">
+        <v>25</v>
+      </c>
+      <c r="L503" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="M503" s="109" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="504" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A504" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B504" s="42" t="s">
+        <v>489</v>
+      </c>
+      <c r="C504" s="148" t="s">
+        <v>66</v>
+      </c>
+      <c r="D504" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="E504" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F504" s="118">
+        <v>0.625</v>
+      </c>
+      <c r="G504" s="108">
+        <v>0.75</v>
+      </c>
+      <c r="H504" s="48">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="I504" s="108">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="J504" s="118">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="K504" s="108">
+        <v>0.6875</v>
+      </c>
+      <c r="L504" s="48">
+        <v>0.5625</v>
+      </c>
+      <c r="M504" s="108">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="505" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A505" s="49"/>
+      <c r="B505" s="42" t="s">
+        <v>490</v>
+      </c>
+      <c r="C505" s="148">
+        <v>2.8</v>
+      </c>
+      <c r="D505" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="E505" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F505" s="118">
+        <v>0.875</v>
+      </c>
+      <c r="G505" s="109" t="s">
+        <v>7</v>
+      </c>
+      <c r="H505" s="48">
+        <v>0.875</v>
+      </c>
+      <c r="I505" s="109" t="s">
+        <v>7</v>
+      </c>
+      <c r="J505" s="118">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K505" s="108">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="L505" s="48">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="M505" s="109" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="506" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A506" s="51"/>
+      <c r="B506" s="54"/>
+      <c r="C506" s="150"/>
+      <c r="D506" s="54"/>
+      <c r="E506" s="55"/>
+      <c r="F506" s="120"/>
+      <c r="G506" s="110"/>
+      <c r="H506" s="56"/>
+      <c r="I506" s="110"/>
+      <c r="J506" s="120"/>
+      <c r="K506" s="110"/>
+      <c r="L506" s="56"/>
+      <c r="M506" s="110"/>
+    </row>
+    <row r="507" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A507" s="1"/>
+      <c r="B507" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C507" s="151" t="s">
+        <v>89</v>
+      </c>
+      <c r="D507" s="4">
+        <v>0.1875</v>
+      </c>
+      <c r="E507" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F507" s="136" t="s">
+        <v>7</v>
+      </c>
+      <c r="G507" s="111" t="s">
+        <v>58</v>
+      </c>
+      <c r="H507" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="I507" s="112" t="s">
+        <v>58</v>
+      </c>
+      <c r="J507" s="136" t="s">
+        <v>216</v>
+      </c>
+      <c r="K507" s="111" t="s">
+        <v>6</v>
+      </c>
+      <c r="L507" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="M507" s="112" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="508" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A508" s="82">
+        <v>46214</v>
+      </c>
+      <c r="B508" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="C508" s="152" t="s">
+        <v>190</v>
+      </c>
+      <c r="D508" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="E508" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F508" s="139" t="s">
+        <v>58</v>
+      </c>
+      <c r="G508" s="113">
+        <v>0.46875</v>
+      </c>
+      <c r="H508" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="I508" s="104">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="J508" s="139" t="s">
+        <v>6</v>
+      </c>
+      <c r="K508" s="115" t="s">
+        <v>68</v>
+      </c>
+      <c r="L508" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="M508" s="105">
+        <v>0.39583333333333331</v>
+      </c>
+    </row>
+    <row r="509" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A509" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B509" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="C509" s="152">
+        <v>0.4</v>
+      </c>
+      <c r="D509" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E509" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F509" s="124">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G509" s="113">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="H509" s="18">
+        <v>0.6875</v>
+      </c>
+      <c r="I509" s="104">
+        <v>0.78125</v>
+      </c>
+      <c r="J509" s="124">
+        <v>0.6875</v>
+      </c>
+      <c r="K509" s="113">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="L509" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="M509" s="104">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="510" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A510" s="114"/>
+      <c r="B510" s="12"/>
+      <c r="C510" s="152"/>
+      <c r="D510" s="12"/>
+      <c r="E510" s="13"/>
+      <c r="F510" s="124"/>
+      <c r="G510" s="113"/>
+      <c r="H510" s="18"/>
+      <c r="I510" s="104"/>
+      <c r="J510" s="124"/>
+      <c r="K510" s="113"/>
+      <c r="L510" s="18"/>
+      <c r="M510" s="104"/>
+    </row>
+    <row r="511" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A511" s="125"/>
+      <c r="B511" s="26"/>
+      <c r="C511" s="153"/>
+      <c r="D511" s="26"/>
+      <c r="E511" s="27"/>
+      <c r="F511" s="116"/>
+      <c r="G511" s="116"/>
+      <c r="H511" s="28"/>
+      <c r="I511" s="106"/>
+      <c r="J511" s="116"/>
+      <c r="K511" s="116"/>
+      <c r="L511" s="28"/>
+      <c r="M511" s="106"/>
+    </row>
+    <row r="512" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A512" s="70"/>
+      <c r="B512" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C512" s="147" t="s">
+        <v>183</v>
+      </c>
+      <c r="D512" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E512" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F512" s="143">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="G512" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="H512" s="143">
+        <v>0.96875</v>
+      </c>
+      <c r="I512" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="J512" s="143">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="K512" s="122">
+        <v>0.9375</v>
+      </c>
+      <c r="L512" s="143">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="M512" s="107" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="513" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A513" s="73">
+        <v>46215</v>
+      </c>
+      <c r="B513" s="42" t="s">
+        <v>494</v>
+      </c>
+      <c r="C513" s="148" t="s">
+        <v>136</v>
+      </c>
+      <c r="D513" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="E513" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F513" s="119" t="s">
+        <v>24</v>
+      </c>
+      <c r="G513" s="109" t="s">
+        <v>57</v>
+      </c>
+      <c r="H513" s="119" t="s">
+        <v>24</v>
+      </c>
+      <c r="I513" s="109" t="s">
+        <v>57</v>
+      </c>
+      <c r="J513" s="119" t="s">
+        <v>56</v>
+      </c>
+      <c r="K513" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="L513" s="119" t="s">
+        <v>216</v>
+      </c>
+      <c r="M513" s="109" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="514" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A514" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="B514" s="42" t="s">
+        <v>495</v>
+      </c>
+      <c r="C514" s="148" t="s">
+        <v>87</v>
+      </c>
+      <c r="D514" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="E514" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F514" s="119" t="s">
+        <v>57</v>
+      </c>
+      <c r="G514" s="108">
+        <v>0.5</v>
+      </c>
+      <c r="H514" s="119" t="s">
+        <v>57</v>
+      </c>
+      <c r="I514" s="108">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="J514" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="K514" s="109">
+        <v>0.3125</v>
+      </c>
+      <c r="L514" s="119">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M514" s="108">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="515" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A515" s="49"/>
+      <c r="B515" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C515" s="148" t="s">
+        <v>129</v>
+      </c>
+      <c r="D515" s="42">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E515" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F515" s="118">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G515" s="108">
+        <v>0.84375</v>
+      </c>
+      <c r="H515" s="118">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="I515" s="108">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="J515" s="118">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K515" s="108">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="L515" s="118">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M515" s="108">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="516" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A516" s="51"/>
+      <c r="B516" s="54"/>
+      <c r="C516" s="150"/>
+      <c r="D516" s="54"/>
+      <c r="E516" s="55"/>
+      <c r="F516" s="120"/>
+      <c r="G516" s="110"/>
+      <c r="H516" s="120"/>
+      <c r="I516" s="110"/>
+      <c r="J516" s="120"/>
+      <c r="K516" s="110"/>
+      <c r="L516" s="120"/>
+      <c r="M516" s="110"/>
+    </row>
+    <row r="517" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A517" s="1"/>
+      <c r="B517" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C517" s="151" t="s">
+        <v>87</v>
+      </c>
+      <c r="D517" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E517" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F517" s="136">
+        <v>0</v>
+      </c>
+      <c r="G517" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="H517" s="58">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="I517" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="J517" s="201">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="K517" s="121">
+        <v>0</v>
+      </c>
+      <c r="L517" s="58">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="M517" s="112" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="518" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A518" s="62">
+        <v>46216</v>
+      </c>
+      <c r="B518" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="C518" s="152" t="s">
+        <v>136</v>
+      </c>
+      <c r="D518" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E518" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F518" s="139" t="s">
+        <v>3</v>
+      </c>
+      <c r="G518" s="105" t="s">
+        <v>59</v>
+      </c>
+      <c r="H518" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="I518" s="105" t="s">
+        <v>59</v>
+      </c>
+      <c r="J518" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="K518" s="105" t="s">
+        <v>68</v>
+      </c>
+      <c r="L518" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="M518" s="105" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="519" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A519" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="B519" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="C519" s="152" t="s">
+        <v>2</v>
+      </c>
+      <c r="D519" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E519" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F519" s="139" t="s">
+        <v>59</v>
+      </c>
+      <c r="G519" s="104">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H519" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="I519" s="104">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J519" s="139" t="s">
+        <v>68</v>
+      </c>
+      <c r="K519" s="105">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L519" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="M519" s="104">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="520" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A520" s="65"/>
+      <c r="B520" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="C520" s="152" t="s">
+        <v>325</v>
+      </c>
+      <c r="D520" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E520" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F520" s="124">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="G520" s="104">
+        <v>0.875</v>
+      </c>
+      <c r="H520" s="18">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I520" s="105" t="s">
+        <v>235</v>
+      </c>
+      <c r="J520" s="124">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="K520" s="104">
+        <v>0.8125</v>
+      </c>
+      <c r="L520" s="18">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M520" s="104">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="521" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A521" s="67"/>
+      <c r="B521" s="26"/>
+      <c r="C521" s="153"/>
+      <c r="D521" s="26"/>
+      <c r="E521" s="27"/>
+      <c r="F521" s="86"/>
+      <c r="G521" s="87"/>
+      <c r="H521" s="85"/>
+      <c r="I521" s="87"/>
+      <c r="J521" s="86"/>
+      <c r="K521" s="87"/>
+      <c r="L521" s="85"/>
+      <c r="M521" s="87"/>
+    </row>
+    <row r="522" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A522" s="31"/>
+      <c r="B522" s="34" t="s">
+        <v>500</v>
+      </c>
+      <c r="C522" s="147" t="s">
+        <v>2</v>
+      </c>
+      <c r="D522" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="E522" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F522" s="117" t="s">
+        <v>22</v>
+      </c>
+      <c r="G522" s="107" t="s">
+        <v>8</v>
+      </c>
+      <c r="H522" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="I522" s="107" t="s">
+        <v>8</v>
+      </c>
+      <c r="J522" s="143">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="K522" s="107">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="L522" s="36">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="M522" s="107" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="523" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A523" s="39">
+        <v>46217</v>
+      </c>
+      <c r="B523" s="42" t="s">
+        <v>501</v>
+      </c>
+      <c r="C523" s="148" t="s">
+        <v>136</v>
+      </c>
+      <c r="D523" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E523" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F523" s="119" t="s">
+        <v>8</v>
+      </c>
+      <c r="G523" s="108">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H523" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="I523" s="108">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J523" s="119" t="s">
+        <v>68</v>
+      </c>
+      <c r="K523" s="109" t="s">
+        <v>46</v>
+      </c>
+      <c r="L523" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="M523" s="109" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="524" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A524" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B524" s="42" t="s">
+        <v>502</v>
+      </c>
+      <c r="C524" s="148" t="s">
+        <v>16</v>
+      </c>
+      <c r="D524" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="E524" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F524" s="118">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G524" s="108">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H524" s="48">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I524" s="108">
+        <v>0.5625</v>
+      </c>
+      <c r="J524" s="119" t="s">
+        <v>46</v>
+      </c>
+      <c r="K524" s="108">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L524" s="48">
+        <v>0.4375</v>
+      </c>
+      <c r="M524" s="108">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="525" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A525" s="49"/>
+      <c r="B525" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="C525" s="148" t="s">
+        <v>408</v>
+      </c>
+      <c r="D525" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="E525" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F525" s="118">
+        <v>0.8125</v>
+      </c>
+      <c r="G525" s="108">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="H525" s="48">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I525" s="108">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="J525" s="118">
+        <v>0.8125</v>
+      </c>
+      <c r="K525" s="108">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L525" s="48">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M525" s="108">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="526" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A526" s="51"/>
+      <c r="B526" s="54"/>
+      <c r="C526" s="150"/>
+      <c r="D526" s="54"/>
+      <c r="E526" s="55"/>
+      <c r="F526" s="120"/>
+      <c r="G526" s="110"/>
+      <c r="H526" s="56"/>
+      <c r="I526" s="110"/>
+      <c r="J526" s="120"/>
+      <c r="K526" s="110"/>
+      <c r="L526" s="56"/>
+      <c r="M526" s="110"/>
+    </row>
+    <row r="527" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A527" s="1"/>
+      <c r="B527" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C527" s="151" t="s">
+        <v>16</v>
+      </c>
+      <c r="D527" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E527" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F527" s="157">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G527" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="H527" s="159">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="I527" s="158" t="s">
+        <v>6</v>
+      </c>
+      <c r="J527" s="157" t="s">
+        <v>38</v>
+      </c>
+      <c r="K527" s="158" t="s">
+        <v>39</v>
+      </c>
+      <c r="L527" s="159" t="s">
+        <v>53</v>
+      </c>
+      <c r="M527" s="158" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="528" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A528" s="62">
+        <v>46218</v>
+      </c>
+      <c r="B528" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="C528" s="152" t="s">
+        <v>98</v>
+      </c>
+      <c r="D528" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E528" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F528" s="212" t="s">
+        <v>25</v>
+      </c>
+      <c r="G528" s="161">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H528" s="214" t="s">
+        <v>68</v>
+      </c>
+      <c r="I528" s="161">
+        <v>0.4375</v>
+      </c>
+      <c r="J528" s="212" t="s">
+        <v>57</v>
+      </c>
+      <c r="K528" s="213" t="s">
+        <v>59</v>
+      </c>
+      <c r="L528" s="214" t="s">
+        <v>6</v>
+      </c>
+      <c r="M528" s="213" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="529" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A529" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B529" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C529" s="152" t="s">
+        <v>41</v>
+      </c>
+      <c r="D529" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E529" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F529" s="160">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="G529" s="161">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H529" s="162">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I529" s="161">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J529" s="212" t="s">
+        <v>31</v>
+      </c>
+      <c r="K529" s="161">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="L529" s="162">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="M529" s="161">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="530" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A530" s="65"/>
+      <c r="B530" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="C530" s="152" t="s">
+        <v>408</v>
+      </c>
+      <c r="D530" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E530" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F530" s="160">
+        <v>0.84375</v>
+      </c>
+      <c r="G530" s="161">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="H530" s="162">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="I530" s="161">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="J530" s="160">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K530" s="161">
+        <v>0.875</v>
+      </c>
+      <c r="L530" s="162">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="M530" s="161">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="531" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A531" s="67"/>
+      <c r="B531" s="26"/>
+      <c r="C531" s="153"/>
+      <c r="D531" s="26"/>
+      <c r="E531" s="27"/>
+      <c r="F531" s="163"/>
+      <c r="G531" s="164"/>
+      <c r="H531" s="165"/>
+      <c r="I531" s="164"/>
+      <c r="J531" s="163"/>
+      <c r="K531" s="164"/>
+      <c r="L531" s="165"/>
+      <c r="M531" s="164"/>
+    </row>
+    <row r="532" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A532" s="31"/>
+      <c r="B532" s="34" t="s">
+        <v>505</v>
+      </c>
+      <c r="C532" s="147" t="s">
+        <v>16</v>
+      </c>
+      <c r="D532" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="E532" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F532" s="154" t="s">
+        <v>216</v>
+      </c>
+      <c r="G532" s="168" t="s">
+        <v>45</v>
+      </c>
+      <c r="H532" s="154" t="s">
+        <v>44</v>
+      </c>
+      <c r="I532" s="168" t="s">
+        <v>55</v>
+      </c>
+      <c r="J532" s="154" t="s">
+        <v>39</v>
+      </c>
+      <c r="K532" s="168" t="s">
+        <v>53</v>
+      </c>
+      <c r="L532" s="154" t="s">
+        <v>148</v>
+      </c>
+      <c r="M532" s="168" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="533" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A533" s="39">
+        <v>46219</v>
+      </c>
+      <c r="B533" s="42" t="s">
+        <v>506</v>
+      </c>
+      <c r="C533" s="148">
+        <v>2.4</v>
+      </c>
+      <c r="D533" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="E533" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F533" s="119" t="s">
+        <v>43</v>
+      </c>
+      <c r="G533" s="108">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H533" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="I533" s="108">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="J533" s="119" t="s">
+        <v>46</v>
+      </c>
+      <c r="K533" s="108">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L533" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="M533" s="109" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="534" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A534" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B534" s="42" t="s">
+        <v>465</v>
+      </c>
+      <c r="C534" s="148" t="s">
+        <v>41</v>
+      </c>
+      <c r="D534" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="E534" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F534" s="118">
+        <v>0.5</v>
+      </c>
+      <c r="G534" s="108">
+        <v>0.65625</v>
+      </c>
+      <c r="H534" s="118">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I534" s="108">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="J534" s="118">
+        <v>0.4375</v>
+      </c>
+      <c r="K534" s="108">
+        <v>0.5</v>
+      </c>
+      <c r="L534" s="118">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="M534" s="108">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="535" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A535" s="49"/>
+      <c r="B535" s="42" t="s">
+        <v>507</v>
+      </c>
+      <c r="C535" s="148" t="s">
+        <v>317</v>
+      </c>
+      <c r="D535" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="E535" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F535" s="118">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="G535" s="108">
+        <v>0.96875</v>
+      </c>
+      <c r="H535" s="118">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="I535" s="108">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="J535" s="118">
+        <v>0.875</v>
+      </c>
+      <c r="K535" s="108">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="L535" s="118">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M535" s="108">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="536" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A536" s="51"/>
+      <c r="B536" s="100"/>
+      <c r="C536" s="102"/>
+      <c r="D536" s="100"/>
+      <c r="E536" s="102"/>
+      <c r="F536" s="120"/>
+      <c r="G536" s="110"/>
+      <c r="H536" s="120"/>
+      <c r="I536" s="110"/>
+      <c r="J536" s="120"/>
+      <c r="K536" s="110"/>
+      <c r="L536" s="120"/>
+      <c r="M536" s="110"/>
+    </row>
+    <row r="537" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A537" s="169"/>
+      <c r="B537" s="170" t="s">
+        <v>508</v>
+      </c>
+      <c r="C537" s="171" t="s">
+        <v>16</v>
+      </c>
+      <c r="D537" s="172" t="s">
+        <v>170</v>
+      </c>
+      <c r="E537" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F537" s="58">
+        <v>0.125</v>
+      </c>
+      <c r="G537" s="112" t="s">
+        <v>45</v>
+      </c>
+      <c r="H537" s="58">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="I537" s="112" t="s">
+        <v>55</v>
+      </c>
+      <c r="J537" s="58" t="s">
+        <v>53</v>
+      </c>
+      <c r="K537" s="112" t="s">
+        <v>148</v>
+      </c>
+      <c r="L537" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="M537" s="112" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="538" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A538" s="62">
+        <v>46220</v>
+      </c>
+      <c r="B538" s="170" t="s">
+        <v>509</v>
+      </c>
+      <c r="C538" s="171" t="s">
+        <v>80</v>
+      </c>
+      <c r="D538" s="173" t="s">
+        <v>140</v>
+      </c>
+      <c r="E538" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F538" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G538" s="104">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H538" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="I538" s="104">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="J538" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K538" s="104">
+        <v>0.4375</v>
+      </c>
+      <c r="L538" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M538" s="105" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="539" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A539" s="174" t="s">
+        <v>48</v>
+      </c>
+      <c r="B539" s="170" t="s">
+        <v>510</v>
+      </c>
+      <c r="C539" s="171" t="s">
+        <v>16</v>
+      </c>
+      <c r="D539" s="173" t="s">
+        <v>186</v>
+      </c>
+      <c r="E539" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F539" s="18">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="G539" s="104">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="H539" s="18">
+        <v>0.5625</v>
+      </c>
+      <c r="I539" s="104">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="J539" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="K539" s="104">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="L539" s="18">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="M539" s="104">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="540" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A540" s="169"/>
+      <c r="B540" s="170" t="s">
+        <v>469</v>
+      </c>
+      <c r="C540" s="175" t="s">
+        <v>330</v>
+      </c>
+      <c r="D540" s="173" t="s">
+        <v>226</v>
+      </c>
+      <c r="E540" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F540" s="18">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="G540" s="105" t="s">
+        <v>37</v>
+      </c>
+      <c r="H540" s="18">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I540" s="104">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="J540" s="18">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="K540" s="104">
+        <v>0.9375</v>
+      </c>
+      <c r="L540" s="18">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="M540" s="104">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="541" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A541" s="169"/>
+      <c r="B541" s="170"/>
+      <c r="C541" s="175"/>
+      <c r="D541" s="173"/>
+      <c r="E541" s="176"/>
+      <c r="F541" s="28"/>
+      <c r="G541" s="106"/>
+      <c r="H541" s="28"/>
+      <c r="I541" s="106"/>
+      <c r="J541" s="28"/>
+      <c r="K541" s="106"/>
+      <c r="L541" s="28"/>
+      <c r="M541" s="106"/>
+    </row>
+    <row r="542" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A542" s="177"/>
+      <c r="B542" s="32" t="s">
+        <v>511</v>
+      </c>
+      <c r="C542" s="142" t="s">
+        <v>2</v>
+      </c>
+      <c r="D542" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="E542" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F542" s="36">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G542" s="107" t="s">
+        <v>78</v>
+      </c>
+      <c r="H542" s="36">
+        <v>0.1875</v>
+      </c>
+      <c r="I542" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="J542" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="K542" s="107" t="s">
+        <v>216</v>
+      </c>
+      <c r="L542" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="M542" s="107" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="543" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A543" s="73">
+        <v>46221</v>
+      </c>
+      <c r="B543" s="40" t="s">
+        <v>512</v>
+      </c>
+      <c r="C543" s="144" t="s">
+        <v>71</v>
+      </c>
+      <c r="D543" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="E543" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F543" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G543" s="108">
+        <v>0.5625</v>
+      </c>
+      <c r="H543" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="I543" s="108">
+        <v>0.53125</v>
+      </c>
+      <c r="J543" s="48">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K543" s="108">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="L543" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="M543" s="109" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="544" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A544" s="131" t="s">
+        <v>62</v>
+      </c>
+      <c r="B544" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="C544" s="144" t="s">
+        <v>87</v>
+      </c>
+      <c r="D544" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="E544" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F544" s="48">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G544" s="108">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="H544" s="48">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I544" s="108">
+        <v>0.71875</v>
+      </c>
+      <c r="J544" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="K544" s="108">
+        <v>0.5625</v>
+      </c>
+      <c r="L544" s="48">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="M544" s="108">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="545" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A545" s="131"/>
+      <c r="B545" s="40" t="s">
+        <v>513</v>
+      </c>
+      <c r="C545" s="144" t="s">
+        <v>364</v>
+      </c>
+      <c r="D545" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E545" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F545" s="48">
+        <v>0.90625</v>
+      </c>
+      <c r="G545" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="H545" s="48">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="I545" s="109" t="s">
+        <v>77</v>
+      </c>
+      <c r="J545" s="48">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K545" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="L545" s="48">
+        <v>0.875</v>
+      </c>
+      <c r="M545" s="108">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="546" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A546" s="178"/>
+      <c r="B546" s="52"/>
+      <c r="C546" s="145"/>
+      <c r="D546" s="54"/>
+      <c r="E546" s="55"/>
+      <c r="F546" s="56"/>
+      <c r="G546" s="110"/>
+      <c r="H546" s="56"/>
+      <c r="I546" s="110"/>
+      <c r="J546" s="56"/>
+      <c r="K546" s="110"/>
+      <c r="L546" s="56"/>
+      <c r="M546" s="110"/>
+    </row>
+    <row r="547" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A547" s="179"/>
+      <c r="B547" s="170" t="s">
+        <v>514</v>
+      </c>
+      <c r="C547" s="171" t="s">
+        <v>87</v>
+      </c>
+      <c r="D547" s="173" t="s">
+        <v>45</v>
+      </c>
+      <c r="E547" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F547" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="G547" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="H547" s="58" t="s">
+        <v>8</v>
+      </c>
+      <c r="I547" s="112" t="s">
+        <v>78</v>
+      </c>
+      <c r="J547" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="K547" s="111" t="s">
+        <v>44</v>
+      </c>
+      <c r="L547" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="M547" s="112" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="548" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A548" s="82">
+        <v>46222</v>
+      </c>
+      <c r="B548" s="170" t="s">
+        <v>515</v>
+      </c>
+      <c r="C548" s="171" t="s">
+        <v>249</v>
+      </c>
+      <c r="D548" s="173" t="s">
+        <v>47</v>
+      </c>
+      <c r="E548" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F548" s="18">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="G548" s="113">
+        <v>0.59375</v>
+      </c>
+      <c r="H548" s="18">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="I548" s="104">
+        <v>0.5625</v>
+      </c>
+      <c r="J548" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="K548" s="113">
+        <v>0.5</v>
+      </c>
+      <c r="L548" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="M548" s="104">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="549" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A549" s="180" t="s">
+        <v>73</v>
+      </c>
+      <c r="B549" s="170" t="s">
+        <v>516</v>
+      </c>
+      <c r="C549" s="171" t="s">
+        <v>183</v>
+      </c>
+      <c r="D549" s="173" t="s">
+        <v>122</v>
+      </c>
+      <c r="E549" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F549" s="18">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="G549" s="113">
+        <v>0.78125</v>
+      </c>
+      <c r="H549" s="18">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="I549" s="104">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="J549" s="18">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="K549" s="113">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="L549" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="M549" s="104">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="550" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A550" s="169"/>
+      <c r="B550" s="170" t="s">
+        <v>329</v>
+      </c>
+      <c r="C550" s="171" t="s">
+        <v>66</v>
+      </c>
+      <c r="D550" s="173" t="s">
+        <v>37</v>
+      </c>
+      <c r="E550" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F550" s="18">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G550" s="115" t="s">
+        <v>22</v>
+      </c>
+      <c r="H550" s="18">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="I550" s="105" t="s">
+        <v>85</v>
+      </c>
+      <c r="J550" s="18">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="K550" s="115" t="s">
+        <v>37</v>
+      </c>
+      <c r="L550" s="18">
+        <v>0.875</v>
+      </c>
+      <c r="M550" s="104">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="551" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A551" s="169"/>
+      <c r="B551" s="170"/>
+      <c r="C551" s="171"/>
+      <c r="D551" s="173"/>
+      <c r="E551" s="13"/>
+      <c r="F551" s="28"/>
+      <c r="G551" s="116"/>
+      <c r="H551" s="28"/>
+      <c r="I551" s="106"/>
+      <c r="J551" s="28"/>
+      <c r="K551" s="116"/>
+      <c r="L551" s="28"/>
+      <c r="M551" s="106"/>
+    </row>
+    <row r="552" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A552" s="177"/>
+      <c r="B552" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="C552" s="147" t="s">
+        <v>190</v>
+      </c>
+      <c r="D552" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="E552" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F552" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="G552" s="107" t="s">
+        <v>46</v>
+      </c>
+      <c r="H552" s="117" t="s">
+        <v>170</v>
+      </c>
+      <c r="I552" s="107" t="s">
+        <v>57</v>
+      </c>
+      <c r="J552" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="K552" s="107" t="s">
+        <v>3</v>
+      </c>
+      <c r="L552" s="117" t="s">
+        <v>56</v>
+      </c>
+      <c r="M552" s="107" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="553" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A553" s="181">
+        <v>46223</v>
+      </c>
+      <c r="B553" s="42" t="s">
+        <v>517</v>
+      </c>
+      <c r="C553" s="148" t="s">
+        <v>112</v>
+      </c>
+      <c r="D553" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="E553" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F553" s="48">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="G553" s="108">
+        <v>0.625</v>
+      </c>
+      <c r="H553" s="118">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I553" s="108">
+        <v>0.59375</v>
+      </c>
+      <c r="J553" s="48">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="K553" s="108">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="L553" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="M553" s="108">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="554" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A554" s="181" t="s">
+        <v>82</v>
+      </c>
+      <c r="B554" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="C554" s="148" t="s">
+        <v>158</v>
+      </c>
+      <c r="D554" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="E554" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F554" s="48">
+        <v>0.65625</v>
+      </c>
+      <c r="G554" s="108">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H554" s="118">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="I554" s="108">
+        <v>0.8125</v>
+      </c>
+      <c r="J554" s="48">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="K554" s="108">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="L554" s="118">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M554" s="108">
+        <v>0.77083333333333337</v>
+      </c>
+    </row>
+    <row r="555" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A555" s="181"/>
+      <c r="B555" s="42" t="s">
+        <v>518</v>
+      </c>
+      <c r="C555" s="148" t="s">
+        <v>36</v>
+      </c>
+      <c r="D555" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="E555" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F555" s="48">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="G555" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="H555" s="118">
+        <v>0.96875</v>
+      </c>
+      <c r="I555" s="109" t="s">
+        <v>39</v>
+      </c>
+      <c r="J555" s="48">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="K555" s="109">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="L555" s="118">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="M555" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="556" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A556" s="182"/>
+      <c r="B556" s="54"/>
+      <c r="C556" s="150"/>
+      <c r="D556" s="54"/>
+      <c r="E556" s="55"/>
+      <c r="F556" s="56"/>
+      <c r="G556" s="110"/>
+      <c r="H556" s="120"/>
+      <c r="I556" s="110"/>
+      <c r="J556" s="56"/>
+      <c r="K556" s="110"/>
+      <c r="L556" s="120"/>
+      <c r="M556" s="110"/>
+    </row>
+    <row r="557" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A557" s="169"/>
+      <c r="B557" s="170" t="s">
+        <v>519</v>
+      </c>
+      <c r="C557" s="171" t="s">
+        <v>190</v>
+      </c>
+      <c r="D557" s="173" t="s">
+        <v>78</v>
+      </c>
+      <c r="E557" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F557" s="58" t="s">
+        <v>170</v>
+      </c>
+      <c r="G557" s="112" t="s">
+        <v>59</v>
+      </c>
+      <c r="H557" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="I557" s="112" t="s">
+        <v>46</v>
+      </c>
+      <c r="J557" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="K557" s="112" t="s">
+        <v>56</v>
+      </c>
+      <c r="L557" s="58" t="s">
+        <v>8</v>
+      </c>
+      <c r="M557" s="112" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="558" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A558" s="169">
+        <v>46224</v>
+      </c>
+      <c r="B558" s="170" t="s">
+        <v>520</v>
+      </c>
+      <c r="C558" s="171" t="s">
+        <v>19</v>
+      </c>
+      <c r="D558" s="173" t="s">
+        <v>99</v>
+      </c>
+      <c r="E558" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F558" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="G558" s="104">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H558" s="18">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I558" s="104">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J558" s="18">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="K558" s="104">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L558" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="M558" s="104">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="559" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A559" s="169" t="s">
+        <v>91</v>
+      </c>
+      <c r="B559" s="170" t="s">
+        <v>521</v>
+      </c>
+      <c r="C559" s="171" t="s">
+        <v>132</v>
+      </c>
+      <c r="D559" s="173" t="s">
+        <v>227</v>
+      </c>
+      <c r="E559" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F559" s="18">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="G559" s="104">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="H559" s="18">
+        <v>0.71875</v>
+      </c>
+      <c r="I559" s="104">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="J559" s="18">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="K559" s="104">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="L559" s="18">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M559" s="104">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="560" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A560" s="169"/>
+      <c r="B560" s="170"/>
+      <c r="C560" s="171"/>
+      <c r="D560" s="173"/>
+      <c r="E560" s="176"/>
+      <c r="F560" s="18"/>
+      <c r="G560" s="104"/>
+      <c r="H560" s="18"/>
+      <c r="I560" s="104"/>
+      <c r="J560" s="18"/>
+      <c r="K560" s="104"/>
+      <c r="L560" s="18"/>
+      <c r="M560" s="104"/>
+    </row>
+    <row r="561" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A561" s="169"/>
+      <c r="B561" s="170"/>
+      <c r="C561" s="171"/>
+      <c r="D561" s="173"/>
+      <c r="E561" s="13"/>
+      <c r="F561" s="85"/>
+      <c r="G561" s="87"/>
+      <c r="H561" s="85"/>
+      <c r="I561" s="87"/>
+      <c r="J561" s="85"/>
+      <c r="K561" s="87"/>
+      <c r="L561" s="85"/>
+      <c r="M561" s="87"/>
+    </row>
+    <row r="562" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A562" s="177"/>
+      <c r="B562" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="C562" s="147" t="s">
+        <v>60</v>
+      </c>
+      <c r="D562" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="E562" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F562" s="156">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G562" s="107" t="s">
+        <v>44</v>
+      </c>
+      <c r="H562" s="156">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I562" s="107" t="s">
+        <v>26</v>
+      </c>
+      <c r="J562" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="K562" s="107" t="s">
+        <v>39</v>
+      </c>
+      <c r="L562" s="156">
+        <v>0.875</v>
+      </c>
+      <c r="M562" s="122">
+        <v>0.97916666666666663</v>
+      </c>
+    </row>
+    <row r="563" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A563" s="183">
+        <v>46225</v>
+      </c>
+      <c r="B563" s="42" t="s">
+        <v>522</v>
+      </c>
+      <c r="C563" s="148" t="s">
+        <v>96</v>
+      </c>
+      <c r="D563" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E563" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F563" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="G563" s="109" t="s">
+        <v>13</v>
+      </c>
+      <c r="H563" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="I563" s="109" t="s">
+        <v>69</v>
+      </c>
+      <c r="J563" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="K563" s="109" t="s">
+        <v>8</v>
+      </c>
+      <c r="L563" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="M563" s="109">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="564" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A564" s="183" t="s">
+        <v>14</v>
+      </c>
+      <c r="B564" s="42" t="s">
+        <v>523</v>
+      </c>
+      <c r="C564" s="148" t="s">
+        <v>29</v>
+      </c>
+      <c r="D564" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="E564" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F564" s="48">
+        <v>0.53125</v>
+      </c>
+      <c r="G564" s="108">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="H564" s="48">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="I564" s="108">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J564" s="48">
+        <v>0.5625</v>
+      </c>
+      <c r="K564" s="108">
+        <v>0.625</v>
+      </c>
+      <c r="L564" s="48">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="M564" s="108">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="565" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A565" s="183"/>
+      <c r="B565" s="42" t="s">
+        <v>524</v>
+      </c>
+      <c r="C565" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="D565" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="E565" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F565" s="48">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="G565" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="H565" s="48">
+        <v>0.78125</v>
+      </c>
+      <c r="I565" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="J565" s="48">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K565" s="108">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L565" s="48">
+        <v>0.8125</v>
+      </c>
+      <c r="M565" s="108">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="566" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A566" s="202"/>
+      <c r="B566" s="54"/>
+      <c r="C566" s="150"/>
+      <c r="D566" s="54"/>
+      <c r="E566" s="55"/>
+      <c r="F566" s="56"/>
+      <c r="G566" s="110"/>
+      <c r="H566" s="56"/>
+      <c r="I566" s="110"/>
+      <c r="J566" s="56"/>
+      <c r="K566" s="110"/>
+      <c r="L566" s="56"/>
+      <c r="M566" s="110"/>
+    </row>
+    <row r="567" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A567" s="169"/>
+      <c r="B567" s="173" t="s">
+        <v>525</v>
+      </c>
+      <c r="C567" s="185" t="s">
+        <v>259</v>
+      </c>
+      <c r="D567" s="173" t="s">
+        <v>53</v>
+      </c>
+      <c r="E567" s="184" t="s">
+        <v>12</v>
+      </c>
+      <c r="F567" s="132">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="G567" s="112" t="s">
+        <v>56</v>
+      </c>
+      <c r="H567" s="132">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="I567" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="J567" s="132">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K567" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="L567" s="132">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="M567" s="121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A568" s="169">
+        <v>46226</v>
+      </c>
+      <c r="B568" s="173" t="s">
+        <v>526</v>
+      </c>
+      <c r="C568" s="185" t="s">
+        <v>183</v>
+      </c>
+      <c r="D568" s="173" t="s">
+        <v>46</v>
+      </c>
+      <c r="E568" s="184" t="s">
+        <v>4</v>
+      </c>
+      <c r="F568" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G568" s="105" t="s">
+        <v>114</v>
+      </c>
+      <c r="H568" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I568" s="105" t="s">
+        <v>13</v>
+      </c>
+      <c r="J568" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="K568" s="105" t="s">
+        <v>6</v>
+      </c>
+      <c r="L568" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M568" s="105" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="569" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A569" s="169" t="s">
+        <v>32</v>
+      </c>
+      <c r="B569" s="173" t="s">
+        <v>472</v>
+      </c>
+      <c r="C569" s="185" t="s">
+        <v>36</v>
+      </c>
+      <c r="D569" s="173" t="s">
+        <v>193</v>
+      </c>
+      <c r="E569" s="184" t="s">
+        <v>12</v>
+      </c>
+      <c r="F569" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G569" s="104">
+        <v>0.75</v>
+      </c>
+      <c r="H569" s="18">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I569" s="104">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="J569" s="18">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="K569" s="104">
+        <v>0.6875</v>
+      </c>
+      <c r="L569" s="18">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="M569" s="105">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="570" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A570" s="169"/>
+      <c r="B570" s="173" t="s">
+        <v>527</v>
+      </c>
+      <c r="C570" s="185" t="s">
+        <v>132</v>
+      </c>
+      <c r="D570" s="173" t="s">
+        <v>226</v>
+      </c>
+      <c r="E570" s="92" t="s">
+        <v>4</v>
+      </c>
+      <c r="F570" s="18">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G570" s="105" t="s">
+        <v>37</v>
+      </c>
+      <c r="H570" s="18">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="I570" s="105" t="s">
+        <v>37</v>
+      </c>
+      <c r="J570" s="18">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K570" s="104">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L570" s="18">
+        <v>0.875</v>
+      </c>
+      <c r="M570" s="105" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="571" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A571" s="169"/>
+      <c r="B571" s="173"/>
+      <c r="C571" s="185"/>
+      <c r="D571" s="173"/>
+      <c r="E571" s="13"/>
+      <c r="F571" s="28"/>
+      <c r="G571" s="106"/>
+      <c r="H571" s="28"/>
+      <c r="I571" s="106"/>
+      <c r="J571" s="28"/>
+      <c r="K571" s="106"/>
+      <c r="L571" s="28"/>
+      <c r="M571" s="106"/>
+    </row>
+    <row r="572" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A572" s="186"/>
+      <c r="B572" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C572" s="147">
+        <v>2.4</v>
+      </c>
+      <c r="D572" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E572" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F572" s="126" t="s">
+        <v>37</v>
+      </c>
+      <c r="G572" s="168" t="s">
+        <v>27</v>
+      </c>
+      <c r="H572" s="154" t="s">
+        <v>37</v>
+      </c>
+      <c r="I572" s="168" t="s">
+        <v>27</v>
+      </c>
+      <c r="J572" s="126" t="s">
+        <v>39</v>
+      </c>
+      <c r="K572" s="168" t="s">
+        <v>56</v>
+      </c>
+      <c r="L572" s="154" t="s">
+        <v>21</v>
+      </c>
+      <c r="M572" s="168" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="573" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A573" s="187">
+        <v>46227</v>
+      </c>
+      <c r="B573" s="42" t="s">
+        <v>528</v>
+      </c>
+      <c r="C573" s="148" t="s">
+        <v>183</v>
+      </c>
+      <c r="D573" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="E573" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F573" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="G573" s="108">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H573" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="I573" s="109" t="s">
+        <v>114</v>
+      </c>
+      <c r="J573" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="K573" s="109">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="L573" s="119">
+        <v>0.25</v>
+      </c>
+      <c r="M573" s="109" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="574" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A574" s="187" t="s">
+        <v>48</v>
+      </c>
+      <c r="B574" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="C574" s="148" t="s">
+        <v>52</v>
+      </c>
+      <c r="D574" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="E574" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F574" s="48">
+        <v>0.625</v>
+      </c>
+      <c r="G574" s="108">
+        <v>0.78125</v>
+      </c>
+      <c r="H574" s="118">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="I574" s="108">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="J574" s="48">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="K574" s="108">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="L574" s="118">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="M574" s="108">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="575" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A575" s="187"/>
+      <c r="B575" s="42"/>
+      <c r="C575" s="148"/>
+      <c r="D575" s="42"/>
+      <c r="E575" s="43"/>
+      <c r="F575" s="48"/>
+      <c r="G575" s="108"/>
+      <c r="H575" s="118"/>
+      <c r="I575" s="108"/>
+      <c r="J575" s="48"/>
+      <c r="K575" s="108"/>
+      <c r="L575" s="118"/>
+      <c r="M575" s="108"/>
+    </row>
+    <row r="576" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A576" s="188"/>
+      <c r="B576" s="189"/>
+      <c r="C576" s="190"/>
+      <c r="D576" s="100"/>
+      <c r="E576" s="102"/>
+      <c r="F576" s="56"/>
+      <c r="G576" s="110"/>
+      <c r="H576" s="120"/>
+      <c r="I576" s="110"/>
+      <c r="J576" s="56"/>
+      <c r="K576" s="110"/>
+      <c r="L576" s="120"/>
+      <c r="M576" s="110"/>
+    </row>
+    <row r="577" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A577" s="191"/>
+      <c r="B577" s="172" t="s">
+        <v>300</v>
+      </c>
+      <c r="C577" s="192" t="s">
+        <v>136</v>
+      </c>
+      <c r="D577" s="172" t="s">
+        <v>38</v>
+      </c>
+      <c r="E577" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F577" s="132">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="G577" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="H577" s="137">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="I577" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="J577" s="132">
+        <v>0.875</v>
+      </c>
+      <c r="K577" s="91">
+        <v>0.9375</v>
+      </c>
+      <c r="L577" s="137">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="M577" s="61" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="578" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A578" s="193">
+        <v>46228</v>
+      </c>
+      <c r="B578" s="173" t="s">
+        <v>455</v>
+      </c>
+      <c r="C578" s="185" t="s">
+        <v>98</v>
+      </c>
+      <c r="D578" s="173" t="s">
+        <v>163</v>
+      </c>
+      <c r="E578" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F578" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G578" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H578" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="I578" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="J578" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="K578" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="L578" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="M578" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="579" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A579" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="B579" s="173" t="s">
+        <v>529</v>
+      </c>
+      <c r="C579" s="185" t="s">
+        <v>183</v>
+      </c>
+      <c r="D579" s="173" t="s">
+        <v>114</v>
+      </c>
+      <c r="E579" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F579" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G579" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H579" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="I579" s="15">
+        <v>0.4375</v>
+      </c>
+      <c r="J579" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="K579" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="L579" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="M579" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="580" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A580" s="194"/>
+      <c r="B580" s="173" t="s">
+        <v>34</v>
+      </c>
+      <c r="C580" s="185" t="s">
+        <v>66</v>
+      </c>
+      <c r="D580" s="173" t="s">
+        <v>50</v>
+      </c>
+      <c r="E580" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F580" s="18">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G580" s="15">
+        <v>0.8125</v>
+      </c>
+      <c r="H580" s="16">
+        <v>0.6875</v>
+      </c>
+      <c r="I580" s="15">
+        <v>0.78125</v>
+      </c>
+      <c r="J580" s="18">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="K580" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="L580" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="M580" s="15">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="581" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A581" s="194"/>
+      <c r="B581" s="173"/>
+      <c r="C581" s="185"/>
+      <c r="D581" s="173"/>
+      <c r="E581" s="176"/>
+      <c r="F581" s="28"/>
+      <c r="G581" s="29"/>
+      <c r="H581" s="69"/>
+      <c r="I581" s="29"/>
+      <c r="J581" s="28"/>
+      <c r="K581" s="29"/>
+      <c r="L581" s="69"/>
+      <c r="M581" s="29"/>
+    </row>
+    <row r="582" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A582" s="195"/>
+      <c r="B582" s="34" t="s">
+        <v>530</v>
+      </c>
+      <c r="C582" s="147" t="s">
+        <v>142</v>
+      </c>
+      <c r="D582" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="E582" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F582" s="156">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="G582" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="H582" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="I582" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="J582" s="156">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K582" s="96">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="L582" s="200">
+        <v>0</v>
+      </c>
+      <c r="M582" s="37" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="583" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A583" s="196">
+        <v>46229</v>
+      </c>
+      <c r="B583" s="42" t="s">
+        <v>531</v>
+      </c>
+      <c r="C583" s="148" t="s">
+        <v>136</v>
+      </c>
+      <c r="D583" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="E583" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F583" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="G583" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="H583" s="88" t="s">
+        <v>44</v>
+      </c>
+      <c r="I583" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="J583" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="K583" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="L583" s="88" t="s">
+        <v>148</v>
+      </c>
+      <c r="M583" s="50" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="584" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A584" s="196" t="s">
+        <v>73</v>
+      </c>
+      <c r="B584" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C584" s="148" t="s">
+        <v>183</v>
+      </c>
+      <c r="D584" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E584" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F584" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G584" s="45">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H584" s="88" t="s">
+        <v>58</v>
+      </c>
+      <c r="I584" s="45">
+        <v>0.46875</v>
+      </c>
+      <c r="J584" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="K584" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="L584" s="88" t="s">
+        <v>68</v>
+      </c>
+      <c r="M584" s="45">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="585" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A585" s="187"/>
+      <c r="B585" s="42" t="s">
+        <v>532</v>
+      </c>
+      <c r="C585" s="148" t="s">
+        <v>274</v>
+      </c>
+      <c r="D585" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="E585" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F585" s="48">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G585" s="45">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="H585" s="46">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="I585" s="45">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J585" s="48">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K585" s="45">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L585" s="46">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="M585" s="45">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="586" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A586" s="197"/>
+      <c r="B586" s="54"/>
+      <c r="C586" s="150"/>
+      <c r="D586" s="54"/>
+      <c r="E586" s="55"/>
+      <c r="F586" s="56"/>
+      <c r="G586" s="57"/>
+      <c r="H586" s="54"/>
+      <c r="I586" s="57"/>
+      <c r="J586" s="56"/>
+      <c r="K586" s="57"/>
+      <c r="L586" s="54"/>
+      <c r="M586" s="57"/>
+    </row>
+    <row r="587" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A587" s="198"/>
+      <c r="B587" s="173" t="s">
+        <v>487</v>
+      </c>
+      <c r="C587" s="185" t="s">
+        <v>183</v>
+      </c>
+      <c r="D587" s="173" t="s">
+        <v>26</v>
+      </c>
+      <c r="E587" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F587" s="58">
+        <v>0</v>
+      </c>
+      <c r="G587" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="H587" s="60">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="I587" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="J587" s="132">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K587" s="244">
+        <v>0</v>
+      </c>
+      <c r="L587" s="60">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="M587" s="61" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="588" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A588" s="199">
+        <v>46230</v>
+      </c>
+      <c r="B588" s="173" t="s">
+        <v>519</v>
+      </c>
+      <c r="C588" s="185" t="s">
+        <v>98</v>
+      </c>
+      <c r="D588" s="173" t="s">
+        <v>43</v>
+      </c>
+      <c r="E588" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F588" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G588" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="H588" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="I588" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="J588" s="18">
+        <v>0.25</v>
+      </c>
+      <c r="K588" s="63">
+        <v>0.3125</v>
+      </c>
+      <c r="L588" s="84" t="s">
+        <v>216</v>
+      </c>
+      <c r="M588" s="22">
+        <v>0.22916666666666666</v>
+      </c>
+    </row>
+    <row r="589" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A589" s="199" t="s">
+        <v>82</v>
+      </c>
+      <c r="B589" s="173" t="s">
+        <v>327</v>
+      </c>
+      <c r="C589" s="185" t="s">
+        <v>96</v>
+      </c>
+      <c r="D589" s="173" t="s">
+        <v>113</v>
+      </c>
+      <c r="E589" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F589" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G589" s="63">
+        <v>0.53125</v>
+      </c>
+      <c r="H589" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I589" s="15">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="J589" s="18">
+        <v>0.3125</v>
+      </c>
+      <c r="K589" s="63">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L589" s="84">
+        <v>0.375</v>
+      </c>
+      <c r="M589" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="590" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A590" s="198"/>
+      <c r="B590" s="173" t="s">
+        <v>533</v>
+      </c>
+      <c r="C590" s="185" t="s">
+        <v>147</v>
+      </c>
+      <c r="D590" s="173" t="s">
+        <v>154</v>
+      </c>
+      <c r="E590" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F590" s="18">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="G590" s="63">
+        <v>0.875</v>
+      </c>
+      <c r="H590" s="16">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="I590" s="15">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J590" s="18">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="K590" s="63">
+        <v>0.8125</v>
+      </c>
+      <c r="L590" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M590" s="15">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="591" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A591" s="198"/>
+      <c r="B591" s="173"/>
+      <c r="C591" s="185"/>
+      <c r="D591" s="173"/>
+      <c r="E591" s="176"/>
+      <c r="F591" s="28"/>
+      <c r="G591" s="321" t="s">
+        <v>546</v>
+      </c>
+      <c r="H591" s="69"/>
+      <c r="I591" s="29"/>
+      <c r="J591" s="28"/>
+      <c r="K591" s="30"/>
+      <c r="L591" s="69"/>
+      <c r="M591" s="29"/>
+    </row>
+    <row r="592" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A592" s="186"/>
+      <c r="B592" s="34" t="s">
+        <v>534</v>
+      </c>
+      <c r="C592" s="147" t="s">
+        <v>96</v>
+      </c>
+      <c r="D592" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E592" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F592" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="G592" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="H592" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="I592" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="J592" s="322">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="K592" s="323">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="L592" s="72">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="M592" s="37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="593" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A593" s="187">
+        <v>46231</v>
+      </c>
+      <c r="B593" s="42" t="s">
+        <v>535</v>
+      </c>
+      <c r="C593" s="148" t="s">
+        <v>132</v>
+      </c>
+      <c r="D593" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E593" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F593" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="G593" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="H593" s="99" t="s">
+        <v>8</v>
+      </c>
+      <c r="I593" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J593" s="324" t="s">
+        <v>68</v>
+      </c>
+      <c r="K593" s="325" t="s">
+        <v>57</v>
+      </c>
+      <c r="L593" s="99" t="s">
+        <v>3</v>
+      </c>
+      <c r="M593" s="50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="594" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A594" s="187" t="s">
+        <v>91</v>
+      </c>
+      <c r="B594" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="C594" s="148" t="s">
+        <v>96</v>
+      </c>
+      <c r="D594" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E594" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F594" s="44">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="G594" s="45">
+        <v>0.5625</v>
+      </c>
+      <c r="H594" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="I594" s="45">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J594" s="324" t="s">
+        <v>57</v>
+      </c>
+      <c r="K594" s="325">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="L594" s="75">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M594" s="45">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="595" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A595" s="187"/>
+      <c r="B595" s="42" t="s">
+        <v>536</v>
+      </c>
+      <c r="C595" s="148" t="s">
+        <v>117</v>
+      </c>
+      <c r="D595" s="42" t="s">
+        <v>355</v>
+      </c>
+      <c r="E595" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F595" s="48">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="G595" s="45">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="H595" s="75">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I595" s="45">
+        <v>0.875</v>
+      </c>
+      <c r="J595" s="326">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K595" s="327">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L595" s="75">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M595" s="45">
+        <v>0.77083333333333337</v>
+      </c>
+    </row>
+    <row r="596" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A596" s="197"/>
+      <c r="B596" s="54"/>
+      <c r="C596" s="150"/>
+      <c r="D596" s="54"/>
+      <c r="E596" s="55"/>
+      <c r="F596" s="56"/>
+      <c r="G596" s="57"/>
+      <c r="H596" s="80"/>
+      <c r="I596" s="57"/>
+      <c r="J596" s="56"/>
+      <c r="K596" s="57"/>
+      <c r="L596" s="80"/>
+      <c r="M596" s="57"/>
+    </row>
+    <row r="597" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A597" s="198"/>
+      <c r="B597" s="173" t="s">
+        <v>537</v>
+      </c>
+      <c r="C597" s="185" t="s">
+        <v>190</v>
+      </c>
+      <c r="D597" s="173" t="s">
+        <v>229</v>
+      </c>
+      <c r="E597" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F597" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="G597" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="H597" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="I597" s="61" t="s">
+        <v>170</v>
+      </c>
+      <c r="J597" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="K597" s="61" t="s">
+        <v>38</v>
+      </c>
+      <c r="L597" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="M597" s="61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="598" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A598" s="198">
+        <v>46232</v>
+      </c>
+      <c r="B598" s="173" t="s">
+        <v>538</v>
+      </c>
+      <c r="C598" s="185" t="s">
+        <v>89</v>
+      </c>
+      <c r="D598" s="173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E598" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F598" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G598" s="15">
+        <v>0.4375</v>
+      </c>
+      <c r="H598" s="84" t="s">
+        <v>25</v>
+      </c>
+      <c r="I598" s="15">
+        <v>0.4375</v>
+      </c>
+      <c r="J598" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="K598" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="L598" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="M598" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="599" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A599" s="198" t="s">
+        <v>14</v>
+      </c>
+      <c r="B599" s="173" t="s">
+        <v>362</v>
+      </c>
+      <c r="C599" s="185" t="s">
+        <v>190</v>
+      </c>
+      <c r="D599" s="173" t="s">
+        <v>81</v>
+      </c>
+      <c r="E599" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F599" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="G599" s="15">
+        <v>0.59375</v>
+      </c>
+      <c r="H599" s="16">
+        <v>0.4375</v>
+      </c>
+      <c r="I599" s="15">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="J599" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K599" s="15">
+        <v>0.4375</v>
+      </c>
+      <c r="L599" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="M599" s="15">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="600" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A600" s="198"/>
+      <c r="B600" s="173" t="s">
+        <v>539</v>
+      </c>
+      <c r="C600" s="185" t="s">
+        <v>364</v>
+      </c>
+      <c r="D600" s="173" t="s">
+        <v>51</v>
+      </c>
+      <c r="E600" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F600" s="18">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G600" s="15">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="H600" s="16">
+        <v>0.8125</v>
+      </c>
+      <c r="I600" s="15">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="J600" s="18">
+        <v>0.8125</v>
+      </c>
+      <c r="K600" s="15">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L600" s="16">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M600" s="15">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="601" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A601" s="198"/>
+      <c r="B601" s="173"/>
+      <c r="C601" s="185"/>
+      <c r="D601" s="173"/>
+      <c r="E601" s="176"/>
+      <c r="F601" s="85"/>
+      <c r="G601" s="87"/>
+      <c r="H601" s="85"/>
+      <c r="I601" s="87"/>
+      <c r="J601" s="85"/>
+      <c r="K601" s="87"/>
+      <c r="L601" s="85"/>
+      <c r="M601" s="87"/>
+    </row>
+    <row r="602" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A602" s="186"/>
+      <c r="B602" s="34" t="s">
+        <v>491</v>
+      </c>
+      <c r="C602" s="147" t="s">
+        <v>190</v>
+      </c>
+      <c r="D602" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E602" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F602" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="G602" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="H602" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="I602" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="J602" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K602" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="L602" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="M602" s="37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="603" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A603" s="187">
+        <v>46233</v>
+      </c>
+      <c r="B603" s="42" t="s">
+        <v>540</v>
+      </c>
+      <c r="C603" s="148" t="s">
+        <v>264</v>
+      </c>
+      <c r="D603" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E603" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F603" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="G603" s="45">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H603" s="88" t="s">
+        <v>68</v>
+      </c>
+      <c r="I603" s="45">
+        <v>0.4375</v>
+      </c>
+      <c r="J603" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="K603" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="L603" s="88" t="s">
+        <v>6</v>
+      </c>
+      <c r="M603" s="50" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="604" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A604" s="187" t="s">
+        <v>32</v>
+      </c>
+      <c r="B604" s="42" t="s">
+        <v>541</v>
+      </c>
+      <c r="C604" s="148" t="s">
+        <v>87</v>
+      </c>
+      <c r="D604" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="E604" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F604" s="48">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="G604" s="45">
+        <v>0.625</v>
+      </c>
+      <c r="H604" s="46">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="I604" s="45">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="J604" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="K604" s="45">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="L604" s="46">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="M604" s="45">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="605" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A605" s="187"/>
+      <c r="B605" s="42" t="s">
+        <v>542</v>
+      </c>
+      <c r="C605" s="148" t="s">
+        <v>124</v>
+      </c>
+      <c r="D605" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="E605" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F605" s="48">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="G605" s="45">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="H605" s="46">
+        <v>0.84375</v>
+      </c>
+      <c r="I605" s="45">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="J605" s="48">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K605" s="45">
+        <v>0.875</v>
+      </c>
+      <c r="L605" s="46">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M605" s="45">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="606" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A606" s="197"/>
+      <c r="B606" s="54"/>
+      <c r="C606" s="150"/>
+      <c r="D606" s="54"/>
+      <c r="E606" s="55"/>
+      <c r="F606" s="56"/>
+      <c r="G606" s="57"/>
+      <c r="H606" s="54"/>
+      <c r="I606" s="57"/>
+      <c r="J606" s="56"/>
+      <c r="K606" s="57"/>
+      <c r="L606" s="54"/>
+      <c r="M606" s="57"/>
+    </row>
+    <row r="607" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A607" s="191"/>
+      <c r="B607" s="172" t="s">
+        <v>229</v>
+      </c>
+      <c r="C607" s="192" t="s">
+        <v>87</v>
+      </c>
+      <c r="D607" s="172" t="s">
+        <v>56</v>
+      </c>
+      <c r="E607" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F607" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="G607" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="H607" s="60" t="s">
+        <v>216</v>
+      </c>
+      <c r="I607" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="J607" s="58">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="K607" s="61">
+        <v>6.25E-2</v>
+      </c>
+      <c r="L607" s="60">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="M607" s="61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="608" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A608" s="198">
+        <v>46234</v>
+      </c>
+      <c r="B608" s="173" t="s">
+        <v>543</v>
+      </c>
+      <c r="C608" s="185" t="s">
+        <v>80</v>
+      </c>
+      <c r="D608" s="173" t="s">
+        <v>231</v>
+      </c>
+      <c r="E608" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F608" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G608" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="H608" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="I608" s="15">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="J608" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="K608" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="L608" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="M608" s="22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="609" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A609" s="198" t="s">
+        <v>48</v>
+      </c>
+      <c r="B609" s="173" t="s">
+        <v>544</v>
+      </c>
+      <c r="C609" s="185" t="s">
+        <v>87</v>
+      </c>
+      <c r="D609" s="173" t="s">
+        <v>228</v>
+      </c>
+      <c r="E609" s="176" t="s">
+        <v>4</v>
+      </c>
+      <c r="F609" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="G609" s="15">
+        <v>0.65625</v>
+      </c>
+      <c r="H609" s="16">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I609" s="15">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="J609" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K609" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="L609" s="16">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="M609" s="15">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="610" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A610" s="198"/>
+      <c r="B610" s="173" t="s">
+        <v>545</v>
+      </c>
+      <c r="C610" s="185" t="s">
+        <v>364</v>
+      </c>
+      <c r="D610" s="173" t="s">
+        <v>161</v>
+      </c>
+      <c r="E610" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F610" s="130">
+        <v>0.84375</v>
+      </c>
+      <c r="G610" s="217">
+        <v>0.96875</v>
+      </c>
+      <c r="H610" s="218">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="I610" s="217">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="J610" s="130">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="K610" s="217">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="L610" s="218">
+        <v>0.8125</v>
+      </c>
+      <c r="M610" s="217">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="611" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A611" s="328"/>
+      <c r="B611" s="233"/>
+      <c r="C611" s="234"/>
+      <c r="D611" s="233"/>
+      <c r="E611" s="234"/>
+      <c r="F611" s="28"/>
+      <c r="G611" s="29"/>
+      <c r="H611" s="69"/>
+      <c r="I611" s="29"/>
+      <c r="J611" s="28"/>
+      <c r="K611" s="29"/>
+      <c r="L611" s="69"/>
+      <c r="M611" s="29"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
